--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>127118</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>75.0599975585938</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>73.4400024414062</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>73.4400024414062</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>73.9000015258789</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>132601</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>74.2799987792969</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>73.1399993896484</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>73.7200012207031</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>74.1800003051758</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>145848</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>75.3399963378906</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>73.6800003051758</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>75.2799987792969</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>288055</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>76.6600036621094</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>74.9400024414062</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>75.2799987792969</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>76.2600021362305</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>103721</v>
+        <v>163535</v>
       </c>
       <c r="C2715" t="n">
-        <v>74.3600006103516</v>
+        <v>75.1999969482422</v>
       </c>
       <c r="D2715" t="n">
-        <v>73.2600021362305</v>
+        <v>73.6399993896484</v>
       </c>
       <c r="E2715" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F2715" t="n">
-        <v>73.620002746582</v>
+        <v>74.0400009155273</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>124787</v>
+        <v>103721</v>
       </c>
       <c r="C2716" t="n">
-        <v>75.0599975585938</v>
+        <v>74.3600006103516</v>
       </c>
       <c r="D2716" t="n">
-        <v>73.0999984741211</v>
+        <v>73.2600021362305</v>
       </c>
       <c r="E2716" t="n">
-        <v>73.1999969482422</v>
+        <v>74</v>
       </c>
       <c r="F2716" t="n">
-        <v>74</v>
+        <v>73.620002746582</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>77399</v>
+        <v>124787</v>
       </c>
       <c r="C2717" t="n">
-        <v>74.6999969482422</v>
+        <v>75.0599975585938</v>
       </c>
       <c r="D2717" t="n">
-        <v>73.1800003051758</v>
+        <v>73.0999984741211</v>
       </c>
       <c r="E2717" t="n">
-        <v>74.2200012207031</v>
+        <v>73.1999969482422</v>
       </c>
       <c r="F2717" t="n">
-        <v>73.5999984741211</v>
+        <v>74</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>73181</v>
+        <v>77399</v>
       </c>
       <c r="C2718" t="n">
-        <v>73.9000015258789</v>
+        <v>74.6999969482422</v>
       </c>
       <c r="D2718" t="n">
-        <v>72.6999969482422</v>
+        <v>73.1800003051758</v>
       </c>
       <c r="E2718" t="n">
-        <v>73.620002746582</v>
+        <v>74.2200012207031</v>
       </c>
       <c r="F2718" t="n">
-        <v>73.4000015258789</v>
+        <v>73.5999984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>127118</v>
+        <v>73181</v>
       </c>
       <c r="C2719" t="n">
-        <v>75.0599975585938</v>
+        <v>73.9000015258789</v>
       </c>
       <c r="D2719" t="n">
-        <v>73.4400024414062</v>
+        <v>72.6999969482422</v>
       </c>
       <c r="E2719" t="n">
-        <v>73.4400024414062</v>
+        <v>73.620002746582</v>
       </c>
       <c r="F2719" t="n">
-        <v>73.9000015258789</v>
+        <v>73.4000015258789</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>132601</v>
+        <v>127118</v>
       </c>
       <c r="C2720" t="n">
-        <v>74.2799987792969</v>
+        <v>75.0599975585938</v>
       </c>
       <c r="D2720" t="n">
-        <v>73.1399993896484</v>
+        <v>73.4400024414062</v>
       </c>
       <c r="E2720" t="n">
-        <v>73.7200012207031</v>
+        <v>73.4400024414062</v>
       </c>
       <c r="F2720" t="n">
-        <v>74.1800003051758</v>
+        <v>73.9000015258789</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>145848</v>
+        <v>132601</v>
       </c>
       <c r="C2721" t="n">
-        <v>75.3399963378906</v>
+        <v>74.2799987792969</v>
       </c>
       <c r="D2721" t="n">
-        <v>73.6800003051758</v>
+        <v>73.1399993896484</v>
       </c>
       <c r="E2721" t="n">
-        <v>74</v>
+        <v>73.7200012207031</v>
       </c>
       <c r="F2721" t="n">
-        <v>75.2799987792969</v>
+        <v>74.1800003051758</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>288055</v>
+        <v>145848</v>
       </c>
       <c r="C2722" t="n">
-        <v>76.6600036621094</v>
+        <v>75.3399963378906</v>
       </c>
       <c r="D2722" t="n">
-        <v>74.9400024414062</v>
+        <v>73.6800003051758</v>
       </c>
       <c r="E2722" t="n">
+        <v>74</v>
+      </c>
+      <c r="F2722" t="n">
         <v>75.2799987792969</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1156676</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>78.5199966430664</v>
+      </c>
+      <c r="D2723" t="n">
         <v>76.2600021362305</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>76.4000015258789</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>76.620002746582</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>75.0599975585938</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>75.9199981689453</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>271260</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>79.6999969482422</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>76</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>76</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>76</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>76.9400024414062</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>159165</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>78.8399963378906</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>77.2200012207031</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>77.2200012207031</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>76.620002746582</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>165596</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>76.9599990844727</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>74.8399963378906</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>76.3399963378906</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>76.3399963378906</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>75.4199981689453</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>119017</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>77.8399963378906</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>76.1800003051758</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>76.1800003051758</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>66289</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>78.3600006103516</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>77.2399978637695</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>77.2399978637695</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>77.8000030517578</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>48.1800003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>41.7114105224609</v>
+        <v>41.7114067077637</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>49.0900001525879</v>
       </c>
       <c r="G3" t="n">
-        <v>42.4992408752441</v>
+        <v>42.4992256164551</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>42.2481651306152</v>
+        <v>42.2481689453125</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G5" t="n">
-        <v>42.1356239318848</v>
+        <v>42.1356201171875</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G8" t="n">
-        <v>41.6854362487793</v>
+        <v>41.6854400634766</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>47.310001373291</v>
       </c>
       <c r="G9" t="n">
-        <v>40.9582099914551</v>
+        <v>40.9582138061523</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>44.5299987792969</v>
       </c>
       <c r="G12" t="n">
-        <v>38.5514488220215</v>
+        <v>38.5514526367188</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>43.1699981689453</v>
       </c>
       <c r="G13" t="n">
-        <v>37.3740463256836</v>
+        <v>37.3740425109863</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>42.9000015258789</v>
       </c>
       <c r="G14" t="n">
-        <v>37.1403007507324</v>
+        <v>37.1402893066406</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>44.1699981689453</v>
       </c>
       <c r="G16" t="n">
-        <v>38.2397842407227</v>
+        <v>38.2397880554199</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>45.6399993896484</v>
       </c>
       <c r="G17" t="n">
-        <v>39.5124282836914</v>
+        <v>39.5124244689941</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G18" t="n">
-        <v>40.4993667602539</v>
+        <v>40.4993705749512</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>40.6032638549805</v>
+        <v>40.6032600402832</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>48.5</v>
       </c>
       <c r="G21" t="n">
-        <v>41.9884452819824</v>
+        <v>41.9884414672852</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>48.8300018310547</v>
       </c>
       <c r="G22" t="n">
-        <v>42.2741394042969</v>
+        <v>42.2741432189941</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>41.1053924560547</v>
+        <v>41.1053886413574</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>42.810001373291</v>
       </c>
       <c r="G27" t="n">
-        <v>37.0623817443848</v>
+        <v>37.0623779296875</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>37.3134422302246</v>
+        <v>37.3134460449219</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>39.6509475708008</v>
+        <v>39.6509399414062</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>45.9099998474121</v>
       </c>
       <c r="G34" t="n">
-        <v>39.7461776733398</v>
+        <v>39.7461738586426</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G35" t="n">
-        <v>40.6378936767578</v>
+        <v>40.6378974914551</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G36" t="n">
-        <v>40.4993667602539</v>
+        <v>40.4993705749512</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="G37" t="n">
-        <v>41.7633514404297</v>
+        <v>41.7633476257324</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G38" t="n">
-        <v>41.1659965515137</v>
+        <v>41.1659927368164</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G40" t="n">
-        <v>42.4126586914062</v>
+        <v>42.412654876709</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G41" t="n">
-        <v>42.1356239318848</v>
+        <v>42.1356201171875</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>49.0099983215332</v>
       </c>
       <c r="G43" t="n">
-        <v>42.4299774169922</v>
+        <v>42.4299697875977</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>48.25</v>
       </c>
       <c r="G44" t="n">
-        <v>41.7720069885254</v>
+        <v>41.7720108032227</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>41.0361289978027</v>
+        <v>41.0361328125</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>41.858585357666</v>
+        <v>41.8585815429688</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G48" t="n">
-        <v>41.971134185791</v>
+        <v>41.9711303710938</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>45.75</v>
       </c>
       <c r="G50" t="n">
-        <v>39.6076622009277</v>
+        <v>39.6076583862305</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>39.2700119018555</v>
+        <v>39.27001953125</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>46.6699981689453</v>
       </c>
       <c r="G52" t="n">
-        <v>40.4041328430176</v>
+        <v>40.4041366577148</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>46</v>
       </c>
       <c r="G53" t="n">
-        <v>39.8240966796875</v>
+        <v>39.824089050293</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>45.4799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>39.3739051818848</v>
+        <v>39.3739128112793</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>45.6800003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>39.547061920166</v>
+        <v>39.5470542907715</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>45.1699981689453</v>
       </c>
       <c r="G58" t="n">
-        <v>39.105525970459</v>
+        <v>39.1055297851562</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>39.6509475708008</v>
+        <v>39.6509399414062</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>45.5</v>
       </c>
       <c r="G60" t="n">
-        <v>39.3912200927734</v>
+        <v>39.3912239074707</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>43.287052154541</v>
+        <v>43.2870559692383</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>44.5423812866211</v>
+        <v>44.5423851013184</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>44.845386505127</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>45.9708557128906</v>
+        <v>45.9708480834961</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618286132812</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>44.845386505127</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>51.5</v>
       </c>
       <c r="G72" t="n">
-        <v>44.5856704711914</v>
+        <v>44.5856666564941</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>51.25</v>
       </c>
       <c r="G73" t="n">
-        <v>44.3692321777344</v>
+        <v>44.3692283630371</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>44.0662269592285</v>
+        <v>44.0662307739258</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>44.1095123291016</v>
+        <v>44.109504699707</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G77" t="n">
-        <v>44.4990921020508</v>
+        <v>44.499095916748</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>51.5</v>
       </c>
       <c r="G78" t="n">
-        <v>44.5856704711914</v>
+        <v>44.5856666564941</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>43.9796485900879</v>
+        <v>43.9796409606934</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>43.8930702209473</v>
+        <v>43.8930816650391</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>43.8930702209473</v>
+        <v>43.8930816650391</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G82" t="n">
-        <v>43.9796485900879</v>
+        <v>43.9796409606934</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>51</v>
       </c>
       <c r="G84" t="n">
-        <v>44.1527938842773</v>
+        <v>44.1528015136719</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>44.1095123291016</v>
+        <v>44.109504699707</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G87" t="n">
-        <v>44.9319725036621</v>
+        <v>44.9319610595703</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>51.75</v>
       </c>
       <c r="G88" t="n">
-        <v>44.8021049499512</v>
+        <v>44.8020973205566</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>44.9752578735352</v>
+        <v>44.9752502441406</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>52.5</v>
       </c>
       <c r="G90" t="n">
-        <v>45.451416015625</v>
+        <v>45.4514045715332</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>52.5</v>
       </c>
       <c r="G91" t="n">
-        <v>45.451416015625</v>
+        <v>45.4514045715332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G92" t="n">
-        <v>45.3215446472168</v>
+        <v>45.3215408325195</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>52.4500007629395</v>
       </c>
       <c r="G93" t="n">
-        <v>45.4081230163574</v>
+        <v>45.4081268310547</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>45.7544136047363</v>
+        <v>45.7544174194336</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>52.25</v>
       </c>
       <c r="G95" t="n">
-        <v>45.2349739074707</v>
+        <v>45.234977722168</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618286132812</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>51</v>
       </c>
       <c r="G97" t="n">
-        <v>44.1527938842773</v>
+        <v>44.1528015136719</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>52.4500007629395</v>
       </c>
       <c r="G99" t="n">
-        <v>45.4081230163574</v>
+        <v>45.4081268310547</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>52.75</v>
       </c>
       <c r="G102" t="n">
-        <v>46.2408905029297</v>
+        <v>46.240894317627</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>55</v>
       </c>
       <c r="G105" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>47.6872940063477</v>
+        <v>47.6872978210449</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>55.5</v>
       </c>
       <c r="G107" t="n">
-        <v>48.6515579223633</v>
+        <v>48.6515617370605</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>48.7392196655273</v>
+        <v>48.7392158508301</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>56.25</v>
       </c>
       <c r="G109" t="n">
-        <v>49.3090171813965</v>
+        <v>49.3090133666992</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>48.1694259643555</v>
+        <v>48.1694297790527</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>49.0460357666016</v>
+        <v>49.046028137207</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G117" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>46.0655784606934</v>
+        <v>46.0655746459961</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G121" t="n">
-        <v>47.2051658630371</v>
+        <v>47.2051582336426</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>45.3204536437988</v>
+        <v>45.3204650878906</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G125" t="n">
-        <v>44.1808738708496</v>
+        <v>44.1808776855469</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>54.75</v>
       </c>
       <c r="G127" t="n">
-        <v>47.9940986633301</v>
+        <v>47.9941062927246</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>55</v>
       </c>
       <c r="G128" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>48.8268814086914</v>
+        <v>48.8268852233887</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>49.4843368530273</v>
+        <v>49.4843330383301</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>54.75</v>
       </c>
       <c r="G131" t="n">
-        <v>47.9940986633301</v>
+        <v>47.9941062927246</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G133" t="n">
-        <v>47.2489929199219</v>
+        <v>47.2489852905273</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>48.0379333496094</v>
+        <v>48.0379371643066</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G135" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>49.0460357666016</v>
+        <v>49.046028137207</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>48.8268814086914</v>
+        <v>48.8268852233887</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>48.1255989074707</v>
+        <v>48.1255950927734</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G141" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732772827148</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>50.3171119689941</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102996826172</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G144" t="n">
-        <v>49.9226303100586</v>
+        <v>49.9226417541504</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>58</v>
       </c>
       <c r="G146" t="n">
-        <v>50.843074798584</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G147" t="n">
-        <v>50.054126739502</v>
+        <v>50.0541229248047</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G148" t="n">
-        <v>49.8349800109863</v>
+        <v>49.8349723815918</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>49.3528480529785</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>56.0499992370605</v>
       </c>
       <c r="G150" t="n">
-        <v>49.1336860656738</v>
+        <v>49.1336936950684</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>55.8499984741211</v>
       </c>
       <c r="G151" t="n">
-        <v>48.9583702087402</v>
+        <v>48.958366394043</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G153" t="n">
-        <v>50.6677474975586</v>
+        <v>50.6677551269531</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>60</v>
       </c>
       <c r="G154" t="n">
-        <v>52.5962791442871</v>
+        <v>52.5962829589844</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>59.4500007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>52.1141510009766</v>
+        <v>52.1141471862793</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G156" t="n">
-        <v>53.166072845459</v>
+        <v>53.1660842895508</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>60.8499984741211</v>
       </c>
       <c r="G157" t="n">
-        <v>53.3413887023926</v>
+        <v>53.3413963317871</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>62</v>
       </c>
       <c r="G158" t="n">
-        <v>54.3494873046875</v>
+        <v>54.349494934082</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G159" t="n">
-        <v>53.1222381591797</v>
+        <v>53.1222457885742</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>50.7115783691406</v>
+        <v>50.7115821838379</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>56.75</v>
       </c>
       <c r="G163" t="n">
-        <v>49.7473182678223</v>
+        <v>49.7473068237305</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>56.75</v>
       </c>
       <c r="G164" t="n">
-        <v>49.7473182678223</v>
+        <v>49.7473068237305</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G165" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G166" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102996826172</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>49.8349800109863</v>
+        <v>49.8349723815918</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>58.5</v>
       </c>
       <c r="G170" t="n">
-        <v>51.2813758850098</v>
+        <v>51.2813720703125</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>50.4924240112305</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G173" t="n">
-        <v>50.4924240112305</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>50.3171119689941</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>50.9307327270508</v>
+        <v>50.9307289123535</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>56.5</v>
       </c>
       <c r="G178" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281715393066</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>48.3885765075684</v>
+        <v>48.3885803222656</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>49.9226303100586</v>
+        <v>49.9226417541504</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>56.75</v>
       </c>
       <c r="G184" t="n">
-        <v>49.7473182678223</v>
+        <v>49.7473068237305</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>51.0183906555176</v>
+        <v>51.0183944702148</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G187" t="n">
-        <v>51.5443496704102</v>
+        <v>51.5443572998047</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>50.4924240112305</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>50.4924240112305</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G194" t="n">
-        <v>51.3690338134766</v>
+        <v>51.3690299987793</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>51.632022857666</v>
+        <v>51.6320152282715</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>51.3252029418945</v>
+        <v>51.3251991271973</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>52.2018089294434</v>
+        <v>52.2018051147461</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>51.0183906555176</v>
+        <v>51.0183944702148</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>51.3252029418945</v>
+        <v>51.3251991271973</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>51.0183906555176</v>
+        <v>51.0183944702148</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>50.7554130554199</v>
+        <v>50.7554168701172</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>58</v>
       </c>
       <c r="G205" t="n">
-        <v>50.843074798584</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>50.2294425964355</v>
+        <v>50.2294464111328</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>50.2294425964355</v>
+        <v>50.2294464111328</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911415100098</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G211" t="n">
-        <v>48.7392196655273</v>
+        <v>48.7392158508301</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>56.25</v>
       </c>
       <c r="G212" t="n">
-        <v>49.3090171813965</v>
+        <v>49.3090133666992</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>56</v>
       </c>
       <c r="G214" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8187828063965</v>
+        <v>47.818790435791</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>47.2051658630371</v>
+        <v>47.2051582336426</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>46.7668571472168</v>
+        <v>46.7668609619141</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>46.9421806335449</v>
+        <v>46.9421730041504</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>47.2051658630371</v>
+        <v>47.2051582336426</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>51</v>
       </c>
       <c r="G224" t="n">
-        <v>44.7068405151367</v>
+        <v>44.706844329834</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>51</v>
       </c>
       <c r="G225" t="n">
-        <v>44.7068405151367</v>
+        <v>44.706844329834</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>45.5396156311035</v>
+        <v>45.5396194458008</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>52.25</v>
       </c>
       <c r="G228" t="n">
-        <v>45.8025932312012</v>
+        <v>45.8025970458984</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G230" t="n">
-        <v>45.3204536437988</v>
+        <v>45.3204650878906</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>51.25</v>
       </c>
       <c r="G231" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259834289551</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>45.2766304016113</v>
+        <v>45.2766342163086</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>52</v>
       </c>
       <c r="G234" t="n">
-        <v>45.583438873291</v>
+        <v>45.5834465026855</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>51.5</v>
       </c>
       <c r="G235" t="n">
-        <v>45.1451416015625</v>
+        <v>45.1451377868652</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>44.6191825866699</v>
+        <v>44.6191787719727</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>51.25</v>
       </c>
       <c r="G237" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259834289551</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>51.25</v>
       </c>
       <c r="G239" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259834289551</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>45.6711006164551</v>
+        <v>45.6711044311523</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>45.6711006164551</v>
+        <v>45.6711044311523</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>46.0655784606934</v>
+        <v>46.0655746459961</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>51.8499984741211</v>
       </c>
       <c r="G246" t="n">
-        <v>45.4519500732422</v>
+        <v>45.4519538879395</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>46.372386932373</v>
+        <v>46.3723945617676</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>46.5915451049805</v>
+        <v>46.5915412902832</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>48.3009147644043</v>
+        <v>48.3009185791016</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281715393066</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>49.0460357666016</v>
+        <v>49.046028137207</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>49.3528480529785</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>56.25</v>
       </c>
       <c r="G257" t="n">
-        <v>49.3090171813965</v>
+        <v>49.3090133666992</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>50.3171119689941</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G262" t="n">
-        <v>51.1937141418457</v>
+        <v>51.193717956543</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G263" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732772827148</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G264" t="n">
-        <v>50.054126739502</v>
+        <v>50.0541229248047</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G266" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732772827148</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911415100098</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911415100098</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>56</v>
       </c>
       <c r="G272" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>49.3528480529785</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>55</v>
       </c>
       <c r="G274" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G275" t="n">
-        <v>47.6872940063477</v>
+        <v>47.6872978210449</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>48.695384979248</v>
+        <v>48.6953926086426</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>55.5</v>
       </c>
       <c r="G278" t="n">
-        <v>48.6515579223633</v>
+        <v>48.6515617370605</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>56</v>
       </c>
       <c r="G280" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>51.1937141418457</v>
+        <v>51.193717956543</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G287" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102996826172</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102996826172</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>50.6677474975586</v>
+        <v>50.6677551269531</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>58.5</v>
       </c>
       <c r="G290" t="n">
-        <v>51.2813758850098</v>
+        <v>51.2813720703125</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G291" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G292" t="n">
-        <v>49.8788108825684</v>
+        <v>49.8788070678711</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>50.3171119689941</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>57.25</v>
       </c>
       <c r="G294" t="n">
-        <v>50.1856117248535</v>
+        <v>50.185619354248</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>51.237548828125</v>
+        <v>51.2375411987305</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>58.75</v>
       </c>
       <c r="G298" t="n">
-        <v>51.5005264282227</v>
+        <v>51.5005302429199</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>59.75</v>
       </c>
       <c r="G299" t="n">
-        <v>52.3771324157715</v>
+        <v>52.377124786377</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>60</v>
       </c>
       <c r="G300" t="n">
-        <v>52.5962791442871</v>
+        <v>52.5962829589844</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>52.4209594726562</v>
+        <v>52.420955657959</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>52.4209594726562</v>
+        <v>52.420955657959</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>52.4647941589355</v>
+        <v>52.4647903442383</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G304" t="n">
-        <v>52.6839408874512</v>
+        <v>52.6839370727539</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>51.5443496704102</v>
+        <v>51.5443572998047</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>51.5443496704102</v>
+        <v>51.5443572998047</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>52.4647941589355</v>
+        <v>52.4647903442383</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G310" t="n">
-        <v>52.859260559082</v>
+        <v>52.8592643737793</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>53.7796897888184</v>
+        <v>53.7796936035156</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>53.7796897888184</v>
+        <v>53.7796936035156</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>62.25</v>
       </c>
       <c r="G313" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686378479004</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>54.3056602478027</v>
+        <v>54.3056564331055</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>54.4809837341309</v>
+        <v>54.4809875488281</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>63</v>
       </c>
       <c r="G316" t="n">
-        <v>55.2260932922363</v>
+        <v>55.2260971069336</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>55.0946006774902</v>
+        <v>55.0946044921875</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G319" t="n">
-        <v>55.0946006774902</v>
+        <v>55.0946044921875</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>62.25</v>
       </c>
       <c r="G320" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686378479004</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>55.4890785217285</v>
+        <v>55.4890823364258</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>55.927375793457</v>
+        <v>55.9273796081543</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>56.0150413513184</v>
+        <v>56.0150375366211</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G325" t="n">
-        <v>56.3656845092773</v>
+        <v>56.3656768798828</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>56.2780151367188</v>
+        <v>56.278018951416</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>65</v>
       </c>
       <c r="G327" t="n">
-        <v>56.9793090820312</v>
+        <v>56.9793014526367</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G328" t="n">
-        <v>57.8120803833008</v>
+        <v>57.812084197998</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G330" t="n">
-        <v>57.680591583252</v>
+        <v>57.6805953979492</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>64</v>
       </c>
       <c r="G332" t="n">
-        <v>56.1026992797852</v>
+        <v>56.1027030944824</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>64.25</v>
       </c>
       <c r="G333" t="n">
-        <v>56.321849822998</v>
+        <v>56.3218574523926</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G335" t="n">
-        <v>57.5052719116211</v>
+        <v>57.5052604675293</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G336" t="n">
-        <v>58.9078254699707</v>
+        <v>58.9078330993652</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>66</v>
       </c>
       <c r="G337" t="n">
-        <v>57.8559150695801</v>
+        <v>57.8559112548828</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G338" t="n">
-        <v>58.2065467834473</v>
+        <v>58.2065505981445</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>67.5</v>
       </c>
       <c r="G339" t="n">
-        <v>59.1708106994629</v>
+        <v>59.1708183288574</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>71</v>
       </c>
       <c r="G341" t="n">
-        <v>62.2389373779297</v>
+        <v>62.2389221191406</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>69.5999984741211</v>
       </c>
       <c r="G342" t="n">
-        <v>61.0116844177246</v>
+        <v>61.0116767883301</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>69</v>
       </c>
       <c r="G343" t="n">
-        <v>60.485725402832</v>
+        <v>60.4857215881348</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G344" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G345" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G346" t="n">
-        <v>61.6691474914551</v>
+        <v>61.6691436767578</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G347" t="n">
-        <v>61.5376472473145</v>
+        <v>61.5376434326172</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>61.230842590332</v>
+        <v>61.2308311462402</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>70.25</v>
       </c>
       <c r="G349" t="n">
-        <v>61.5814781188965</v>
+        <v>61.5814743041992</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>70</v>
       </c>
       <c r="G350" t="n">
-        <v>61.3623313903809</v>
+        <v>61.3623352050781</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>70</v>
       </c>
       <c r="G351" t="n">
-        <v>61.3623313903809</v>
+        <v>61.3623352050781</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>59.7405967712402</v>
+        <v>59.7406005859375</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>59.0831565856934</v>
+        <v>59.0831642150879</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>68.25</v>
       </c>
       <c r="G354" t="n">
-        <v>59.8282699584961</v>
+        <v>59.8282737731934</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>68.25</v>
       </c>
       <c r="G355" t="n">
-        <v>60.5378723144531</v>
+        <v>60.5378761291504</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G356" t="n">
-        <v>60.8039703369141</v>
+        <v>60.8039817810059</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G358" t="n">
-        <v>61.1587715148926</v>
+        <v>61.1587677001953</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G359" t="n">
-        <v>61.3805160522461</v>
+        <v>61.3805198669434</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G362" t="n">
-        <v>61.1587715148926</v>
+        <v>61.1587677001953</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G364" t="n">
-        <v>62.5779876708984</v>
+        <v>62.5779800415039</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>71.4499969482422</v>
       </c>
       <c r="G366" t="n">
-        <v>63.3762741088867</v>
+        <v>63.3762702941895</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>62.8884239196777</v>
+        <v>62.8884201049805</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>71.75</v>
       </c>
       <c r="G368" t="n">
-        <v>63.6423873901367</v>
+        <v>63.6423759460449</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>62.0014190673828</v>
+        <v>62.0014114379883</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>69.75</v>
       </c>
       <c r="G371" t="n">
-        <v>61.8683776855469</v>
+        <v>61.8683700561523</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G372" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319358825684</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G373" t="n">
-        <v>62.7110137939453</v>
+        <v>62.7110290527344</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G374" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432250976562</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>71</v>
       </c>
       <c r="G376" t="n">
-        <v>62.9771385192871</v>
+        <v>62.9771118164062</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G377" t="n">
-        <v>62.5779876708984</v>
+        <v>62.5779800415039</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>72.6999969482422</v>
       </c>
       <c r="G379" t="n">
-        <v>64.4850234985352</v>
+        <v>64.4850158691406</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G380" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432250976562</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>62.0014190673828</v>
+        <v>62.0014114379883</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G382" t="n">
-        <v>59.9613265991211</v>
+        <v>59.9613189697266</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>67.25</v>
       </c>
       <c r="G384" t="n">
-        <v>59.6508712768555</v>
+        <v>59.6508636474609</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G385" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743179321289</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G386" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743179321289</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>67.25</v>
       </c>
       <c r="G387" t="n">
-        <v>59.6508712768555</v>
+        <v>59.6508636474609</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G388" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743179321289</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G389" t="n">
-        <v>59.6952133178711</v>
+        <v>59.6952209472656</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>58.5864677429199</v>
+        <v>58.5864715576172</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>67.0999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>59.5178184509277</v>
+        <v>59.517822265625</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G395" t="n">
-        <v>61.2474708557129</v>
+        <v>61.2474670410156</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>69.75</v>
       </c>
       <c r="G396" t="n">
-        <v>61.8683776855469</v>
+        <v>61.8683700561523</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>62.4005661010742</v>
+        <v>62.4005813598633</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G399" t="n">
-        <v>62.2231750488281</v>
+        <v>62.2231712341309</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G400" t="n">
-        <v>62.5779876708984</v>
+        <v>62.5779800415039</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>61.9570617675781</v>
+        <v>61.9570693969727</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G402" t="n">
-        <v>65.0172424316406</v>
+        <v>65.0172271728516</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G404" t="n">
-        <v>64.7954788208008</v>
+        <v>64.7954864501953</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>65.2833251953125</v>
+        <v>65.283317565918</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>73</v>
       </c>
       <c r="G407" t="n">
-        <v>64.7511367797852</v>
+        <v>64.7511215209961</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>64.7954788208008</v>
+        <v>64.7954864501953</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>64.6624145507812</v>
+        <v>64.6624298095703</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>71.9499969482422</v>
       </c>
       <c r="G411" t="n">
-        <v>63.8197708129883</v>
+        <v>63.8197784423828</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>72.1500015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>63.9971694946289</v>
+        <v>63.9971733093262</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G413" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319358825684</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G414" t="n">
-        <v>62.7110137939453</v>
+        <v>62.7110290527344</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>63.5536880493164</v>
+        <v>63.5536804199219</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319358825684</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>71.6999969482422</v>
       </c>
       <c r="G417" t="n">
-        <v>63.5980262756348</v>
+        <v>63.5980224609375</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>63.4649772644043</v>
+        <v>63.4649887084961</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>63.2875633239746</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319358825684</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G421" t="n">
-        <v>63.2875633239746</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G422" t="n">
-        <v>62.7997245788574</v>
+        <v>62.7997283935547</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>62.5779876708984</v>
+        <v>62.5779800415039</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>63.2875633239746</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>64.2189254760742</v>
+        <v>64.2189331054688</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>72.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>64.2632827758789</v>
+        <v>64.2632904052734</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>73</v>
       </c>
       <c r="G430" t="n">
-        <v>64.7511367797852</v>
+        <v>64.7511215209961</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>73.3499984741211</v>
       </c>
       <c r="G431" t="n">
-        <v>65.0615768432617</v>
+        <v>65.0615844726562</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>73.6999969482422</v>
       </c>
       <c r="G432" t="n">
-        <v>65.3720321655273</v>
+        <v>65.3720245361328</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>73</v>
       </c>
       <c r="G435" t="n">
-        <v>64.7511367797852</v>
+        <v>64.7511215209961</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>74</v>
       </c>
       <c r="G436" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>74</v>
       </c>
       <c r="G437" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>64.8398284912109</v>
+        <v>64.8398361206055</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>74</v>
       </c>
       <c r="G440" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>74.25</v>
       </c>
       <c r="G441" t="n">
-        <v>65.8598785400391</v>
+        <v>65.8598861694336</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>66.1703186035156</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>67.2790832519531</v>
+        <v>67.2790985107422</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G445" t="n">
-        <v>66.8799285888672</v>
+        <v>66.8799209594727</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G447" t="n">
-        <v>66.702522277832</v>
+        <v>66.7025299072266</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>75.4499969482422</v>
       </c>
       <c r="G448" t="n">
-        <v>66.9242782592773</v>
+        <v>66.9242706298828</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>76.5</v>
       </c>
       <c r="G449" t="n">
-        <v>67.8556289672852</v>
+        <v>67.8556365966797</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G450" t="n">
-        <v>69.0087509155273</v>
+        <v>69.0087432861328</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>79</v>
       </c>
       <c r="G453" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>78.75</v>
       </c>
       <c r="G456" t="n">
-        <v>69.8513870239258</v>
+        <v>69.8513793945312</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>78.75</v>
       </c>
       <c r="G458" t="n">
-        <v>69.8513870239258</v>
+        <v>69.8513793945312</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>79</v>
       </c>
       <c r="G459" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>79</v>
       </c>
       <c r="G460" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>77.75</v>
       </c>
       <c r="G462" t="n">
-        <v>68.9644012451172</v>
+        <v>68.9643936157227</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G464" t="n">
-        <v>69.0087509155273</v>
+        <v>69.0087432861328</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G465" t="n">
-        <v>69.2304840087891</v>
+        <v>69.2304763793945</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>69.4965744018555</v>
+        <v>69.49658203125</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>78</v>
       </c>
       <c r="G469" t="n">
-        <v>69.1861343383789</v>
+        <v>69.1861419677734</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>69.2748413085938</v>
+        <v>69.2748336791992</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G471" t="n">
-        <v>70.0287857055664</v>
+        <v>70.0287933349609</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G472" t="n">
-        <v>69.1417846679688</v>
+        <v>69.1417922973633</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G473" t="n">
-        <v>70.2505416870117</v>
+        <v>70.2505340576172</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>78.25</v>
       </c>
       <c r="G475" t="n">
-        <v>69.4078826904297</v>
+        <v>69.4078903198242</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>77.75</v>
       </c>
       <c r="G476" t="n">
-        <v>68.9644012451172</v>
+        <v>68.9643936157227</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G477" t="n">
-        <v>63.9084815979004</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>74</v>
       </c>
       <c r="G481" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G482" t="n">
-        <v>66.8799285888672</v>
+        <v>66.8799209594727</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>67.9886856079102</v>
+        <v>67.9886779785156</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>77.1999969482422</v>
       </c>
       <c r="G486" t="n">
-        <v>68.4765472412109</v>
+        <v>68.4765319824219</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>76.3499984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>67.7225799560547</v>
+        <v>67.7225723266602</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>75.6500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>67.101692199707</v>
+        <v>67.101676940918</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>77.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>68.6539459228516</v>
+        <v>68.653938293457</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G493" t="n">
-        <v>69.2304840087891</v>
+        <v>69.2304763793945</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>68.8756790161133</v>
+        <v>68.8756942749023</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>79.5500030517578</v>
       </c>
       <c r="G497" t="n">
-        <v>70.5609893798828</v>
+        <v>70.5609970092773</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>71.2705841064453</v>
+        <v>71.2706069946289</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>77.3499984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>68.6095809936523</v>
+        <v>68.6095733642578</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>66.8799285888672</v>
+        <v>66.8799209594727</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G506" t="n">
-        <v>67.1460418701172</v>
+        <v>67.1460266113281</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G507" t="n">
-        <v>66.1703186035156</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G510" t="n">
-        <v>66.1703186035156</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>74</v>
       </c>
       <c r="G511" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>74.8499984741211</v>
       </c>
       <c r="G513" t="n">
-        <v>66.3920822143555</v>
+        <v>66.39208984375</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>67.2790832519531</v>
+        <v>67.2790985107422</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>76.8000030517578</v>
       </c>
       <c r="G515" t="n">
-        <v>68.1217422485352</v>
+        <v>68.1217346191406</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>79.25</v>
       </c>
       <c r="G518" t="n">
-        <v>70.2948989868164</v>
+        <v>70.2948837280273</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G520" t="n">
-        <v>70.6940307617188</v>
+        <v>70.6940460205078</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G521" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G526" t="n">
-        <v>70.1618423461914</v>
+        <v>70.1618270874023</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>79</v>
       </c>
       <c r="G528" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>77.25</v>
       </c>
       <c r="G532" t="n">
-        <v>68.520881652832</v>
+        <v>68.5208892822266</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G533" t="n">
-        <v>69.1417846679688</v>
+        <v>69.1417922973633</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>79.4000015258789</v>
       </c>
       <c r="G534" t="n">
-        <v>70.4279479980469</v>
+        <v>70.4279403686523</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>66.8355941772461</v>
+        <v>66.8355865478516</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G538" t="n">
-        <v>67.1460418701172</v>
+        <v>67.1460266113281</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>74.0999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>65.7268295288086</v>
+        <v>65.7268371582031</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G540" t="n">
-        <v>61.6909828186035</v>
+        <v>61.6909713745117</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G541" t="n">
-        <v>63.1545181274414</v>
+        <v>63.1545295715332</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>71</v>
       </c>
       <c r="G542" t="n">
-        <v>62.9771385192871</v>
+        <v>62.9771118164062</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>70</v>
       </c>
       <c r="G543" t="n">
-        <v>62.0901260375977</v>
+        <v>62.0901336669922</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G544" t="n">
-        <v>62.444938659668</v>
+        <v>62.4449310302734</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G545" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432250976562</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>62.0014190673828</v>
+        <v>62.0014114379883</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G547" t="n">
-        <v>61.6909828186035</v>
+        <v>61.6909713745117</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G548" t="n">
-        <v>61.912727355957</v>
+        <v>61.9127235412598</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>69.6500015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>61.7796783447266</v>
+        <v>61.7796821594238</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>69.75</v>
       </c>
       <c r="G550" t="n">
-        <v>61.8683776855469</v>
+        <v>61.8683700561523</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>68.5</v>
       </c>
       <c r="G552" t="n">
-        <v>60.7596282958984</v>
+        <v>60.7596092224121</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>59.8282623291016</v>
+        <v>59.8282699584961</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>58.6308059692383</v>
+        <v>58.6308097839355</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>67.3499984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>59.739574432373</v>
+        <v>59.7395668029785</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>60.6709213256836</v>
+        <v>60.6709251403809</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>62.6223182678223</v>
+        <v>62.6223220825195</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>74.75</v>
       </c>
       <c r="G560" t="n">
-        <v>66.3033905029297</v>
+        <v>66.3033752441406</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>73.8499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>65.5050735473633</v>
+        <v>65.5050811767578</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>74</v>
       </c>
       <c r="G562" t="n">
-        <v>65.6381454467773</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G563" t="n">
-        <v>64.6624145507812</v>
+        <v>64.6624298095703</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G564" t="n">
-        <v>64.7954788208008</v>
+        <v>64.7954864501953</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G565" t="n">
-        <v>64.0415191650391</v>
+        <v>64.0415344238281</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G567" t="n">
-        <v>63.9084815979004</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G569" t="n">
-        <v>64.4406967163086</v>
+        <v>64.4406661987305</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>63.5536880493164</v>
+        <v>63.5536804199219</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G571" t="n">
-        <v>62.4005661010742</v>
+        <v>62.4005813598633</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G572" t="n">
-        <v>64.4406967163086</v>
+        <v>64.4406661987305</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>64.6624145507812</v>
+        <v>64.6624298095703</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>64.8398284912109</v>
+        <v>64.8398361206055</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>71.75</v>
       </c>
       <c r="G576" t="n">
-        <v>63.6423873901367</v>
+        <v>63.6423759460449</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>72.25</v>
       </c>
       <c r="G577" t="n">
-        <v>64.0858764648438</v>
+        <v>64.0858840942383</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>73.8499984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>65.5050735473633</v>
+        <v>65.5050811767578</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>64.7954788208008</v>
+        <v>64.7954864501953</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>73</v>
       </c>
       <c r="G580" t="n">
-        <v>64.7511367797852</v>
+        <v>64.7511215209961</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G581" t="n">
-        <v>63.9084815979004</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>73.5</v>
       </c>
       <c r="G582" t="n">
-        <v>65.1946411132812</v>
+        <v>65.1946334838867</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>73.5</v>
       </c>
       <c r="G583" t="n">
-        <v>65.1946411132812</v>
+        <v>65.1946334838867</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G584" t="n">
-        <v>66.8355941772461</v>
+        <v>66.8355865478516</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G585" t="n">
-        <v>67.0130004882812</v>
+        <v>67.0129852294922</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>68.8313293457031</v>
+        <v>68.8313446044922</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>74.75</v>
       </c>
       <c r="G587" t="n">
-        <v>66.3033905029297</v>
+        <v>66.3033752441406</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>66.1703186035156</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>76.1999969482422</v>
       </c>
       <c r="G589" t="n">
-        <v>67.5895309448242</v>
+        <v>67.5895385742188</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>77.3000030517578</v>
       </c>
       <c r="G591" t="n">
-        <v>68.5652313232422</v>
+        <v>68.5652465820312</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>78.1500015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>69.3191909790039</v>
+        <v>69.3191833496094</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>69.4965744018555</v>
+        <v>69.49658203125</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>78.6999969482422</v>
       </c>
       <c r="G595" t="n">
-        <v>69.8070297241211</v>
+        <v>69.8070449829102</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>78</v>
       </c>
       <c r="G596" t="n">
-        <v>69.1861343383789</v>
+        <v>69.1861419677734</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>78.6500015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>69.7626953125</v>
+        <v>69.7627029418945</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>80.4000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>71.3149337768555</v>
+        <v>71.3149566650391</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G602" t="n">
-        <v>71.1375427246094</v>
+        <v>71.1375350952148</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>81</v>
       </c>
       <c r="G604" t="n">
-        <v>71.8471450805664</v>
+        <v>71.8471374511719</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G605" t="n">
-        <v>72.024543762207</v>
+        <v>72.0245361328125</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>81.4000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>72.2019348144531</v>
+        <v>72.2019500732422</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>81.25</v>
       </c>
       <c r="G608" t="n">
-        <v>72.8293991088867</v>
+        <v>72.8294067382812</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>81.9000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>73.4120330810547</v>
+        <v>73.4120254516602</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>80.6999969482422</v>
       </c>
       <c r="G610" t="n">
-        <v>72.3363952636719</v>
+        <v>72.3364028930664</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>83</v>
       </c>
       <c r="G613" t="n">
-        <v>74.3980255126953</v>
+        <v>74.3980178833008</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G614" t="n">
-        <v>72.7845687866211</v>
+        <v>72.7845764160156</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G615" t="n">
-        <v>75.8321990966797</v>
+        <v>75.8322143554688</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>85.5</v>
       </c>
       <c r="G617" t="n">
-        <v>76.638916015625</v>
+        <v>76.6389389038086</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>88.25</v>
       </c>
       <c r="G619" t="n">
-        <v>79.1039352416992</v>
+        <v>79.1039199829102</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>88</v>
       </c>
       <c r="G620" t="n">
-        <v>78.8798446655273</v>
+        <v>78.8798522949219</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>78.7902145385742</v>
+        <v>78.7902069091797</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>79.7313919067383</v>
+        <v>79.7313842773438</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>91</v>
       </c>
       <c r="G624" t="n">
-        <v>81.5689315795898</v>
+        <v>81.5689239501953</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>93</v>
       </c>
       <c r="G627" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616485595703</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>92.3000030517578</v>
       </c>
       <c r="G628" t="n">
-        <v>82.7342071533203</v>
+        <v>82.7341918945312</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>90.9499969482422</v>
       </c>
       <c r="G629" t="n">
-        <v>81.5241088867188</v>
+        <v>81.5240936279297</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>89.1500015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>79.9106597900391</v>
+        <v>79.9106521606445</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>95.0500030517578</v>
       </c>
       <c r="G633" t="n">
-        <v>85.1991882324219</v>
+        <v>85.1991958618164</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G634" t="n">
-        <v>85.7818222045898</v>
+        <v>85.7818145751953</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G635" t="n">
-        <v>87.2160110473633</v>
+        <v>87.2160186767578</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>96.3499984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>86.3644561767578</v>
+        <v>86.3644638061523</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>96.3000030517578</v>
       </c>
       <c r="G638" t="n">
-        <v>86.3196411132812</v>
+        <v>86.3196487426758</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>86.4092788696289</v>
+        <v>86.4092712402344</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G644" t="n">
-        <v>85.9610977172852</v>
+        <v>85.9611129760742</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G645" t="n">
-        <v>86.1851806640625</v>
+        <v>86.185188293457</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>87.5297317504883</v>
+        <v>87.5297393798828</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>96.75</v>
       </c>
       <c r="G651" t="n">
-        <v>86.723014831543</v>
+        <v>86.7229995727539</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G652" t="n">
-        <v>86.4092788696289</v>
+        <v>86.4092712402344</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>94.5</v>
       </c>
       <c r="G653" t="n">
-        <v>84.706184387207</v>
+        <v>84.7061996459961</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G656" t="n">
-        <v>82.8686370849609</v>
+        <v>82.86865234375</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>93</v>
       </c>
       <c r="G657" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616485595703</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>93</v>
       </c>
       <c r="G660" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616485595703</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>88.75</v>
       </c>
       <c r="G664" t="n">
-        <v>79.5521087646484</v>
+        <v>79.552116394043</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>78.7453765869141</v>
+        <v>78.7453842163086</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>78.9694747924805</v>
+        <v>78.9694671630859</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>78.7453765869141</v>
+        <v>78.7453842163086</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>88.1500015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>79.014289855957</v>
+        <v>79.0142974853516</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G671" t="n">
-        <v>77.8490142822266</v>
+        <v>77.8490219116211</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>93.1999969482422</v>
       </c>
       <c r="G672" t="n">
-        <v>83.5409317016602</v>
+        <v>83.5409164428711</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>93.75</v>
       </c>
       <c r="G673" t="n">
-        <v>84.0339202880859</v>
+        <v>84.0339126586914</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>91.5</v>
       </c>
       <c r="G674" t="n">
-        <v>82.0171051025391</v>
+        <v>82.0171127319336</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>91.8499984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>82.3308258056641</v>
+        <v>82.3308410644531</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G676" t="n">
-        <v>82.1067428588867</v>
+        <v>82.1067352294922</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>91.6999969482422</v>
       </c>
       <c r="G678" t="n">
-        <v>82.1963729858398</v>
+        <v>82.1963806152344</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>92.9000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>83.2720108032227</v>
+        <v>83.2720184326172</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>93.8000030517578</v>
       </c>
       <c r="G680" t="n">
-        <v>84.0787353515625</v>
+        <v>84.078742980957</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>93.8000030517578</v>
       </c>
       <c r="G681" t="n">
-        <v>84.0787353515625</v>
+        <v>84.078742980957</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G682" t="n">
-        <v>82.8686370849609</v>
+        <v>82.86865234375</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>92.3499984741211</v>
       </c>
       <c r="G683" t="n">
-        <v>82.7790069580078</v>
+        <v>82.7789993286133</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>89.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>80.1347427368164</v>
+        <v>80.1347503662109</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>89.6999969482422</v>
       </c>
       <c r="G685" t="n">
-        <v>80.4036407470703</v>
+        <v>80.4036560058594</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>78.7902145385742</v>
+        <v>78.7902069091797</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G687" t="n">
-        <v>79.7313919067383</v>
+        <v>79.7313842773438</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>89</v>
       </c>
       <c r="G691" t="n">
-        <v>79.7762069702148</v>
+        <v>79.7761993408203</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>93.75</v>
       </c>
       <c r="G693" t="n">
-        <v>84.0339202880859</v>
+        <v>84.0339126586914</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>85.9162826538086</v>
+        <v>85.9162673950195</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>92.25</v>
       </c>
       <c r="G696" t="n">
-        <v>82.6893768310547</v>
+        <v>82.6893844604492</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>91.5</v>
       </c>
       <c r="G697" t="n">
-        <v>82.0171051025391</v>
+        <v>82.0171127319336</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>92.9499969482422</v>
       </c>
       <c r="G699" t="n">
-        <v>83.3168182373047</v>
+        <v>83.3168258666992</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>91</v>
       </c>
       <c r="G700" t="n">
-        <v>81.5689315795898</v>
+        <v>81.5689239501953</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G702" t="n">
-        <v>81.8378448486328</v>
+        <v>81.8378295898438</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>91</v>
       </c>
       <c r="G703" t="n">
-        <v>81.5689315795898</v>
+        <v>81.5689239501953</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>89.1999969482422</v>
       </c>
       <c r="G705" t="n">
-        <v>79.9554672241211</v>
+        <v>79.9554748535156</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>80.3000030517578</v>
       </c>
       <c r="G709" t="n">
-        <v>71.9778518676758</v>
+        <v>71.9778366088867</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G710" t="n">
-        <v>71.4400329589844</v>
+        <v>71.4400405883789</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>73.1431198120117</v>
+        <v>73.1431274414062</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>82</v>
       </c>
       <c r="G715" t="n">
-        <v>73.5016632080078</v>
+        <v>73.5016555786133</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>82.4000015258789</v>
       </c>
       <c r="G716" t="n">
-        <v>73.8602142333984</v>
+        <v>73.8602294921875</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>83.6999969482422</v>
       </c>
       <c r="G717" t="n">
-        <v>75.0254821777344</v>
+        <v>75.0254745483398</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>79.75</v>
       </c>
       <c r="G718" t="n">
-        <v>71.4848709106445</v>
+        <v>71.4848556518555</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G719" t="n">
-        <v>72.2019348144531</v>
+        <v>72.2019500732422</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>80.8499984741211</v>
       </c>
       <c r="G720" t="n">
-        <v>72.4708557128906</v>
+        <v>72.4708480834961</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>81</v>
       </c>
       <c r="G722" t="n">
-        <v>72.6053009033203</v>
+        <v>72.6053085327148</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>83.8000030517578</v>
       </c>
       <c r="G724" t="n">
-        <v>75.115119934082</v>
+        <v>75.1151275634766</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>77.8490142822266</v>
+        <v>77.8490219116211</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G729" t="n">
-        <v>73.1431198120117</v>
+        <v>73.1431274414062</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G734" t="n">
-        <v>73.1431198120117</v>
+        <v>73.1431274414062</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>80</v>
       </c>
       <c r="G735" t="n">
-        <v>71.7089385986328</v>
+        <v>71.7089309692383</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G736" t="n">
-        <v>72.7845687866211</v>
+        <v>72.7845764160156</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>81</v>
       </c>
       <c r="G737" t="n">
-        <v>72.6053009033203</v>
+        <v>72.6053085327148</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>77.25</v>
       </c>
       <c r="G738" t="n">
-        <v>69.2439498901367</v>
+        <v>69.2439422607422</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>78.8000030517578</v>
       </c>
       <c r="G741" t="n">
-        <v>70.6333236694336</v>
+        <v>70.6333084106445</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G743" t="n">
-        <v>70.9918441772461</v>
+        <v>70.9918518066406</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G744" t="n">
-        <v>69.7369613647461</v>
+        <v>69.7369537353516</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G745" t="n">
-        <v>69.5576782226562</v>
+        <v>69.5576858520508</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>75</v>
       </c>
       <c r="G747" t="n">
-        <v>67.2271270751953</v>
+        <v>67.2271347045898</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G752" t="n">
-        <v>65.7033233642578</v>
+        <v>65.7033157348633</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>72.9499969482422</v>
       </c>
       <c r="G753" t="n">
-        <v>65.3895874023438</v>
+        <v>65.3895950317383</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>74</v>
       </c>
       <c r="G754" t="n">
-        <v>66.3307800292969</v>
+        <v>66.3307723999023</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G755" t="n">
-        <v>65.6136856079102</v>
+        <v>65.6136779785156</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>71.75</v>
       </c>
       <c r="G756" t="n">
-        <v>64.31396484375</v>
+        <v>64.3139572143555</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G757" t="n">
-        <v>62.8349571228027</v>
+        <v>62.8349609375</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G758" t="n">
-        <v>63.2383346557617</v>
+        <v>63.2383308410645</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>63.1038818359375</v>
+        <v>63.1038780212402</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G760" t="n">
-        <v>63.596866607666</v>
+        <v>63.5968551635742</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>72.4499969482422</v>
       </c>
       <c r="G761" t="n">
-        <v>64.94140625</v>
+        <v>64.9414215087891</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>69.3499984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>63.746452331543</v>
+        <v>63.7464447021484</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G763" t="n">
-        <v>64.9873657226562</v>
+        <v>64.9873733520508</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G764" t="n">
-        <v>65.4469604492188</v>
+        <v>65.4469680786133</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G765" t="n">
-        <v>65.0792922973633</v>
+        <v>65.0792999267578</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G767" t="n">
-        <v>68.2045593261719</v>
+        <v>68.2045669555664</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G770" t="n">
-        <v>69.4454956054688</v>
+        <v>69.4454879760742</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G773" t="n">
-        <v>69.5833740234375</v>
+        <v>69.583366394043</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>77.5</v>
       </c>
       <c r="G774" t="n">
-        <v>71.237922668457</v>
+        <v>71.2379379272461</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>78</v>
       </c>
       <c r="G775" t="n">
-        <v>71.6975173950195</v>
+        <v>71.6975250244141</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G776" t="n">
-        <v>73.8576354980469</v>
+        <v>73.8576431274414</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G779" t="n">
-        <v>73.2142028808594</v>
+        <v>73.2141952514648</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>80.1500015258789</v>
       </c>
       <c r="G780" t="n">
-        <v>73.6738128662109</v>
+        <v>73.6738052368164</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>79.75</v>
       </c>
       <c r="G782" t="n">
-        <v>73.3061447143555</v>
+        <v>73.3061294555664</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>81.75</v>
       </c>
       <c r="G783" t="n">
-        <v>75.1445159912109</v>
+        <v>75.1445236206055</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>81.3000030517578</v>
       </c>
       <c r="G784" t="n">
-        <v>74.7308883666992</v>
+        <v>74.7308807373047</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>79.9499969482422</v>
       </c>
       <c r="G785" t="n">
-        <v>73.4899597167969</v>
+        <v>73.4899673461914</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>83.9499969482422</v>
       </c>
       <c r="G789" t="n">
-        <v>77.1667556762695</v>
+        <v>77.166748046875</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>84.8000030517578</v>
       </c>
       <c r="G795" t="n">
-        <v>77.9480819702148</v>
+        <v>77.9480895996094</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>85.1999969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>78.3157577514648</v>
+        <v>78.3157501220703</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G797" t="n">
-        <v>78.5455474853516</v>
+        <v>78.5455627441406</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>85.3000030517578</v>
       </c>
       <c r="G800" t="n">
-        <v>78.4076766967773</v>
+        <v>78.4076843261719</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>85.75</v>
       </c>
       <c r="G804" t="n">
-        <v>78.8213119506836</v>
+        <v>78.8212966918945</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>86.25</v>
       </c>
       <c r="G805" t="n">
-        <v>79.2809219360352</v>
+        <v>79.2809143066406</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G809" t="n">
-        <v>79.8324279785156</v>
+        <v>79.8324356079102</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G810" t="n">
-        <v>79.8324279785156</v>
+        <v>79.8324356079102</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>86.75</v>
       </c>
       <c r="G811" t="n">
-        <v>79.7405090332031</v>
+        <v>79.7405166625977</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>86.75</v>
       </c>
       <c r="G812" t="n">
-        <v>79.7405090332031</v>
+        <v>79.7405166625977</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G813" t="n">
-        <v>80.7056732177734</v>
+        <v>80.7056884765625</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G815" t="n">
-        <v>78.8672637939453</v>
+        <v>78.8672866821289</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G818" t="n">
-        <v>80.7516250610352</v>
+        <v>80.7516403198242</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G819" t="n">
-        <v>80.9814376831055</v>
+        <v>80.9814300537109</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G820" t="n">
-        <v>81.4870071411133</v>
+        <v>81.4869995117188</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>88.5500030517578</v>
       </c>
       <c r="G822" t="n">
-        <v>81.3950653076172</v>
+        <v>81.3950805664062</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>89.3499984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>82.1304397583008</v>
+        <v>82.1304244995117</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>88.5999984741211</v>
       </c>
       <c r="G824" t="n">
-        <v>81.441032409668</v>
+        <v>81.4410247802734</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>89.75</v>
       </c>
       <c r="G825" t="n">
-        <v>82.4981155395508</v>
+        <v>82.4981079101562</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>90.5500030517578</v>
       </c>
       <c r="G827" t="n">
-        <v>83.2334671020508</v>
+        <v>83.2334747314453</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>92.75</v>
       </c>
       <c r="G829" t="n">
-        <v>85.2557067871094</v>
+        <v>85.2557144165039</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>92</v>
       </c>
       <c r="G830" t="n">
-        <v>84.5663146972656</v>
+        <v>84.5663070678711</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>92</v>
       </c>
       <c r="G831" t="n">
-        <v>84.5663146972656</v>
+        <v>84.5663070678711</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>91.6500015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>84.2445983886719</v>
+        <v>84.2445907592773</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>91</v>
       </c>
       <c r="G834" t="n">
-        <v>83.6471252441406</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>91</v>
       </c>
       <c r="G835" t="n">
-        <v>83.6471252441406</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>91.4499969482422</v>
       </c>
       <c r="G837" t="n">
-        <v>84.0607452392578</v>
+        <v>84.0607528686523</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>91</v>
       </c>
       <c r="G838" t="n">
-        <v>83.6471252441406</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>87.6500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>80.5678024291992</v>
+        <v>80.5677947998047</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>79.8324279785156</v>
+        <v>79.8324356079102</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G841" t="n">
-        <v>80.7056732177734</v>
+        <v>80.7056884765625</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>85.75</v>
       </c>
       <c r="G842" t="n">
-        <v>78.8213119506836</v>
+        <v>78.8212966918945</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>85.1500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>78.2697982788086</v>
+        <v>78.2697906494141</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G848" t="n">
-        <v>81.4870071411133</v>
+        <v>81.4869995117188</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>90</v>
       </c>
       <c r="G852" t="n">
-        <v>82.7279205322266</v>
+        <v>82.7279052734375</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>94.1500015258789</v>
       </c>
       <c r="G855" t="n">
-        <v>86.5425872802734</v>
+        <v>86.542594909668</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>97.4499969482422</v>
       </c>
       <c r="G857" t="n">
-        <v>89.5759429931641</v>
+        <v>89.5759506225586</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>96.4499969482422</v>
       </c>
       <c r="G860" t="n">
-        <v>89.4835968017578</v>
+        <v>89.4836044311523</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>89.1588821411133</v>
+        <v>89.1588745117188</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>93.4499969482422</v>
       </c>
       <c r="G866" t="n">
-        <v>86.7002868652344</v>
+        <v>86.7002792358398</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>89.6691513061523</v>
+        <v>89.6691589355469</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>98.5</v>
       </c>
       <c r="G872" t="n">
-        <v>91.3855285644531</v>
+        <v>91.3855361938477</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>93.797737121582</v>
+        <v>93.7977294921875</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>98.5</v>
       </c>
       <c r="G875" t="n">
-        <v>91.3855285644531</v>
+        <v>91.3855361938477</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>99.25</v>
       </c>
       <c r="G876" t="n">
-        <v>92.0813674926758</v>
+        <v>92.0813598632812</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G877" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>103.5</v>
       </c>
       <c r="G878" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>105</v>
       </c>
       <c r="G882" t="n">
-        <v>97.4160461425781</v>
+        <v>97.4160385131836</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>103.300003051758</v>
       </c>
       <c r="G884" t="n">
-        <v>95.8388366699219</v>
+        <v>95.8388519287109</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>101.5</v>
       </c>
       <c r="G886" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G887" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399703979492</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>102.900001525879</v>
       </c>
       <c r="G889" t="n">
-        <v>95.4677352905273</v>
+        <v>95.4677200317383</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G890" t="n">
-        <v>95.1893997192383</v>
+        <v>95.1893920898438</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G891" t="n">
-        <v>97.6943817138672</v>
+        <v>97.6943969726562</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>103</v>
       </c>
       <c r="G893" t="n">
-        <v>95.5605010986328</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>102.800003051758</v>
       </c>
       <c r="G895" t="n">
-        <v>95.3749542236328</v>
+        <v>95.3749618530273</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G896" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G897" t="n">
-        <v>95.7460556030273</v>
+        <v>95.7460479736328</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>103</v>
       </c>
       <c r="G899" t="n">
-        <v>95.5605010986328</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>101.800003051758</v>
       </c>
       <c r="G900" t="n">
-        <v>94.4471893310547</v>
+        <v>94.4471817016602</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399703979492</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G903" t="n">
-        <v>93.9832916259766</v>
+        <v>93.9832992553711</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G904" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G906" t="n">
-        <v>94.0760803222656</v>
+        <v>94.0760650634766</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>101</v>
       </c>
       <c r="G907" t="n">
-        <v>93.7049560546875</v>
+        <v>93.704963684082</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G908" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399703979492</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G910" t="n">
-        <v>93.9832916259766</v>
+        <v>93.9832992553711</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>105</v>
       </c>
       <c r="G911" t="n">
-        <v>97.4160461425781</v>
+        <v>97.4160385131836</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>108</v>
       </c>
       <c r="G912" t="n">
-        <v>100.199371337891</v>
+        <v>100.199363708496</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>98.6221542358398</v>
+        <v>98.6221618652344</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G915" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>98.6221542358398</v>
+        <v>98.6221618652344</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G917" t="n">
-        <v>99.9210357666016</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>106.5</v>
       </c>
       <c r="G918" t="n">
-        <v>98.8077163696289</v>
+        <v>98.8077087402344</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G920" t="n">
-        <v>98.0654907226562</v>
+        <v>98.0654830932617</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G921" t="n">
-        <v>96.5810394287109</v>
+        <v>96.5810470581055</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>106</v>
       </c>
       <c r="G922" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>108.099998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>100.292137145996</v>
+        <v>100.292144775391</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>109</v>
       </c>
       <c r="G926" t="n">
-        <v>101.127143859863</v>
+        <v>101.127136230469</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G927" t="n">
-        <v>98.1582641601562</v>
+        <v>98.1582717895508</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>107</v>
       </c>
       <c r="G928" t="n">
-        <v>99.271598815918</v>
+        <v>99.2715911865234</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>99.9210357666016</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>106.5</v>
       </c>
       <c r="G930" t="n">
-        <v>98.8077163696289</v>
+        <v>98.8077087402344</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G931" t="n">
-        <v>99.828254699707</v>
+        <v>99.8282699584961</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G932" t="n">
-        <v>99.9210357666016</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>109.5</v>
       </c>
       <c r="G934" t="n">
-        <v>101.591011047363</v>
+        <v>101.591018676758</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>107</v>
       </c>
       <c r="G936" t="n">
-        <v>99.271598815918</v>
+        <v>99.2715911865234</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>101</v>
       </c>
       <c r="G939" t="n">
-        <v>93.7049560546875</v>
+        <v>93.704963684082</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>103.800003051758</v>
       </c>
       <c r="G941" t="n">
-        <v>96.302734375</v>
+        <v>96.3027267456055</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>101.5</v>
       </c>
       <c r="G943" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G944" t="n">
-        <v>95.1893997192383</v>
+        <v>95.1893920898438</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>106</v>
       </c>
       <c r="G946" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>104.800003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>97.2304992675781</v>
+        <v>97.2304916381836</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G949" t="n">
-        <v>99.0860443115234</v>
+        <v>99.0860366821289</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G950" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G953" t="n">
-        <v>98.9932556152344</v>
+        <v>98.9932632446289</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>105.400001525879</v>
       </c>
       <c r="G954" t="n">
-        <v>97.7871627807617</v>
+        <v>97.7871704101562</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>101.5</v>
       </c>
       <c r="G955" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>103.800003051758</v>
       </c>
       <c r="G956" t="n">
-        <v>96.302734375</v>
+        <v>96.3027267456055</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G957" t="n">
-        <v>98.9932556152344</v>
+        <v>98.9932632446289</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>106</v>
       </c>
       <c r="G958" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>99.9000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>92.6844100952148</v>
+        <v>92.6844177246094</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>100.199996948242</v>
       </c>
       <c r="G960" t="n">
-        <v>92.9627456665039</v>
+        <v>92.9627380371094</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G961" t="n">
-        <v>92.1277465820312</v>
+        <v>92.1277618408203</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>99.25</v>
       </c>
       <c r="G962" t="n">
-        <v>92.0813674926758</v>
+        <v>92.0813598632812</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G963" t="n">
-        <v>92.3596954345703</v>
+        <v>92.3596878051758</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G967" t="n">
-        <v>92.3596954345703</v>
+        <v>92.3596878051758</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>96.9499969482422</v>
       </c>
       <c r="G968" t="n">
-        <v>89.9474792480469</v>
+        <v>89.9474716186523</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>97.0500030517578</v>
       </c>
       <c r="G972" t="n">
-        <v>90.0402679443359</v>
+        <v>90.0402755737305</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>101</v>
       </c>
       <c r="G976" t="n">
-        <v>93.7049560546875</v>
+        <v>93.704963684082</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>93.797737121582</v>
+        <v>93.7977294921875</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G982" t="n">
-        <v>97.0449523925781</v>
+        <v>97.0449371337891</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>103.5</v>
       </c>
       <c r="G983" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>103.599998474121</v>
       </c>
       <c r="G984" t="n">
-        <v>96.1171646118164</v>
+        <v>96.1171722412109</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G985" t="n">
-        <v>98.9004898071289</v>
+        <v>98.9004745483398</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G986" t="n">
-        <v>101.219909667969</v>
+        <v>101.219917297363</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G987" t="n">
-        <v>102.70435333252</v>
+        <v>102.70433807373</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>114.5</v>
       </c>
       <c r="G989" t="n">
-        <v>106.229881286621</v>
+        <v>106.229888916016</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>105.673217773438</v>
+        <v>105.673225402832</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>115.400001525879</v>
       </c>
       <c r="G991" t="n">
-        <v>107.064872741699</v>
+        <v>107.064888000488</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G994" t="n">
-        <v>111.703750610352</v>
+        <v>111.703735351562</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G995" t="n">
-        <v>111.147087097168</v>
+        <v>111.147071838379</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G996" t="n">
-        <v>111.425407409668</v>
+        <v>111.425399780273</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>112.538726806641</v>
+        <v>112.53874206543</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G999" t="n">
-        <v>112.817054748535</v>
+        <v>112.81706237793</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G1002" t="n">
-        <v>114.858169555664</v>
+        <v>114.85816192627</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>122</v>
       </c>
       <c r="G1003" t="n">
-        <v>113.188179016113</v>
+        <v>113.188171386719</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>122</v>
       </c>
       <c r="G1004" t="n">
-        <v>113.188179016113</v>
+        <v>113.188171386719</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>121</v>
       </c>
       <c r="G1005" t="n">
-        <v>112.260406494141</v>
+        <v>112.260398864746</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>120</v>
       </c>
       <c r="G1006" t="n">
-        <v>111.332626342773</v>
+        <v>111.332633972168</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>116</v>
       </c>
       <c r="G1007" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>117</v>
       </c>
       <c r="G1009" t="n">
-        <v>108.549324035645</v>
+        <v>108.54931640625</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1010" t="n">
-        <v>108.270988464355</v>
+        <v>108.270965576172</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>117.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>109.013191223145</v>
+        <v>109.013198852539</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>116</v>
       </c>
       <c r="G1014" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>115.400001525879</v>
       </c>
       <c r="G1015" t="n">
-        <v>107.064872741699</v>
+        <v>107.064888000488</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>116.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>108.085418701172</v>
+        <v>108.085426330566</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G1019" t="n">
-        <v>109.848197937012</v>
+        <v>109.848190307617</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>119.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>110.86873626709</v>
+        <v>110.868743896484</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1022" t="n">
-        <v>108.82763671875</v>
+        <v>108.827651977539</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1023" t="n">
-        <v>108.270988464355</v>
+        <v>108.270965576172</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>117</v>
       </c>
       <c r="G1025" t="n">
-        <v>108.549324035645</v>
+        <v>108.54931640625</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>116.900001525879</v>
       </c>
       <c r="G1027" t="n">
-        <v>108.456535339355</v>
+        <v>108.456527709961</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>106.044326782227</v>
+        <v>106.044334411621</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G1032" t="n">
-        <v>106.78653717041</v>
+        <v>106.786544799805</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>112.599998474121</v>
       </c>
       <c r="G1033" t="n">
-        <v>104.467124938965</v>
+        <v>104.46711730957</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>115.599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>107.250427246094</v>
+        <v>107.250434875488</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>111</v>
       </c>
       <c r="G1037" t="n">
-        <v>102.982681274414</v>
+        <v>102.98267364502</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>103.817672729492</v>
+        <v>103.817680358887</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>114</v>
       </c>
       <c r="G1039" t="n">
-        <v>105.766006469727</v>
+        <v>105.765998840332</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1042" t="n">
-        <v>106.044326782227</v>
+        <v>106.044334411621</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>114.699996948242</v>
       </c>
       <c r="G1043" t="n">
-        <v>106.415435791016</v>
+        <v>106.415420532227</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>116</v>
       </c>
       <c r="G1044" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>108.82763671875</v>
+        <v>108.827651977539</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>117.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>109.013191223145</v>
+        <v>109.013198852539</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>107.899864196777</v>
+        <v>107.899887084961</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G1054" t="n">
-        <v>98.6221542358398</v>
+        <v>98.6221618652344</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G1059" t="n">
-        <v>97.6943817138672</v>
+        <v>97.6943969726562</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G1060" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>104.5</v>
       </c>
       <c r="G1061" t="n">
-        <v>96.9521636962891</v>
+        <v>96.9521713256836</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>101</v>
       </c>
       <c r="G1063" t="n">
-        <v>93.7049560546875</v>
+        <v>93.704963684082</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>103</v>
       </c>
       <c r="G1066" t="n">
-        <v>95.5605010986328</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>109.599998474121</v>
       </c>
       <c r="G1067" t="n">
-        <v>101.683807373047</v>
+        <v>101.683799743652</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>107.800003051758</v>
       </c>
       <c r="G1068" t="n">
-        <v>100.013809204102</v>
+        <v>100.013816833496</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>99.0860443115234</v>
+        <v>99.0860366821289</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>114.400001525879</v>
       </c>
       <c r="G1071" t="n">
-        <v>106.137107849121</v>
+        <v>106.137092590332</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1072" t="n">
-        <v>103.539360046387</v>
+        <v>103.539344787598</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>116.800003051758</v>
       </c>
       <c r="G1073" t="n">
-        <v>108.363761901855</v>
+        <v>108.363754272461</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>115.199996948242</v>
       </c>
       <c r="G1074" t="n">
-        <v>106.879318237305</v>
+        <v>106.879325866699</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>110.5</v>
       </c>
       <c r="G1076" t="n">
-        <v>102.518798828125</v>
+        <v>102.51879119873</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>116.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>108.085418701172</v>
+        <v>108.085426330566</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>109.569862365723</v>
+        <v>109.569869995117</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G1084" t="n">
-        <v>115.878715515137</v>
+        <v>115.878707885742</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>129.399993896484</v>
       </c>
       <c r="G1085" t="n">
-        <v>120.053680419922</v>
+        <v>120.053688049316</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1086" t="n">
-        <v>123.764770507812</v>
+        <v>123.764762878418</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>140</v>
       </c>
       <c r="G1087" t="n">
-        <v>129.888046264648</v>
+        <v>129.888092041016</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>149.800003051758</v>
       </c>
       <c r="G1088" t="n">
-        <v>138.980239868164</v>
+        <v>138.980224609375</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>144.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>134.063049316406</v>
+        <v>134.063034057617</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>153.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>142.412994384766</v>
+        <v>142.413024902344</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G1092" t="n">
-        <v>141.577987670898</v>
+        <v>141.578002929688</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>165</v>
       </c>
       <c r="G1093" t="n">
-        <v>153.082382202148</v>
+        <v>153.082366943359</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1094" t="n">
-        <v>147.608489990234</v>
+        <v>147.608505249023</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>166.899993896484</v>
       </c>
       <c r="G1096" t="n">
-        <v>154.845108032227</v>
+        <v>154.845123291016</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1097" t="n">
-        <v>155.030685424805</v>
+        <v>155.030700683594</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1098" t="n">
-        <v>150.484619140625</v>
+        <v>150.484588623047</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>155.300003051758</v>
       </c>
       <c r="G1099" t="n">
-        <v>144.082977294922</v>
+        <v>144.0830078125</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1100" t="n">
-        <v>144.175765991211</v>
+        <v>144.175750732422</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1103" t="n">
-        <v>143.619094848633</v>
+        <v>143.619079589844</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>156.199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>144.91796875</v>
+        <v>144.917984008789</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>162.5</v>
       </c>
       <c r="G1105" t="n">
-        <v>150.762924194336</v>
+        <v>150.762939453125</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>160.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>148.90739440918</v>
+        <v>148.907379150391</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>184.800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>171.452255249023</v>
+        <v>171.452239990234</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>179.199996948242</v>
       </c>
       <c r="G1111" t="n">
-        <v>166.256729125977</v>
+        <v>166.256744384766</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>190.899993896484</v>
       </c>
       <c r="G1113" t="n">
-        <v>177.111663818359</v>
+        <v>177.11164855957</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>202.800003051758</v>
       </c>
       <c r="G1114" t="n">
-        <v>188.152160644531</v>
+        <v>188.152130126953</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>209.399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>194.275405883789</v>
+        <v>194.275421142578</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>197</v>
       </c>
       <c r="G1116" t="n">
-        <v>182.771057128906</v>
+        <v>182.771072387695</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>188.5</v>
       </c>
       <c r="G1119" t="n">
-        <v>174.885025024414</v>
+        <v>174.884994506836</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>181.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>168.390594482422</v>
+        <v>168.390625</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>178.899993896484</v>
       </c>
       <c r="G1121" t="n">
-        <v>165.978393554688</v>
+        <v>165.978408813477</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>173.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>160.968414306641</v>
+        <v>160.968444824219</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1123" t="n">
-        <v>161.617889404297</v>
+        <v>161.617858886719</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>161.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>149.835174560547</v>
+        <v>149.835159301758</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>164</v>
       </c>
       <c r="G1127" t="n">
-        <v>152.154602050781</v>
+        <v>152.154586791992</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>167</v>
       </c>
       <c r="G1129" t="n">
-        <v>154.937911987305</v>
+        <v>154.937896728516</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>169.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>158.157012939453</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1134" t="n">
-        <v>156.197555541992</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1135" t="n">
-        <v>159.276718139648</v>
+        <v>159.276702880859</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>175.800003051758</v>
       </c>
       <c r="G1136" t="n">
-        <v>164.035461425781</v>
+        <v>164.035446166992</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>173</v>
       </c>
       <c r="G1138" t="n">
-        <v>161.422805786133</v>
+        <v>161.422821044922</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>169.699996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>158.343658447266</v>
+        <v>158.343643188477</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>170.399993896484</v>
       </c>
       <c r="G1141" t="n">
-        <v>158.996795654297</v>
+        <v>158.996810913086</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>171.300003051758</v>
       </c>
       <c r="G1143" t="n">
-        <v>159.836563110352</v>
+        <v>159.836578369141</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>171.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>160.023178100586</v>
+        <v>160.023193359375</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>172.899993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>161.329483032227</v>
+        <v>161.329498291016</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>175.800003051758</v>
       </c>
       <c r="G1152" t="n">
-        <v>164.035461425781</v>
+        <v>164.035446166992</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>178.199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>166.274841308594</v>
+        <v>166.274826049805</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>180.899993896484</v>
       </c>
       <c r="G1155" t="n">
-        <v>168.794143676758</v>
+        <v>168.794128417969</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>178.300003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>166.368133544922</v>
+        <v>166.368148803711</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>162.699996948242</v>
       </c>
       <c r="G1159" t="n">
-        <v>151.812072753906</v>
+        <v>151.812103271484</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>142.574584960938</v>
+        <v>142.574600219727</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>160.199996948242</v>
       </c>
       <c r="G1172" t="n">
-        <v>149.479400634766</v>
+        <v>149.479370117188</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>159.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>148.826248168945</v>
+        <v>148.826232910156</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1176" t="n">
-        <v>148.452987670898</v>
+        <v>148.453002929688</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1177" t="n">
-        <v>151.345565795898</v>
+        <v>151.345550537109</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>163</v>
       </c>
       <c r="G1179" t="n">
-        <v>152.092010498047</v>
+        <v>152.091995239258</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>163.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>152.558532714844</v>
+        <v>152.558547973633</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>163.899993896484</v>
       </c>
       <c r="G1181" t="n">
-        <v>152.931777954102</v>
+        <v>152.931762695312</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1182" t="n">
-        <v>156.477508544922</v>
+        <v>156.477493286133</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1183" t="n">
-        <v>142.947830200195</v>
+        <v>142.947814941406</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>151.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>141.361587524414</v>
+        <v>141.361602783203</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>151</v>
       </c>
       <c r="G1187" t="n">
-        <v>140.895065307617</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G1188" t="n">
-        <v>133.057205200195</v>
+        <v>133.057189941406</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G1189" t="n">
-        <v>132.310729980469</v>
+        <v>132.31071472168</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>144.300003051758</v>
       </c>
       <c r="G1191" t="n">
-        <v>134.643417358398</v>
+        <v>134.643432617188</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G1192" t="n">
-        <v>142.108047485352</v>
+        <v>142.108062744141</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G1193" t="n">
-        <v>140.615127563477</v>
+        <v>140.615142822266</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>154.699996948242</v>
       </c>
       <c r="G1194" t="n">
-        <v>144.347442626953</v>
+        <v>144.347457885742</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1195" t="n">
-        <v>145.000610351562</v>
+        <v>145.000595092773</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>157</v>
       </c>
       <c r="G1196" t="n">
-        <v>146.493530273438</v>
+        <v>146.493515014648</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>160.899993896484</v>
       </c>
       <c r="G1197" t="n">
-        <v>150.132553100586</v>
+        <v>150.132537841797</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1198" t="n">
-        <v>147.613235473633</v>
+        <v>147.613220214844</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>156.197555541992</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>156.477508544922</v>
+        <v>156.477493286133</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>170.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>159.090118408203</v>
+        <v>159.090133666992</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>171.899993896484</v>
       </c>
       <c r="G1207" t="n">
-        <v>160.396423339844</v>
+        <v>160.396408081055</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>182.5</v>
       </c>
       <c r="G1213" t="n">
-        <v>170.287063598633</v>
+        <v>170.287048339844</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>188</v>
       </c>
       <c r="G1214" t="n">
-        <v>175.418991088867</v>
+        <v>175.419021606445</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>191.300003051758</v>
       </c>
       <c r="G1217" t="n">
-        <v>178.498168945312</v>
+        <v>178.498153686523</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>189</v>
       </c>
       <c r="G1218" t="n">
-        <v>176.352081298828</v>
+        <v>176.352111816406</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>194.600006103516</v>
       </c>
       <c r="G1219" t="n">
-        <v>181.577331542969</v>
+        <v>181.577346801758</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>193.600006103516</v>
       </c>
       <c r="G1220" t="n">
-        <v>180.644256591797</v>
+        <v>180.644271850586</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>192.600006103516</v>
       </c>
       <c r="G1223" t="n">
-        <v>179.711166381836</v>
+        <v>179.711181640625</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>188</v>
       </c>
       <c r="G1224" t="n">
-        <v>175.418991088867</v>
+        <v>175.419021606445</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>189</v>
       </c>
       <c r="G1225" t="n">
-        <v>176.352081298828</v>
+        <v>176.352111816406</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>188.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>175.885559082031</v>
+        <v>175.885528564453</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>185.699996948242</v>
       </c>
       <c r="G1230" t="n">
-        <v>173.272918701172</v>
+        <v>173.272903442383</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>187.100006103516</v>
       </c>
       <c r="G1231" t="n">
-        <v>174.579238891602</v>
+        <v>174.579223632812</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>168</v>
       </c>
       <c r="G1235" t="n">
-        <v>156.757431030273</v>
+        <v>156.757415771484</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>173</v>
       </c>
       <c r="G1238" t="n">
-        <v>161.422805786133</v>
+        <v>161.422821044922</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>173.800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>162.169296264648</v>
+        <v>162.169281005859</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>165.100006103516</v>
       </c>
       <c r="G1246" t="n">
-        <v>154.051467895508</v>
+        <v>154.051483154297</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>169.199996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>157.877090454102</v>
+        <v>157.87712097168</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>168.399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>157.130645751953</v>
+        <v>157.130661010742</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>171.199996948242</v>
       </c>
       <c r="G1256" t="n">
-        <v>159.743255615234</v>
+        <v>159.743286132812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>169.699996948242</v>
       </c>
       <c r="G1258" t="n">
-        <v>158.343658447266</v>
+        <v>158.343643188477</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>170.5</v>
       </c>
       <c r="G1259" t="n">
-        <v>159.090118408203</v>
+        <v>159.090133666992</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1260" t="n">
-        <v>159.276718139648</v>
+        <v>159.276702880859</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>167.600006103516</v>
       </c>
       <c r="G1261" t="n">
-        <v>156.384170532227</v>
+        <v>156.384185791016</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1264" t="n">
-        <v>159.276718139648</v>
+        <v>159.276702880859</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>171.699996948242</v>
       </c>
       <c r="G1265" t="n">
-        <v>160.209823608398</v>
+        <v>160.209808349609</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1267" t="n">
-        <v>156.197555541992</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>167.300003051758</v>
       </c>
       <c r="G1268" t="n">
-        <v>156.104263305664</v>
+        <v>156.104248046875</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>170.100006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>158.716888427734</v>
+        <v>158.716873168945</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1271" t="n">
-        <v>158.250350952148</v>
+        <v>158.250335693359</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1273" t="n">
-        <v>150.97233581543</v>
+        <v>150.972320556641</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>150.97233581543</v>
+        <v>150.972320556641</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>159.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>148.826248168945</v>
+        <v>148.826232910156</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>159.399993896484</v>
       </c>
       <c r="G1277" t="n">
-        <v>148.732925415039</v>
+        <v>148.73291015625</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>151.718795776367</v>
+        <v>151.718780517578</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>171.199996948242</v>
       </c>
       <c r="G1282" t="n">
-        <v>159.743255615234</v>
+        <v>159.743286132812</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>179.699996948242</v>
       </c>
       <c r="G1286" t="n">
-        <v>167.674423217773</v>
+        <v>167.674453735352</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1287" t="n">
-        <v>166.834671020508</v>
+        <v>166.834686279297</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>180.600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>168.514236450195</v>
+        <v>168.514221191406</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>179.399993896484</v>
       </c>
       <c r="G1292" t="n">
-        <v>167.394515991211</v>
+        <v>167.39453125</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>176.5</v>
       </c>
       <c r="G1293" t="n">
-        <v>164.688598632812</v>
+        <v>164.688583374023</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>179.100006103516</v>
       </c>
       <c r="G1295" t="n">
-        <v>167.11457824707</v>
+        <v>167.114608764648</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>182.899993896484</v>
       </c>
       <c r="G1297" t="n">
-        <v>170.660293579102</v>
+        <v>170.660308837891</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>182.199996948242</v>
       </c>
       <c r="G1298" t="n">
-        <v>170.007141113281</v>
+        <v>170.007171630859</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>184.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>172.153228759766</v>
+        <v>172.153213500977</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>185.600006103516</v>
       </c>
       <c r="G1300" t="n">
-        <v>173.179611206055</v>
+        <v>173.179626464844</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>186.399993896484</v>
       </c>
       <c r="G1302" t="n">
-        <v>173.926086425781</v>
+        <v>173.926055908203</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>166.834671020508</v>
+        <v>166.834686279297</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>169.5</v>
       </c>
       <c r="G1305" t="n">
-        <v>158.157012939453</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>164.300003051758</v>
       </c>
       <c r="G1306" t="n">
-        <v>153.305023193359</v>
+        <v>153.305038452148</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>159.699996948242</v>
       </c>
       <c r="G1307" t="n">
-        <v>149.012847900391</v>
+        <v>149.01286315918</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1308" t="n">
-        <v>147.613235473633</v>
+        <v>147.613220214844</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1309" t="n">
-        <v>153.118408203125</v>
+        <v>153.118392944336</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1310" t="n">
-        <v>151.532150268555</v>
+        <v>151.532165527344</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>164</v>
       </c>
       <c r="G1311" t="n">
-        <v>153.025100708008</v>
+        <v>153.025085449219</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>150.97233581543</v>
+        <v>150.972320556641</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1314" t="n">
-        <v>153.118408203125</v>
+        <v>153.118392944336</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>158</v>
       </c>
       <c r="G1316" t="n">
-        <v>147.426605224609</v>
+        <v>147.42658996582</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G1317" t="n">
-        <v>146.306915283203</v>
+        <v>146.306930541992</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>144.300003051758</v>
       </c>
       <c r="G1319" t="n">
-        <v>134.643417358398</v>
+        <v>134.643432617188</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G1320" t="n">
-        <v>130.257949829102</v>
+        <v>130.257934570312</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>145.899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>136.136322021484</v>
+        <v>136.136337280273</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>140.100006103516</v>
       </c>
       <c r="G1324" t="n">
-        <v>130.724487304688</v>
+        <v>130.724502563477</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>133.523712158203</v>
+        <v>133.523727416992</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>141</v>
       </c>
       <c r="G1327" t="n">
-        <v>131.564254760742</v>
+        <v>131.564239501953</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>140</v>
       </c>
       <c r="G1328" t="n">
-        <v>130.631164550781</v>
+        <v>130.63117980957</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>142.300003051758</v>
       </c>
       <c r="G1329" t="n">
-        <v>132.777252197266</v>
+        <v>132.777267456055</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>139</v>
       </c>
       <c r="G1330" t="n">
-        <v>129.698089599609</v>
+        <v>129.698104858398</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>128.111862182617</v>
+        <v>128.111877441406</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>139.75</v>
       </c>
       <c r="G1334" t="n">
-        <v>130.397903442383</v>
+        <v>130.397918701172</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>139.75</v>
       </c>
       <c r="G1337" t="n">
-        <v>130.397903442383</v>
+        <v>130.397918701172</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>130.257949829102</v>
+        <v>130.257934570312</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>153.050003051758</v>
       </c>
       <c r="G1339" t="n">
-        <v>142.807861328125</v>
+        <v>142.807876586914</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>151.050003051758</v>
       </c>
       <c r="G1340" t="n">
-        <v>140.941711425781</v>
+        <v>140.941696166992</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>151</v>
       </c>
       <c r="G1342" t="n">
-        <v>140.895065307617</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1343" t="n">
-        <v>142.947830200195</v>
+        <v>142.947814941406</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>155.899993896484</v>
       </c>
       <c r="G1345" t="n">
-        <v>145.467132568359</v>
+        <v>145.467147827148</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>155.75</v>
       </c>
       <c r="G1346" t="n">
-        <v>145.327178955078</v>
+        <v>145.327194213867</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1347" t="n">
-        <v>143.600967407227</v>
+        <v>143.600982666016</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>152.550003051758</v>
       </c>
       <c r="G1348" t="n">
-        <v>142.341339111328</v>
+        <v>142.341323852539</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>152.399993896484</v>
       </c>
       <c r="G1349" t="n">
-        <v>142.201354980469</v>
+        <v>142.20133972168</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>144.100006103516</v>
       </c>
       <c r="G1350" t="n">
-        <v>134.456802368164</v>
+        <v>134.456817626953</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>140.25</v>
       </c>
       <c r="G1352" t="n">
-        <v>130.864456176758</v>
+        <v>130.864440917969</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>141.25</v>
       </c>
       <c r="G1353" t="n">
-        <v>131.797546386719</v>
+        <v>131.79753112793</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1354" t="n">
-        <v>131.424301147461</v>
+        <v>131.424285888672</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>142.649993896484</v>
       </c>
       <c r="G1359" t="n">
-        <v>133.103851318359</v>
+        <v>133.10383605957</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>138.25</v>
       </c>
       <c r="G1360" t="n">
-        <v>128.998275756836</v>
+        <v>128.998291015625</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G1362" t="n">
-        <v>129.044937133789</v>
+        <v>129.044967651367</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>138</v>
       </c>
       <c r="G1363" t="n">
-        <v>128.765014648438</v>
+        <v>128.765029907227</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>131.424301147461</v>
+        <v>131.424285888672</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>141.649993896484</v>
       </c>
       <c r="G1365" t="n">
-        <v>132.170745849609</v>
+        <v>132.170761108398</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>144</v>
       </c>
       <c r="G1367" t="n">
-        <v>134.363494873047</v>
+        <v>134.363510131836</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>78.4800033569336</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>103702</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>78.7600021362305</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>76.9800033569336</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>78.0599975585938</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>48.1800003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>41.7114067077637</v>
+        <v>41.7114105224609</v>
       </c>
       <c r="H2" t="n">
         <v>50491</v>
@@ -456,7 +456,7 @@
         <v>49.0900001525879</v>
       </c>
       <c r="G3" t="n">
-        <v>42.4992332458496</v>
+        <v>42.4992294311523</v>
       </c>
       <c r="H3" t="n">
         <v>89363</v>
@@ -485,7 +485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>42.2481689453125</v>
+        <v>42.2481651306152</v>
       </c>
       <c r="H4" t="n">
         <v>42997</v>
@@ -514,7 +514,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G5" t="n">
-        <v>42.1356163024902</v>
+        <v>42.1356239318848</v>
       </c>
       <c r="H5" t="n">
         <v>91520</v>
@@ -688,7 +688,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>39.2613639831543</v>
+        <v>39.261360168457</v>
       </c>
       <c r="H11" t="n">
         <v>122604</v>
@@ -717,7 +717,7 @@
         <v>44.5299987792969</v>
       </c>
       <c r="G12" t="n">
-        <v>38.5514488220215</v>
+        <v>38.5514526367188</v>
       </c>
       <c r="H12" t="n">
         <v>78904</v>
@@ -804,7 +804,7 @@
         <v>42.6800003051758</v>
       </c>
       <c r="G15" t="n">
-        <v>36.9498329162598</v>
+        <v>36.9498291015625</v>
       </c>
       <c r="H15" t="n">
         <v>170667</v>
@@ -833,7 +833,7 @@
         <v>44.1699981689453</v>
       </c>
       <c r="G16" t="n">
-        <v>38.2397880554199</v>
+        <v>38.2397918701172</v>
       </c>
       <c r="H16" t="n">
         <v>186077</v>
@@ -862,7 +862,7 @@
         <v>45.6399993896484</v>
       </c>
       <c r="G17" t="n">
-        <v>39.5124320983887</v>
+        <v>39.5124244689941</v>
       </c>
       <c r="H17" t="n">
         <v>218430</v>
@@ -920,7 +920,7 @@
         <v>47.6800003051758</v>
       </c>
       <c r="G19" t="n">
-        <v>41.2785453796387</v>
+        <v>41.2785415649414</v>
       </c>
       <c r="H19" t="n">
         <v>97163</v>
@@ -949,7 +949,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>40.6032600402832</v>
+        <v>40.6032638549805</v>
       </c>
       <c r="H20" t="n">
         <v>145072</v>
@@ -978,7 +978,7 @@
         <v>48.5</v>
       </c>
       <c r="G21" t="n">
-        <v>41.9884376525879</v>
+        <v>41.9884490966797</v>
       </c>
       <c r="H21" t="n">
         <v>102390</v>
@@ -1007,7 +1007,7 @@
         <v>48.8300018310547</v>
       </c>
       <c r="G22" t="n">
-        <v>42.2741432189941</v>
+        <v>42.2741394042969</v>
       </c>
       <c r="H22" t="n">
         <v>142479</v>
@@ -1036,7 +1036,7 @@
         <v>48.75</v>
       </c>
       <c r="G23" t="n">
-        <v>42.2048835754395</v>
+        <v>42.2048797607422</v>
       </c>
       <c r="H23" t="n">
         <v>112008</v>
@@ -1094,7 +1094,7 @@
         <v>46.75</v>
       </c>
       <c r="G25" t="n">
-        <v>40.4734001159668</v>
+        <v>40.4734039306641</v>
       </c>
       <c r="H25" t="n">
         <v>58114</v>
@@ -1123,7 +1123,7 @@
         <v>44.689998626709</v>
       </c>
       <c r="G26" t="n">
-        <v>38.6899642944336</v>
+        <v>38.6899719238281</v>
       </c>
       <c r="H26" t="n">
         <v>47084</v>
@@ -1152,7 +1152,7 @@
         <v>42.810001373291</v>
       </c>
       <c r="G27" t="n">
-        <v>37.0623779296875</v>
+        <v>37.0623817443848</v>
       </c>
       <c r="H27" t="n">
         <v>79262</v>
@@ -1181,7 +1181,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>37.3134460449219</v>
+        <v>37.3134422302246</v>
       </c>
       <c r="H28" t="n">
         <v>129293</v>
@@ -1239,7 +1239,7 @@
         <v>43.7700004577637</v>
       </c>
       <c r="G30" t="n">
-        <v>37.8934898376465</v>
+        <v>37.893482208252</v>
       </c>
       <c r="H30" t="n">
         <v>96253</v>
@@ -1268,7 +1268,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G31" t="n">
-        <v>37.6943702697754</v>
+        <v>37.6943664550781</v>
       </c>
       <c r="H31" t="n">
         <v>98162</v>
@@ -1297,7 +1297,7 @@
         <v>45.4900016784668</v>
       </c>
       <c r="G32" t="n">
-        <v>39.3825607299805</v>
+        <v>39.3825645446777</v>
       </c>
       <c r="H32" t="n">
         <v>72531</v>
@@ -1326,7 +1326,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>39.650951385498</v>
+        <v>39.6509437561035</v>
       </c>
       <c r="H33" t="n">
         <v>45200</v>
@@ -1355,7 +1355,7 @@
         <v>45.9099998474121</v>
       </c>
       <c r="G34" t="n">
-        <v>39.7461853027344</v>
+        <v>39.7461776733398</v>
       </c>
       <c r="H34" t="n">
         <v>76568</v>
@@ -1384,7 +1384,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G35" t="n">
-        <v>40.6378860473633</v>
+        <v>40.6378898620605</v>
       </c>
       <c r="H35" t="n">
         <v>46426</v>
@@ -1442,7 +1442,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="G37" t="n">
-        <v>41.7633514404297</v>
+        <v>41.7633590698242</v>
       </c>
       <c r="H37" t="n">
         <v>101109</v>
@@ -1471,7 +1471,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G38" t="n">
-        <v>41.1659851074219</v>
+        <v>41.1659889221191</v>
       </c>
       <c r="H38" t="n">
         <v>78199</v>
@@ -1500,7 +1500,7 @@
         <v>48.2900009155273</v>
       </c>
       <c r="G39" t="n">
-        <v>41.8066368103027</v>
+        <v>41.806640625</v>
       </c>
       <c r="H39" t="n">
         <v>92020</v>
@@ -1529,7 +1529,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G40" t="n">
-        <v>42.4126625061035</v>
+        <v>42.4126586914062</v>
       </c>
       <c r="H40" t="n">
         <v>70387</v>
@@ -1558,7 +1558,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G41" t="n">
-        <v>42.1356163024902</v>
+        <v>42.1356239318848</v>
       </c>
       <c r="H41" t="n">
         <v>51830</v>
@@ -1587,7 +1587,7 @@
         <v>48.6399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>42.1096496582031</v>
+        <v>42.1096458435059</v>
       </c>
       <c r="H42" t="n">
         <v>26989</v>
@@ -1616,7 +1616,7 @@
         <v>49.0099983215332</v>
       </c>
       <c r="G43" t="n">
-        <v>42.4299697875977</v>
+        <v>42.4299659729004</v>
       </c>
       <c r="H43" t="n">
         <v>93647</v>
@@ -1674,7 +1674,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G45" t="n">
-        <v>41.0361328125</v>
+        <v>41.0361289978027</v>
       </c>
       <c r="H45" t="n">
         <v>49878</v>
@@ -1819,7 +1819,7 @@
         <v>45.75</v>
       </c>
       <c r="G50" t="n">
-        <v>39.6076583862305</v>
+        <v>39.6076545715332</v>
       </c>
       <c r="H50" t="n">
         <v>108080</v>
@@ -1848,7 +1848,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>39.2700157165527</v>
+        <v>39.2700233459473</v>
       </c>
       <c r="H51" t="n">
         <v>118250</v>
@@ -1906,7 +1906,7 @@
         <v>46</v>
       </c>
       <c r="G53" t="n">
-        <v>39.8240966796875</v>
+        <v>39.8240928649902</v>
       </c>
       <c r="H53" t="n">
         <v>39106</v>
@@ -1935,7 +1935,7 @@
         <v>45.5299987792969</v>
       </c>
       <c r="G54" t="n">
-        <v>39.4171981811523</v>
+        <v>39.4171905517578</v>
       </c>
       <c r="H54" t="n">
         <v>51747</v>
@@ -1964,7 +1964,7 @@
         <v>44.9199981689453</v>
       </c>
       <c r="G55" t="n">
-        <v>38.8890914916992</v>
+        <v>38.889087677002</v>
       </c>
       <c r="H55" t="n">
         <v>53754</v>
@@ -1993,7 +1993,7 @@
         <v>45.4799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>39.3739051818848</v>
+        <v>39.3739128112793</v>
       </c>
       <c r="H56" t="n">
         <v>99139</v>
@@ -2051,7 +2051,7 @@
         <v>45.1699981689453</v>
       </c>
       <c r="G58" t="n">
-        <v>39.1055221557617</v>
+        <v>39.1055297851562</v>
       </c>
       <c r="H58" t="n">
         <v>71459</v>
@@ -2080,7 +2080,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>39.650951385498</v>
+        <v>39.6509437561035</v>
       </c>
       <c r="H59" t="n">
         <v>54272</v>
@@ -2109,7 +2109,7 @@
         <v>45.5</v>
       </c>
       <c r="G60" t="n">
-        <v>39.3912200927734</v>
+        <v>39.3912162780762</v>
       </c>
       <c r="H60" t="n">
         <v>58510</v>
@@ -2138,7 +2138,7 @@
         <v>45.8800010681152</v>
       </c>
       <c r="G61" t="n">
-        <v>39.7201995849609</v>
+        <v>39.7202033996582</v>
       </c>
       <c r="H61" t="n">
         <v>48377</v>
@@ -2167,7 +2167,7 @@
         <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>43.287052154541</v>
+        <v>43.2870559692383</v>
       </c>
       <c r="H62" t="n">
         <v>415378</v>
@@ -2196,7 +2196,7 @@
         <v>50.75</v>
       </c>
       <c r="G63" t="n">
-        <v>43.9363632202148</v>
+        <v>43.9363555908203</v>
       </c>
       <c r="H63" t="n">
         <v>128937</v>
@@ -2225,7 +2225,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>44.4558067321777</v>
+        <v>44.455810546875</v>
       </c>
       <c r="H64" t="n">
         <v>210539</v>
@@ -2254,7 +2254,7 @@
         <v>52</v>
       </c>
       <c r="G65" t="n">
-        <v>45.0185394287109</v>
+        <v>45.0185356140137</v>
       </c>
       <c r="H65" t="n">
         <v>75333</v>
@@ -2283,7 +2283,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>44.5423812866211</v>
+        <v>44.5423851013184</v>
       </c>
       <c r="H66" t="n">
         <v>64536</v>
@@ -2341,7 +2341,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>45.9708518981934</v>
+        <v>45.9708480834961</v>
       </c>
       <c r="H68" t="n">
         <v>102885</v>
@@ -2370,7 +2370,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>45.0618286132812</v>
+        <v>45.0618324279785</v>
       </c>
       <c r="H69" t="n">
         <v>49881</v>
@@ -2399,7 +2399,7 @@
         <v>52</v>
       </c>
       <c r="G70" t="n">
-        <v>45.0185394287109</v>
+        <v>45.0185356140137</v>
       </c>
       <c r="H70" t="n">
         <v>54828</v>
@@ -2457,7 +2457,7 @@
         <v>51.5</v>
       </c>
       <c r="G72" t="n">
-        <v>44.5856666564941</v>
+        <v>44.5856704711914</v>
       </c>
       <c r="H72" t="n">
         <v>48281</v>
@@ -2486,7 +2486,7 @@
         <v>51.25</v>
       </c>
       <c r="G73" t="n">
-        <v>44.3692283630371</v>
+        <v>44.3692321777344</v>
       </c>
       <c r="H73" t="n">
         <v>51163</v>
@@ -2515,7 +2515,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>44.0662231445312</v>
+        <v>44.066234588623</v>
       </c>
       <c r="H74" t="n">
         <v>33163</v>
@@ -2573,7 +2573,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>44.4558067321777</v>
+        <v>44.455810546875</v>
       </c>
       <c r="H76" t="n">
         <v>38314</v>
@@ -2631,7 +2631,7 @@
         <v>51.5</v>
       </c>
       <c r="G78" t="n">
-        <v>44.5856666564941</v>
+        <v>44.5856704711914</v>
       </c>
       <c r="H78" t="n">
         <v>45300</v>
@@ -2660,7 +2660,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>43.9796524047852</v>
+        <v>43.9796447753906</v>
       </c>
       <c r="H79" t="n">
         <v>48596</v>
@@ -2689,7 +2689,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>43.8930740356445</v>
+        <v>43.8930778503418</v>
       </c>
       <c r="H80" t="n">
         <v>23134</v>
@@ -2718,7 +2718,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>43.8930740356445</v>
+        <v>43.8930778503418</v>
       </c>
       <c r="H81" t="n">
         <v>44420</v>
@@ -2747,7 +2747,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G82" t="n">
-        <v>43.9796524047852</v>
+        <v>43.9796447753906</v>
       </c>
       <c r="H82" t="n">
         <v>25530</v>
@@ -2776,7 +2776,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>44.4125137329102</v>
+        <v>44.4125213623047</v>
       </c>
       <c r="H83" t="n">
         <v>50375</v>
@@ -2892,7 +2892,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G87" t="n">
-        <v>44.9319686889648</v>
+        <v>44.9319648742676</v>
       </c>
       <c r="H87" t="n">
         <v>30778</v>
@@ -2921,7 +2921,7 @@
         <v>51.75</v>
       </c>
       <c r="G88" t="n">
-        <v>44.8021011352539</v>
+        <v>44.8021049499512</v>
       </c>
       <c r="H88" t="n">
         <v>26493</v>
@@ -2950,7 +2950,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>44.9752540588379</v>
+        <v>44.9752502441406</v>
       </c>
       <c r="H89" t="n">
         <v>44495</v>
@@ -2979,7 +2979,7 @@
         <v>52.5</v>
       </c>
       <c r="G90" t="n">
-        <v>45.4514045715332</v>
+        <v>45.4514122009277</v>
       </c>
       <c r="H90" t="n">
         <v>86395</v>
@@ -3008,7 +3008,7 @@
         <v>52.5</v>
       </c>
       <c r="G91" t="n">
-        <v>45.4514045715332</v>
+        <v>45.4514122009277</v>
       </c>
       <c r="H91" t="n">
         <v>38800</v>
@@ -3037,7 +3037,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G92" t="n">
-        <v>45.3215446472168</v>
+        <v>45.3215484619141</v>
       </c>
       <c r="H92" t="n">
         <v>34602</v>
@@ -3095,7 +3095,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>45.7544212341309</v>
+        <v>45.7544174194336</v>
       </c>
       <c r="H94" t="n">
         <v>40411</v>
@@ -3153,7 +3153,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>45.0618286132812</v>
+        <v>45.0618324279785</v>
       </c>
       <c r="H96" t="n">
         <v>56148</v>
@@ -3211,7 +3211,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>45.1484107971191</v>
+        <v>45.1483993530273</v>
       </c>
       <c r="H98" t="n">
         <v>38023</v>
@@ -3269,7 +3269,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H100" t="n">
         <v>139068</v>
@@ -3298,7 +3298,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>46.6353721618652</v>
+        <v>46.635368347168</v>
       </c>
       <c r="H101" t="n">
         <v>108486</v>
@@ -3385,7 +3385,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G104" t="n">
-        <v>47.2928161621094</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H104" t="n">
         <v>65854</v>
@@ -3414,7 +3414,7 @@
         <v>55</v>
       </c>
       <c r="G105" t="n">
-        <v>48.2132568359375</v>
+        <v>48.2132606506348</v>
       </c>
       <c r="H105" t="n">
         <v>139286</v>
@@ -3472,7 +3472,7 @@
         <v>55.5</v>
       </c>
       <c r="G107" t="n">
-        <v>48.651554107666</v>
+        <v>48.6515579223633</v>
       </c>
       <c r="H107" t="n">
         <v>133330</v>
@@ -3501,7 +3501,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>48.7392196655273</v>
+        <v>48.7392158508301</v>
       </c>
       <c r="H108" t="n">
         <v>80155</v>
@@ -3530,7 +3530,7 @@
         <v>56.25</v>
       </c>
       <c r="G109" t="n">
-        <v>49.3090057373047</v>
+        <v>49.309009552002</v>
       </c>
       <c r="H109" t="n">
         <v>116556</v>
@@ -3559,7 +3559,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>48.1694297790527</v>
+        <v>48.1694259643555</v>
       </c>
       <c r="H110" t="n">
         <v>65714</v>
@@ -3646,7 +3646,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H113" t="n">
         <v>93852</v>
@@ -3675,7 +3675,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G114" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H114" t="n">
         <v>71011</v>
@@ -3704,7 +3704,7 @@
         <v>53.25</v>
       </c>
       <c r="G115" t="n">
-        <v>46.6791915893555</v>
+        <v>46.6791954040527</v>
       </c>
       <c r="H115" t="n">
         <v>44939</v>
@@ -3733,7 +3733,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>46.8545265197754</v>
+        <v>46.8545227050781</v>
       </c>
       <c r="H116" t="n">
         <v>59443</v>
@@ -3762,7 +3762,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G117" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H117" t="n">
         <v>44774</v>
@@ -3791,7 +3791,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>45.7587623596191</v>
+        <v>45.7587661743164</v>
       </c>
       <c r="H118" t="n">
         <v>92065</v>
@@ -3994,7 +3994,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G125" t="n">
-        <v>44.1808776855469</v>
+        <v>44.1808738708496</v>
       </c>
       <c r="H125" t="n">
         <v>216125</v>
@@ -4023,7 +4023,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>45.1889762878418</v>
+        <v>45.18896484375</v>
       </c>
       <c r="H126" t="n">
         <v>159639</v>
@@ -4052,7 +4052,7 @@
         <v>54.75</v>
       </c>
       <c r="G127" t="n">
-        <v>47.9941024780273</v>
+        <v>47.9941101074219</v>
       </c>
       <c r="H127" t="n">
         <v>154132</v>
@@ -4081,7 +4081,7 @@
         <v>55</v>
       </c>
       <c r="G128" t="n">
-        <v>48.2132568359375</v>
+        <v>48.2132606506348</v>
       </c>
       <c r="H128" t="n">
         <v>131299</v>
@@ -4139,7 +4139,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>49.4843368530273</v>
+        <v>49.4843330383301</v>
       </c>
       <c r="H130" t="n">
         <v>76647</v>
@@ -4168,7 +4168,7 @@
         <v>54.75</v>
       </c>
       <c r="G131" t="n">
-        <v>47.9941024780273</v>
+        <v>47.9941101074219</v>
       </c>
       <c r="H131" t="n">
         <v>118701</v>
@@ -4197,7 +4197,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G132" t="n">
-        <v>47.2928161621094</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H132" t="n">
         <v>211604</v>
@@ -4226,7 +4226,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G133" t="n">
-        <v>47.2489929199219</v>
+        <v>47.2489852905273</v>
       </c>
       <c r="H133" t="n">
         <v>109249</v>
@@ -4255,7 +4255,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>48.0379371643066</v>
+        <v>48.0379409790039</v>
       </c>
       <c r="H134" t="n">
         <v>26738</v>
@@ -4284,7 +4284,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G135" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H135" t="n">
         <v>31502</v>
@@ -4313,7 +4313,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G136" t="n">
-        <v>48.9145393371582</v>
+        <v>48.9145431518555</v>
       </c>
       <c r="H136" t="n">
         <v>53508</v>
@@ -4400,7 +4400,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>48.125602722168</v>
+        <v>48.1255989074707</v>
       </c>
       <c r="H139" t="n">
         <v>53234</v>
@@ -4458,7 +4458,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G141" t="n">
-        <v>50.2732772827148</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H141" t="n">
         <v>46628</v>
@@ -4516,7 +4516,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0103034973145</v>
       </c>
       <c r="H143" t="n">
         <v>17674</v>
@@ -4545,7 +4545,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G144" t="n">
-        <v>49.9226379394531</v>
+        <v>49.9226303100586</v>
       </c>
       <c r="H144" t="n">
         <v>47333</v>
@@ -4574,7 +4574,7 @@
         <v>57.75</v>
       </c>
       <c r="G145" t="n">
-        <v>50.6239204406738</v>
+        <v>50.6239242553711</v>
       </c>
       <c r="H145" t="n">
         <v>55081</v>
@@ -4632,7 +4632,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G147" t="n">
-        <v>50.0541305541992</v>
+        <v>50.0541229248047</v>
       </c>
       <c r="H147" t="n">
         <v>63617</v>
@@ -4690,7 +4690,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>49.3528442382812</v>
+        <v>49.3528480529785</v>
       </c>
       <c r="H149" t="n">
         <v>68662</v>
@@ -4748,7 +4748,7 @@
         <v>55.8499984741211</v>
       </c>
       <c r="G151" t="n">
-        <v>48.9583740234375</v>
+        <v>48.9583587646484</v>
       </c>
       <c r="H151" t="n">
         <v>64253</v>
@@ -4777,7 +4777,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G152" t="n">
-        <v>49.2651786804199</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H152" t="n">
         <v>32194</v>
@@ -4806,7 +4806,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G153" t="n">
-        <v>50.6677474975586</v>
+        <v>50.6677551269531</v>
       </c>
       <c r="H153" t="n">
         <v>128897</v>
@@ -4835,7 +4835,7 @@
         <v>60</v>
       </c>
       <c r="G154" t="n">
-        <v>52.5962829589844</v>
+        <v>52.5962791442871</v>
       </c>
       <c r="H154" t="n">
         <v>118253</v>
@@ -4893,7 +4893,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G156" t="n">
-        <v>53.1660690307617</v>
+        <v>53.1660766601562</v>
       </c>
       <c r="H156" t="n">
         <v>97868</v>
@@ -4922,7 +4922,7 @@
         <v>60.8499984741211</v>
       </c>
       <c r="G157" t="n">
-        <v>53.3413963317871</v>
+        <v>53.3413925170898</v>
       </c>
       <c r="H157" t="n">
         <v>76402</v>
@@ -4980,7 +4980,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G159" t="n">
-        <v>53.1222381591797</v>
+        <v>53.122241973877</v>
       </c>
       <c r="H159" t="n">
         <v>79159</v>
@@ -5009,7 +5009,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H160" t="n">
         <v>136886</v>
@@ -5038,7 +5038,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H161" t="n">
         <v>48119</v>
@@ -5096,7 +5096,7 @@
         <v>56.75</v>
       </c>
       <c r="G163" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473182678223</v>
       </c>
       <c r="H163" t="n">
         <v>52533</v>
@@ -5125,7 +5125,7 @@
         <v>56.75</v>
       </c>
       <c r="G164" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473182678223</v>
       </c>
       <c r="H164" t="n">
         <v>117677</v>
@@ -5154,7 +5154,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G165" t="n">
-        <v>50.4485969543457</v>
+        <v>50.4486045837402</v>
       </c>
       <c r="H165" t="n">
         <v>92163</v>
@@ -5183,7 +5183,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G166" t="n">
-        <v>50.4485969543457</v>
+        <v>50.4486045837402</v>
       </c>
       <c r="H166" t="n">
         <v>57849</v>
@@ -5212,7 +5212,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>49.7034873962402</v>
+        <v>49.703483581543</v>
       </c>
       <c r="H167" t="n">
         <v>44573</v>
@@ -5241,7 +5241,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0103034973145</v>
       </c>
       <c r="H168" t="n">
         <v>23183</v>
@@ -5357,7 +5357,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>50.4924278259277</v>
+        <v>50.4924240112305</v>
       </c>
       <c r="H172" t="n">
         <v>76973</v>
@@ -5386,7 +5386,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G173" t="n">
-        <v>50.4924278259277</v>
+        <v>50.4924240112305</v>
       </c>
       <c r="H173" t="n">
         <v>41557</v>
@@ -5473,7 +5473,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>50.9307289123535</v>
+        <v>50.9307327270508</v>
       </c>
       <c r="H176" t="n">
         <v>60405</v>
@@ -5502,7 +5502,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>50.1417846679688</v>
+        <v>50.1417922973633</v>
       </c>
       <c r="H177" t="n">
         <v>42536</v>
@@ -5531,7 +5531,7 @@
         <v>56.5</v>
       </c>
       <c r="G178" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281600952148</v>
       </c>
       <c r="H178" t="n">
         <v>77478</v>
@@ -5589,7 +5589,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G180" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H180" t="n">
         <v>71976</v>
@@ -5647,7 +5647,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H182" t="n">
         <v>108065</v>
@@ -5676,7 +5676,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>49.9226379394531</v>
+        <v>49.9226303100586</v>
       </c>
       <c r="H183" t="n">
         <v>94123</v>
@@ -5705,7 +5705,7 @@
         <v>56.75</v>
       </c>
       <c r="G184" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473182678223</v>
       </c>
       <c r="H184" t="n">
         <v>55629</v>
@@ -5734,7 +5734,7 @@
         <v>57.75</v>
       </c>
       <c r="G185" t="n">
-        <v>50.6239204406738</v>
+        <v>50.6239242553711</v>
       </c>
       <c r="H185" t="n">
         <v>94987</v>
@@ -5763,7 +5763,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>51.0184020996094</v>
+        <v>51.0183982849121</v>
       </c>
       <c r="H186" t="n">
         <v>57040</v>
@@ -5821,7 +5821,7 @@
         <v>59</v>
       </c>
       <c r="G188" t="n">
-        <v>51.7196731567383</v>
+        <v>51.7196769714355</v>
       </c>
       <c r="H188" t="n">
         <v>61805</v>
@@ -5879,7 +5879,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>50.4485969543457</v>
+        <v>50.4486045837402</v>
       </c>
       <c r="H190" t="n">
         <v>45041</v>
@@ -5908,7 +5908,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>50.4924278259277</v>
+        <v>50.4924240112305</v>
       </c>
       <c r="H191" t="n">
         <v>37966</v>
@@ -5937,7 +5937,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>50.4924278259277</v>
+        <v>50.4924240112305</v>
       </c>
       <c r="H192" t="n">
         <v>35774</v>
@@ -5966,7 +5966,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G193" t="n">
-        <v>50.1417846679688</v>
+        <v>50.1417922973633</v>
       </c>
       <c r="H193" t="n">
         <v>52407</v>
@@ -6024,7 +6024,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>51.632022857666</v>
+        <v>51.6320152282715</v>
       </c>
       <c r="H195" t="n">
         <v>59969</v>
@@ -6053,7 +6053,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>51.3252029418945</v>
+        <v>51.3252067565918</v>
       </c>
       <c r="H196" t="n">
         <v>55058</v>
@@ -6082,7 +6082,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G197" t="n">
-        <v>52.2018165588379</v>
+        <v>52.2018051147461</v>
       </c>
       <c r="H197" t="n">
         <v>74545</v>
@@ -6111,7 +6111,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>51.0184020996094</v>
+        <v>51.0183982849121</v>
       </c>
       <c r="H198" t="n">
         <v>51975</v>
@@ -6140,7 +6140,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>51.3252029418945</v>
+        <v>51.3252067565918</v>
       </c>
       <c r="H199" t="n">
         <v>26888</v>
@@ -6169,7 +6169,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>51.0184020996094</v>
+        <v>51.0183982849121</v>
       </c>
       <c r="H200" t="n">
         <v>32999</v>
@@ -6198,7 +6198,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H201" t="n">
         <v>63932</v>
@@ -6227,7 +6227,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="G202" t="n">
-        <v>50.7554168701172</v>
+        <v>50.7554092407227</v>
       </c>
       <c r="H202" t="n">
         <v>47317</v>
@@ -6285,7 +6285,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>50.4485969543457</v>
+        <v>50.4486045837402</v>
       </c>
       <c r="H204" t="n">
         <v>44376</v>
@@ -6343,7 +6343,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>50.2294464111328</v>
+        <v>50.2294425964355</v>
       </c>
       <c r="H206" t="n">
         <v>41484</v>
@@ -6372,7 +6372,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>50.2294464111328</v>
+        <v>50.2294425964355</v>
       </c>
       <c r="H207" t="n">
         <v>51815</v>
@@ -6401,7 +6401,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H208" t="n">
         <v>37855</v>
@@ -6430,7 +6430,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G209" t="n">
-        <v>49.2213554382324</v>
+        <v>49.2213516235352</v>
       </c>
       <c r="H209" t="n">
         <v>55693</v>
@@ -6488,7 +6488,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G211" t="n">
-        <v>48.7392196655273</v>
+        <v>48.7392158508301</v>
       </c>
       <c r="H211" t="n">
         <v>60350</v>
@@ -6517,7 +6517,7 @@
         <v>56.25</v>
       </c>
       <c r="G212" t="n">
-        <v>49.3090057373047</v>
+        <v>49.309009552002</v>
       </c>
       <c r="H212" t="n">
         <v>100530</v>
@@ -6604,7 +6604,7 @@
         <v>54.5499992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>47.8187828063965</v>
+        <v>47.8187866210938</v>
       </c>
       <c r="H215" t="n">
         <v>68484</v>
@@ -6662,7 +6662,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>47.2928161621094</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H217" t="n">
         <v>91776</v>
@@ -6691,7 +6691,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>46.7668609619141</v>
+        <v>46.7668571472168</v>
       </c>
       <c r="H218" t="n">
         <v>69051</v>
@@ -6749,7 +6749,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>46.5477066040039</v>
+        <v>46.5477027893066</v>
       </c>
       <c r="H220" t="n">
         <v>96961</v>
@@ -6807,7 +6807,7 @@
         <v>50.75</v>
       </c>
       <c r="G222" t="n">
-        <v>44.4876937866211</v>
+        <v>44.4876861572266</v>
       </c>
       <c r="H222" t="n">
         <v>236609</v>
@@ -6865,7 +6865,7 @@
         <v>51</v>
       </c>
       <c r="G224" t="n">
-        <v>44.7068405151367</v>
+        <v>44.7068367004395</v>
       </c>
       <c r="H224" t="n">
         <v>144844</v>
@@ -6894,7 +6894,7 @@
         <v>51</v>
       </c>
       <c r="G225" t="n">
-        <v>44.7068405151367</v>
+        <v>44.7068367004395</v>
       </c>
       <c r="H225" t="n">
         <v>74954</v>
@@ -6923,7 +6923,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>45.5396156311035</v>
+        <v>45.5396118164062</v>
       </c>
       <c r="H226" t="n">
         <v>159762</v>
@@ -6952,7 +6952,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>45.7587623596191</v>
+        <v>45.7587661743164</v>
       </c>
       <c r="H227" t="n">
         <v>99562</v>
@@ -7010,7 +7010,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>45.4081192016602</v>
+        <v>45.4081153869629</v>
       </c>
       <c r="H229" t="n">
         <v>76726</v>
@@ -7068,7 +7068,7 @@
         <v>51.25</v>
       </c>
       <c r="G231" t="n">
-        <v>44.9259872436523</v>
+        <v>44.9259948730469</v>
       </c>
       <c r="H231" t="n">
         <v>72155</v>
@@ -7097,7 +7097,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>45.2766304016113</v>
+        <v>45.2766342163086</v>
       </c>
       <c r="H232" t="n">
         <v>43249</v>
@@ -7126,7 +7126,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>45.7149391174316</v>
+        <v>45.7149314880371</v>
       </c>
       <c r="H233" t="n">
         <v>26119</v>
@@ -7155,7 +7155,7 @@
         <v>52</v>
       </c>
       <c r="G234" t="n">
-        <v>45.5834426879883</v>
+        <v>45.5834465026855</v>
       </c>
       <c r="H234" t="n">
         <v>65255</v>
@@ -7213,7 +7213,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>44.6191787719727</v>
+        <v>44.6191825866699</v>
       </c>
       <c r="H236" t="n">
         <v>77799</v>
@@ -7242,7 +7242,7 @@
         <v>51.25</v>
       </c>
       <c r="G237" t="n">
-        <v>44.9259872436523</v>
+        <v>44.9259948730469</v>
       </c>
       <c r="H237" t="n">
         <v>109858</v>
@@ -7300,7 +7300,7 @@
         <v>51.25</v>
       </c>
       <c r="G239" t="n">
-        <v>44.9259872436523</v>
+        <v>44.9259948730469</v>
       </c>
       <c r="H239" t="n">
         <v>58604</v>
@@ -7329,7 +7329,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>45.7587623596191</v>
+        <v>45.7587661743164</v>
       </c>
       <c r="H240" t="n">
         <v>63619</v>
@@ -7358,7 +7358,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>45.6711006164551</v>
+        <v>45.6710968017578</v>
       </c>
       <c r="H241" t="n">
         <v>108454</v>
@@ -7387,7 +7387,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>45.6711006164551</v>
+        <v>45.6710968017578</v>
       </c>
       <c r="H242" t="n">
         <v>106069</v>
@@ -7416,7 +7416,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>45.7149391174316</v>
+        <v>45.7149314880371</v>
       </c>
       <c r="H243" t="n">
         <v>96572</v>
@@ -7474,7 +7474,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>45.4081192016602</v>
+        <v>45.4081153869629</v>
       </c>
       <c r="H245" t="n">
         <v>73074</v>
@@ -7503,7 +7503,7 @@
         <v>51.8499984741211</v>
       </c>
       <c r="G246" t="n">
-        <v>45.4519538879395</v>
+        <v>45.4519500732422</v>
       </c>
       <c r="H246" t="n">
         <v>76582</v>
@@ -7561,7 +7561,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>46.5915374755859</v>
+        <v>46.5915489196777</v>
       </c>
       <c r="H248" t="n">
         <v>101275</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281600952148</v>
       </c>
       <c r="H251" t="n">
         <v>175588</v>
@@ -7735,7 +7735,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G254" t="n">
-        <v>49.4405097961426</v>
+        <v>49.440502166748</v>
       </c>
       <c r="H254" t="n">
         <v>21800</v>
@@ -7764,7 +7764,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>49.2651786804199</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H255" t="n">
         <v>41254</v>
@@ -7793,7 +7793,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>49.3528442382812</v>
+        <v>49.3528480529785</v>
       </c>
       <c r="H256" t="n">
         <v>18333</v>
@@ -7822,7 +7822,7 @@
         <v>56.25</v>
       </c>
       <c r="G257" t="n">
-        <v>49.3090057373047</v>
+        <v>49.309009552002</v>
       </c>
       <c r="H257" t="n">
         <v>13680</v>
@@ -7851,7 +7851,7 @@
         <v>57.75</v>
       </c>
       <c r="G258" t="n">
-        <v>50.6239204406738</v>
+        <v>50.6239242553711</v>
       </c>
       <c r="H258" t="n">
         <v>52631</v>
@@ -7909,7 +7909,7 @@
         <v>57.75</v>
       </c>
       <c r="G260" t="n">
-        <v>50.6239204406738</v>
+        <v>50.6239242553711</v>
       </c>
       <c r="H260" t="n">
         <v>43287</v>
@@ -7967,7 +7967,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G262" t="n">
-        <v>51.1937141418457</v>
+        <v>51.1937103271484</v>
       </c>
       <c r="H262" t="n">
         <v>44010</v>
@@ -7996,7 +7996,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G263" t="n">
-        <v>50.2732772827148</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H263" t="n">
         <v>39353</v>
@@ -8025,7 +8025,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G264" t="n">
-        <v>50.0541305541992</v>
+        <v>50.0541229248047</v>
       </c>
       <c r="H264" t="n">
         <v>61270</v>
@@ -8083,7 +8083,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G266" t="n">
-        <v>50.2732772827148</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H266" t="n">
         <v>55893</v>
@@ -8141,7 +8141,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H268" t="n">
         <v>46171</v>
@@ -8228,7 +8228,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H271" t="n">
         <v>35621</v>
@@ -8286,7 +8286,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>49.3528442382812</v>
+        <v>49.3528480529785</v>
       </c>
       <c r="H273" t="n">
         <v>54452</v>
@@ -8315,7 +8315,7 @@
         <v>55</v>
       </c>
       <c r="G274" t="n">
-        <v>48.2132568359375</v>
+        <v>48.2132606506348</v>
       </c>
       <c r="H274" t="n">
         <v>183138</v>
@@ -8373,7 +8373,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>47.9502716064453</v>
+        <v>47.9502792358398</v>
       </c>
       <c r="H276" t="n">
         <v>115124</v>
@@ -8431,7 +8431,7 @@
         <v>55.5</v>
       </c>
       <c r="G278" t="n">
-        <v>48.651554107666</v>
+        <v>48.6515579223633</v>
       </c>
       <c r="H278" t="n">
         <v>67978</v>
@@ -8518,7 +8518,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>51.1937141418457</v>
+        <v>51.1937103271484</v>
       </c>
       <c r="H281" t="n">
         <v>176623</v>
@@ -8605,7 +8605,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G284" t="n">
-        <v>49.2651786804199</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H284" t="n">
         <v>60368</v>
@@ -8692,7 +8692,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G287" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0103034973145</v>
       </c>
       <c r="H287" t="n">
         <v>68947</v>
@@ -8721,7 +8721,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0103034973145</v>
       </c>
       <c r="H288" t="n">
         <v>33003</v>
@@ -8750,7 +8750,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>50.6677474975586</v>
+        <v>50.6677551269531</v>
       </c>
       <c r="H289" t="n">
         <v>47641</v>
@@ -8837,7 +8837,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G292" t="n">
-        <v>49.8788108825684</v>
+        <v>49.8788070678711</v>
       </c>
       <c r="H292" t="n">
         <v>84201</v>
@@ -8924,7 +8924,7 @@
         <v>59</v>
       </c>
       <c r="G295" t="n">
-        <v>51.7196731567383</v>
+        <v>51.7196769714355</v>
       </c>
       <c r="H295" t="n">
         <v>116359</v>
@@ -8953,7 +8953,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>51.1060485839844</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H296" t="n">
         <v>80368</v>
@@ -8982,7 +8982,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>51.2375450134277</v>
+        <v>51.2375411987305</v>
       </c>
       <c r="H297" t="n">
         <v>126567</v>
@@ -9011,7 +9011,7 @@
         <v>58.75</v>
       </c>
       <c r="G298" t="n">
-        <v>51.5005226135254</v>
+        <v>51.5005187988281</v>
       </c>
       <c r="H298" t="n">
         <v>75849</v>
@@ -9040,7 +9040,7 @@
         <v>59.75</v>
       </c>
       <c r="G299" t="n">
-        <v>52.3771286010742</v>
+        <v>52.3771324157715</v>
       </c>
       <c r="H299" t="n">
         <v>83441</v>
@@ -9069,7 +9069,7 @@
         <v>60</v>
       </c>
       <c r="G300" t="n">
-        <v>52.5962829589844</v>
+        <v>52.5962791442871</v>
       </c>
       <c r="H300" t="n">
         <v>115569</v>
@@ -9098,7 +9098,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>52.420955657959</v>
+        <v>52.4209594726562</v>
       </c>
       <c r="H301" t="n">
         <v>69522</v>
@@ -9127,7 +9127,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>52.420955657959</v>
+        <v>52.4209594726562</v>
       </c>
       <c r="H302" t="n">
         <v>60828</v>
@@ -9156,7 +9156,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>52.464786529541</v>
+        <v>52.4647827148438</v>
       </c>
       <c r="H303" t="n">
         <v>87140</v>
@@ -9243,7 +9243,7 @@
         <v>59.25</v>
       </c>
       <c r="G306" t="n">
-        <v>51.9388275146484</v>
+        <v>51.938835144043</v>
       </c>
       <c r="H306" t="n">
         <v>85958</v>
@@ -9330,7 +9330,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>52.464786529541</v>
+        <v>52.4647827148438</v>
       </c>
       <c r="H309" t="n">
         <v>105806</v>
@@ -9359,7 +9359,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G310" t="n">
-        <v>52.8592681884766</v>
+        <v>52.8592643737793</v>
       </c>
       <c r="H310" t="n">
         <v>99450</v>
@@ -9388,7 +9388,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>53.7796936035156</v>
+        <v>53.7796974182129</v>
       </c>
       <c r="H311" t="n">
         <v>99357</v>
@@ -9417,7 +9417,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>53.7796936035156</v>
+        <v>53.7796974182129</v>
       </c>
       <c r="H312" t="n">
         <v>90388</v>
@@ -9446,7 +9446,7 @@
         <v>62.25</v>
       </c>
       <c r="G313" t="n">
-        <v>54.5686378479004</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H313" t="n">
         <v>168323</v>
@@ -9475,7 +9475,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>54.3056602478027</v>
+        <v>54.3056640625</v>
       </c>
       <c r="H314" t="n">
         <v>112926</v>
@@ -9504,7 +9504,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>54.4809761047363</v>
+        <v>54.4809837341309</v>
       </c>
       <c r="H315" t="n">
         <v>94164</v>
@@ -9562,7 +9562,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>55.094596862793</v>
+        <v>55.0946006774902</v>
       </c>
       <c r="H317" t="n">
         <v>93970</v>
@@ -9620,7 +9620,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G319" t="n">
-        <v>55.094596862793</v>
+        <v>55.0946006774902</v>
       </c>
       <c r="H319" t="n">
         <v>86476</v>
@@ -9649,7 +9649,7 @@
         <v>62.25</v>
       </c>
       <c r="G320" t="n">
-        <v>54.5686378479004</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H320" t="n">
         <v>73391</v>
@@ -9707,7 +9707,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>55.4890747070312</v>
+        <v>55.4890823364258</v>
       </c>
       <c r="H322" t="n">
         <v>87596</v>
@@ -9736,7 +9736,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>55.9273834228516</v>
+        <v>55.9273796081543</v>
       </c>
       <c r="H323" t="n">
         <v>63561</v>
@@ -9765,7 +9765,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>56.0150413513184</v>
+        <v>56.0150337219238</v>
       </c>
       <c r="H324" t="n">
         <v>56528</v>
@@ -9794,7 +9794,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G325" t="n">
-        <v>56.3656768798828</v>
+        <v>56.3656806945801</v>
       </c>
       <c r="H325" t="n">
         <v>54692</v>
@@ -9823,7 +9823,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>56.2780113220215</v>
+        <v>56.2780151367188</v>
       </c>
       <c r="H326" t="n">
         <v>93016</v>
@@ -9852,7 +9852,7 @@
         <v>65</v>
       </c>
       <c r="G327" t="n">
-        <v>56.979305267334</v>
+        <v>56.9793014526367</v>
       </c>
       <c r="H327" t="n">
         <v>61355</v>
@@ -9881,7 +9881,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G328" t="n">
-        <v>57.812068939209</v>
+        <v>57.8120727539062</v>
       </c>
       <c r="H328" t="n">
         <v>105326</v>
@@ -9910,7 +9910,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G329" t="n">
-        <v>57.9435653686523</v>
+        <v>57.9435691833496</v>
       </c>
       <c r="H329" t="n">
         <v>88839</v>
@@ -9939,7 +9939,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G330" t="n">
-        <v>57.680591583252</v>
+        <v>57.6805877685547</v>
       </c>
       <c r="H330" t="n">
         <v>61993</v>
@@ -9968,7 +9968,7 @@
         <v>65.0500030517578</v>
       </c>
       <c r="G331" t="n">
-        <v>57.023136138916</v>
+        <v>57.0231399536133</v>
       </c>
       <c r="H331" t="n">
         <v>95522</v>
@@ -9997,7 +9997,7 @@
         <v>64</v>
       </c>
       <c r="G332" t="n">
-        <v>56.1027030944824</v>
+        <v>56.1026992797852</v>
       </c>
       <c r="H332" t="n">
         <v>205806</v>
@@ -10026,7 +10026,7 @@
         <v>64.25</v>
       </c>
       <c r="G333" t="n">
-        <v>56.3218460083008</v>
+        <v>56.321849822998</v>
       </c>
       <c r="H333" t="n">
         <v>67592</v>
@@ -10055,7 +10055,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G334" t="n">
-        <v>57.9435653686523</v>
+        <v>57.9435691833496</v>
       </c>
       <c r="H334" t="n">
         <v>121496</v>
@@ -10084,7 +10084,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G335" t="n">
-        <v>57.5052719116211</v>
+        <v>57.5052680969238</v>
       </c>
       <c r="H335" t="n">
         <v>103682</v>
@@ -10113,7 +10113,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G336" t="n">
-        <v>58.907829284668</v>
+        <v>58.9078254699707</v>
       </c>
       <c r="H336" t="n">
         <v>121938</v>
@@ -10171,7 +10171,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G338" t="n">
-        <v>58.2065467834473</v>
+        <v>58.2065505981445</v>
       </c>
       <c r="H338" t="n">
         <v>84175</v>
@@ -10229,7 +10229,7 @@
         <v>68.8000030517578</v>
       </c>
       <c r="G340" t="n">
-        <v>60.3104095458984</v>
+        <v>60.3104019165039</v>
       </c>
       <c r="H340" t="n">
         <v>93918</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="G341" t="n">
-        <v>62.2389259338379</v>
+        <v>62.2389335632324</v>
       </c>
       <c r="H341" t="n">
         <v>130581</v>
@@ -10287,7 +10287,7 @@
         <v>69.5999984741211</v>
       </c>
       <c r="G342" t="n">
-        <v>61.0116920471191</v>
+        <v>61.0116882324219</v>
       </c>
       <c r="H342" t="n">
         <v>146465</v>
@@ -10316,7 +10316,7 @@
         <v>69</v>
       </c>
       <c r="G343" t="n">
-        <v>60.485725402832</v>
+        <v>60.4857330322266</v>
       </c>
       <c r="H343" t="n">
         <v>124118</v>
@@ -10345,7 +10345,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G344" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487144470215</v>
       </c>
       <c r="H344" t="n">
         <v>113418</v>
@@ -10374,7 +10374,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G345" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487144470215</v>
       </c>
       <c r="H345" t="n">
         <v>142132</v>
@@ -10403,7 +10403,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G346" t="n">
-        <v>61.6691474914551</v>
+        <v>61.6691360473633</v>
       </c>
       <c r="H346" t="n">
         <v>203289</v>
@@ -10461,7 +10461,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>61.230842590332</v>
+        <v>61.2308387756348</v>
       </c>
       <c r="H348" t="n">
         <v>156756</v>
@@ -10490,7 +10490,7 @@
         <v>70.25</v>
       </c>
       <c r="G349" t="n">
-        <v>61.5814819335938</v>
+        <v>61.5814895629883</v>
       </c>
       <c r="H349" t="n">
         <v>91255</v>
@@ -10519,7 +10519,7 @@
         <v>70</v>
       </c>
       <c r="G350" t="n">
-        <v>61.3623237609863</v>
+        <v>61.3623275756836</v>
       </c>
       <c r="H350" t="n">
         <v>67704</v>
@@ -10548,7 +10548,7 @@
         <v>70</v>
       </c>
       <c r="G351" t="n">
-        <v>61.3623237609863</v>
+        <v>61.3623275756836</v>
       </c>
       <c r="H351" t="n">
         <v>93071</v>
@@ -10577,7 +10577,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>59.740608215332</v>
+        <v>59.7406158447266</v>
       </c>
       <c r="H352" t="n">
         <v>78818</v>
@@ -10606,7 +10606,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>59.0831642150879</v>
+        <v>59.0831604003906</v>
       </c>
       <c r="H353" t="n">
         <v>90559</v>
@@ -10635,7 +10635,7 @@
         <v>68.25</v>
       </c>
       <c r="G354" t="n">
-        <v>59.8282661437988</v>
+        <v>59.8282623291016</v>
       </c>
       <c r="H354" t="n">
         <v>78001</v>
@@ -10664,7 +10664,7 @@
         <v>68.25</v>
       </c>
       <c r="G355" t="n">
-        <v>60.5378761291504</v>
+        <v>60.5378684997559</v>
       </c>
       <c r="H355" t="n">
         <v>58161</v>
@@ -10693,7 +10693,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G356" t="n">
-        <v>60.8039665222168</v>
+        <v>60.8039741516113</v>
       </c>
       <c r="H356" t="n">
         <v>86355</v>
@@ -10780,7 +10780,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G359" t="n">
-        <v>61.3805160522461</v>
+        <v>61.3805236816406</v>
       </c>
       <c r="H359" t="n">
         <v>69316</v>
@@ -10809,7 +10809,7 @@
         <v>68.0500030517578</v>
       </c>
       <c r="G360" t="n">
-        <v>60.3604736328125</v>
+        <v>60.3604774475098</v>
       </c>
       <c r="H360" t="n">
         <v>44961</v>
@@ -10896,7 +10896,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G363" t="n">
-        <v>62.2675285339355</v>
+        <v>62.267520904541</v>
       </c>
       <c r="H363" t="n">
         <v>76993</v>
@@ -10925,7 +10925,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G364" t="n">
-        <v>62.5779762268066</v>
+        <v>62.5779914855957</v>
       </c>
       <c r="H364" t="n">
         <v>48079</v>
@@ -10954,7 +10954,7 @@
         <v>70.25</v>
       </c>
       <c r="G365" t="n">
-        <v>62.3118743896484</v>
+        <v>62.3118782043457</v>
       </c>
       <c r="H365" t="n">
         <v>50482</v>
@@ -10983,7 +10983,7 @@
         <v>71.4499969482422</v>
       </c>
       <c r="G366" t="n">
-        <v>63.3762741088867</v>
+        <v>63.3762702941895</v>
       </c>
       <c r="H366" t="n">
         <v>85002</v>
@@ -11012,7 +11012,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>62.8884315490723</v>
+        <v>62.8884239196777</v>
       </c>
       <c r="H367" t="n">
         <v>88768</v>
@@ -11041,7 +11041,7 @@
         <v>71.75</v>
       </c>
       <c r="G368" t="n">
-        <v>63.6423835754395</v>
+        <v>63.6423683166504</v>
       </c>
       <c r="H368" t="n">
         <v>78174</v>
@@ -11099,7 +11099,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>62.0014305114746</v>
+        <v>62.0014190673828</v>
       </c>
       <c r="H370" t="n">
         <v>126134</v>
@@ -11128,7 +11128,7 @@
         <v>69.75</v>
       </c>
       <c r="G371" t="n">
-        <v>61.8683624267578</v>
+        <v>61.8683738708496</v>
       </c>
       <c r="H371" t="n">
         <v>83211</v>
@@ -11157,7 +11157,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G372" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319244384766</v>
       </c>
       <c r="H372" t="n">
         <v>68728</v>
@@ -11186,7 +11186,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G373" t="n">
-        <v>62.711009979248</v>
+        <v>62.7110252380371</v>
       </c>
       <c r="H373" t="n">
         <v>62075</v>
@@ -11215,7 +11215,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G374" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432327270508</v>
       </c>
       <c r="H374" t="n">
         <v>80009</v>
@@ -11244,7 +11244,7 @@
         <v>71.1500015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>63.1101722717285</v>
+        <v>63.1101837158203</v>
       </c>
       <c r="H375" t="n">
         <v>41602</v>
@@ -11273,7 +11273,7 @@
         <v>71</v>
       </c>
       <c r="G376" t="n">
-        <v>62.9771308898926</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H376" t="n">
         <v>55189</v>
@@ -11302,7 +11302,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G377" t="n">
-        <v>62.5779762268066</v>
+        <v>62.5779914855957</v>
       </c>
       <c r="H377" t="n">
         <v>47892</v>
@@ -11331,7 +11331,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G378" t="n">
-        <v>62.2675285339355</v>
+        <v>62.267520904541</v>
       </c>
       <c r="H378" t="n">
         <v>44527</v>
@@ -11360,7 +11360,7 @@
         <v>72.6999969482422</v>
       </c>
       <c r="G379" t="n">
-        <v>64.4850234985352</v>
+        <v>64.4850158691406</v>
       </c>
       <c r="H379" t="n">
         <v>193672</v>
@@ -11389,7 +11389,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G380" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432327270508</v>
       </c>
       <c r="H380" t="n">
         <v>131749</v>
@@ -11418,7 +11418,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>62.0014305114746</v>
+        <v>62.0014190673828</v>
       </c>
       <c r="H381" t="n">
         <v>151026</v>
@@ -11447,7 +11447,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G382" t="n">
-        <v>59.9613189697266</v>
+        <v>59.9613227844238</v>
       </c>
       <c r="H382" t="n">
         <v>148751</v>
@@ -11476,7 +11476,7 @@
         <v>66</v>
       </c>
       <c r="G383" t="n">
-        <v>58.5421104431152</v>
+        <v>58.5421142578125</v>
       </c>
       <c r="H383" t="n">
         <v>152369</v>
@@ -11505,7 +11505,7 @@
         <v>67.25</v>
       </c>
       <c r="G384" t="n">
-        <v>59.6508674621582</v>
+        <v>59.6508712768555</v>
       </c>
       <c r="H384" t="n">
         <v>94522</v>
@@ -11534,7 +11534,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G385" t="n">
-        <v>59.0743103027344</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H385" t="n">
         <v>79441</v>
@@ -11563,7 +11563,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G386" t="n">
-        <v>59.0743103027344</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H386" t="n">
         <v>35043</v>
@@ -11592,7 +11592,7 @@
         <v>67.25</v>
       </c>
       <c r="G387" t="n">
-        <v>59.6508674621582</v>
+        <v>59.6508712768555</v>
       </c>
       <c r="H387" t="n">
         <v>75320</v>
@@ -11621,7 +11621,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G388" t="n">
-        <v>59.0743103027344</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H388" t="n">
         <v>68536</v>
@@ -11650,7 +11650,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G389" t="n">
-        <v>59.6952209472656</v>
+        <v>59.6952247619629</v>
       </c>
       <c r="H389" t="n">
         <v>31158</v>
@@ -11679,7 +11679,7 @@
         <v>67</v>
       </c>
       <c r="G390" t="n">
-        <v>59.429126739502</v>
+        <v>59.4291152954102</v>
       </c>
       <c r="H390" t="n">
         <v>83527</v>
@@ -11708,7 +11708,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>58.5864677429199</v>
+        <v>58.5864715576172</v>
       </c>
       <c r="H391" t="n">
         <v>60337</v>
@@ -11737,7 +11737,7 @@
         <v>67</v>
       </c>
       <c r="G392" t="n">
-        <v>59.429126739502</v>
+        <v>59.4291152954102</v>
       </c>
       <c r="H392" t="n">
         <v>65587</v>
@@ -11824,7 +11824,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G395" t="n">
-        <v>61.2474784851074</v>
+        <v>61.2474746704102</v>
       </c>
       <c r="H395" t="n">
         <v>74590</v>
@@ -11853,7 +11853,7 @@
         <v>69.75</v>
       </c>
       <c r="G396" t="n">
-        <v>61.8683624267578</v>
+        <v>61.8683738708496</v>
       </c>
       <c r="H396" t="n">
         <v>106303</v>
@@ -11882,7 +11882,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G397" t="n">
-        <v>62.0457611083984</v>
+        <v>62.045768737793</v>
       </c>
       <c r="H397" t="n">
         <v>56355</v>
@@ -11911,7 +11911,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>62.4005813598633</v>
+        <v>62.4005699157715</v>
       </c>
       <c r="H398" t="n">
         <v>82183</v>
@@ -11940,7 +11940,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G399" t="n">
-        <v>62.2231750488281</v>
+        <v>62.2231712341309</v>
       </c>
       <c r="H399" t="n">
         <v>53923</v>
@@ -11969,7 +11969,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G400" t="n">
-        <v>62.5779762268066</v>
+        <v>62.5779914855957</v>
       </c>
       <c r="H400" t="n">
         <v>57929</v>
@@ -11998,7 +11998,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>61.9570732116699</v>
+        <v>61.9570770263672</v>
       </c>
       <c r="H401" t="n">
         <v>84754</v>
@@ -12172,7 +12172,7 @@
         <v>73</v>
       </c>
       <c r="G407" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511291503906</v>
       </c>
       <c r="H407" t="n">
         <v>66371</v>
@@ -12259,7 +12259,7 @@
         <v>72.5999984741211</v>
       </c>
       <c r="G410" t="n">
-        <v>64.3963470458984</v>
+        <v>64.3963394165039</v>
       </c>
       <c r="H410" t="n">
         <v>118089</v>
@@ -12288,7 +12288,7 @@
         <v>71.9499969482422</v>
       </c>
       <c r="G411" t="n">
-        <v>63.8197784423828</v>
+        <v>63.8197822570801</v>
       </c>
       <c r="H411" t="n">
         <v>175766</v>
@@ -12317,7 +12317,7 @@
         <v>72.1500015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>63.9971771240234</v>
+        <v>63.9971809387207</v>
       </c>
       <c r="H412" t="n">
         <v>138872</v>
@@ -12346,7 +12346,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G413" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319244384766</v>
       </c>
       <c r="H413" t="n">
         <v>52658</v>
@@ -12375,7 +12375,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G414" t="n">
-        <v>62.711009979248</v>
+        <v>62.7110252380371</v>
       </c>
       <c r="H414" t="n">
         <v>53923</v>
@@ -12404,7 +12404,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>63.5536804199219</v>
+        <v>63.5536842346191</v>
       </c>
       <c r="H415" t="n">
         <v>58212</v>
@@ -12433,7 +12433,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319244384766</v>
       </c>
       <c r="H416" t="n">
         <v>73224</v>
@@ -12462,7 +12462,7 @@
         <v>71.6999969482422</v>
       </c>
       <c r="G417" t="n">
-        <v>63.5980186462402</v>
+        <v>63.5980262756348</v>
       </c>
       <c r="H417" t="n">
         <v>60605</v>
@@ -12491,7 +12491,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>63.4649848937988</v>
+        <v>63.464973449707</v>
       </c>
       <c r="H418" t="n">
         <v>57244</v>
@@ -12520,7 +12520,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875823974609</v>
       </c>
       <c r="H419" t="n">
         <v>32790</v>
@@ -12549,7 +12549,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>63.3319320678711</v>
+        <v>63.3319244384766</v>
       </c>
       <c r="H420" t="n">
         <v>52903</v>
@@ -12578,7 +12578,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G421" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875823974609</v>
       </c>
       <c r="H421" t="n">
         <v>54279</v>
@@ -12607,7 +12607,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G422" t="n">
-        <v>62.7997283935547</v>
+        <v>62.7997360229492</v>
       </c>
       <c r="H422" t="n">
         <v>37097</v>
@@ -12636,7 +12636,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G423" t="n">
-        <v>62.5779762268066</v>
+        <v>62.5779914855957</v>
       </c>
       <c r="H423" t="n">
         <v>42983</v>
@@ -12665,7 +12665,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>62.1344757080078</v>
+        <v>62.1344718933105</v>
       </c>
       <c r="H424" t="n">
         <v>69545</v>
@@ -12694,7 +12694,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G425" t="n">
-        <v>62.0457611083984</v>
+        <v>62.045768737793</v>
       </c>
       <c r="H425" t="n">
         <v>96037</v>
@@ -12723,7 +12723,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875823974609</v>
       </c>
       <c r="H426" t="n">
         <v>67312</v>
@@ -12752,7 +12752,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>64.2189331054688</v>
+        <v>64.2189254760742</v>
       </c>
       <c r="H427" t="n">
         <v>125587</v>
@@ -12839,7 +12839,7 @@
         <v>73</v>
       </c>
       <c r="G430" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511291503906</v>
       </c>
       <c r="H430" t="n">
         <v>68493</v>
@@ -12868,7 +12868,7 @@
         <v>73.3499984741211</v>
       </c>
       <c r="G431" t="n">
-        <v>65.0615844726562</v>
+        <v>65.0615692138672</v>
       </c>
       <c r="H431" t="n">
         <v>79399</v>
@@ -12897,7 +12897,7 @@
         <v>73.6999969482422</v>
       </c>
       <c r="G432" t="n">
-        <v>65.3720321655273</v>
+        <v>65.3720397949219</v>
       </c>
       <c r="H432" t="n">
         <v>96313</v>
@@ -12926,7 +12926,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G433" t="n">
-        <v>65.2389907836914</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H433" t="n">
         <v>52881</v>
@@ -12984,7 +12984,7 @@
         <v>73</v>
       </c>
       <c r="G435" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511291503906</v>
       </c>
       <c r="H435" t="n">
         <v>68517</v>
@@ -13071,7 +13071,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>64.8398361206055</v>
+        <v>64.8398284912109</v>
       </c>
       <c r="H438" t="n">
         <v>73428</v>
@@ -13100,7 +13100,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G439" t="n">
-        <v>65.1502685546875</v>
+        <v>65.150276184082</v>
       </c>
       <c r="H439" t="n">
         <v>48041</v>
@@ -13158,7 +13158,7 @@
         <v>74.25</v>
       </c>
       <c r="G441" t="n">
-        <v>65.8598861694336</v>
+        <v>65.8598785400391</v>
       </c>
       <c r="H441" t="n">
         <v>71180</v>
@@ -13216,7 +13216,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G443" t="n">
-        <v>66.1703262329102</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H443" t="n">
         <v>32023</v>
@@ -13245,7 +13245,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>67.2790985107422</v>
+        <v>67.2790908813477</v>
       </c>
       <c r="H444" t="n">
         <v>98607</v>
@@ -13274,7 +13274,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G445" t="n">
-        <v>66.8799362182617</v>
+        <v>66.8799438476562</v>
       </c>
       <c r="H445" t="n">
         <v>59301</v>
@@ -13303,7 +13303,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G446" t="n">
-        <v>66.6138229370117</v>
+        <v>66.6138381958008</v>
       </c>
       <c r="H446" t="n">
         <v>162554</v>
@@ -13332,7 +13332,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G447" t="n">
-        <v>66.7025299072266</v>
+        <v>66.702522277832</v>
       </c>
       <c r="H447" t="n">
         <v>296297</v>
@@ -13477,7 +13477,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>70.6496810913086</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H452" t="n">
         <v>107042</v>
@@ -13506,7 +13506,7 @@
         <v>79</v>
       </c>
       <c r="G453" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H453" t="n">
         <v>44675</v>
@@ -13535,7 +13535,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G454" t="n">
-        <v>70.2061920166016</v>
+        <v>70.206184387207</v>
       </c>
       <c r="H454" t="n">
         <v>46715</v>
@@ -13564,7 +13564,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G455" t="n">
-        <v>69.5409393310547</v>
+        <v>69.5409469604492</v>
       </c>
       <c r="H455" t="n">
         <v>59456</v>
@@ -13593,7 +13593,7 @@
         <v>78.75</v>
       </c>
       <c r="G456" t="n">
-        <v>69.8513793945312</v>
+        <v>69.8513870239258</v>
       </c>
       <c r="H456" t="n">
         <v>105461</v>
@@ -13622,7 +13622,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G457" t="n">
-        <v>71.4479904174805</v>
+        <v>71.4479827880859</v>
       </c>
       <c r="H457" t="n">
         <v>165700</v>
@@ -13651,7 +13651,7 @@
         <v>78.75</v>
       </c>
       <c r="G458" t="n">
-        <v>69.8513793945312</v>
+        <v>69.8513870239258</v>
       </c>
       <c r="H458" t="n">
         <v>206055</v>
@@ -13680,7 +13680,7 @@
         <v>79</v>
       </c>
       <c r="G459" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H459" t="n">
         <v>72167</v>
@@ -13709,7 +13709,7 @@
         <v>79</v>
       </c>
       <c r="G460" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H460" t="n">
         <v>72203</v>
@@ -13738,7 +13738,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G461" t="n">
-        <v>69.5852966308594</v>
+        <v>69.5852813720703</v>
       </c>
       <c r="H461" t="n">
         <v>88886</v>
@@ -13912,7 +13912,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G467" t="n">
-        <v>69.4522399902344</v>
+        <v>69.4522476196289</v>
       </c>
       <c r="H467" t="n">
         <v>99295</v>
@@ -13941,7 +13941,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>69.4965744018555</v>
+        <v>69.49658203125</v>
       </c>
       <c r="H468" t="n">
         <v>105046</v>
@@ -13970,7 +13970,7 @@
         <v>78</v>
       </c>
       <c r="G469" t="n">
-        <v>69.1861419677734</v>
+        <v>69.1861267089844</v>
       </c>
       <c r="H469" t="n">
         <v>75889</v>
@@ -14028,7 +14028,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G471" t="n">
-        <v>70.0287857055664</v>
+        <v>70.0287780761719</v>
       </c>
       <c r="H471" t="n">
         <v>89387</v>
@@ -14057,7 +14057,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G472" t="n">
-        <v>69.1417846679688</v>
+        <v>69.1417999267578</v>
       </c>
       <c r="H472" t="n">
         <v>67354</v>
@@ -14086,7 +14086,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G473" t="n">
-        <v>70.2505493164062</v>
+        <v>70.2505416870117</v>
       </c>
       <c r="H473" t="n">
         <v>98034</v>
@@ -14144,7 +14144,7 @@
         <v>78.25</v>
       </c>
       <c r="G475" t="n">
-        <v>69.4078826904297</v>
+        <v>69.4078903198242</v>
       </c>
       <c r="H475" t="n">
         <v>56037</v>
@@ -14202,7 +14202,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G477" t="n">
-        <v>63.9084892272949</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H477" t="n">
         <v>325556</v>
@@ -14289,7 +14289,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>66.2146987915039</v>
+        <v>66.2146759033203</v>
       </c>
       <c r="H480" t="n">
         <v>137194</v>
@@ -14347,7 +14347,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G482" t="n">
-        <v>66.8799362182617</v>
+        <v>66.8799438476562</v>
       </c>
       <c r="H482" t="n">
         <v>37603</v>
@@ -14376,7 +14376,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G483" t="n">
-        <v>66.5694732666016</v>
+        <v>66.5694961547852</v>
       </c>
       <c r="H483" t="n">
         <v>31199</v>
@@ -14405,7 +14405,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>67.9886779785156</v>
+        <v>67.9886932373047</v>
       </c>
       <c r="H484" t="n">
         <v>41631</v>
@@ -14463,7 +14463,7 @@
         <v>77.1999969482422</v>
       </c>
       <c r="G486" t="n">
-        <v>68.4765396118164</v>
+        <v>68.4765319824219</v>
       </c>
       <c r="H486" t="n">
         <v>53142</v>
@@ -14608,7 +14608,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G491" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999938964844</v>
       </c>
       <c r="H491" t="n">
         <v>52899</v>
@@ -14637,7 +14637,7 @@
         <v>77.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>68.653938293457</v>
+        <v>68.6539306640625</v>
       </c>
       <c r="H492" t="n">
         <v>86207</v>
@@ -14695,7 +14695,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>68.8756866455078</v>
+        <v>68.8756713867188</v>
       </c>
       <c r="H494" t="n">
         <v>87616</v>
@@ -14724,7 +14724,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>69.5409393310547</v>
+        <v>69.5409469604492</v>
       </c>
       <c r="H495" t="n">
         <v>55937</v>
@@ -14753,7 +14753,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G496" t="n">
-        <v>69.5852966308594</v>
+        <v>69.5852813720703</v>
       </c>
       <c r="H496" t="n">
         <v>53005</v>
@@ -14782,7 +14782,7 @@
         <v>79.5500030517578</v>
       </c>
       <c r="G497" t="n">
-        <v>70.5609970092773</v>
+        <v>70.5610046386719</v>
       </c>
       <c r="H497" t="n">
         <v>66956</v>
@@ -14811,7 +14811,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G498" t="n">
-        <v>71.4479904174805</v>
+        <v>71.4479827880859</v>
       </c>
       <c r="H498" t="n">
         <v>114724</v>
@@ -14840,7 +14840,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>71.2705764770508</v>
+        <v>71.2705841064453</v>
       </c>
       <c r="H499" t="n">
         <v>61927</v>
@@ -14898,7 +14898,7 @@
         <v>77.3499984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>68.6095962524414</v>
+        <v>68.6095809936523</v>
       </c>
       <c r="H501" t="n">
         <v>77973</v>
@@ -14956,7 +14956,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G503" t="n">
-        <v>67.2347412109375</v>
+        <v>67.234733581543</v>
       </c>
       <c r="H503" t="n">
         <v>98841</v>
@@ -14985,7 +14985,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G504" t="n">
-        <v>66.8799362182617</v>
+        <v>66.8799438476562</v>
       </c>
       <c r="H504" t="n">
         <v>99164</v>
@@ -15014,7 +15014,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G505" t="n">
-        <v>66.5694732666016</v>
+        <v>66.5694961547852</v>
       </c>
       <c r="H505" t="n">
         <v>78401</v>
@@ -15043,7 +15043,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G506" t="n">
-        <v>67.1460342407227</v>
+        <v>67.1460266113281</v>
       </c>
       <c r="H506" t="n">
         <v>111441</v>
@@ -15072,7 +15072,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G507" t="n">
-        <v>66.1703262329102</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H507" t="n">
         <v>70211</v>
@@ -15101,7 +15101,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G508" t="n">
-        <v>66.0372848510742</v>
+        <v>66.0372772216797</v>
       </c>
       <c r="H508" t="n">
         <v>31305</v>
@@ -15130,7 +15130,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G509" t="n">
-        <v>66.2146987915039</v>
+        <v>66.2146759033203</v>
       </c>
       <c r="H509" t="n">
         <v>49015</v>
@@ -15159,7 +15159,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G510" t="n">
-        <v>66.1703262329102</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H510" t="n">
         <v>37983</v>
@@ -15275,7 +15275,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>67.2790985107422</v>
+        <v>67.2790908813477</v>
       </c>
       <c r="H514" t="n">
         <v>71685</v>
@@ -15333,7 +15333,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G516" t="n">
-        <v>71.0045013427734</v>
+        <v>71.004508972168</v>
       </c>
       <c r="H516" t="n">
         <v>183028</v>
@@ -15362,7 +15362,7 @@
         <v>79.4499969482422</v>
       </c>
       <c r="G517" t="n">
-        <v>70.4722747802734</v>
+        <v>70.4722900390625</v>
       </c>
       <c r="H517" t="n">
         <v>80894</v>
@@ -15420,7 +15420,7 @@
         <v>79.5999984741211</v>
       </c>
       <c r="G519" t="n">
-        <v>70.605339050293</v>
+        <v>70.6053314208984</v>
       </c>
       <c r="H519" t="n">
         <v>39031</v>
@@ -15449,7 +15449,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G520" t="n">
-        <v>70.6940460205078</v>
+        <v>70.6940383911133</v>
       </c>
       <c r="H520" t="n">
         <v>91810</v>
@@ -15478,7 +15478,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G521" t="n">
-        <v>70.6496810913086</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H521" t="n">
         <v>32110</v>
@@ -15536,7 +15536,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>70.6496810913086</v>
+        <v>70.6496887207031</v>
       </c>
       <c r="H523" t="n">
         <v>44134</v>
@@ -15565,7 +15565,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G524" t="n">
-        <v>71.0045013427734</v>
+        <v>71.004508972168</v>
       </c>
       <c r="H524" t="n">
         <v>30428</v>
@@ -15594,7 +15594,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>70.2061920166016</v>
+        <v>70.206184387207</v>
       </c>
       <c r="H525" t="n">
         <v>54095</v>
@@ -15623,7 +15623,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G526" t="n">
-        <v>70.1618270874023</v>
+        <v>70.1618347167969</v>
       </c>
       <c r="H526" t="n">
         <v>32335</v>
@@ -15652,7 +15652,7 @@
         <v>79.0500030517578</v>
       </c>
       <c r="G527" t="n">
-        <v>70.1175003051758</v>
+        <v>70.1174926757812</v>
       </c>
       <c r="H527" t="n">
         <v>54775</v>
@@ -15681,7 +15681,7 @@
         <v>79</v>
       </c>
       <c r="G528" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731430053711</v>
       </c>
       <c r="H528" t="n">
         <v>24694</v>
@@ -15710,7 +15710,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>69.5409393310547</v>
+        <v>69.5409469604492</v>
       </c>
       <c r="H529" t="n">
         <v>38771</v>
@@ -15826,7 +15826,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G533" t="n">
-        <v>69.1417846679688</v>
+        <v>69.1417999267578</v>
       </c>
       <c r="H533" t="n">
         <v>79064</v>
@@ -15884,7 +15884,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G535" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999938964844</v>
       </c>
       <c r="H535" t="n">
         <v>80635</v>
@@ -15913,7 +15913,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>66.8355865478516</v>
+        <v>66.835578918457</v>
       </c>
       <c r="H536" t="n">
         <v>74286</v>
@@ -15942,7 +15942,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G537" t="n">
-        <v>65.1502685546875</v>
+        <v>65.150276184082</v>
       </c>
       <c r="H537" t="n">
         <v>108860</v>
@@ -15971,7 +15971,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G538" t="n">
-        <v>67.1460342407227</v>
+        <v>67.1460266113281</v>
       </c>
       <c r="H538" t="n">
         <v>141070</v>
@@ -16000,7 +16000,7 @@
         <v>74.0999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>65.7268295288086</v>
+        <v>65.7268218994141</v>
       </c>
       <c r="H539" t="n">
         <v>74319</v>
@@ -16029,7 +16029,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G540" t="n">
-        <v>61.6909790039062</v>
+        <v>61.690975189209</v>
       </c>
       <c r="H540" t="n">
         <v>177993</v>
@@ -16087,7 +16087,7 @@
         <v>71</v>
       </c>
       <c r="G542" t="n">
-        <v>62.9771308898926</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H542" t="n">
         <v>60963</v>
@@ -16116,7 +16116,7 @@
         <v>70</v>
       </c>
       <c r="G543" t="n">
-        <v>62.0901298522949</v>
+        <v>62.0901222229004</v>
       </c>
       <c r="H543" t="n">
         <v>98122</v>
@@ -16145,7 +16145,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G544" t="n">
-        <v>62.4449157714844</v>
+        <v>62.4449234008789</v>
       </c>
       <c r="H544" t="n">
         <v>107264</v>
@@ -16174,7 +16174,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G545" t="n">
-        <v>63.2432289123535</v>
+        <v>63.2432327270508</v>
       </c>
       <c r="H545" t="n">
         <v>109455</v>
@@ -16203,7 +16203,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>62.0014305114746</v>
+        <v>62.0014190673828</v>
       </c>
       <c r="H546" t="n">
         <v>100665</v>
@@ -16232,7 +16232,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G547" t="n">
-        <v>61.6909790039062</v>
+        <v>61.690975189209</v>
       </c>
       <c r="H547" t="n">
         <v>113369</v>
@@ -16261,7 +16261,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G548" t="n">
-        <v>61.9127197265625</v>
+        <v>61.9127349853516</v>
       </c>
       <c r="H548" t="n">
         <v>73072</v>
@@ -16319,7 +16319,7 @@
         <v>69.75</v>
       </c>
       <c r="G550" t="n">
-        <v>61.8683624267578</v>
+        <v>61.8683738708496</v>
       </c>
       <c r="H550" t="n">
         <v>130511</v>
@@ -16377,7 +16377,7 @@
         <v>68.5</v>
       </c>
       <c r="G552" t="n">
-        <v>60.7596244812012</v>
+        <v>60.7596206665039</v>
       </c>
       <c r="H552" t="n">
         <v>106726</v>
@@ -16406,7 +16406,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>59.8282661437988</v>
+        <v>59.8282623291016</v>
       </c>
       <c r="H553" t="n">
         <v>167258</v>
@@ -16493,7 +16493,7 @@
         <v>67.3499984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>59.7395706176758</v>
+        <v>59.7395668029785</v>
       </c>
       <c r="H556" t="n">
         <v>65605</v>
@@ -16522,7 +16522,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>60.6709213256836</v>
+        <v>60.6709251403809</v>
       </c>
       <c r="H557" t="n">
         <v>96155</v>
@@ -16551,7 +16551,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>62.6223182678223</v>
+        <v>62.6223258972168</v>
       </c>
       <c r="H558" t="n">
         <v>201361</v>
@@ -16580,7 +16580,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G559" t="n">
-        <v>65.2389907836914</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H559" t="n">
         <v>157061</v>
@@ -16609,7 +16609,7 @@
         <v>74.75</v>
       </c>
       <c r="G560" t="n">
-        <v>66.3033828735352</v>
+        <v>66.3033752441406</v>
       </c>
       <c r="H560" t="n">
         <v>162714</v>
@@ -16754,7 +16754,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G565" t="n">
-        <v>64.0415344238281</v>
+        <v>64.0415267944336</v>
       </c>
       <c r="H565" t="n">
         <v>111591</v>
@@ -16783,7 +16783,7 @@
         <v>71.8000030517578</v>
       </c>
       <c r="G566" t="n">
-        <v>63.6867218017578</v>
+        <v>63.6867370605469</v>
       </c>
       <c r="H566" t="n">
         <v>464005</v>
@@ -16812,7 +16812,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G567" t="n">
-        <v>63.9084892272949</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H567" t="n">
         <v>196304</v>
@@ -16870,7 +16870,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G569" t="n">
-        <v>64.440673828125</v>
+        <v>64.4406814575195</v>
       </c>
       <c r="H569" t="n">
         <v>112305</v>
@@ -16899,7 +16899,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>63.5536804199219</v>
+        <v>63.5536842346191</v>
       </c>
       <c r="H570" t="n">
         <v>72259</v>
@@ -16928,7 +16928,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G571" t="n">
-        <v>62.4005813598633</v>
+        <v>62.4005699157715</v>
       </c>
       <c r="H571" t="n">
         <v>80142</v>
@@ -16957,7 +16957,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G572" t="n">
-        <v>64.440673828125</v>
+        <v>64.4406814575195</v>
       </c>
       <c r="H572" t="n">
         <v>116056</v>
@@ -17015,7 +17015,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>64.8398361206055</v>
+        <v>64.8398284912109</v>
       </c>
       <c r="H574" t="n">
         <v>52352</v>
@@ -17073,7 +17073,7 @@
         <v>71.75</v>
       </c>
       <c r="G576" t="n">
-        <v>63.6423835754395</v>
+        <v>63.6423683166504</v>
       </c>
       <c r="H576" t="n">
         <v>105782</v>
@@ -17189,7 +17189,7 @@
         <v>73</v>
       </c>
       <c r="G580" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511291503906</v>
       </c>
       <c r="H580" t="n">
         <v>91866</v>
@@ -17218,7 +17218,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G581" t="n">
-        <v>63.9084892272949</v>
+        <v>63.9084777832031</v>
       </c>
       <c r="H581" t="n">
         <v>69529</v>
@@ -17247,7 +17247,7 @@
         <v>73.5</v>
       </c>
       <c r="G582" t="n">
-        <v>65.1946334838867</v>
+        <v>65.1946258544922</v>
       </c>
       <c r="H582" t="n">
         <v>45972</v>
@@ -17276,7 +17276,7 @@
         <v>73.5</v>
       </c>
       <c r="G583" t="n">
-        <v>65.1946334838867</v>
+        <v>65.1946258544922</v>
       </c>
       <c r="H583" t="n">
         <v>44775</v>
@@ -17305,7 +17305,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G584" t="n">
-        <v>66.8355865478516</v>
+        <v>66.835578918457</v>
       </c>
       <c r="H584" t="n">
         <v>90831</v>
@@ -17334,7 +17334,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G585" t="n">
-        <v>67.0129852294922</v>
+        <v>67.0130004882812</v>
       </c>
       <c r="H585" t="n">
         <v>77497</v>
@@ -17363,7 +17363,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>68.8313217163086</v>
+        <v>68.8313446044922</v>
       </c>
       <c r="H586" t="n">
         <v>170948</v>
@@ -17392,7 +17392,7 @@
         <v>74.75</v>
       </c>
       <c r="G587" t="n">
-        <v>66.3033828735352</v>
+        <v>66.3033752441406</v>
       </c>
       <c r="H587" t="n">
         <v>136648</v>
@@ -17421,7 +17421,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>66.1703262329102</v>
+        <v>66.1703338623047</v>
       </c>
       <c r="H588" t="n">
         <v>51993</v>
@@ -17450,7 +17450,7 @@
         <v>76.1999969482422</v>
       </c>
       <c r="G589" t="n">
-        <v>67.5895156860352</v>
+        <v>67.5895309448242</v>
       </c>
       <c r="H589" t="n">
         <v>77037</v>
@@ -17479,7 +17479,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>69.5409393310547</v>
+        <v>69.5409469604492</v>
       </c>
       <c r="H590" t="n">
         <v>130725</v>
@@ -17508,7 +17508,7 @@
         <v>77.3000030517578</v>
       </c>
       <c r="G591" t="n">
-        <v>68.5652236938477</v>
+        <v>68.5652313232422</v>
       </c>
       <c r="H591" t="n">
         <v>67536</v>
@@ -17537,7 +17537,7 @@
         <v>78.1500015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>69.3191909790039</v>
+        <v>69.3191833496094</v>
       </c>
       <c r="H592" t="n">
         <v>49026</v>
@@ -17566,7 +17566,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>69.5409393310547</v>
+        <v>69.5409469604492</v>
       </c>
       <c r="H593" t="n">
         <v>58135</v>
@@ -17595,7 +17595,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>69.4965744018555</v>
+        <v>69.49658203125</v>
       </c>
       <c r="H594" t="n">
         <v>39491</v>
@@ -17653,7 +17653,7 @@
         <v>78</v>
       </c>
       <c r="G596" t="n">
-        <v>69.1861419677734</v>
+        <v>69.1861267089844</v>
       </c>
       <c r="H596" t="n">
         <v>101024</v>
@@ -17711,7 +17711,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G598" t="n">
-        <v>70.2061920166016</v>
+        <v>70.206184387207</v>
       </c>
       <c r="H598" t="n">
         <v>39356</v>
@@ -17740,7 +17740,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G599" t="n">
-        <v>69.4522399902344</v>
+        <v>69.4522476196289</v>
       </c>
       <c r="H599" t="n">
         <v>102601</v>
@@ -17827,7 +17827,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G602" t="n">
-        <v>71.1375274658203</v>
+        <v>71.1375350952148</v>
       </c>
       <c r="H602" t="n">
         <v>87659</v>
@@ -17856,7 +17856,7 @@
         <v>81.3000030517578</v>
       </c>
       <c r="G603" t="n">
-        <v>72.1132431030273</v>
+        <v>72.1132583618164</v>
       </c>
       <c r="H603" t="n">
         <v>111150</v>
@@ -17943,7 +17943,7 @@
         <v>82.6500015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>73.3106918334961</v>
+        <v>73.3106994628906</v>
       </c>
       <c r="H606" t="n">
         <v>90912</v>
@@ -18001,7 +18001,7 @@
         <v>81.25</v>
       </c>
       <c r="G608" t="n">
-        <v>72.8294067382812</v>
+        <v>72.8293991088867</v>
       </c>
       <c r="H608" t="n">
         <v>62147</v>
@@ -18030,7 +18030,7 @@
         <v>81.9000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>73.4120407104492</v>
+        <v>73.4120330810547</v>
       </c>
       <c r="H609" t="n">
         <v>82870</v>
@@ -18059,7 +18059,7 @@
         <v>80.6999969482422</v>
       </c>
       <c r="G610" t="n">
-        <v>72.3364105224609</v>
+        <v>72.3363952636719</v>
       </c>
       <c r="H610" t="n">
         <v>120090</v>
@@ -18146,7 +18146,7 @@
         <v>83</v>
       </c>
       <c r="G613" t="n">
-        <v>74.3980178833008</v>
+        <v>74.3980331420898</v>
       </c>
       <c r="H613" t="n">
         <v>81300</v>
@@ -18204,7 +18204,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G615" t="n">
-        <v>75.8322067260742</v>
+        <v>75.8322143554688</v>
       </c>
       <c r="H615" t="n">
         <v>139846</v>
@@ -18233,7 +18233,7 @@
         <v>82.5999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>74.0394821166992</v>
+        <v>74.0394897460938</v>
       </c>
       <c r="H616" t="n">
         <v>132486</v>
@@ -18262,7 +18262,7 @@
         <v>85.5</v>
       </c>
       <c r="G617" t="n">
-        <v>76.6389312744141</v>
+        <v>76.6389389038086</v>
       </c>
       <c r="H617" t="n">
         <v>117653</v>
@@ -18291,7 +18291,7 @@
         <v>87.5</v>
       </c>
       <c r="G618" t="n">
-        <v>78.4316558837891</v>
+        <v>78.4316635131836</v>
       </c>
       <c r="H618" t="n">
         <v>108629</v>
@@ -18378,7 +18378,7 @@
         <v>88.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>79.238395690918</v>
+        <v>79.2383880615234</v>
       </c>
       <c r="H621" t="n">
         <v>84613</v>
@@ -18407,7 +18407,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>78.7901992797852</v>
+        <v>78.7901916503906</v>
       </c>
       <c r="H622" t="n">
         <v>109981</v>
@@ -18436,7 +18436,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>79.7313766479492</v>
+        <v>79.7313690185547</v>
       </c>
       <c r="H623" t="n">
         <v>42192</v>
@@ -18494,7 +18494,7 @@
         <v>92.4000015258789</v>
       </c>
       <c r="G625" t="n">
-        <v>82.8238296508789</v>
+        <v>82.8238220214844</v>
       </c>
       <c r="H625" t="n">
         <v>127436</v>
@@ -18523,7 +18523,7 @@
         <v>93.3499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>83.6753692626953</v>
+        <v>83.6753616333008</v>
       </c>
       <c r="H626" t="n">
         <v>69385</v>
@@ -18552,7 +18552,7 @@
         <v>93</v>
       </c>
       <c r="G627" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H627" t="n">
         <v>96749</v>
@@ -18581,7 +18581,7 @@
         <v>92.3000030517578</v>
       </c>
       <c r="G628" t="n">
-        <v>82.7342071533203</v>
+        <v>82.7341918945312</v>
       </c>
       <c r="H628" t="n">
         <v>47449</v>
@@ -18610,7 +18610,7 @@
         <v>90.9499969482422</v>
       </c>
       <c r="G629" t="n">
-        <v>81.5241165161133</v>
+        <v>81.5241012573242</v>
       </c>
       <c r="H629" t="n">
         <v>123549</v>
@@ -18668,7 +18668,7 @@
         <v>89.1500015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>79.9106597900391</v>
+        <v>79.9106521606445</v>
       </c>
       <c r="H631" t="n">
         <v>85755</v>
@@ -18755,7 +18755,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G634" t="n">
-        <v>85.7818298339844</v>
+        <v>85.7818145751953</v>
       </c>
       <c r="H634" t="n">
         <v>55163</v>
@@ -18784,7 +18784,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G635" t="n">
-        <v>87.2160034179688</v>
+        <v>87.2160110473633</v>
       </c>
       <c r="H635" t="n">
         <v>119198</v>
@@ -18813,7 +18813,7 @@
         <v>96.3499984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>86.3644714355469</v>
+        <v>86.3644561767578</v>
       </c>
       <c r="H636" t="n">
         <v>136400</v>
@@ -18929,7 +18929,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>86.4092864990234</v>
+        <v>86.4092788696289</v>
       </c>
       <c r="H640" t="n">
         <v>48560</v>
@@ -18958,7 +18958,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>85.6473846435547</v>
+        <v>85.6473922729492</v>
       </c>
       <c r="H641" t="n">
         <v>108916</v>
@@ -19016,7 +19016,7 @@
         <v>95.8000030517578</v>
       </c>
       <c r="G643" t="n">
-        <v>85.8714599609375</v>
+        <v>85.871467590332</v>
       </c>
       <c r="H643" t="n">
         <v>46270</v>
@@ -19074,7 +19074,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G645" t="n">
-        <v>86.1851806640625</v>
+        <v>86.185188293457</v>
       </c>
       <c r="H645" t="n">
         <v>49001</v>
@@ -19103,7 +19103,7 @@
         <v>98.1999969482422</v>
       </c>
       <c r="G646" t="n">
-        <v>88.0227127075195</v>
+        <v>88.0227279663086</v>
       </c>
       <c r="H646" t="n">
         <v>48947</v>
@@ -19132,7 +19132,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>87.5297317504883</v>
+        <v>87.5297241210938</v>
       </c>
       <c r="H647" t="n">
         <v>29778</v>
@@ -19161,7 +19161,7 @@
         <v>97.9000015258789</v>
       </c>
       <c r="G648" t="n">
-        <v>87.7538146972656</v>
+        <v>87.7538375854492</v>
       </c>
       <c r="H648" t="n">
         <v>36696</v>
@@ -19219,7 +19219,7 @@
         <v>95.9499969482422</v>
       </c>
       <c r="G650" t="n">
-        <v>86.0058975219727</v>
+        <v>86.0059204101562</v>
       </c>
       <c r="H650" t="n">
         <v>65806</v>
@@ -19277,7 +19277,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G652" t="n">
-        <v>86.4092864990234</v>
+        <v>86.4092788696289</v>
       </c>
       <c r="H652" t="n">
         <v>50636</v>
@@ -19364,7 +19364,7 @@
         <v>94.3499984741211</v>
       </c>
       <c r="G655" t="n">
-        <v>84.5717391967773</v>
+        <v>84.5717315673828</v>
       </c>
       <c r="H655" t="n">
         <v>105068</v>
@@ -19393,7 +19393,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G656" t="n">
-        <v>82.8686447143555</v>
+        <v>82.8686370849609</v>
       </c>
       <c r="H656" t="n">
         <v>119477</v>
@@ -19422,7 +19422,7 @@
         <v>93</v>
       </c>
       <c r="G657" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H657" t="n">
         <v>92816</v>
@@ -19451,7 +19451,7 @@
         <v>92.5</v>
       </c>
       <c r="G658" t="n">
-        <v>82.9134826660156</v>
+        <v>82.9134674072266</v>
       </c>
       <c r="H658" t="n">
         <v>79668</v>
@@ -19509,7 +19509,7 @@
         <v>93</v>
       </c>
       <c r="G660" t="n">
-        <v>83.3616561889648</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H660" t="n">
         <v>69462</v>
@@ -19538,7 +19538,7 @@
         <v>85.0500030517578</v>
       </c>
       <c r="G661" t="n">
-        <v>76.2355728149414</v>
+        <v>76.2355651855469</v>
       </c>
       <c r="H661" t="n">
         <v>377231</v>
@@ -19567,7 +19567,7 @@
         <v>87.3499984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>78.2971954345703</v>
+        <v>78.2972106933594</v>
       </c>
       <c r="H662" t="n">
         <v>169305</v>
@@ -19596,7 +19596,7 @@
         <v>87.5</v>
       </c>
       <c r="G663" t="n">
-        <v>78.4316558837891</v>
+        <v>78.4316635131836</v>
       </c>
       <c r="H663" t="n">
         <v>89704</v>
@@ -19654,7 +19654,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>78.7453918457031</v>
+        <v>78.7453842163086</v>
       </c>
       <c r="H665" t="n">
         <v>107411</v>
@@ -19683,7 +19683,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>78.9694595336914</v>
+        <v>78.9694747924805</v>
       </c>
       <c r="H666" t="n">
         <v>78905</v>
@@ -19712,7 +19712,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>78.7453918457031</v>
+        <v>78.7453842163086</v>
       </c>
       <c r="H667" t="n">
         <v>58890</v>
@@ -19828,7 +19828,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G671" t="n">
-        <v>77.8490295410156</v>
+        <v>77.8490142822266</v>
       </c>
       <c r="H671" t="n">
         <v>30505</v>
@@ -19857,7 +19857,7 @@
         <v>93.1999969482422</v>
       </c>
       <c r="G672" t="n">
-        <v>83.5409240722656</v>
+        <v>83.5409164428711</v>
       </c>
       <c r="H672" t="n">
         <v>124136</v>
@@ -19886,7 +19886,7 @@
         <v>93.75</v>
       </c>
       <c r="G673" t="n">
-        <v>84.0339279174805</v>
+        <v>84.0339202880859</v>
       </c>
       <c r="H673" t="n">
         <v>153238</v>
@@ -19915,7 +19915,7 @@
         <v>91.5</v>
       </c>
       <c r="G674" t="n">
-        <v>82.0170822143555</v>
+        <v>82.0170974731445</v>
       </c>
       <c r="H674" t="n">
         <v>117256</v>
@@ -19944,7 +19944,7 @@
         <v>91.8499984741211</v>
       </c>
       <c r="G675" t="n">
-        <v>82.3308258056641</v>
+        <v>82.3308334350586</v>
       </c>
       <c r="H675" t="n">
         <v>44726</v>
@@ -20002,7 +20002,7 @@
         <v>91.1500015258789</v>
       </c>
       <c r="G677" t="n">
-        <v>81.7033843994141</v>
+        <v>81.7033767700195</v>
       </c>
       <c r="H677" t="n">
         <v>62973</v>
@@ -20147,7 +20147,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G682" t="n">
-        <v>82.8686447143555</v>
+        <v>82.8686370849609</v>
       </c>
       <c r="H682" t="n">
         <v>33661</v>
@@ -20176,7 +20176,7 @@
         <v>92.3499984741211</v>
       </c>
       <c r="G683" t="n">
-        <v>82.7790145874023</v>
+        <v>82.7790069580078</v>
       </c>
       <c r="H683" t="n">
         <v>59883</v>
@@ -20205,7 +20205,7 @@
         <v>89.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>80.1347503662109</v>
+        <v>80.1347427368164</v>
       </c>
       <c r="H684" t="n">
         <v>61358</v>
@@ -20234,7 +20234,7 @@
         <v>89.6999969482422</v>
       </c>
       <c r="G685" t="n">
-        <v>80.4036407470703</v>
+        <v>80.4036560058594</v>
       </c>
       <c r="H685" t="n">
         <v>34402</v>
@@ -20263,7 +20263,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>78.7901992797852</v>
+        <v>78.7901916503906</v>
       </c>
       <c r="H686" t="n">
         <v>66724</v>
@@ -20292,7 +20292,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G687" t="n">
-        <v>79.7313766479492</v>
+        <v>79.7313690185547</v>
       </c>
       <c r="H687" t="n">
         <v>31413</v>
@@ -20321,7 +20321,7 @@
         <v>88.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>79.238395690918</v>
+        <v>79.2383880615234</v>
       </c>
       <c r="H688" t="n">
         <v>25769</v>
@@ -20350,7 +20350,7 @@
         <v>88.6999969482422</v>
       </c>
       <c r="G689" t="n">
-        <v>79.5072937011719</v>
+        <v>79.5072860717773</v>
       </c>
       <c r="H689" t="n">
         <v>31366</v>
@@ -20408,7 +20408,7 @@
         <v>89</v>
       </c>
       <c r="G691" t="n">
-        <v>79.7762069702148</v>
+        <v>79.7761917114258</v>
       </c>
       <c r="H691" t="n">
         <v>27813</v>
@@ -20437,7 +20437,7 @@
         <v>90.6999969482422</v>
       </c>
       <c r="G692" t="n">
-        <v>81.3000030517578</v>
+        <v>81.3000106811523</v>
       </c>
       <c r="H692" t="n">
         <v>81645</v>
@@ -20466,7 +20466,7 @@
         <v>93.75</v>
       </c>
       <c r="G693" t="n">
-        <v>84.0339279174805</v>
+        <v>84.0339202880859</v>
       </c>
       <c r="H693" t="n">
         <v>162492</v>
@@ -20524,7 +20524,7 @@
         <v>97.1999969482422</v>
       </c>
       <c r="G695" t="n">
-        <v>87.1263656616211</v>
+        <v>87.1263732910156</v>
       </c>
       <c r="H695" t="n">
         <v>153783</v>
@@ -20582,7 +20582,7 @@
         <v>91.5</v>
       </c>
       <c r="G697" t="n">
-        <v>82.0170822143555</v>
+        <v>82.0170974731445</v>
       </c>
       <c r="H697" t="n">
         <v>122508</v>
@@ -20611,7 +20611,7 @@
         <v>93.0999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>83.4512939453125</v>
+        <v>83.4512634277344</v>
       </c>
       <c r="H698" t="n">
         <v>72943</v>
@@ -20640,7 +20640,7 @@
         <v>92.9499969482422</v>
       </c>
       <c r="G699" t="n">
-        <v>83.3168334960938</v>
+        <v>83.3168258666992</v>
       </c>
       <c r="H699" t="n">
         <v>72035</v>
@@ -20698,7 +20698,7 @@
         <v>90.5999984741211</v>
       </c>
       <c r="G701" t="n">
-        <v>81.2103805541992</v>
+        <v>81.2103729248047</v>
       </c>
       <c r="H701" t="n">
         <v>145913</v>
@@ -20727,7 +20727,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G702" t="n">
-        <v>81.8378295898438</v>
+        <v>81.8378219604492</v>
       </c>
       <c r="H702" t="n">
         <v>82540</v>
@@ -20785,7 +20785,7 @@
         <v>90.5999984741211</v>
       </c>
       <c r="G704" t="n">
-        <v>81.2103805541992</v>
+        <v>81.2103729248047</v>
       </c>
       <c r="H704" t="n">
         <v>37461</v>
@@ -20843,7 +20843,7 @@
         <v>86.8000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>77.8042068481445</v>
+        <v>77.80419921875</v>
       </c>
       <c r="H706" t="n">
         <v>256998</v>
@@ -20872,7 +20872,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G707" t="n">
-        <v>73.7705841064453</v>
+        <v>73.7705764770508</v>
       </c>
       <c r="H707" t="n">
         <v>126590</v>
@@ -20901,7 +20901,7 @@
         <v>81.5</v>
       </c>
       <c r="G708" t="n">
-        <v>73.0534896850586</v>
+        <v>73.0535049438477</v>
       </c>
       <c r="H708" t="n">
         <v>106072</v>
@@ -20930,7 +20930,7 @@
         <v>80.3000030517578</v>
       </c>
       <c r="G709" t="n">
-        <v>71.9778518676758</v>
+        <v>71.9778671264648</v>
       </c>
       <c r="H709" t="n">
         <v>108422</v>
@@ -20959,7 +20959,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G710" t="n">
-        <v>71.4400405883789</v>
+        <v>71.4400253295898</v>
       </c>
       <c r="H710" t="n">
         <v>100334</v>
@@ -21104,7 +21104,7 @@
         <v>82</v>
       </c>
       <c r="G715" t="n">
-        <v>73.5016632080078</v>
+        <v>73.5016708374023</v>
       </c>
       <c r="H715" t="n">
         <v>86910</v>
@@ -21162,7 +21162,7 @@
         <v>83.6999969482422</v>
       </c>
       <c r="G717" t="n">
-        <v>75.0254745483398</v>
+        <v>75.0254821777344</v>
       </c>
       <c r="H717" t="n">
         <v>60661</v>
@@ -21191,7 +21191,7 @@
         <v>79.75</v>
       </c>
       <c r="G718" t="n">
-        <v>71.4848556518555</v>
+        <v>71.4848480224609</v>
       </c>
       <c r="H718" t="n">
         <v>148610</v>
@@ -21249,7 +21249,7 @@
         <v>80.8499984741211</v>
       </c>
       <c r="G720" t="n">
-        <v>72.4708404541016</v>
+        <v>72.4708480834961</v>
       </c>
       <c r="H720" t="n">
         <v>52507</v>
@@ -21278,7 +21278,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G721" t="n">
-        <v>70.9470367431641</v>
+        <v>70.9470443725586</v>
       </c>
       <c r="H721" t="n">
         <v>83718</v>
@@ -21307,7 +21307,7 @@
         <v>81</v>
       </c>
       <c r="G722" t="n">
-        <v>72.6053009033203</v>
+        <v>72.6053085327148</v>
       </c>
       <c r="H722" t="n">
         <v>74067</v>
@@ -21365,7 +21365,7 @@
         <v>83.8000030517578</v>
       </c>
       <c r="G724" t="n">
-        <v>75.115119934082</v>
+        <v>75.1151275634766</v>
       </c>
       <c r="H724" t="n">
         <v>192896</v>
@@ -21452,7 +21452,7 @@
         <v>87.5500030517578</v>
       </c>
       <c r="G727" t="n">
-        <v>78.4764785766602</v>
+        <v>78.4764862060547</v>
       </c>
       <c r="H727" t="n">
         <v>78626</v>
@@ -21481,7 +21481,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>77.8490295410156</v>
+        <v>77.8490142822266</v>
       </c>
       <c r="H728" t="n">
         <v>95580</v>
@@ -21539,7 +21539,7 @@
         <v>82.5</v>
       </c>
       <c r="G730" t="n">
-        <v>73.9498519897461</v>
+        <v>73.9498596191406</v>
       </c>
       <c r="H730" t="n">
         <v>122029</v>
@@ -21568,7 +21568,7 @@
         <v>83.3499984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>74.7117614746094</v>
+        <v>74.7117538452148</v>
       </c>
       <c r="H731" t="n">
         <v>73577</v>
@@ -21626,7 +21626,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G733" t="n">
-        <v>73.7705841064453</v>
+        <v>73.7705764770508</v>
       </c>
       <c r="H733" t="n">
         <v>77523</v>
@@ -21684,7 +21684,7 @@
         <v>80</v>
       </c>
       <c r="G735" t="n">
-        <v>71.7089462280273</v>
+        <v>71.7089385986328</v>
       </c>
       <c r="H735" t="n">
         <v>76591</v>
@@ -21742,7 +21742,7 @@
         <v>81</v>
       </c>
       <c r="G737" t="n">
-        <v>72.6053009033203</v>
+        <v>72.6053085327148</v>
       </c>
       <c r="H737" t="n">
         <v>90532</v>
@@ -21771,7 +21771,7 @@
         <v>77.25</v>
       </c>
       <c r="G738" t="n">
-        <v>69.2439498901367</v>
+        <v>69.2439575195312</v>
       </c>
       <c r="H738" t="n">
         <v>126656</v>
@@ -21800,7 +21800,7 @@
         <v>77.4000015258789</v>
       </c>
       <c r="G739" t="n">
-        <v>69.3784103393555</v>
+        <v>69.37841796875</v>
       </c>
       <c r="H739" t="n">
         <v>85381</v>
@@ -21858,7 +21858,7 @@
         <v>78.8000030517578</v>
       </c>
       <c r="G741" t="n">
-        <v>70.6333084106445</v>
+        <v>70.63330078125</v>
       </c>
       <c r="H741" t="n">
         <v>77805</v>
@@ -21887,7 +21887,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G742" t="n">
-        <v>71.7537612915039</v>
+        <v>71.753776550293</v>
       </c>
       <c r="H742" t="n">
         <v>109282</v>
@@ -21974,7 +21974,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G745" t="n">
-        <v>69.5576705932617</v>
+        <v>69.5576858520508</v>
       </c>
       <c r="H745" t="n">
         <v>105516</v>
@@ -22003,7 +22003,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G746" t="n">
-        <v>67.3167724609375</v>
+        <v>67.316764831543</v>
       </c>
       <c r="H746" t="n">
         <v>166307</v>
@@ -22090,7 +22090,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>70.005859375</v>
+        <v>70.0058670043945</v>
       </c>
       <c r="H749" t="n">
         <v>206228</v>
@@ -22119,7 +22119,7 @@
         <v>73.1500015258789</v>
       </c>
       <c r="G750" t="n">
-        <v>65.5688629150391</v>
+        <v>65.5688705444336</v>
       </c>
       <c r="H750" t="n">
         <v>439461</v>
@@ -22148,7 +22148,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G751" t="n">
-        <v>66.1515045166016</v>
+        <v>66.151496887207</v>
       </c>
       <c r="H751" t="n">
         <v>99584</v>
@@ -22177,7 +22177,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G752" t="n">
-        <v>65.7033233642578</v>
+        <v>65.7033309936523</v>
       </c>
       <c r="H752" t="n">
         <v>98961</v>
@@ -22206,7 +22206,7 @@
         <v>72.9499969482422</v>
       </c>
       <c r="G753" t="n">
-        <v>65.3895950317383</v>
+        <v>65.3895874023438</v>
       </c>
       <c r="H753" t="n">
         <v>81159</v>
@@ -22264,7 +22264,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G755" t="n">
-        <v>65.6136856079102</v>
+        <v>65.6136779785156</v>
       </c>
       <c r="H755" t="n">
         <v>136727</v>
@@ -22293,7 +22293,7 @@
         <v>71.75</v>
       </c>
       <c r="G756" t="n">
-        <v>64.31396484375</v>
+        <v>64.3139572143555</v>
       </c>
       <c r="H756" t="n">
         <v>131555</v>
@@ -22322,7 +22322,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G757" t="n">
-        <v>62.8349571228027</v>
+        <v>62.8349647521973</v>
       </c>
       <c r="H757" t="n">
         <v>168734</v>
@@ -22409,7 +22409,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G760" t="n">
-        <v>63.5968742370605</v>
+        <v>63.5968704223633</v>
       </c>
       <c r="H760" t="n">
         <v>142583</v>
@@ -22438,7 +22438,7 @@
         <v>72.4499969482422</v>
       </c>
       <c r="G761" t="n">
-        <v>64.9414138793945</v>
+        <v>64.94140625</v>
       </c>
       <c r="H761" t="n">
         <v>642524</v>
@@ -22467,7 +22467,7 @@
         <v>69.3499984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>63.7464447021484</v>
+        <v>63.746452331543</v>
       </c>
       <c r="H762" t="n">
         <v>134941</v>
@@ -22670,7 +22670,7 @@
         <v>74.3499984741211</v>
       </c>
       <c r="G769" t="n">
-        <v>68.3424453735352</v>
+        <v>68.3424606323242</v>
       </c>
       <c r="H769" t="n">
         <v>129576</v>
@@ -22699,7 +22699,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G770" t="n">
-        <v>69.4454879760742</v>
+        <v>69.4454803466797</v>
       </c>
       <c r="H770" t="n">
         <v>69821</v>
@@ -22728,7 +22728,7 @@
         <v>74.9000015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>68.8480072021484</v>
+        <v>68.8480224609375</v>
       </c>
       <c r="H771" t="n">
         <v>58124</v>
@@ -22786,7 +22786,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G773" t="n">
-        <v>69.5833587646484</v>
+        <v>69.5833740234375</v>
       </c>
       <c r="H773" t="n">
         <v>72777</v>
@@ -22815,7 +22815,7 @@
         <v>77.5</v>
       </c>
       <c r="G774" t="n">
-        <v>71.2379302978516</v>
+        <v>71.2379150390625</v>
       </c>
       <c r="H774" t="n">
         <v>75923</v>
@@ -22844,7 +22844,7 @@
         <v>78</v>
       </c>
       <c r="G775" t="n">
-        <v>71.6975250244141</v>
+        <v>71.6975173950195</v>
       </c>
       <c r="H775" t="n">
         <v>84212</v>
@@ -22931,7 +22931,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G778" t="n">
-        <v>73.581901550293</v>
+        <v>73.5818862915039</v>
       </c>
       <c r="H778" t="n">
         <v>152719</v>
@@ -22989,7 +22989,7 @@
         <v>80.1500015258789</v>
       </c>
       <c r="G780" t="n">
-        <v>73.6738052368164</v>
+        <v>73.6737976074219</v>
       </c>
       <c r="H780" t="n">
         <v>67535</v>
@@ -23163,7 +23163,7 @@
         <v>82.0999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>75.4662475585938</v>
+        <v>75.4662322998047</v>
       </c>
       <c r="H786" t="n">
         <v>190749</v>
@@ -23221,7 +23221,7 @@
         <v>84.0500030517578</v>
       </c>
       <c r="G788" t="n">
-        <v>77.2586822509766</v>
+        <v>77.258674621582</v>
       </c>
       <c r="H788" t="n">
         <v>88125</v>
@@ -23250,7 +23250,7 @@
         <v>83.9499969482422</v>
       </c>
       <c r="G789" t="n">
-        <v>77.166748046875</v>
+        <v>77.1667556762695</v>
       </c>
       <c r="H789" t="n">
         <v>89975</v>
@@ -23279,7 +23279,7 @@
         <v>85.0999984741211</v>
       </c>
       <c r="G790" t="n">
-        <v>78.2238388061523</v>
+        <v>78.2238311767578</v>
       </c>
       <c r="H790" t="n">
         <v>123407</v>
@@ -23366,7 +23366,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G793" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H793" t="n">
         <v>114380</v>
@@ -23482,7 +23482,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G797" t="n">
-        <v>78.5455551147461</v>
+        <v>78.5455474853516</v>
       </c>
       <c r="H797" t="n">
         <v>105022</v>
@@ -23540,7 +23540,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H799" t="n">
         <v>72446</v>
@@ -23598,7 +23598,7 @@
         <v>85.0999984741211</v>
       </c>
       <c r="G801" t="n">
-        <v>78.2238388061523</v>
+        <v>78.2238311767578</v>
       </c>
       <c r="H801" t="n">
         <v>75109</v>
@@ -23627,7 +23627,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H802" t="n">
         <v>78894</v>
@@ -23656,7 +23656,7 @@
         <v>86.1500015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>79.1890029907227</v>
+        <v>79.1889953613281</v>
       </c>
       <c r="H803" t="n">
         <v>109844</v>
@@ -23714,7 +23714,7 @@
         <v>86.25</v>
       </c>
       <c r="G805" t="n">
-        <v>79.2809219360352</v>
+        <v>79.2809143066406</v>
       </c>
       <c r="H805" t="n">
         <v>103167</v>
@@ -23801,7 +23801,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>79.8783874511719</v>
+        <v>79.8783950805664</v>
       </c>
       <c r="H808" t="n">
         <v>109186</v>
@@ -23830,7 +23830,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G809" t="n">
-        <v>79.8324356079102</v>
+        <v>79.8324279785156</v>
       </c>
       <c r="H809" t="n">
         <v>66533</v>
@@ -23859,7 +23859,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G810" t="n">
-        <v>79.8324356079102</v>
+        <v>79.8324279785156</v>
       </c>
       <c r="H810" t="n">
         <v>86148</v>
@@ -23888,7 +23888,7 @@
         <v>86.75</v>
       </c>
       <c r="G811" t="n">
-        <v>79.7405090332031</v>
+        <v>79.7405242919922</v>
       </c>
       <c r="H811" t="n">
         <v>82074</v>
@@ -23917,7 +23917,7 @@
         <v>86.75</v>
       </c>
       <c r="G812" t="n">
-        <v>79.7405090332031</v>
+        <v>79.7405242919922</v>
       </c>
       <c r="H812" t="n">
         <v>53324</v>
@@ -23946,7 +23946,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G813" t="n">
-        <v>80.705680847168</v>
+        <v>80.7056732177734</v>
       </c>
       <c r="H813" t="n">
         <v>67619</v>
@@ -24004,7 +24004,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G815" t="n">
-        <v>78.8672714233398</v>
+        <v>78.8672790527344</v>
       </c>
       <c r="H815" t="n">
         <v>202818</v>
@@ -24091,7 +24091,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G818" t="n">
-        <v>80.7516403198242</v>
+        <v>80.7516250610352</v>
       </c>
       <c r="H818" t="n">
         <v>157322</v>
@@ -24149,7 +24149,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G820" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4869918823242</v>
       </c>
       <c r="H820" t="n">
         <v>70750</v>
@@ -24178,7 +24178,7 @@
         <v>88.9000015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>81.716796875</v>
+        <v>81.7167892456055</v>
       </c>
       <c r="H821" t="n">
         <v>108185</v>
@@ -24236,7 +24236,7 @@
         <v>89.3499984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>82.1304321289062</v>
+        <v>82.1304244995117</v>
       </c>
       <c r="H823" t="n">
         <v>108948</v>
@@ -24294,7 +24294,7 @@
         <v>89.75</v>
       </c>
       <c r="G825" t="n">
-        <v>82.4981231689453</v>
+        <v>82.4981155395508</v>
       </c>
       <c r="H825" t="n">
         <v>86069</v>
@@ -24352,7 +24352,7 @@
         <v>90.5500030517578</v>
       </c>
       <c r="G827" t="n">
-        <v>83.2334671020508</v>
+        <v>83.2334823608398</v>
       </c>
       <c r="H827" t="n">
         <v>113522</v>
@@ -24410,7 +24410,7 @@
         <v>92.75</v>
       </c>
       <c r="G829" t="n">
-        <v>85.2557144165039</v>
+        <v>85.2556991577148</v>
       </c>
       <c r="H829" t="n">
         <v>126038</v>
@@ -24439,7 +24439,7 @@
         <v>92</v>
       </c>
       <c r="G830" t="n">
-        <v>84.5663070678711</v>
+        <v>84.5663146972656</v>
       </c>
       <c r="H830" t="n">
         <v>129196</v>
@@ -24468,7 +24468,7 @@
         <v>92</v>
       </c>
       <c r="G831" t="n">
-        <v>84.5663070678711</v>
+        <v>84.5663146972656</v>
       </c>
       <c r="H831" t="n">
         <v>97582</v>
@@ -24497,7 +24497,7 @@
         <v>91.6500015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>84.2446060180664</v>
+        <v>84.2445907592773</v>
       </c>
       <c r="H832" t="n">
         <v>119763</v>
@@ -24526,7 +24526,7 @@
         <v>91.5</v>
       </c>
       <c r="G833" t="n">
-        <v>84.1066970825195</v>
+        <v>84.1067123413086</v>
       </c>
       <c r="H833" t="n">
         <v>83242</v>
@@ -24729,7 +24729,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G840" t="n">
-        <v>79.8324356079102</v>
+        <v>79.8324279785156</v>
       </c>
       <c r="H840" t="n">
         <v>83348</v>
@@ -24758,7 +24758,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G841" t="n">
-        <v>80.705680847168</v>
+        <v>80.7056732177734</v>
       </c>
       <c r="H841" t="n">
         <v>122041</v>
@@ -24816,7 +24816,7 @@
         <v>85.1500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>78.2698059082031</v>
+        <v>78.2697982788086</v>
       </c>
       <c r="H843" t="n">
         <v>80115</v>
@@ -24874,7 +24874,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>80.0622329711914</v>
+        <v>80.0622482299805</v>
       </c>
       <c r="H845" t="n">
         <v>103640</v>
@@ -24903,7 +24903,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G846" t="n">
-        <v>80.0622329711914</v>
+        <v>80.0622482299805</v>
       </c>
       <c r="H846" t="n">
         <v>116286</v>
@@ -24932,7 +24932,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G847" t="n">
-        <v>80.0622329711914</v>
+        <v>80.0622482299805</v>
       </c>
       <c r="H847" t="n">
         <v>87670</v>
@@ -24961,7 +24961,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G848" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4869918823242</v>
       </c>
       <c r="H848" t="n">
         <v>104300</v>
@@ -25019,7 +25019,7 @@
         <v>89.5</v>
       </c>
       <c r="G850" t="n">
-        <v>82.2683181762695</v>
+        <v>82.2683258056641</v>
       </c>
       <c r="H850" t="n">
         <v>211859</v>
@@ -25048,7 +25048,7 @@
         <v>89.9000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>82.6359939575195</v>
+        <v>82.635986328125</v>
       </c>
       <c r="H851" t="n">
         <v>95610</v>
@@ -25077,7 +25077,7 @@
         <v>90</v>
       </c>
       <c r="G852" t="n">
-        <v>82.727897644043</v>
+        <v>82.727912902832</v>
       </c>
       <c r="H852" t="n">
         <v>97652</v>
@@ -25135,7 +25135,7 @@
         <v>91.5</v>
       </c>
       <c r="G854" t="n">
-        <v>84.1066970825195</v>
+        <v>84.1067123413086</v>
       </c>
       <c r="H854" t="n">
         <v>90352</v>
@@ -25193,7 +25193,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G856" t="n">
-        <v>87.8294677734375</v>
+        <v>87.829475402832</v>
       </c>
       <c r="H856" t="n">
         <v>153602</v>
@@ -25251,7 +25251,7 @@
         <v>97.4000015258789</v>
       </c>
       <c r="G858" t="n">
-        <v>89.5299987792969</v>
+        <v>89.5299911499023</v>
       </c>
       <c r="H858" t="n">
         <v>151572</v>
@@ -25338,7 +25338,7 @@
         <v>97.5</v>
       </c>
       <c r="G861" t="n">
-        <v>90.457763671875</v>
+        <v>90.4577560424805</v>
       </c>
       <c r="H861" t="n">
         <v>91444</v>
@@ -25367,7 +25367,7 @@
         <v>96.8499984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>89.8547134399414</v>
+        <v>89.8547058105469</v>
       </c>
       <c r="H862" t="n">
         <v>74155</v>
@@ -25425,7 +25425,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>88.9269332885742</v>
+        <v>88.9269256591797</v>
       </c>
       <c r="H864" t="n">
         <v>34520</v>
@@ -25512,7 +25512,7 @@
         <v>93.9499969482422</v>
       </c>
       <c r="G867" t="n">
-        <v>87.1641616821289</v>
+        <v>87.1641693115234</v>
       </c>
       <c r="H867" t="n">
         <v>57035</v>
@@ -25570,7 +25570,7 @@
         <v>95.3000030517578</v>
       </c>
       <c r="G869" t="n">
-        <v>88.4166564941406</v>
+        <v>88.4166641235352</v>
       </c>
       <c r="H869" t="n">
         <v>177997</v>
@@ -25599,7 +25599,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>89.6691513061523</v>
+        <v>89.6691589355469</v>
       </c>
       <c r="H870" t="n">
         <v>197967</v>
@@ -25628,7 +25628,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G871" t="n">
-        <v>90.2722091674805</v>
+        <v>90.272216796875</v>
       </c>
       <c r="H871" t="n">
         <v>173154</v>
@@ -25657,7 +25657,7 @@
         <v>98.5</v>
       </c>
       <c r="G872" t="n">
-        <v>91.3855285644531</v>
+        <v>91.3855361938477</v>
       </c>
       <c r="H872" t="n">
         <v>105393</v>
@@ -25686,7 +25686,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>93.797737121582</v>
+        <v>93.7977447509766</v>
       </c>
       <c r="H873" t="n">
         <v>182843</v>
@@ -25744,7 +25744,7 @@
         <v>98.5</v>
       </c>
       <c r="G875" t="n">
-        <v>91.3855285644531</v>
+        <v>91.3855361938477</v>
       </c>
       <c r="H875" t="n">
         <v>346930</v>
@@ -25802,7 +25802,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G877" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H877" t="n">
         <v>157366</v>
@@ -25831,7 +25831,7 @@
         <v>103.5</v>
       </c>
       <c r="G878" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H878" t="n">
         <v>247114</v>
@@ -25918,7 +25918,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G881" t="n">
-        <v>96.859375</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H881" t="n">
         <v>280147</v>
@@ -25976,7 +25976,7 @@
         <v>102.5</v>
       </c>
       <c r="G883" t="n">
-        <v>95.0966110229492</v>
+        <v>95.0966262817383</v>
       </c>
       <c r="H883" t="n">
         <v>256349</v>
@@ -26121,7 +26121,7 @@
         <v>102.099998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>94.7255020141602</v>
+        <v>94.7255172729492</v>
       </c>
       <c r="H888" t="n">
         <v>120137</v>
@@ -26208,7 +26208,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G891" t="n">
-        <v>97.6943817138672</v>
+        <v>97.6943893432617</v>
       </c>
       <c r="H891" t="n">
         <v>134615</v>
@@ -26237,7 +26237,7 @@
         <v>104</v>
       </c>
       <c r="G892" t="n">
-        <v>96.48828125</v>
+        <v>96.4882736206055</v>
       </c>
       <c r="H892" t="n">
         <v>83587</v>
@@ -26266,7 +26266,7 @@
         <v>103</v>
       </c>
       <c r="G893" t="n">
-        <v>95.5605163574219</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H893" t="n">
         <v>66201</v>
@@ -26324,7 +26324,7 @@
         <v>102.800003051758</v>
       </c>
       <c r="G895" t="n">
-        <v>95.3749618530273</v>
+        <v>95.3749542236328</v>
       </c>
       <c r="H895" t="n">
         <v>100438</v>
@@ -26353,7 +26353,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G896" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H896" t="n">
         <v>87631</v>
@@ -26411,7 +26411,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H898" t="n">
         <v>64823</v>
@@ -26440,7 +26440,7 @@
         <v>103</v>
       </c>
       <c r="G899" t="n">
-        <v>95.5605163574219</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H899" t="n">
         <v>49645</v>
@@ -26469,7 +26469,7 @@
         <v>101.800003051758</v>
       </c>
       <c r="G900" t="n">
-        <v>94.4471740722656</v>
+        <v>94.4471817016602</v>
       </c>
       <c r="H900" t="n">
         <v>114464</v>
@@ -26527,7 +26527,7 @@
         <v>102.5</v>
       </c>
       <c r="G902" t="n">
-        <v>95.0966110229492</v>
+        <v>95.0966262817383</v>
       </c>
       <c r="H902" t="n">
         <v>60591</v>
@@ -26556,7 +26556,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G903" t="n">
-        <v>93.9833068847656</v>
+        <v>93.9832992553711</v>
       </c>
       <c r="H903" t="n">
         <v>64496</v>
@@ -26585,7 +26585,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G904" t="n">
-        <v>95.2821731567383</v>
+        <v>95.2821655273438</v>
       </c>
       <c r="H904" t="n">
         <v>63705</v>
@@ -26643,7 +26643,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G906" t="n">
-        <v>94.0760726928711</v>
+        <v>94.0760803222656</v>
       </c>
       <c r="H906" t="n">
         <v>114741</v>
@@ -26730,7 +26730,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>95.0038375854492</v>
+        <v>95.0038528442383</v>
       </c>
       <c r="H909" t="n">
         <v>87642</v>
@@ -26759,7 +26759,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G910" t="n">
-        <v>93.9833068847656</v>
+        <v>93.9832992553711</v>
       </c>
       <c r="H910" t="n">
         <v>229110</v>
@@ -26817,7 +26817,7 @@
         <v>108</v>
       </c>
       <c r="G912" t="n">
-        <v>100.199363708496</v>
+        <v>100.199378967285</v>
       </c>
       <c r="H912" t="n">
         <v>154537</v>
@@ -26962,7 +26962,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G917" t="n">
-        <v>99.921028137207</v>
+        <v>99.9210357666016</v>
       </c>
       <c r="H917" t="n">
         <v>127807</v>
@@ -26991,7 +26991,7 @@
         <v>106.5</v>
       </c>
       <c r="G918" t="n">
-        <v>98.8077087402344</v>
+        <v>98.8077163696289</v>
       </c>
       <c r="H918" t="n">
         <v>120718</v>
@@ -27049,7 +27049,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G920" t="n">
-        <v>98.0654907226562</v>
+        <v>98.0654830932617</v>
       </c>
       <c r="H920" t="n">
         <v>97185</v>
@@ -27107,7 +27107,7 @@
         <v>106</v>
       </c>
       <c r="G922" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H922" t="n">
         <v>79480</v>
@@ -27136,7 +27136,7 @@
         <v>108.300003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>100.477699279785</v>
+        <v>100.47770690918</v>
       </c>
       <c r="H923" t="n">
         <v>125584</v>
@@ -27165,7 +27165,7 @@
         <v>108.099998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>100.292152404785</v>
+        <v>100.292137145996</v>
       </c>
       <c r="H924" t="n">
         <v>67236</v>
@@ -27194,7 +27194,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G925" t="n">
-        <v>101.869361877441</v>
+        <v>101.869354248047</v>
       </c>
       <c r="H925" t="n">
         <v>82352</v>
@@ -27223,7 +27223,7 @@
         <v>109</v>
       </c>
       <c r="G926" t="n">
-        <v>101.127128601074</v>
+        <v>101.127143859863</v>
       </c>
       <c r="H926" t="n">
         <v>61146</v>
@@ -27252,7 +27252,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G927" t="n">
-        <v>98.1582717895508</v>
+        <v>98.1582641601562</v>
       </c>
       <c r="H927" t="n">
         <v>215221</v>
@@ -27310,7 +27310,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>99.921028137207</v>
+        <v>99.9210357666016</v>
       </c>
       <c r="H929" t="n">
         <v>92387</v>
@@ -27339,7 +27339,7 @@
         <v>106.5</v>
       </c>
       <c r="G930" t="n">
-        <v>98.8077087402344</v>
+        <v>98.8077163696289</v>
       </c>
       <c r="H930" t="n">
         <v>90528</v>
@@ -27368,7 +27368,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G931" t="n">
-        <v>99.828254699707</v>
+        <v>99.8282470703125</v>
       </c>
       <c r="H931" t="n">
         <v>120053</v>
@@ -27397,7 +27397,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G932" t="n">
-        <v>99.921028137207</v>
+        <v>99.9210357666016</v>
       </c>
       <c r="H932" t="n">
         <v>95300</v>
@@ -27542,7 +27542,7 @@
         <v>106.199996948242</v>
       </c>
       <c r="G937" t="n">
-        <v>98.5293807983398</v>
+        <v>98.5293731689453</v>
       </c>
       <c r="H937" t="n">
         <v>184635</v>
@@ -27629,7 +27629,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G940" t="n">
-        <v>94.9110717773438</v>
+        <v>94.9110641479492</v>
       </c>
       <c r="H940" t="n">
         <v>272397</v>
@@ -27687,7 +27687,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G942" t="n">
-        <v>95.0038375854492</v>
+        <v>95.0038528442383</v>
       </c>
       <c r="H942" t="n">
         <v>140833</v>
@@ -27803,7 +27803,7 @@
         <v>106</v>
       </c>
       <c r="G946" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H946" t="n">
         <v>144699</v>
@@ -27832,7 +27832,7 @@
         <v>104.800003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>97.2304916381836</v>
+        <v>97.2304992675781</v>
       </c>
       <c r="H947" t="n">
         <v>105910</v>
@@ -27861,7 +27861,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G948" t="n">
-        <v>96.859375</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H948" t="n">
         <v>58835</v>
@@ -27890,7 +27890,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G949" t="n">
-        <v>99.0860443115234</v>
+        <v>99.0860366821289</v>
       </c>
       <c r="H949" t="n">
         <v>112018</v>
@@ -28006,7 +28006,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G953" t="n">
-        <v>98.9932632446289</v>
+        <v>98.9932556152344</v>
       </c>
       <c r="H953" t="n">
         <v>107796</v>
@@ -28035,7 +28035,7 @@
         <v>105.400001525879</v>
       </c>
       <c r="G954" t="n">
-        <v>97.7871704101562</v>
+        <v>97.7871627807617</v>
       </c>
       <c r="H954" t="n">
         <v>147656</v>
@@ -28122,7 +28122,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G957" t="n">
-        <v>98.9932632446289</v>
+        <v>98.9932556152344</v>
       </c>
       <c r="H957" t="n">
         <v>166516</v>
@@ -28151,7 +28151,7 @@
         <v>106</v>
       </c>
       <c r="G958" t="n">
-        <v>98.3438186645508</v>
+        <v>98.3438339233398</v>
       </c>
       <c r="H958" t="n">
         <v>202867</v>
@@ -28180,7 +28180,7 @@
         <v>99.9000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>92.6844100952148</v>
+        <v>92.6844024658203</v>
       </c>
       <c r="H959" t="n">
         <v>476496</v>
@@ -28238,7 +28238,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G961" t="n">
-        <v>92.1277465820312</v>
+        <v>92.1277542114258</v>
       </c>
       <c r="H961" t="n">
         <v>113845</v>
@@ -28325,7 +28325,7 @@
         <v>99.75</v>
       </c>
       <c r="G964" t="n">
-        <v>92.5452499389648</v>
+        <v>92.5452423095703</v>
       </c>
       <c r="H964" t="n">
         <v>117390</v>
@@ -28441,7 +28441,7 @@
         <v>96.9499969482422</v>
       </c>
       <c r="G968" t="n">
-        <v>89.9474868774414</v>
+        <v>89.9474792480469</v>
       </c>
       <c r="H968" t="n">
         <v>145555</v>
@@ -28499,7 +28499,7 @@
         <v>96.5999984741211</v>
       </c>
       <c r="G970" t="n">
-        <v>89.6227569580078</v>
+        <v>89.6227722167969</v>
       </c>
       <c r="H970" t="n">
         <v>108199</v>
@@ -28528,7 +28528,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>90.5969314575195</v>
+        <v>90.5969390869141</v>
       </c>
       <c r="H971" t="n">
         <v>91441</v>
@@ -28586,7 +28586,7 @@
         <v>97.3499984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>90.3185882568359</v>
+        <v>90.3185958862305</v>
       </c>
       <c r="H973" t="n">
         <v>106448</v>
@@ -28615,7 +28615,7 @@
         <v>98.5500030517578</v>
       </c>
       <c r="G974" t="n">
-        <v>91.4319152832031</v>
+        <v>91.4319229125977</v>
       </c>
       <c r="H974" t="n">
         <v>135210</v>
@@ -28644,7 +28644,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G975" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H975" t="n">
         <v>180644</v>
@@ -28702,7 +28702,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>93.797737121582</v>
+        <v>93.7977447509766</v>
       </c>
       <c r="H977" t="n">
         <v>61642</v>
@@ -28731,7 +28731,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G978" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H978" t="n">
         <v>85549</v>
@@ -28760,7 +28760,7 @@
         <v>100.300003051758</v>
       </c>
       <c r="G979" t="n">
-        <v>93.055534362793</v>
+        <v>93.0555267333984</v>
       </c>
       <c r="H979" t="n">
         <v>135989</v>
@@ -28876,7 +28876,7 @@
         <v>103.5</v>
       </c>
       <c r="G983" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H983" t="n">
         <v>123220</v>
@@ -28905,7 +28905,7 @@
         <v>103.599998474121</v>
       </c>
       <c r="G984" t="n">
-        <v>96.1171646118164</v>
+        <v>96.1171798706055</v>
       </c>
       <c r="H984" t="n">
         <v>142262</v>
@@ -28934,7 +28934,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G985" t="n">
-        <v>98.9004898071289</v>
+        <v>98.9004821777344</v>
       </c>
       <c r="H985" t="n">
         <v>152430</v>
@@ -28963,7 +28963,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G986" t="n">
-        <v>101.219909667969</v>
+        <v>101.219917297363</v>
       </c>
       <c r="H986" t="n">
         <v>313302</v>
@@ -28992,7 +28992,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G987" t="n">
-        <v>102.704345703125</v>
+        <v>102.70435333252</v>
       </c>
       <c r="H987" t="n">
         <v>195641</v>
@@ -29050,7 +29050,7 @@
         <v>114.5</v>
       </c>
       <c r="G989" t="n">
-        <v>106.229888916016</v>
+        <v>106.229881286621</v>
       </c>
       <c r="H989" t="n">
         <v>207841</v>
@@ -29079,7 +29079,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>105.673225402832</v>
+        <v>105.673233032227</v>
       </c>
       <c r="H990" t="n">
         <v>252377</v>
@@ -29137,7 +29137,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G992" t="n">
-        <v>110.49764251709</v>
+        <v>110.497634887695</v>
       </c>
       <c r="H992" t="n">
         <v>336887</v>
@@ -29166,7 +29166,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G993" t="n">
-        <v>110.49764251709</v>
+        <v>110.497634887695</v>
       </c>
       <c r="H993" t="n">
         <v>190913</v>
@@ -29195,7 +29195,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G994" t="n">
-        <v>111.703735351562</v>
+        <v>111.703742980957</v>
       </c>
       <c r="H994" t="n">
         <v>169221</v>
@@ -29253,7 +29253,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G996" t="n">
-        <v>111.425399780273</v>
+        <v>111.425415039062</v>
       </c>
       <c r="H996" t="n">
         <v>122685</v>
@@ -29369,7 +29369,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G1000" t="n">
-        <v>113.837600708008</v>
+        <v>113.837608337402</v>
       </c>
       <c r="H1000" t="n">
         <v>300033</v>
@@ -29427,7 +29427,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G1002" t="n">
-        <v>114.85816192627</v>
+        <v>114.858169555664</v>
       </c>
       <c r="H1002" t="n">
         <v>113540</v>
@@ -29456,7 +29456,7 @@
         <v>122</v>
       </c>
       <c r="G1003" t="n">
-        <v>113.188179016113</v>
+        <v>113.188171386719</v>
       </c>
       <c r="H1003" t="n">
         <v>152129</v>
@@ -29485,7 +29485,7 @@
         <v>122</v>
       </c>
       <c r="G1004" t="n">
-        <v>113.188179016113</v>
+        <v>113.188171386719</v>
       </c>
       <c r="H1004" t="n">
         <v>164174</v>
@@ -29514,7 +29514,7 @@
         <v>121</v>
       </c>
       <c r="G1005" t="n">
-        <v>112.260414123535</v>
+        <v>112.260406494141</v>
       </c>
       <c r="H1005" t="n">
         <v>82885</v>
@@ -29543,7 +29543,7 @@
         <v>120</v>
       </c>
       <c r="G1006" t="n">
-        <v>111.332626342773</v>
+        <v>111.332618713379</v>
       </c>
       <c r="H1006" t="n">
         <v>171715</v>
@@ -29572,7 +29572,7 @@
         <v>116</v>
       </c>
       <c r="G1007" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1007" t="n">
         <v>205478</v>
@@ -29601,7 +29601,7 @@
         <v>117.699996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>109.198753356934</v>
+        <v>109.198760986328</v>
       </c>
       <c r="H1008" t="n">
         <v>113611</v>
@@ -29630,7 +29630,7 @@
         <v>117</v>
       </c>
       <c r="G1009" t="n">
-        <v>108.549301147461</v>
+        <v>108.549308776855</v>
       </c>
       <c r="H1009" t="n">
         <v>147068</v>
@@ -29659,7 +29659,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1010" t="n">
-        <v>108.270980834961</v>
+        <v>108.270973205566</v>
       </c>
       <c r="H1010" t="n">
         <v>91707</v>
@@ -29688,7 +29688,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1011" t="n">
-        <v>109.105972290039</v>
+        <v>109.105964660645</v>
       </c>
       <c r="H1011" t="n">
         <v>118695</v>
@@ -29775,7 +29775,7 @@
         <v>116</v>
       </c>
       <c r="G1014" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1014" t="n">
         <v>126846</v>
@@ -29862,7 +29862,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1017" t="n">
-        <v>107.807075500488</v>
+        <v>107.807090759277</v>
       </c>
       <c r="H1017" t="n">
         <v>83294</v>
@@ -29891,7 +29891,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>106.50821685791</v>
+        <v>106.508224487305</v>
       </c>
       <c r="H1018" t="n">
         <v>93251</v>
@@ -29978,7 +29978,7 @@
         <v>119.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>110.868743896484</v>
+        <v>110.86873626709</v>
       </c>
       <c r="H1021" t="n">
         <v>83655</v>
@@ -30036,7 +30036,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1023" t="n">
-        <v>108.270980834961</v>
+        <v>108.270973205566</v>
       </c>
       <c r="H1023" t="n">
         <v>157652</v>
@@ -30065,7 +30065,7 @@
         <v>115.800003051758</v>
       </c>
       <c r="G1024" t="n">
-        <v>107.435989379883</v>
+        <v>107.435997009277</v>
       </c>
       <c r="H1024" t="n">
         <v>279546</v>
@@ -30094,7 +30094,7 @@
         <v>117</v>
       </c>
       <c r="G1025" t="n">
-        <v>108.549301147461</v>
+        <v>108.549308776855</v>
       </c>
       <c r="H1025" t="n">
         <v>142080</v>
@@ -30152,7 +30152,7 @@
         <v>116.900001525879</v>
       </c>
       <c r="G1027" t="n">
-        <v>108.456535339355</v>
+        <v>108.45654296875</v>
       </c>
       <c r="H1027" t="n">
         <v>134188</v>
@@ -30181,7 +30181,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1028" t="n">
-        <v>106.50821685791</v>
+        <v>106.508224487305</v>
       </c>
       <c r="H1028" t="n">
         <v>114599</v>
@@ -30210,7 +30210,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>106.044319152832</v>
+        <v>106.044326782227</v>
       </c>
       <c r="H1029" t="n">
         <v>142027</v>
@@ -30239,7 +30239,7 @@
         <v>115.800003051758</v>
       </c>
       <c r="G1030" t="n">
-        <v>107.435989379883</v>
+        <v>107.435997009277</v>
       </c>
       <c r="H1030" t="n">
         <v>133213</v>
@@ -30268,7 +30268,7 @@
         <v>114.099998474121</v>
       </c>
       <c r="G1031" t="n">
-        <v>105.858772277832</v>
+        <v>105.858764648438</v>
       </c>
       <c r="H1031" t="n">
         <v>134155</v>
@@ -30326,7 +30326,7 @@
         <v>112.599998474121</v>
       </c>
       <c r="G1033" t="n">
-        <v>104.467124938965</v>
+        <v>104.467109680176</v>
       </c>
       <c r="H1033" t="n">
         <v>133869</v>
@@ -30384,7 +30384,7 @@
         <v>115.599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>107.250434875488</v>
+        <v>107.250427246094</v>
       </c>
       <c r="H1035" t="n">
         <v>79387</v>
@@ -30413,7 +30413,7 @@
         <v>113.199996948242</v>
       </c>
       <c r="G1036" t="n">
-        <v>105.023773193359</v>
+        <v>105.023780822754</v>
       </c>
       <c r="H1036" t="n">
         <v>82899</v>
@@ -30471,7 +30471,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>103.817672729492</v>
+        <v>103.817680358887</v>
       </c>
       <c r="H1038" t="n">
         <v>118544</v>
@@ -30500,7 +30500,7 @@
         <v>114</v>
       </c>
       <c r="G1039" t="n">
-        <v>105.765998840332</v>
+        <v>105.765991210938</v>
       </c>
       <c r="H1039" t="n">
         <v>100652</v>
@@ -30558,7 +30558,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1041" t="n">
-        <v>106.50821685791</v>
+        <v>106.508224487305</v>
       </c>
       <c r="H1041" t="n">
         <v>270734</v>
@@ -30587,7 +30587,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1042" t="n">
-        <v>106.044319152832</v>
+        <v>106.044326782227</v>
       </c>
       <c r="H1042" t="n">
         <v>76827</v>
@@ -30616,7 +30616,7 @@
         <v>114.699996948242</v>
       </c>
       <c r="G1043" t="n">
-        <v>106.415435791016</v>
+        <v>106.415428161621</v>
       </c>
       <c r="H1043" t="n">
         <v>54246</v>
@@ -30645,7 +30645,7 @@
         <v>116</v>
       </c>
       <c r="G1044" t="n">
-        <v>107.621543884277</v>
+        <v>107.621536254883</v>
       </c>
       <c r="H1044" t="n">
         <v>152525</v>
@@ -30674,7 +30674,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>106.50821685791</v>
+        <v>106.508224487305</v>
       </c>
       <c r="H1045" t="n">
         <v>108233</v>
@@ -30703,7 +30703,7 @@
         <v>114.599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>106.322647094727</v>
+        <v>106.322654724121</v>
       </c>
       <c r="H1046" t="n">
         <v>99356</v>
@@ -30790,7 +30790,7 @@
         <v>120.900001525879</v>
       </c>
       <c r="G1049" t="n">
-        <v>112.167625427246</v>
+        <v>112.167633056641</v>
       </c>
       <c r="H1049" t="n">
         <v>253057</v>
@@ -30877,7 +30877,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>107.899864196777</v>
+        <v>107.899879455566</v>
       </c>
       <c r="H1052" t="n">
         <v>119025</v>
@@ -30993,7 +30993,7 @@
         <v>106.199996948242</v>
       </c>
       <c r="G1056" t="n">
-        <v>98.5293807983398</v>
+        <v>98.5293731689453</v>
       </c>
       <c r="H1056" t="n">
         <v>286763</v>
@@ -31022,7 +31022,7 @@
         <v>102.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>95.0966110229492</v>
+        <v>95.0966262817383</v>
       </c>
       <c r="H1057" t="n">
         <v>355146</v>
@@ -31051,7 +31051,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G1058" t="n">
-        <v>94.9110717773438</v>
+        <v>94.9110641479492</v>
       </c>
       <c r="H1058" t="n">
         <v>235831</v>
@@ -31080,7 +31080,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G1059" t="n">
-        <v>97.6943817138672</v>
+        <v>97.6943893432617</v>
       </c>
       <c r="H1059" t="n">
         <v>294872</v>
@@ -31138,7 +31138,7 @@
         <v>104.5</v>
       </c>
       <c r="G1061" t="n">
-        <v>96.9521560668945</v>
+        <v>96.9521636962891</v>
       </c>
       <c r="H1061" t="n">
         <v>141963</v>
@@ -31225,7 +31225,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>96.859375</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H1064" t="n">
         <v>945948</v>
@@ -31254,7 +31254,7 @@
         <v>113</v>
       </c>
       <c r="G1065" t="n">
-        <v>104.838226318359</v>
+        <v>104.838218688965</v>
       </c>
       <c r="H1065" t="n">
         <v>732508</v>
@@ -31283,7 +31283,7 @@
         <v>103</v>
       </c>
       <c r="G1066" t="n">
-        <v>95.5605163574219</v>
+        <v>95.5605087280273</v>
       </c>
       <c r="H1066" t="n">
         <v>656130</v>
@@ -31312,7 +31312,7 @@
         <v>109.599998474121</v>
       </c>
       <c r="G1067" t="n">
-        <v>101.683807373047</v>
+        <v>101.683799743652</v>
       </c>
       <c r="H1067" t="n">
         <v>690760</v>
@@ -31341,7 +31341,7 @@
         <v>107.800003051758</v>
       </c>
       <c r="G1068" t="n">
-        <v>100.013801574707</v>
+        <v>100.013809204102</v>
       </c>
       <c r="H1068" t="n">
         <v>729991</v>
@@ -31399,7 +31399,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>99.0860443115234</v>
+        <v>99.0860366821289</v>
       </c>
       <c r="H1070" t="n">
         <v>216222</v>
@@ -31486,7 +31486,7 @@
         <v>116.800003051758</v>
       </c>
       <c r="G1073" t="n">
-        <v>108.363754272461</v>
+        <v>108.363761901855</v>
       </c>
       <c r="H1073" t="n">
         <v>409710</v>
@@ -31515,7 +31515,7 @@
         <v>115.199996948242</v>
       </c>
       <c r="G1074" t="n">
-        <v>106.879325866699</v>
+        <v>106.879318237305</v>
       </c>
       <c r="H1074" t="n">
         <v>401583</v>
@@ -31544,7 +31544,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1075" t="n">
-        <v>104.55989074707</v>
+        <v>104.559883117676</v>
       </c>
       <c r="H1075" t="n">
         <v>436837</v>
@@ -31747,7 +31747,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1082" t="n">
-        <v>109.105972290039</v>
+        <v>109.105964660645</v>
       </c>
       <c r="H1082" t="n">
         <v>167694</v>
@@ -31776,7 +31776,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>109.569854736328</v>
+        <v>109.569847106934</v>
       </c>
       <c r="H1083" t="n">
         <v>144071</v>
@@ -31805,7 +31805,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G1084" t="n">
-        <v>115.878707885742</v>
+        <v>115.878715515137</v>
       </c>
       <c r="H1084" t="n">
         <v>503694</v>
@@ -31863,7 +31863,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1086" t="n">
-        <v>123.764755249023</v>
+        <v>123.764762878418</v>
       </c>
       <c r="H1086" t="n">
         <v>341308</v>
@@ -31921,7 +31921,7 @@
         <v>149.800003051758</v>
       </c>
       <c r="G1088" t="n">
-        <v>138.980239868164</v>
+        <v>138.980255126953</v>
       </c>
       <c r="H1088" t="n">
         <v>518157</v>
@@ -31950,7 +31950,7 @@
         <v>150.100006103516</v>
       </c>
       <c r="G1089" t="n">
-        <v>139.258544921875</v>
+        <v>139.258560180664</v>
       </c>
       <c r="H1089" t="n">
         <v>581970</v>
@@ -31979,7 +31979,7 @@
         <v>144.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>134.063049316406</v>
+        <v>134.063034057617</v>
       </c>
       <c r="H1090" t="n">
         <v>962667</v>
@@ -32008,7 +32008,7 @@
         <v>153.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>142.412994384766</v>
+        <v>142.413009643555</v>
       </c>
       <c r="H1091" t="n">
         <v>430197</v>
@@ -32095,7 +32095,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1094" t="n">
-        <v>147.608489990234</v>
+        <v>147.608505249023</v>
       </c>
       <c r="H1094" t="n">
         <v>583928</v>
@@ -32124,7 +32124,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1095" t="n">
-        <v>150.855697631836</v>
+        <v>150.855712890625</v>
       </c>
       <c r="H1095" t="n">
         <v>300403</v>
@@ -32153,7 +32153,7 @@
         <v>166.899993896484</v>
       </c>
       <c r="G1096" t="n">
-        <v>154.845123291016</v>
+        <v>154.845108032227</v>
       </c>
       <c r="H1096" t="n">
         <v>292389</v>
@@ -32182,7 +32182,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1097" t="n">
-        <v>155.030685424805</v>
+        <v>155.030700683594</v>
       </c>
       <c r="H1097" t="n">
         <v>282090</v>
@@ -32211,7 +32211,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1098" t="n">
-        <v>150.484603881836</v>
+        <v>150.484588623047</v>
       </c>
       <c r="H1098" t="n">
         <v>263041</v>
@@ -32269,7 +32269,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1100" t="n">
-        <v>144.175750732422</v>
+        <v>144.175765991211</v>
       </c>
       <c r="H1100" t="n">
         <v>232643</v>
@@ -32298,7 +32298,7 @@
         <v>155</v>
       </c>
       <c r="G1101" t="n">
-        <v>143.804641723633</v>
+        <v>143.804626464844</v>
       </c>
       <c r="H1101" t="n">
         <v>165262</v>
@@ -32356,7 +32356,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1103" t="n">
-        <v>143.619094848633</v>
+        <v>143.619079589844</v>
       </c>
       <c r="H1103" t="n">
         <v>130241</v>
@@ -32443,7 +32443,7 @@
         <v>160.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>148.907409667969</v>
+        <v>148.90739440918</v>
       </c>
       <c r="H1106" t="n">
         <v>258847</v>
@@ -32530,7 +32530,7 @@
         <v>184.199996948242</v>
       </c>
       <c r="G1109" t="n">
-        <v>170.895584106445</v>
+        <v>170.895568847656</v>
       </c>
       <c r="H1109" t="n">
         <v>355559</v>
@@ -32617,7 +32617,7 @@
         <v>189.199996948242</v>
       </c>
       <c r="G1112" t="n">
-        <v>175.534439086914</v>
+        <v>175.534454345703</v>
       </c>
       <c r="H1112" t="n">
         <v>486038</v>
@@ -32675,7 +32675,7 @@
         <v>202.800003051758</v>
       </c>
       <c r="G1114" t="n">
-        <v>188.152145385742</v>
+        <v>188.152160644531</v>
       </c>
       <c r="H1114" t="n">
         <v>552568</v>
@@ -32704,7 +32704,7 @@
         <v>209.399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>194.275436401367</v>
+        <v>194.275421142578</v>
       </c>
       <c r="H1115" t="n">
         <v>446507</v>
@@ -32733,7 +32733,7 @@
         <v>197</v>
       </c>
       <c r="G1116" t="n">
-        <v>182.771057128906</v>
+        <v>182.771072387695</v>
       </c>
       <c r="H1116" t="n">
         <v>684856</v>
@@ -32762,7 +32762,7 @@
         <v>173</v>
       </c>
       <c r="G1117" t="n">
-        <v>160.50456237793</v>
+        <v>160.504547119141</v>
       </c>
       <c r="H1117" t="n">
         <v>1004392</v>
@@ -32878,7 +32878,7 @@
         <v>178.899993896484</v>
       </c>
       <c r="G1121" t="n">
-        <v>165.978378295898</v>
+        <v>165.978393554688</v>
       </c>
       <c r="H1121" t="n">
         <v>418839</v>
@@ -32907,7 +32907,7 @@
         <v>173.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>160.968414306641</v>
+        <v>160.968444824219</v>
       </c>
       <c r="H1122" t="n">
         <v>549848</v>
@@ -32936,7 +32936,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1123" t="n">
-        <v>161.617858886719</v>
+        <v>161.617889404297</v>
       </c>
       <c r="H1123" t="n">
         <v>528586</v>
@@ -32994,7 +32994,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G1125" t="n">
-        <v>148.072402954102</v>
+        <v>148.072418212891</v>
       </c>
       <c r="H1125" t="n">
         <v>584751</v>
@@ -33052,7 +33052,7 @@
         <v>164</v>
       </c>
       <c r="G1127" t="n">
-        <v>152.154602050781</v>
+        <v>152.154586791992</v>
       </c>
       <c r="H1127" t="n">
         <v>361385</v>
@@ -33110,7 +33110,7 @@
         <v>167</v>
       </c>
       <c r="G1129" t="n">
-        <v>154.937911987305</v>
+        <v>154.937896728516</v>
       </c>
       <c r="H1129" t="n">
         <v>331932</v>
@@ -33168,7 +33168,7 @@
         <v>170.800003051758</v>
       </c>
       <c r="G1131" t="n">
-        <v>159.370025634766</v>
+        <v>159.370040893555</v>
       </c>
       <c r="H1131" t="n">
         <v>304851</v>
@@ -33226,7 +33226,7 @@
         <v>169.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>158.157028198242</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1133" t="n">
         <v>188475</v>
@@ -33284,7 +33284,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1135" t="n">
-        <v>159.276748657227</v>
+        <v>159.276733398438</v>
       </c>
       <c r="H1135" t="n">
         <v>311897</v>
@@ -33313,7 +33313,7 @@
         <v>175.800003051758</v>
       </c>
       <c r="G1136" t="n">
-        <v>164.035446166992</v>
+        <v>164.035430908203</v>
       </c>
       <c r="H1136" t="n">
         <v>319931</v>
@@ -33371,7 +33371,7 @@
         <v>173</v>
       </c>
       <c r="G1138" t="n">
-        <v>161.422821044922</v>
+        <v>161.422805786133</v>
       </c>
       <c r="H1138" t="n">
         <v>266304</v>
@@ -33603,7 +33603,7 @@
         <v>178.5</v>
       </c>
       <c r="G1146" t="n">
-        <v>166.554763793945</v>
+        <v>166.554748535156</v>
       </c>
       <c r="H1146" t="n">
         <v>235569</v>
@@ -33632,7 +33632,7 @@
         <v>179.199996948242</v>
       </c>
       <c r="G1147" t="n">
-        <v>167.207916259766</v>
+        <v>167.207901000977</v>
       </c>
       <c r="H1147" t="n">
         <v>155301</v>
@@ -33661,7 +33661,7 @@
         <v>171.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>160.023193359375</v>
+        <v>160.023178100586</v>
       </c>
       <c r="H1148" t="n">
         <v>273837</v>
@@ -33719,7 +33719,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1150" t="n">
-        <v>162.075958251953</v>
+        <v>162.075942993164</v>
       </c>
       <c r="H1150" t="n">
         <v>162432</v>
@@ -33777,7 +33777,7 @@
         <v>175.800003051758</v>
       </c>
       <c r="G1152" t="n">
-        <v>164.035446166992</v>
+        <v>164.035430908203</v>
       </c>
       <c r="H1152" t="n">
         <v>180746</v>
@@ -33835,7 +33835,7 @@
         <v>178.199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>166.274841308594</v>
+        <v>166.274826049805</v>
       </c>
       <c r="H1154" t="n">
         <v>124171</v>
@@ -33922,7 +33922,7 @@
         <v>175</v>
       </c>
       <c r="G1157" t="n">
-        <v>163.288955688477</v>
+        <v>163.288940429688</v>
       </c>
       <c r="H1157" t="n">
         <v>250110</v>
@@ -33951,7 +33951,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1158" t="n">
-        <v>157.970428466797</v>
+        <v>157.970443725586</v>
       </c>
       <c r="H1158" t="n">
         <v>446703</v>
@@ -34009,7 +34009,7 @@
         <v>170.800003051758</v>
       </c>
       <c r="G1160" t="n">
-        <v>159.370025634766</v>
+        <v>159.370040893555</v>
       </c>
       <c r="H1160" t="n">
         <v>161960</v>
@@ -34038,7 +34038,7 @@
         <v>170.600006103516</v>
       </c>
       <c r="G1161" t="n">
-        <v>159.18342590332</v>
+        <v>159.183441162109</v>
       </c>
       <c r="H1161" t="n">
         <v>116037</v>
@@ -34183,7 +34183,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G1166" t="n">
-        <v>149.852615356445</v>
+        <v>149.852630615234</v>
       </c>
       <c r="H1166" t="n">
         <v>203712</v>
@@ -34212,7 +34212,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G1167" t="n">
-        <v>147.053375244141</v>
+        <v>147.05339050293</v>
       </c>
       <c r="H1167" t="n">
         <v>387121</v>
@@ -34241,7 +34241,7 @@
         <v>154.399993896484</v>
       </c>
       <c r="G1168" t="n">
-        <v>144.067520141602</v>
+        <v>144.067504882812</v>
       </c>
       <c r="H1168" t="n">
         <v>195140</v>
@@ -34270,7 +34270,7 @@
         <v>158.600006103516</v>
       </c>
       <c r="G1169" t="n">
-        <v>147.986480712891</v>
+        <v>147.986465454102</v>
       </c>
       <c r="H1169" t="n">
         <v>133127</v>
@@ -34299,7 +34299,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>142.574600219727</v>
+        <v>142.574615478516</v>
       </c>
       <c r="H1170" t="n">
         <v>182163</v>
@@ -34328,7 +34328,7 @@
         <v>157.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>146.960067749023</v>
+        <v>146.960083007812</v>
       </c>
       <c r="H1171" t="n">
         <v>181402</v>
@@ -34357,7 +34357,7 @@
         <v>160.199996948242</v>
       </c>
       <c r="G1172" t="n">
-        <v>149.479400634766</v>
+        <v>149.479385375977</v>
       </c>
       <c r="H1172" t="n">
         <v>133270</v>
@@ -34444,7 +34444,7 @@
         <v>162.800003051758</v>
       </c>
       <c r="G1175" t="n">
-        <v>151.905395507812</v>
+        <v>151.905380249023</v>
       </c>
       <c r="H1175" t="n">
         <v>138035</v>
@@ -34473,7 +34473,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1176" t="n">
-        <v>148.453002929688</v>
+        <v>148.453018188477</v>
       </c>
       <c r="H1176" t="n">
         <v>116736</v>
@@ -34502,7 +34502,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1177" t="n">
-        <v>151.34553527832</v>
+        <v>151.345520019531</v>
       </c>
       <c r="H1177" t="n">
         <v>111771</v>
@@ -34531,7 +34531,7 @@
         <v>162.899993896484</v>
       </c>
       <c r="G1178" t="n">
-        <v>151.99870300293</v>
+        <v>151.998687744141</v>
       </c>
       <c r="H1178" t="n">
         <v>102684</v>
@@ -34560,7 +34560,7 @@
         <v>163</v>
       </c>
       <c r="G1179" t="n">
-        <v>152.091995239258</v>
+        <v>152.092010498047</v>
       </c>
       <c r="H1179" t="n">
         <v>117685</v>
@@ -34589,7 +34589,7 @@
         <v>163.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>152.558547973633</v>
+        <v>152.558563232422</v>
       </c>
       <c r="H1180" t="n">
         <v>137900</v>
@@ -34647,7 +34647,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1182" t="n">
-        <v>156.477462768555</v>
+        <v>156.477478027344</v>
       </c>
       <c r="H1182" t="n">
         <v>150389</v>
@@ -34705,7 +34705,7 @@
         <v>145.800003051758</v>
       </c>
       <c r="G1184" t="n">
-        <v>136.043060302734</v>
+        <v>136.043075561523</v>
       </c>
       <c r="H1184" t="n">
         <v>460285</v>
@@ -34792,7 +34792,7 @@
         <v>151</v>
       </c>
       <c r="G1187" t="n">
-        <v>140.895065307617</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1187" t="n">
         <v>125409</v>
@@ -34821,7 +34821,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G1188" t="n">
-        <v>133.057189941406</v>
+        <v>133.057205200195</v>
       </c>
       <c r="H1188" t="n">
         <v>237378</v>
@@ -34850,7 +34850,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G1189" t="n">
-        <v>132.310745239258</v>
+        <v>132.310729980469</v>
       </c>
       <c r="H1189" t="n">
         <v>212656</v>
@@ -34937,7 +34937,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G1192" t="n">
-        <v>142.108062744141</v>
+        <v>142.108047485352</v>
       </c>
       <c r="H1192" t="n">
         <v>482399</v>
@@ -34966,7 +34966,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G1193" t="n">
-        <v>140.615112304688</v>
+        <v>140.615142822266</v>
       </c>
       <c r="H1193" t="n">
         <v>173029</v>
@@ -34995,7 +34995,7 @@
         <v>154.699996948242</v>
       </c>
       <c r="G1194" t="n">
-        <v>144.347457885742</v>
+        <v>144.347442626953</v>
       </c>
       <c r="H1194" t="n">
         <v>131020</v>
@@ -35082,7 +35082,7 @@
         <v>160.899993896484</v>
       </c>
       <c r="G1197" t="n">
-        <v>150.132537841797</v>
+        <v>150.132522583008</v>
       </c>
       <c r="H1197" t="n">
         <v>252082</v>
@@ -35111,7 +35111,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1198" t="n">
-        <v>147.613204956055</v>
+        <v>147.613220214844</v>
       </c>
       <c r="H1198" t="n">
         <v>101347</v>
@@ -35169,7 +35169,7 @@
         <v>169.399993896484</v>
       </c>
       <c r="G1200" t="n">
-        <v>158.063720703125</v>
+        <v>158.063735961914</v>
       </c>
       <c r="H1200" t="n">
         <v>546780</v>
@@ -35227,7 +35227,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1202" t="n">
-        <v>157.970428466797</v>
+        <v>157.970443725586</v>
       </c>
       <c r="H1202" t="n">
         <v>215161</v>
@@ -35256,7 +35256,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>156.477462768555</v>
+        <v>156.477478027344</v>
       </c>
       <c r="H1203" t="n">
         <v>158623</v>
@@ -35285,7 +35285,7 @@
         <v>170.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>159.090103149414</v>
+        <v>159.090118408203</v>
       </c>
       <c r="H1204" t="n">
         <v>199198</v>
@@ -35314,7 +35314,7 @@
         <v>170.199996948242</v>
       </c>
       <c r="G1205" t="n">
-        <v>158.810195922852</v>
+        <v>158.810180664062</v>
       </c>
       <c r="H1205" t="n">
         <v>146129</v>
@@ -35546,7 +35546,7 @@
         <v>182.5</v>
       </c>
       <c r="G1213" t="n">
-        <v>170.287094116211</v>
+        <v>170.287078857422</v>
       </c>
       <c r="H1213" t="n">
         <v>180435</v>
@@ -35604,7 +35604,7 @@
         <v>190.100006103516</v>
       </c>
       <c r="G1215" t="n">
-        <v>177.378494262695</v>
+        <v>177.378479003906</v>
       </c>
       <c r="H1215" t="n">
         <v>149173</v>
@@ -35633,7 +35633,7 @@
         <v>187.5</v>
       </c>
       <c r="G1216" t="n">
-        <v>174.95246887207</v>
+        <v>174.952453613281</v>
       </c>
       <c r="H1216" t="n">
         <v>125251</v>
@@ -35662,7 +35662,7 @@
         <v>191.300003051758</v>
       </c>
       <c r="G1217" t="n">
-        <v>178.498168945312</v>
+        <v>178.498184204102</v>
       </c>
       <c r="H1217" t="n">
         <v>183967</v>
@@ -35691,7 +35691,7 @@
         <v>189</v>
       </c>
       <c r="G1218" t="n">
-        <v>176.352096557617</v>
+        <v>176.352081298828</v>
       </c>
       <c r="H1218" t="n">
         <v>203551</v>
@@ -35894,7 +35894,7 @@
         <v>189</v>
       </c>
       <c r="G1225" t="n">
-        <v>176.352096557617</v>
+        <v>176.352081298828</v>
       </c>
       <c r="H1225" t="n">
         <v>159604</v>
@@ -35952,7 +35952,7 @@
         <v>188.600006103516</v>
       </c>
       <c r="G1227" t="n">
-        <v>175.978881835938</v>
+        <v>175.978866577148</v>
       </c>
       <c r="H1227" t="n">
         <v>269042</v>
@@ -35981,7 +35981,7 @@
         <v>187.300003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>174.765853881836</v>
+        <v>174.765838623047</v>
       </c>
       <c r="H1228" t="n">
         <v>154872</v>
@@ -36068,7 +36068,7 @@
         <v>187.100006103516</v>
       </c>
       <c r="G1231" t="n">
-        <v>174.579238891602</v>
+        <v>174.57926940918</v>
       </c>
       <c r="H1231" t="n">
         <v>175470</v>
@@ -36155,7 +36155,7 @@
         <v>201.199996948242</v>
       </c>
       <c r="G1234" t="n">
-        <v>187.735656738281</v>
+        <v>187.73567199707</v>
       </c>
       <c r="H1234" t="n">
         <v>192061</v>
@@ -36242,7 +36242,7 @@
         <v>172.399993896484</v>
       </c>
       <c r="G1237" t="n">
-        <v>160.862976074219</v>
+        <v>160.86296081543</v>
       </c>
       <c r="H1237" t="n">
         <v>458040</v>
@@ -36271,7 +36271,7 @@
         <v>173</v>
       </c>
       <c r="G1238" t="n">
-        <v>161.422821044922</v>
+        <v>161.422805786133</v>
       </c>
       <c r="H1238" t="n">
         <v>275182</v>
@@ -36358,7 +36358,7 @@
         <v>173.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>161.88932800293</v>
+        <v>161.889358520508</v>
       </c>
       <c r="H1241" t="n">
         <v>276931</v>
@@ -36416,7 +36416,7 @@
         <v>172.600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>161.049606323242</v>
+        <v>161.049591064453</v>
       </c>
       <c r="H1243" t="n">
         <v>312144</v>
@@ -36445,7 +36445,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1244" t="n">
-        <v>162.075958251953</v>
+        <v>162.075942993164</v>
       </c>
       <c r="H1244" t="n">
         <v>161137</v>
@@ -36474,7 +36474,7 @@
         <v>173.5</v>
       </c>
       <c r="G1245" t="n">
-        <v>161.88932800293</v>
+        <v>161.889358520508</v>
       </c>
       <c r="H1245" t="n">
         <v>211014</v>
@@ -36590,7 +36590,7 @@
         <v>172.800003051758</v>
       </c>
       <c r="G1249" t="n">
-        <v>161.236190795898</v>
+        <v>161.236175537109</v>
       </c>
       <c r="H1249" t="n">
         <v>221273</v>
@@ -36735,7 +36735,7 @@
         <v>168.399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>157.130615234375</v>
+        <v>157.130645751953</v>
       </c>
       <c r="H1254" t="n">
         <v>168573</v>
@@ -36822,7 +36822,7 @@
         <v>168.5</v>
       </c>
       <c r="G1257" t="n">
-        <v>157.22395324707</v>
+        <v>157.223968505859</v>
       </c>
       <c r="H1257" t="n">
         <v>141131</v>
@@ -36880,7 +36880,7 @@
         <v>170.5</v>
       </c>
       <c r="G1259" t="n">
-        <v>159.090103149414</v>
+        <v>159.090118408203</v>
       </c>
       <c r="H1259" t="n">
         <v>151664</v>
@@ -36909,7 +36909,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1260" t="n">
-        <v>159.276748657227</v>
+        <v>159.276733398438</v>
       </c>
       <c r="H1260" t="n">
         <v>157128</v>
@@ -36967,7 +36967,7 @@
         <v>166.699996948242</v>
       </c>
       <c r="G1262" t="n">
-        <v>155.544403076172</v>
+        <v>155.544372558594</v>
       </c>
       <c r="H1262" t="n">
         <v>174714</v>
@@ -36996,7 +36996,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1263" t="n">
-        <v>155.91764831543</v>
+        <v>155.917663574219</v>
       </c>
       <c r="H1263" t="n">
         <v>126302</v>
@@ -37025,7 +37025,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1264" t="n">
-        <v>159.276748657227</v>
+        <v>159.276733398438</v>
       </c>
       <c r="H1264" t="n">
         <v>230245</v>
@@ -37054,7 +37054,7 @@
         <v>171.699996948242</v>
       </c>
       <c r="G1265" t="n">
-        <v>160.209823608398</v>
+        <v>160.209808349609</v>
       </c>
       <c r="H1265" t="n">
         <v>179244</v>
@@ -37083,7 +37083,7 @@
         <v>170.199996948242</v>
       </c>
       <c r="G1266" t="n">
-        <v>158.810195922852</v>
+        <v>158.810180664062</v>
       </c>
       <c r="H1266" t="n">
         <v>104034</v>
@@ -37199,7 +37199,7 @@
         <v>170.100006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>158.716873168945</v>
+        <v>158.716888427734</v>
       </c>
       <c r="H1270" t="n">
         <v>144762</v>
@@ -37257,7 +37257,7 @@
         <v>168.5</v>
       </c>
       <c r="G1272" t="n">
-        <v>157.22395324707</v>
+        <v>157.223968505859</v>
       </c>
       <c r="H1272" t="n">
         <v>122959</v>
@@ -37315,7 +37315,7 @@
         <v>160.800003051758</v>
       </c>
       <c r="G1274" t="n">
-        <v>150.039245605469</v>
+        <v>150.03923034668</v>
       </c>
       <c r="H1274" t="n">
         <v>204826</v>
@@ -37489,7 +37489,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>151.718780517578</v>
+        <v>151.718795776367</v>
       </c>
       <c r="H1280" t="n">
         <v>185002</v>
@@ -37605,7 +37605,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1284" t="n">
-        <v>162.075958251953</v>
+        <v>162.075942993164</v>
       </c>
       <c r="H1284" t="n">
         <v>157579</v>
@@ -37634,7 +37634,7 @@
         <v>175</v>
       </c>
       <c r="G1285" t="n">
-        <v>163.288955688477</v>
+        <v>163.288940429688</v>
       </c>
       <c r="H1285" t="n">
         <v>135763</v>
@@ -37808,7 +37808,7 @@
         <v>180</v>
       </c>
       <c r="G1291" t="n">
-        <v>167.954345703125</v>
+        <v>167.954376220703</v>
       </c>
       <c r="H1291" t="n">
         <v>201666</v>
@@ -37837,7 +37837,7 @@
         <v>179.399993896484</v>
       </c>
       <c r="G1292" t="n">
-        <v>167.394515991211</v>
+        <v>167.39453125</v>
       </c>
       <c r="H1292" t="n">
         <v>187484</v>
@@ -37895,7 +37895,7 @@
         <v>176.199996948242</v>
       </c>
       <c r="G1294" t="n">
-        <v>164.408645629883</v>
+        <v>164.408660888672</v>
       </c>
       <c r="H1294" t="n">
         <v>132358</v>
@@ -37924,7 +37924,7 @@
         <v>179.100006103516</v>
       </c>
       <c r="G1295" t="n">
-        <v>167.114608764648</v>
+        <v>167.114593505859</v>
       </c>
       <c r="H1295" t="n">
         <v>134646</v>
@@ -38040,7 +38040,7 @@
         <v>184.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>172.153244018555</v>
+        <v>172.153228759766</v>
       </c>
       <c r="H1299" t="n">
         <v>101763</v>
@@ -38127,7 +38127,7 @@
         <v>186.399993896484</v>
       </c>
       <c r="G1302" t="n">
-        <v>173.926086425781</v>
+        <v>173.92610168457</v>
       </c>
       <c r="H1302" t="n">
         <v>85448</v>
@@ -38214,7 +38214,7 @@
         <v>169.5</v>
       </c>
       <c r="G1305" t="n">
-        <v>158.157028198242</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1305" t="n">
         <v>234314</v>
@@ -38243,7 +38243,7 @@
         <v>164.300003051758</v>
       </c>
       <c r="G1306" t="n">
-        <v>153.304992675781</v>
+        <v>153.30500793457</v>
       </c>
       <c r="H1306" t="n">
         <v>212617</v>
@@ -38301,7 +38301,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1308" t="n">
-        <v>147.613204956055</v>
+        <v>147.613220214844</v>
       </c>
       <c r="H1308" t="n">
         <v>193734</v>
@@ -38330,7 +38330,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1309" t="n">
-        <v>153.118408203125</v>
+        <v>153.118392944336</v>
       </c>
       <c r="H1309" t="n">
         <v>351753</v>
@@ -38359,7 +38359,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1310" t="n">
-        <v>151.532150268555</v>
+        <v>151.532165527344</v>
       </c>
       <c r="H1310" t="n">
         <v>218095</v>
@@ -38388,7 +38388,7 @@
         <v>164</v>
       </c>
       <c r="G1311" t="n">
-        <v>153.025100708008</v>
+        <v>153.025085449219</v>
       </c>
       <c r="H1311" t="n">
         <v>236766</v>
@@ -38475,7 +38475,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1314" t="n">
-        <v>153.118408203125</v>
+        <v>153.118392944336</v>
       </c>
       <c r="H1314" t="n">
         <v>159342</v>
@@ -38678,7 +38678,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1321" t="n">
-        <v>132.590637207031</v>
+        <v>132.590621948242</v>
       </c>
       <c r="H1321" t="n">
         <v>295438</v>
@@ -38707,7 +38707,7 @@
         <v>145.899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>136.136352539062</v>
+        <v>136.136337280273</v>
       </c>
       <c r="H1322" t="n">
         <v>350628</v>
@@ -38736,7 +38736,7 @@
         <v>142</v>
       </c>
       <c r="G1323" t="n">
-        <v>132.497344970703</v>
+        <v>132.497329711914</v>
       </c>
       <c r="H1323" t="n">
         <v>223928</v>
@@ -38794,7 +38794,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>133.523727416992</v>
+        <v>133.523712158203</v>
       </c>
       <c r="H1325" t="n">
         <v>319389</v>
@@ -38852,7 +38852,7 @@
         <v>141</v>
       </c>
       <c r="G1327" t="n">
-        <v>131.564254760742</v>
+        <v>131.564270019531</v>
       </c>
       <c r="H1327" t="n">
         <v>210537</v>
@@ -38910,7 +38910,7 @@
         <v>142.300003051758</v>
       </c>
       <c r="G1329" t="n">
-        <v>132.777252197266</v>
+        <v>132.777267456055</v>
       </c>
       <c r="H1329" t="n">
         <v>161218</v>
@@ -38968,7 +38968,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>128.111862182617</v>
+        <v>128.111846923828</v>
       </c>
       <c r="H1331" t="n">
         <v>287517</v>
@@ -38997,7 +38997,7 @@
         <v>137.699996948242</v>
       </c>
       <c r="G1332" t="n">
-        <v>128.485107421875</v>
+        <v>128.485092163086</v>
       </c>
       <c r="H1332" t="n">
         <v>167009</v>
@@ -39026,7 +39026,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G1333" t="n">
-        <v>127.645317077637</v>
+        <v>127.645332336426</v>
       </c>
       <c r="H1333" t="n">
         <v>148192</v>
@@ -39113,7 +39113,7 @@
         <v>140.149993896484</v>
       </c>
       <c r="G1336" t="n">
-        <v>130.771148681641</v>
+        <v>130.771133422852</v>
       </c>
       <c r="H1336" t="n">
         <v>193898</v>
@@ -39200,7 +39200,7 @@
         <v>153.050003051758</v>
       </c>
       <c r="G1339" t="n">
-        <v>142.807876586914</v>
+        <v>142.807861328125</v>
       </c>
       <c r="H1339" t="n">
         <v>892150</v>
@@ -39229,7 +39229,7 @@
         <v>151.050003051758</v>
       </c>
       <c r="G1340" t="n">
-        <v>140.941711425781</v>
+        <v>140.94172668457</v>
       </c>
       <c r="H1340" t="n">
         <v>259903</v>
@@ -39287,7 +39287,7 @@
         <v>151</v>
       </c>
       <c r="G1342" t="n">
-        <v>140.895065307617</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1342" t="n">
         <v>192282</v>
@@ -39345,7 +39345,7 @@
         <v>154.399993896484</v>
       </c>
       <c r="G1344" t="n">
-        <v>144.067520141602</v>
+        <v>144.067504882812</v>
       </c>
       <c r="H1344" t="n">
         <v>181842</v>
@@ -39403,7 +39403,7 @@
         <v>155.75</v>
       </c>
       <c r="G1346" t="n">
-        <v>145.327194213867</v>
+        <v>145.327178955078</v>
       </c>
       <c r="H1346" t="n">
         <v>159518</v>
@@ -39461,7 +39461,7 @@
         <v>152.550003051758</v>
       </c>
       <c r="G1348" t="n">
-        <v>142.341323852539</v>
+        <v>142.341339111328</v>
       </c>
       <c r="H1348" t="n">
         <v>115078</v>
@@ -39519,7 +39519,7 @@
         <v>144.100006103516</v>
       </c>
       <c r="G1350" t="n">
-        <v>134.456817626953</v>
+        <v>134.456802368164</v>
       </c>
       <c r="H1350" t="n">
         <v>415633</v>
@@ -39548,7 +39548,7 @@
         <v>143.899993896484</v>
       </c>
       <c r="G1351" t="n">
-        <v>134.27018737793</v>
+        <v>134.270202636719</v>
       </c>
       <c r="H1351" t="n">
         <v>449860</v>
@@ -39606,7 +39606,7 @@
         <v>141.25</v>
       </c>
       <c r="G1353" t="n">
-        <v>131.79753112793</v>
+        <v>131.797515869141</v>
       </c>
       <c r="H1353" t="n">
         <v>160312</v>
@@ -39635,7 +39635,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1354" t="n">
-        <v>131.424285888672</v>
+        <v>131.424301147461</v>
       </c>
       <c r="H1354" t="n">
         <v>111270</v>
@@ -39664,7 +39664,7 @@
         <v>137.699996948242</v>
       </c>
       <c r="G1355" t="n">
-        <v>128.485107421875</v>
+        <v>128.485092163086</v>
       </c>
       <c r="H1355" t="n">
         <v>200790</v>
@@ -39693,7 +39693,7 @@
         <v>141.199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>131.750869750977</v>
+        <v>131.750885009766</v>
       </c>
       <c r="H1356" t="n">
         <v>146704</v>
@@ -39780,7 +39780,7 @@
         <v>142.649993896484</v>
       </c>
       <c r="G1359" t="n">
-        <v>133.10383605957</v>
+        <v>133.103820800781</v>
       </c>
       <c r="H1359" t="n">
         <v>234905</v>
@@ -39809,7 +39809,7 @@
         <v>138.25</v>
       </c>
       <c r="G1360" t="n">
-        <v>128.998260498047</v>
+        <v>128.998291015625</v>
       </c>
       <c r="H1360" t="n">
         <v>369459</v>
@@ -39896,7 +39896,7 @@
         <v>138</v>
       </c>
       <c r="G1363" t="n">
-        <v>128.765029907227</v>
+        <v>128.764999389648</v>
       </c>
       <c r="H1363" t="n">
         <v>226020</v>
@@ -39925,7 +39925,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>131.424285888672</v>
+        <v>131.424301147461</v>
       </c>
       <c r="H1364" t="n">
         <v>267732</v>
@@ -39983,7 +39983,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1366" t="n">
-        <v>132.590637207031</v>
+        <v>132.590621948242</v>
       </c>
       <c r="H1366" t="n">
         <v>140516</v>
@@ -40012,7 +40012,7 @@
         <v>144</v>
       </c>
       <c r="G1367" t="n">
-        <v>134.363494873047</v>
+        <v>134.363479614258</v>
       </c>
       <c r="H1367" t="n">
         <v>182501</v>
@@ -40070,7 +40070,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1369" t="n">
-        <v>134.456481933594</v>
+        <v>134.456466674805</v>
       </c>
       <c r="H1369" t="n">
         <v>99816</v>
@@ -40186,7 +40186,7 @@
         <v>144.25</v>
       </c>
       <c r="G1373" t="n">
-        <v>135.537002563477</v>
+        <v>135.537017822266</v>
       </c>
       <c r="H1373" t="n">
         <v>159915</v>
@@ -40447,7 +40447,7 @@
         <v>145.399993896484</v>
       </c>
       <c r="G1382" t="n">
-        <v>136.617538452148</v>
+        <v>136.617553710938</v>
       </c>
       <c r="H1382" t="n">
         <v>204702</v>
@@ -40534,7 +40534,7 @@
         <v>150.449996948242</v>
       </c>
       <c r="G1385" t="n">
-        <v>141.362518310547</v>
+        <v>141.362503051758</v>
       </c>
       <c r="H1385" t="n">
         <v>163765</v>
@@ -40563,7 +40563,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1386" t="n">
-        <v>143.570571899414</v>
+        <v>143.570587158203</v>
       </c>
       <c r="H1386" t="n">
         <v>163521</v>
@@ -40621,7 +40621,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>144.604125976562</v>
+        <v>144.604110717773</v>
       </c>
       <c r="H1388" t="n">
         <v>291658</v>
@@ -40766,7 +40766,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1393" t="n">
-        <v>146.671264648438</v>
+        <v>146.671249389648</v>
       </c>
       <c r="H1393" t="n">
         <v>119203</v>
@@ -40824,7 +40824,7 @@
         <v>159.899993896484</v>
       </c>
       <c r="G1395" t="n">
-        <v>150.241729736328</v>
+        <v>150.241714477539</v>
       </c>
       <c r="H1395" t="n">
         <v>150338</v>
@@ -40853,7 +40853,7 @@
         <v>159.5</v>
       </c>
       <c r="G1396" t="n">
-        <v>149.865875244141</v>
+        <v>149.86589050293</v>
       </c>
       <c r="H1396" t="n">
         <v>208336</v>
@@ -40940,7 +40940,7 @@
         <v>156.600006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>147.141052246094</v>
+        <v>147.141067504883</v>
       </c>
       <c r="H1399" t="n">
         <v>129050</v>
@@ -40998,7 +40998,7 @@
         <v>163.300003051758</v>
       </c>
       <c r="G1401" t="n">
-        <v>153.436340332031</v>
+        <v>153.43635559082</v>
       </c>
       <c r="H1401" t="n">
         <v>158512</v>
@@ -41027,7 +41027,7 @@
         <v>159.199996948242</v>
       </c>
       <c r="G1402" t="n">
-        <v>149.583984375</v>
+        <v>149.583999633789</v>
       </c>
       <c r="H1402" t="n">
         <v>139339</v>
@@ -41056,7 +41056,7 @@
         <v>160.649993896484</v>
       </c>
       <c r="G1403" t="n">
-        <v>150.946395874023</v>
+        <v>150.946411132812</v>
       </c>
       <c r="H1403" t="n">
         <v>129314</v>
@@ -41085,7 +41085,7 @@
         <v>162.050003051758</v>
       </c>
       <c r="G1404" t="n">
-        <v>152.261856079102</v>
+        <v>152.261871337891</v>
       </c>
       <c r="H1404" t="n">
         <v>212038</v>
@@ -41143,7 +41143,7 @@
         <v>161.949996948242</v>
       </c>
       <c r="G1406" t="n">
-        <v>152.167892456055</v>
+        <v>152.167907714844</v>
       </c>
       <c r="H1406" t="n">
         <v>99690</v>
@@ -41230,7 +41230,7 @@
         <v>166</v>
       </c>
       <c r="G1409" t="n">
-        <v>155.973281860352</v>
+        <v>155.973266601562</v>
       </c>
       <c r="H1409" t="n">
         <v>167042</v>
@@ -41259,7 +41259,7 @@
         <v>167.300003051758</v>
       </c>
       <c r="G1410" t="n">
-        <v>157.194763183594</v>
+        <v>157.194747924805</v>
       </c>
       <c r="H1410" t="n">
         <v>201939</v>
@@ -41346,7 +41346,7 @@
         <v>172.350006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>161.939727783203</v>
+        <v>161.939712524414</v>
       </c>
       <c r="H1413" t="n">
         <v>141959</v>
@@ -41433,7 +41433,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1416" t="n">
-        <v>159.355834960938</v>
+        <v>159.355850219727</v>
       </c>
       <c r="H1416" t="n">
         <v>97378</v>
@@ -41491,7 +41491,7 @@
         <v>171.149993896484</v>
       </c>
       <c r="G1418" t="n">
-        <v>160.812194824219</v>
+        <v>160.81217956543</v>
       </c>
       <c r="H1418" t="n">
         <v>260602</v>
@@ -41520,7 +41520,7 @@
         <v>176.449996948242</v>
       </c>
       <c r="G1419" t="n">
-        <v>165.792083740234</v>
+        <v>165.792068481445</v>
       </c>
       <c r="H1419" t="n">
         <v>223351</v>
@@ -41636,7 +41636,7 @@
         <v>173.449996948242</v>
       </c>
       <c r="G1423" t="n">
-        <v>162.973266601562</v>
+        <v>162.973281860352</v>
       </c>
       <c r="H1423" t="n">
         <v>138448</v>
@@ -41665,7 +41665,7 @@
         <v>176.199996948242</v>
       </c>
       <c r="G1424" t="n">
-        <v>165.557174682617</v>
+        <v>165.557159423828</v>
       </c>
       <c r="H1424" t="n">
         <v>142117</v>
@@ -41752,7 +41752,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1427" t="n">
-        <v>168.000152587891</v>
+        <v>168.000137329102</v>
       </c>
       <c r="H1427" t="n">
         <v>109222</v>
@@ -41839,7 +41839,7 @@
         <v>183.899993896484</v>
       </c>
       <c r="G1430" t="n">
-        <v>172.792083740234</v>
+        <v>172.792068481445</v>
       </c>
       <c r="H1430" t="n">
         <v>161127</v>
@@ -41868,7 +41868,7 @@
         <v>184.850006103516</v>
       </c>
       <c r="G1431" t="n">
-        <v>173.684692382812</v>
+        <v>173.684707641602</v>
       </c>
       <c r="H1431" t="n">
         <v>119649</v>
@@ -41955,7 +41955,7 @@
         <v>187.550003051758</v>
       </c>
       <c r="G1434" t="n">
-        <v>176.221588134766</v>
+        <v>176.221603393555</v>
       </c>
       <c r="H1434" t="n">
         <v>124411</v>
@@ -42100,7 +42100,7 @@
         <v>190.899993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>179.369247436523</v>
+        <v>179.369262695312</v>
       </c>
       <c r="H1439" t="n">
         <v>118983</v>
@@ -42245,7 +42245,7 @@
         <v>204.300003051758</v>
       </c>
       <c r="G1444" t="n">
-        <v>191.959869384766</v>
+        <v>191.959854125977</v>
       </c>
       <c r="H1444" t="n">
         <v>176720</v>
@@ -42274,7 +42274,7 @@
         <v>200.199996948242</v>
       </c>
       <c r="G1445" t="n">
-        <v>188.107528686523</v>
+        <v>188.107543945312</v>
       </c>
       <c r="H1445" t="n">
         <v>166966</v>
@@ -42303,7 +42303,7 @@
         <v>205.699996948242</v>
       </c>
       <c r="G1446" t="n">
-        <v>193.275314331055</v>
+        <v>193.275299072266</v>
       </c>
       <c r="H1446" t="n">
         <v>177342</v>
@@ -42361,7 +42361,7 @@
         <v>206.199996948242</v>
       </c>
       <c r="G1448" t="n">
-        <v>193.745101928711</v>
+        <v>193.7451171875</v>
       </c>
       <c r="H1448" t="n">
         <v>113142</v>
@@ -42390,7 +42390,7 @@
         <v>196.699996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>184.818939208984</v>
+        <v>184.818923950195</v>
       </c>
       <c r="H1449" t="n">
         <v>244088</v>
@@ -42477,7 +42477,7 @@
         <v>200.600006103516</v>
       </c>
       <c r="G1452" t="n">
-        <v>188.483367919922</v>
+        <v>188.483352661133</v>
       </c>
       <c r="H1452" t="n">
         <v>69766</v>
@@ -42535,7 +42535,7 @@
         <v>200.199996948242</v>
       </c>
       <c r="G1454" t="n">
-        <v>188.107528686523</v>
+        <v>188.107543945312</v>
       </c>
       <c r="H1454" t="n">
         <v>121231</v>
@@ -42593,7 +42593,7 @@
         <v>204.300003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>191.959869384766</v>
+        <v>191.959854125977</v>
       </c>
       <c r="H1456" t="n">
         <v>124690</v>
@@ -42796,7 +42796,7 @@
         <v>175.149993896484</v>
       </c>
       <c r="G1463" t="n">
-        <v>164.570587158203</v>
+        <v>164.570571899414</v>
       </c>
       <c r="H1463" t="n">
         <v>174108</v>
@@ -42825,7 +42825,7 @@
         <v>171.850006103516</v>
       </c>
       <c r="G1464" t="n">
-        <v>161.469924926758</v>
+        <v>161.469940185547</v>
       </c>
       <c r="H1464" t="n">
         <v>148532</v>
@@ -42970,7 +42970,7 @@
         <v>169.350006103516</v>
       </c>
       <c r="G1469" t="n">
-        <v>159.120956420898</v>
+        <v>159.120941162109</v>
       </c>
       <c r="H1469" t="n">
         <v>124991</v>
@@ -43028,7 +43028,7 @@
         <v>178.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>167.718246459961</v>
+        <v>167.71826171875</v>
       </c>
       <c r="H1471" t="n">
         <v>158372</v>
@@ -43057,7 +43057,7 @@
         <v>178.899993896484</v>
       </c>
       <c r="G1472" t="n">
-        <v>168.094085693359</v>
+        <v>168.09407043457</v>
       </c>
       <c r="H1472" t="n">
         <v>116743</v>
@@ -43086,7 +43086,7 @@
         <v>180.100006103516</v>
       </c>
       <c r="G1473" t="n">
-        <v>169.221633911133</v>
+        <v>169.221618652344</v>
       </c>
       <c r="H1473" t="n">
         <v>104846</v>
@@ -43144,7 +43144,7 @@
         <v>181.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>170.537033081055</v>
+        <v>170.537017822266</v>
       </c>
       <c r="H1475" t="n">
         <v>126077</v>
@@ -43376,7 +43376,7 @@
         <v>195.350006103516</v>
       </c>
       <c r="G1483" t="n">
-        <v>183.550491333008</v>
+        <v>183.550476074219</v>
       </c>
       <c r="H1483" t="n">
         <v>135461</v>
@@ -43434,7 +43434,7 @@
         <v>197.649993896484</v>
       </c>
       <c r="G1485" t="n">
-        <v>185.711532592773</v>
+        <v>185.711547851562</v>
       </c>
       <c r="H1485" t="n">
         <v>93144</v>
@@ -43492,7 +43492,7 @@
         <v>193.050003051758</v>
       </c>
       <c r="G1487" t="n">
-        <v>181.389404296875</v>
+        <v>181.389389038086</v>
       </c>
       <c r="H1487" t="n">
         <v>179393</v>
@@ -43608,7 +43608,7 @@
         <v>183.399993896484</v>
       </c>
       <c r="G1491" t="n">
-        <v>172.322265625</v>
+        <v>172.322280883789</v>
       </c>
       <c r="H1491" t="n">
         <v>147063</v>
@@ -43695,7 +43695,7 @@
         <v>188.949996948242</v>
       </c>
       <c r="G1494" t="n">
-        <v>177.537048339844</v>
+        <v>177.537033081055</v>
       </c>
       <c r="H1494" t="n">
         <v>122784</v>
@@ -43724,7 +43724,7 @@
         <v>191.699996948242</v>
       </c>
       <c r="G1495" t="n">
-        <v>180.12092590332</v>
+        <v>180.120910644531</v>
       </c>
       <c r="H1495" t="n">
         <v>162483</v>
@@ -43840,7 +43840,7 @@
         <v>183.649993896484</v>
       </c>
       <c r="G1499" t="n">
-        <v>172.557159423828</v>
+        <v>172.557174682617</v>
       </c>
       <c r="H1499" t="n">
         <v>126554</v>
@@ -43898,7 +43898,7 @@
         <v>177.449996948242</v>
       </c>
       <c r="G1501" t="n">
-        <v>166.731674194336</v>
+        <v>166.731658935547</v>
       </c>
       <c r="H1501" t="n">
         <v>153592</v>
@@ -43927,7 +43927,7 @@
         <v>177.449996948242</v>
       </c>
       <c r="G1502" t="n">
-        <v>166.731674194336</v>
+        <v>166.731658935547</v>
       </c>
       <c r="H1502" t="n">
         <v>75392</v>
@@ -43956,7 +43956,7 @@
         <v>187.300003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>175.986709594727</v>
+        <v>175.986724853516</v>
       </c>
       <c r="H1503" t="n">
         <v>372294</v>
@@ -44014,7 +44014,7 @@
         <v>188.75</v>
       </c>
       <c r="G1505" t="n">
-        <v>177.349105834961</v>
+        <v>177.34912109375</v>
       </c>
       <c r="H1505" t="n">
         <v>359394</v>
@@ -44130,7 +44130,7 @@
         <v>172.300003051758</v>
       </c>
       <c r="G1509" t="n">
-        <v>161.89274597168</v>
+        <v>161.892761230469</v>
       </c>
       <c r="H1509" t="n">
         <v>139544</v>
@@ -44478,7 +44478,7 @@
         <v>161.850006103516</v>
       </c>
       <c r="G1521" t="n">
-        <v>152.073928833008</v>
+        <v>152.073944091797</v>
       </c>
       <c r="H1521" t="n">
         <v>173529</v>
@@ -44565,7 +44565,7 @@
         <v>166</v>
       </c>
       <c r="G1524" t="n">
-        <v>155.973281860352</v>
+        <v>155.973266601562</v>
       </c>
       <c r="H1524" t="n">
         <v>115654</v>
@@ -44594,7 +44594,7 @@
         <v>165</v>
       </c>
       <c r="G1525" t="n">
-        <v>155.033676147461</v>
+        <v>155.033660888672</v>
       </c>
       <c r="H1525" t="n">
         <v>89536</v>
@@ -44623,7 +44623,7 @@
         <v>167.449996948242</v>
       </c>
       <c r="G1526" t="n">
-        <v>157.335678100586</v>
+        <v>157.335662841797</v>
       </c>
       <c r="H1526" t="n">
         <v>110574</v>
@@ -44710,7 +44710,7 @@
         <v>160.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>150.805465698242</v>
+        <v>150.805480957031</v>
       </c>
       <c r="H1529" t="n">
         <v>187469</v>
@@ -44739,7 +44739,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1530" t="n">
-        <v>146.671264648438</v>
+        <v>146.671249389648</v>
       </c>
       <c r="H1530" t="n">
         <v>220701</v>
@@ -44768,7 +44768,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1531" t="n">
-        <v>145.449783325195</v>
+        <v>145.449768066406</v>
       </c>
       <c r="H1531" t="n">
         <v>146624</v>
@@ -44884,7 +44884,7 @@
         <v>147.699996948242</v>
       </c>
       <c r="G1535" t="n">
-        <v>138.778610229492</v>
+        <v>138.778625488281</v>
       </c>
       <c r="H1535" t="n">
         <v>278272</v>
@@ -44971,7 +44971,7 @@
         <v>143.350006103516</v>
       </c>
       <c r="G1538" t="n">
-        <v>134.691360473633</v>
+        <v>134.691375732422</v>
       </c>
       <c r="H1538" t="n">
         <v>179025</v>
@@ -45029,7 +45029,7 @@
         <v>147</v>
       </c>
       <c r="G1540" t="n">
-        <v>138.12092590332</v>
+        <v>138.120910644531</v>
       </c>
       <c r="H1540" t="n">
         <v>200365</v>
@@ -45116,7 +45116,7 @@
         <v>132.550003051758</v>
       </c>
       <c r="G1543" t="n">
-        <v>124.543724060059</v>
+        <v>124.543716430664</v>
       </c>
       <c r="H1543" t="n">
         <v>238575</v>
@@ -45261,7 +45261,7 @@
         <v>137</v>
       </c>
       <c r="G1548" t="n">
-        <v>128.72492980957</v>
+        <v>128.724914550781</v>
       </c>
       <c r="H1548" t="n">
         <v>108718</v>
@@ -45290,7 +45290,7 @@
         <v>137.899993896484</v>
       </c>
       <c r="G1549" t="n">
-        <v>129.570556640625</v>
+        <v>129.570571899414</v>
       </c>
       <c r="H1549" t="n">
         <v>114556</v>
@@ -45377,7 +45377,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>118.295394897461</v>
+        <v>118.295387268066</v>
       </c>
       <c r="H1552" t="n">
         <v>327942</v>
@@ -45522,7 +45522,7 @@
         <v>119.75</v>
       </c>
       <c r="G1557" t="n">
-        <v>112.516860961914</v>
+        <v>112.516868591309</v>
       </c>
       <c r="H1557" t="n">
         <v>221947</v>
@@ -45638,7 +45638,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1561" t="n">
-        <v>110.21484375</v>
+        <v>110.214851379395</v>
       </c>
       <c r="H1561" t="n">
         <v>208572</v>
@@ -45783,7 +45783,7 @@
         <v>128.350006103516</v>
       </c>
       <c r="G1566" t="n">
-        <v>120.59741973877</v>
+        <v>120.597412109375</v>
       </c>
       <c r="H1566" t="n">
         <v>165776</v>
@@ -45870,7 +45870,7 @@
         <v>129.300003051758</v>
       </c>
       <c r="G1569" t="n">
-        <v>121.490020751953</v>
+        <v>121.490028381348</v>
       </c>
       <c r="H1569" t="n">
         <v>217124</v>
@@ -46102,7 +46102,7 @@
         <v>127.300003051758</v>
       </c>
       <c r="G1577" t="n">
-        <v>119.610832214355</v>
+        <v>119.61083984375</v>
       </c>
       <c r="H1577" t="n">
         <v>113985</v>
@@ -46131,7 +46131,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1578" t="n">
-        <v>118.295394897461</v>
+        <v>118.295387268066</v>
       </c>
       <c r="H1578" t="n">
         <v>103471</v>
@@ -46218,7 +46218,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G1581" t="n">
-        <v>129.852447509766</v>
+        <v>129.852432250977</v>
       </c>
       <c r="H1581" t="n">
         <v>241443</v>
@@ -46247,7 +46247,7 @@
         <v>132.350006103516</v>
       </c>
       <c r="G1582" t="n">
-        <v>124.355812072754</v>
+        <v>124.355819702148</v>
       </c>
       <c r="H1582" t="n">
         <v>141438</v>
@@ -46305,7 +46305,7 @@
         <v>130.850006103516</v>
       </c>
       <c r="G1584" t="n">
-        <v>122.946403503418</v>
+        <v>122.946395874023</v>
       </c>
       <c r="H1584" t="n">
         <v>118635</v>
@@ -46450,7 +46450,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G1589" t="n">
-        <v>133.235000610352</v>
+        <v>133.235015869141</v>
       </c>
       <c r="H1589" t="n">
         <v>119680</v>
@@ -46595,7 +46595,7 @@
         <v>145.25</v>
       </c>
       <c r="G1594" t="n">
-        <v>136.476623535156</v>
+        <v>136.476638793945</v>
       </c>
       <c r="H1594" t="n">
         <v>131151</v>
@@ -46769,7 +46769,7 @@
         <v>134.300003051758</v>
       </c>
       <c r="G1600" t="n">
-        <v>126.188026428223</v>
+        <v>126.188011169434</v>
       </c>
       <c r="H1600" t="n">
         <v>82429</v>
@@ -46827,7 +46827,7 @@
         <v>132.100006103516</v>
       </c>
       <c r="G1602" t="n">
-        <v>124.120910644531</v>
+        <v>124.120895385742</v>
       </c>
       <c r="H1602" t="n">
         <v>105461</v>
@@ -46885,7 +46885,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G1604" t="n">
-        <v>118.765190124512</v>
+        <v>118.765182495117</v>
       </c>
       <c r="H1604" t="n">
         <v>210078</v>
@@ -46972,7 +46972,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G1607" t="n">
-        <v>113.127601623535</v>
+        <v>113.12760925293</v>
       </c>
       <c r="H1607" t="n">
         <v>146131</v>
@@ -47001,7 +47001,7 @@
         <v>123.949996948242</v>
       </c>
       <c r="G1608" t="n">
-        <v>116.463172912598</v>
+        <v>116.463165283203</v>
       </c>
       <c r="H1608" t="n">
         <v>144335</v>
@@ -47117,7 +47117,7 @@
         <v>119.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>112.281967163086</v>
+        <v>112.281959533691</v>
       </c>
       <c r="H1612" t="n">
         <v>160766</v>
@@ -47146,7 +47146,7 @@
         <v>119.949996948242</v>
       </c>
       <c r="G1613" t="n">
-        <v>112.704772949219</v>
+        <v>112.704765319824</v>
       </c>
       <c r="H1613" t="n">
         <v>156486</v>
@@ -47204,7 +47204,7 @@
         <v>114.150001525879</v>
       </c>
       <c r="G1615" t="n">
-        <v>107.255111694336</v>
+        <v>107.25511932373</v>
       </c>
       <c r="H1615" t="n">
         <v>216195</v>
@@ -47349,7 +47349,7 @@
         <v>120</v>
       </c>
       <c r="G1620" t="n">
-        <v>112.751762390137</v>
+        <v>112.751754760742</v>
       </c>
       <c r="H1620" t="n">
         <v>140871</v>
@@ -47407,7 +47407,7 @@
         <v>115.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>108.523574829102</v>
+        <v>108.523567199707</v>
       </c>
       <c r="H1622" t="n">
         <v>130263</v>
@@ -47436,7 +47436,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1623" t="n">
-        <v>110.966522216797</v>
+        <v>110.966514587402</v>
       </c>
       <c r="H1623" t="n">
         <v>121109</v>
@@ -79994,7 +79994,7 @@
         <v>77.1399993896484</v>
       </c>
       <c r="D2746" t="n">
-        <v>79.1999969482422</v>
+        <v>79.5</v>
       </c>
       <c r="E2746" t="n">
         <v>77.0199966430664</v>
@@ -80006,9 +80006,38 @@
         <v>79.5</v>
       </c>
       <c r="H2746" t="n">
-        <v>162377</v>
+        <v>165284</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>82.3000030517578</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>77.8000030517578</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>78.1600036621094</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>78.1600036621094</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>461073</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>49.0900001525879</v>
       </c>
       <c r="G3" t="n">
-        <v>42.4992370605469</v>
+        <v>42.4992332458496</v>
       </c>
       <c r="H3" t="n">
         <v>89363</v>
@@ -485,7 +485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>42.2481727600098</v>
+        <v>42.2481689453125</v>
       </c>
       <c r="H4" t="n">
         <v>42997</v>
@@ -572,7 +572,7 @@
         <v>47.7900009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>41.3737678527832</v>
+        <v>41.3737640380859</v>
       </c>
       <c r="H7" t="n">
         <v>75682</v>
@@ -630,7 +630,7 @@
         <v>47.310001373291</v>
       </c>
       <c r="G9" t="n">
-        <v>40.9582138061523</v>
+        <v>40.9582252502441</v>
       </c>
       <c r="H9" t="n">
         <v>75050</v>
@@ -659,7 +659,7 @@
         <v>46.810001373291</v>
       </c>
       <c r="G10" t="n">
-        <v>40.5253410339355</v>
+        <v>40.5253524780273</v>
       </c>
       <c r="H10" t="n">
         <v>44094</v>
@@ -688,7 +688,7 @@
         <v>45.3499984741211</v>
       </c>
       <c r="G11" t="n">
-        <v>39.2613639831543</v>
+        <v>39.2613563537598</v>
       </c>
       <c r="H11" t="n">
         <v>122604</v>
@@ -746,7 +746,7 @@
         <v>43.1699981689453</v>
       </c>
       <c r="G13" t="n">
-        <v>37.3740425109863</v>
+        <v>37.3740386962891</v>
       </c>
       <c r="H13" t="n">
         <v>176212</v>
@@ -804,7 +804,7 @@
         <v>42.6800003051758</v>
       </c>
       <c r="G15" t="n">
-        <v>36.949836730957</v>
+        <v>36.9498291015625</v>
       </c>
       <c r="H15" t="n">
         <v>170667</v>
@@ -833,7 +833,7 @@
         <v>44.1699981689453</v>
       </c>
       <c r="G16" t="n">
-        <v>38.2397842407227</v>
+        <v>38.2397804260254</v>
       </c>
       <c r="H16" t="n">
         <v>186077</v>
@@ -862,7 +862,7 @@
         <v>45.6399993896484</v>
       </c>
       <c r="G17" t="n">
-        <v>39.5124206542969</v>
+        <v>39.5124244689941</v>
       </c>
       <c r="H17" t="n">
         <v>218430</v>
@@ -891,7 +891,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G18" t="n">
-        <v>40.4993705749512</v>
+        <v>40.4993629455566</v>
       </c>
       <c r="H18" t="n">
         <v>171711</v>
@@ -949,7 +949,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>40.6032638549805</v>
+        <v>40.6032600402832</v>
       </c>
       <c r="H20" t="n">
         <v>145072</v>
@@ -978,7 +978,7 @@
         <v>48.5</v>
       </c>
       <c r="G21" t="n">
-        <v>41.9884414672852</v>
+        <v>41.9884452819824</v>
       </c>
       <c r="H21" t="n">
         <v>102390</v>
@@ -1007,7 +1007,7 @@
         <v>48.8300018310547</v>
       </c>
       <c r="G22" t="n">
-        <v>42.2741432189941</v>
+        <v>42.2741470336914</v>
       </c>
       <c r="H22" t="n">
         <v>142479</v>
@@ -1036,7 +1036,7 @@
         <v>48.75</v>
       </c>
       <c r="G23" t="n">
-        <v>42.2048797607422</v>
+        <v>42.2048835754395</v>
       </c>
       <c r="H23" t="n">
         <v>112008</v>
@@ -1065,7 +1065,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>41.1053924560547</v>
+        <v>41.1053886413574</v>
       </c>
       <c r="H24" t="n">
         <v>118381</v>
@@ -1123,7 +1123,7 @@
         <v>44.689998626709</v>
       </c>
       <c r="G26" t="n">
-        <v>38.6899757385254</v>
+        <v>38.6899681091309</v>
       </c>
       <c r="H26" t="n">
         <v>47084</v>
@@ -1152,7 +1152,7 @@
         <v>42.810001373291</v>
       </c>
       <c r="G27" t="n">
-        <v>37.062385559082</v>
+        <v>37.0623817443848</v>
       </c>
       <c r="H27" t="n">
         <v>79262</v>
@@ -1181,7 +1181,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>37.3134460449219</v>
+        <v>37.3134422302246</v>
       </c>
       <c r="H28" t="n">
         <v>129293</v>
@@ -1239,7 +1239,7 @@
         <v>43.7700004577637</v>
       </c>
       <c r="G30" t="n">
-        <v>37.8934936523438</v>
+        <v>37.893482208252</v>
       </c>
       <c r="H30" t="n">
         <v>96253</v>
@@ -1268,7 +1268,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G31" t="n">
-        <v>37.6943740844727</v>
+        <v>37.6943664550781</v>
       </c>
       <c r="H31" t="n">
         <v>98162</v>
@@ -1297,7 +1297,7 @@
         <v>45.4900016784668</v>
       </c>
       <c r="G32" t="n">
-        <v>39.3825569152832</v>
+        <v>39.3825607299805</v>
       </c>
       <c r="H32" t="n">
         <v>72531</v>
@@ -1355,7 +1355,7 @@
         <v>45.9099998474121</v>
       </c>
       <c r="G34" t="n">
-        <v>39.7461738586426</v>
+        <v>39.7461776733398</v>
       </c>
       <c r="H34" t="n">
         <v>76568</v>
@@ -1413,7 +1413,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G36" t="n">
-        <v>40.4993705749512</v>
+        <v>40.4993629455566</v>
       </c>
       <c r="H36" t="n">
         <v>62588</v>
@@ -1442,7 +1442,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="G37" t="n">
-        <v>41.7633514404297</v>
+        <v>41.7633476257324</v>
       </c>
       <c r="H37" t="n">
         <v>101109</v>
@@ -1471,7 +1471,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G38" t="n">
-        <v>41.1659889221191</v>
+        <v>41.1659927368164</v>
       </c>
       <c r="H38" t="n">
         <v>78199</v>
@@ -1500,7 +1500,7 @@
         <v>48.2900009155273</v>
       </c>
       <c r="G39" t="n">
-        <v>41.8066444396973</v>
+        <v>41.806640625</v>
       </c>
       <c r="H39" t="n">
         <v>92020</v>
@@ -1529,7 +1529,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G40" t="n">
-        <v>42.4126586914062</v>
+        <v>42.4126625061035</v>
       </c>
       <c r="H40" t="n">
         <v>70387</v>
@@ -1587,7 +1587,7 @@
         <v>48.6399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>42.1096420288086</v>
+        <v>42.1096534729004</v>
       </c>
       <c r="H42" t="n">
         <v>26989</v>
@@ -1616,7 +1616,7 @@
         <v>49.0099983215332</v>
       </c>
       <c r="G43" t="n">
-        <v>42.4299774169922</v>
+        <v>42.4299697875977</v>
       </c>
       <c r="H43" t="n">
         <v>93647</v>
@@ -1703,7 +1703,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>41.8585777282715</v>
+        <v>41.858585357666</v>
       </c>
       <c r="H46" t="n">
         <v>41036</v>
@@ -1732,7 +1732,7 @@
         <v>48.4199981689453</v>
       </c>
       <c r="G47" t="n">
-        <v>41.9191780090332</v>
+        <v>41.9191856384277</v>
       </c>
       <c r="H47" t="n">
         <v>52500</v>
@@ -1761,7 +1761,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G48" t="n">
-        <v>41.9711303710938</v>
+        <v>41.9711265563965</v>
       </c>
       <c r="H48" t="n">
         <v>46637</v>
@@ -1790,7 +1790,7 @@
         <v>46.2099990844727</v>
       </c>
       <c r="G49" t="n">
-        <v>40.0059013366699</v>
+        <v>40.0058975219727</v>
       </c>
       <c r="H49" t="n">
         <v>135834</v>
@@ -1819,7 +1819,7 @@
         <v>45.75</v>
       </c>
       <c r="G50" t="n">
-        <v>39.6076583862305</v>
+        <v>39.6076622009277</v>
       </c>
       <c r="H50" t="n">
         <v>108080</v>
@@ -1848,7 +1848,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>39.2700157165527</v>
+        <v>39.2700119018555</v>
       </c>
       <c r="H51" t="n">
         <v>118250</v>
@@ -1877,7 +1877,7 @@
         <v>46.6699981689453</v>
       </c>
       <c r="G52" t="n">
-        <v>40.4041404724121</v>
+        <v>40.4041442871094</v>
       </c>
       <c r="H52" t="n">
         <v>59686</v>
@@ -1906,7 +1906,7 @@
         <v>46</v>
       </c>
       <c r="G53" t="n">
-        <v>39.824089050293</v>
+        <v>39.8240928649902</v>
       </c>
       <c r="H53" t="n">
         <v>39106</v>
@@ -1935,7 +1935,7 @@
         <v>45.5299987792969</v>
       </c>
       <c r="G54" t="n">
-        <v>39.4171943664551</v>
+        <v>39.4171905517578</v>
       </c>
       <c r="H54" t="n">
         <v>51747</v>
@@ -1964,7 +1964,7 @@
         <v>44.9199981689453</v>
       </c>
       <c r="G55" t="n">
-        <v>38.889087677002</v>
+        <v>38.8890914916992</v>
       </c>
       <c r="H55" t="n">
         <v>53754</v>
@@ -1993,7 +1993,7 @@
         <v>45.4799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>39.373908996582</v>
+        <v>39.3739051818848</v>
       </c>
       <c r="H56" t="n">
         <v>99139</v>
@@ -2022,7 +2022,7 @@
         <v>45.6800003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>39.5470542907715</v>
+        <v>39.5470504760742</v>
       </c>
       <c r="H57" t="n">
         <v>62232</v>
@@ -2051,7 +2051,7 @@
         <v>45.1699981689453</v>
       </c>
       <c r="G58" t="n">
-        <v>39.1055221557617</v>
+        <v>39.105525970459</v>
       </c>
       <c r="H58" t="n">
         <v>71459</v>
@@ -2109,7 +2109,7 @@
         <v>45.5</v>
       </c>
       <c r="G60" t="n">
-        <v>39.3912200927734</v>
+        <v>39.3912239074707</v>
       </c>
       <c r="H60" t="n">
         <v>58510</v>
@@ -2138,7 +2138,7 @@
         <v>45.8800010681152</v>
       </c>
       <c r="G61" t="n">
-        <v>39.7202110290527</v>
+        <v>39.7202072143555</v>
       </c>
       <c r="H61" t="n">
         <v>48377</v>
@@ -2167,7 +2167,7 @@
         <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>43.2870597839355</v>
+        <v>43.2870559692383</v>
       </c>
       <c r="H62" t="n">
         <v>415378</v>
@@ -2225,7 +2225,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>44.4558029174805</v>
+        <v>44.4557991027832</v>
       </c>
       <c r="H64" t="n">
         <v>210539</v>
@@ -2254,7 +2254,7 @@
         <v>52</v>
       </c>
       <c r="G65" t="n">
-        <v>45.0185470581055</v>
+        <v>45.0185394287109</v>
       </c>
       <c r="H65" t="n">
         <v>75333</v>
@@ -2312,7 +2312,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>44.8453826904297</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H67" t="n">
         <v>68564</v>
@@ -2370,7 +2370,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618362426758</v>
       </c>
       <c r="H69" t="n">
         <v>49881</v>
@@ -2399,7 +2399,7 @@
         <v>52</v>
       </c>
       <c r="G70" t="n">
-        <v>45.0185470581055</v>
+        <v>45.0185394287109</v>
       </c>
       <c r="H70" t="n">
         <v>54828</v>
@@ -2428,7 +2428,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>44.8453826904297</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H71" t="n">
         <v>36065</v>
@@ -2457,7 +2457,7 @@
         <v>51.5</v>
       </c>
       <c r="G72" t="n">
-        <v>44.5856704711914</v>
+        <v>44.5856666564941</v>
       </c>
       <c r="H72" t="n">
         <v>48281</v>
@@ -2544,7 +2544,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>44.1095161437988</v>
+        <v>44.1095085144043</v>
       </c>
       <c r="H75" t="n">
         <v>39623</v>
@@ -2573,7 +2573,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>44.4558029174805</v>
+        <v>44.4557991027832</v>
       </c>
       <c r="H76" t="n">
         <v>38314</v>
@@ -2631,7 +2631,7 @@
         <v>51.5</v>
       </c>
       <c r="G78" t="n">
-        <v>44.5856704711914</v>
+        <v>44.5856666564941</v>
       </c>
       <c r="H78" t="n">
         <v>45300</v>
@@ -2660,7 +2660,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>43.9796447753906</v>
+        <v>43.9796524047852</v>
       </c>
       <c r="H79" t="n">
         <v>48596</v>
@@ -2747,7 +2747,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G82" t="n">
-        <v>43.9796447753906</v>
+        <v>43.9796524047852</v>
       </c>
       <c r="H82" t="n">
         <v>25530</v>
@@ -2776,7 +2776,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>44.4125213623047</v>
+        <v>44.4125175476074</v>
       </c>
       <c r="H83" t="n">
         <v>50375</v>
@@ -2805,7 +2805,7 @@
         <v>51</v>
       </c>
       <c r="G84" t="n">
-        <v>44.1528015136719</v>
+        <v>44.1527976989746</v>
       </c>
       <c r="H84" t="n">
         <v>55134</v>
@@ -2863,7 +2863,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>44.1095161437988</v>
+        <v>44.1095085144043</v>
       </c>
       <c r="H86" t="n">
         <v>35475</v>
@@ -2921,7 +2921,7 @@
         <v>51.75</v>
       </c>
       <c r="G88" t="n">
-        <v>44.8021049499512</v>
+        <v>44.8021011352539</v>
       </c>
       <c r="H88" t="n">
         <v>26493</v>
@@ -2950,7 +2950,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>44.9752464294434</v>
+        <v>44.9752540588379</v>
       </c>
       <c r="H89" t="n">
         <v>44495</v>
@@ -2979,7 +2979,7 @@
         <v>52.5</v>
       </c>
       <c r="G90" t="n">
-        <v>45.451416015625</v>
+        <v>45.4514083862305</v>
       </c>
       <c r="H90" t="n">
         <v>86395</v>
@@ -3008,7 +3008,7 @@
         <v>52.5</v>
       </c>
       <c r="G91" t="n">
-        <v>45.451416015625</v>
+        <v>45.4514083862305</v>
       </c>
       <c r="H91" t="n">
         <v>38800</v>
@@ -3037,7 +3037,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G92" t="n">
-        <v>45.3215522766113</v>
+        <v>45.3215408325195</v>
       </c>
       <c r="H92" t="n">
         <v>34602</v>
@@ -3095,7 +3095,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>45.7544212341309</v>
+        <v>45.7544174194336</v>
       </c>
       <c r="H94" t="n">
         <v>40411</v>
@@ -3124,7 +3124,7 @@
         <v>52.25</v>
       </c>
       <c r="G95" t="n">
-        <v>45.234977722168</v>
+        <v>45.2349739074707</v>
       </c>
       <c r="H95" t="n">
         <v>40512</v>
@@ -3153,7 +3153,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618362426758</v>
       </c>
       <c r="H96" t="n">
         <v>56148</v>
@@ -3182,7 +3182,7 @@
         <v>51</v>
       </c>
       <c r="G97" t="n">
-        <v>44.1528015136719</v>
+        <v>44.1527976989746</v>
       </c>
       <c r="H97" t="n">
         <v>61270</v>
@@ -3298,7 +3298,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>46.6353721618652</v>
+        <v>46.635368347168</v>
       </c>
       <c r="H101" t="n">
         <v>108486</v>
@@ -3385,7 +3385,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G104" t="n">
-        <v>47.2928199768066</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H104" t="n">
         <v>65854</v>
@@ -3414,7 +3414,7 @@
         <v>55</v>
       </c>
       <c r="G105" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H105" t="n">
         <v>139286</v>
@@ -3443,7 +3443,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>47.6872940063477</v>
+        <v>47.6873054504395</v>
       </c>
       <c r="H106" t="n">
         <v>123579</v>
@@ -3559,7 +3559,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>48.1694259643555</v>
+        <v>48.1694221496582</v>
       </c>
       <c r="H110" t="n">
         <v>65714</v>
@@ -3588,7 +3588,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>49.046028137207</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H111" t="n">
         <v>91204</v>
@@ -3646,7 +3646,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>48.7830505371094</v>
+        <v>48.7830581665039</v>
       </c>
       <c r="H113" t="n">
         <v>93852</v>
@@ -3675,7 +3675,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G114" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H114" t="n">
         <v>71011</v>
@@ -3733,7 +3733,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G116" t="n">
-        <v>46.8545188903809</v>
+        <v>46.8545227050781</v>
       </c>
       <c r="H116" t="n">
         <v>59443</v>
@@ -3791,7 +3791,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H118" t="n">
         <v>92065</v>
@@ -3820,7 +3820,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>46.0655746459961</v>
+        <v>46.0655784606934</v>
       </c>
       <c r="H119" t="n">
         <v>163531</v>
@@ -3965,7 +3965,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>45.3204612731934</v>
+        <v>45.3204574584961</v>
       </c>
       <c r="H124" t="n">
         <v>161426</v>
@@ -3994,7 +3994,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G125" t="n">
-        <v>44.1808776855469</v>
+        <v>44.1808738708496</v>
       </c>
       <c r="H125" t="n">
         <v>216125</v>
@@ -4023,7 +4023,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>45.18896484375</v>
+        <v>45.1889724731445</v>
       </c>
       <c r="H126" t="n">
         <v>159639</v>
@@ -4052,7 +4052,7 @@
         <v>54.75</v>
       </c>
       <c r="G127" t="n">
-        <v>47.9941024780273</v>
+        <v>47.9941062927246</v>
       </c>
       <c r="H127" t="n">
         <v>154132</v>
@@ -4081,7 +4081,7 @@
         <v>55</v>
       </c>
       <c r="G128" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H128" t="n">
         <v>131299</v>
@@ -4139,7 +4139,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>49.4843330383301</v>
+        <v>49.4843406677246</v>
       </c>
       <c r="H130" t="n">
         <v>76647</v>
@@ -4168,7 +4168,7 @@
         <v>54.75</v>
       </c>
       <c r="G131" t="n">
-        <v>47.9941024780273</v>
+        <v>47.9941062927246</v>
       </c>
       <c r="H131" t="n">
         <v>118701</v>
@@ -4197,7 +4197,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G132" t="n">
-        <v>47.2928199768066</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H132" t="n">
         <v>211604</v>
@@ -4226,7 +4226,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G133" t="n">
-        <v>47.2489929199219</v>
+        <v>47.2489891052246</v>
       </c>
       <c r="H133" t="n">
         <v>109249</v>
@@ -4255,7 +4255,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>48.0379333496094</v>
+        <v>48.0379371643066</v>
       </c>
       <c r="H134" t="n">
         <v>26738</v>
@@ -4284,7 +4284,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G135" t="n">
-        <v>48.7830505371094</v>
+        <v>48.7830581665039</v>
       </c>
       <c r="H135" t="n">
         <v>31502</v>
@@ -4313,7 +4313,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G136" t="n">
-        <v>48.9145393371582</v>
+        <v>48.9145355224609</v>
       </c>
       <c r="H136" t="n">
         <v>53508</v>
@@ -4342,7 +4342,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>49.046028137207</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H137" t="n">
         <v>46872</v>
@@ -4400,7 +4400,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>48.125602722168</v>
+        <v>48.1255989074707</v>
       </c>
       <c r="H139" t="n">
         <v>53234</v>
@@ -4429,7 +4429,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>49.6596603393555</v>
+        <v>49.6596527099609</v>
       </c>
       <c r="H140" t="n">
         <v>41122</v>
@@ -4487,7 +4487,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>50.3171081542969</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H142" t="n">
         <v>82201</v>
@@ -4516,7 +4516,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102920532227</v>
       </c>
       <c r="H143" t="n">
         <v>17674</v>
@@ -4603,7 +4603,7 @@
         <v>58</v>
       </c>
       <c r="G146" t="n">
-        <v>50.843074798584</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H146" t="n">
         <v>54221</v>
@@ -4719,7 +4719,7 @@
         <v>56.0499992370605</v>
       </c>
       <c r="G150" t="n">
-        <v>49.1336898803711</v>
+        <v>49.1336936950684</v>
       </c>
       <c r="H150" t="n">
         <v>54634</v>
@@ -4748,7 +4748,7 @@
         <v>55.8499984741211</v>
       </c>
       <c r="G151" t="n">
-        <v>48.9583740234375</v>
+        <v>48.9583702087402</v>
       </c>
       <c r="H151" t="n">
         <v>64253</v>
@@ -4777,7 +4777,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G152" t="n">
-        <v>49.2651901245117</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H152" t="n">
         <v>32194</v>
@@ -4806,7 +4806,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G153" t="n">
-        <v>50.6677436828613</v>
+        <v>50.6677474975586</v>
       </c>
       <c r="H153" t="n">
         <v>128897</v>
@@ -4835,7 +4835,7 @@
         <v>60</v>
       </c>
       <c r="G154" t="n">
-        <v>52.5962753295898</v>
+        <v>52.5962791442871</v>
       </c>
       <c r="H154" t="n">
         <v>118253</v>
@@ -4864,7 +4864,7 @@
         <v>59.4500007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>52.1141510009766</v>
+        <v>52.1141548156738</v>
       </c>
       <c r="H155" t="n">
         <v>66348</v>
@@ -4922,7 +4922,7 @@
         <v>60.8499984741211</v>
       </c>
       <c r="G157" t="n">
-        <v>53.3413925170898</v>
+        <v>53.3413887023926</v>
       </c>
       <c r="H157" t="n">
         <v>76402</v>
@@ -5009,7 +5009,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>51.1060562133789</v>
+        <v>51.1060485839844</v>
       </c>
       <c r="H160" t="n">
         <v>136886</v>
@@ -5038,7 +5038,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>51.1060562133789</v>
+        <v>51.1060485839844</v>
       </c>
       <c r="H161" t="n">
         <v>48119</v>
@@ -5096,7 +5096,7 @@
         <v>56.75</v>
       </c>
       <c r="G163" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473106384277</v>
       </c>
       <c r="H163" t="n">
         <v>52533</v>
@@ -5125,7 +5125,7 @@
         <v>56.75</v>
       </c>
       <c r="G164" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473106384277</v>
       </c>
       <c r="H164" t="n">
         <v>117677</v>
@@ -5154,7 +5154,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G165" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H165" t="n">
         <v>92163</v>
@@ -5183,7 +5183,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G166" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H166" t="n">
         <v>57849</v>
@@ -5241,7 +5241,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102920532227</v>
       </c>
       <c r="H168" t="n">
         <v>23183</v>
@@ -5328,7 +5328,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>50.7992401123047</v>
+        <v>50.799243927002</v>
       </c>
       <c r="H171" t="n">
         <v>74536</v>
@@ -5444,7 +5444,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>50.3171081542969</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H175" t="n">
         <v>37130</v>
@@ -5473,7 +5473,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>50.9307327270508</v>
+        <v>50.9307289123535</v>
       </c>
       <c r="H176" t="n">
         <v>60405</v>
@@ -5560,7 +5560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G179" t="n">
-        <v>48.5639038085938</v>
+        <v>48.5638999938965</v>
       </c>
       <c r="H179" t="n">
         <v>78987</v>
@@ -5589,7 +5589,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G180" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H180" t="n">
         <v>71976</v>
@@ -5647,7 +5647,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H182" t="n">
         <v>108065</v>
@@ -5705,7 +5705,7 @@
         <v>56.75</v>
       </c>
       <c r="G184" t="n">
-        <v>49.747314453125</v>
+        <v>49.7473106384277</v>
       </c>
       <c r="H184" t="n">
         <v>55629</v>
@@ -5792,7 +5792,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G187" t="n">
-        <v>51.5443534851074</v>
+        <v>51.5443496704102</v>
       </c>
       <c r="H187" t="n">
         <v>46007</v>
@@ -5821,7 +5821,7 @@
         <v>59</v>
       </c>
       <c r="G188" t="n">
-        <v>51.7196769714355</v>
+        <v>51.7196731567383</v>
       </c>
       <c r="H188" t="n">
         <v>61805</v>
@@ -5850,7 +5850,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>50.5800857543945</v>
+        <v>50.5800933837891</v>
       </c>
       <c r="H189" t="n">
         <v>39531</v>
@@ -5879,7 +5879,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H190" t="n">
         <v>45041</v>
@@ -6024,7 +6024,7 @@
         <v>58.9000015258789</v>
       </c>
       <c r="G195" t="n">
-        <v>51.6320266723633</v>
+        <v>51.632022857666</v>
       </c>
       <c r="H195" t="n">
         <v>59969</v>
@@ -6198,7 +6198,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>51.1060562133789</v>
+        <v>51.1060485839844</v>
       </c>
       <c r="H201" t="n">
         <v>63932</v>
@@ -6256,7 +6256,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>50.7992401123047</v>
+        <v>50.799243927002</v>
       </c>
       <c r="H203" t="n">
         <v>127773</v>
@@ -6285,7 +6285,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>50.4485931396484</v>
+        <v>50.448600769043</v>
       </c>
       <c r="H204" t="n">
         <v>44376</v>
@@ -6314,7 +6314,7 @@
         <v>58</v>
       </c>
       <c r="G205" t="n">
-        <v>50.843074798584</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H205" t="n">
         <v>40883</v>
@@ -6343,7 +6343,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>50.2294464111328</v>
+        <v>50.2294502258301</v>
       </c>
       <c r="H206" t="n">
         <v>41484</v>
@@ -6372,7 +6372,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>50.2294464111328</v>
+        <v>50.2294502258301</v>
       </c>
       <c r="H207" t="n">
         <v>51815</v>
@@ -6401,7 +6401,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>49.7911376953125</v>
+        <v>49.791145324707</v>
       </c>
       <c r="H208" t="n">
         <v>37855</v>
@@ -6546,7 +6546,7 @@
         <v>57</v>
       </c>
       <c r="G213" t="n">
-        <v>49.9664688110352</v>
+        <v>49.9664611816406</v>
       </c>
       <c r="H213" t="n">
         <v>105822</v>
@@ -6575,7 +6575,7 @@
         <v>56</v>
       </c>
       <c r="G214" t="n">
-        <v>49.0898551940918</v>
+        <v>49.0898590087891</v>
       </c>
       <c r="H214" t="n">
         <v>44252</v>
@@ -6662,7 +6662,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>47.2928199768066</v>
+        <v>47.2928276062012</v>
       </c>
       <c r="H217" t="n">
         <v>91776</v>
@@ -6691,7 +6691,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>46.7668609619141</v>
+        <v>46.7668571472168</v>
       </c>
       <c r="H218" t="n">
         <v>69051</v>
@@ -6720,7 +6720,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>46.9421768188477</v>
+        <v>46.9421882629395</v>
       </c>
       <c r="H219" t="n">
         <v>45180</v>
@@ -6807,7 +6807,7 @@
         <v>50.75</v>
       </c>
       <c r="G222" t="n">
-        <v>44.487678527832</v>
+        <v>44.4876899719238</v>
       </c>
       <c r="H222" t="n">
         <v>236609</v>
@@ -6836,7 +6836,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>44.8821678161621</v>
+        <v>44.8821563720703</v>
       </c>
       <c r="H223" t="n">
         <v>156382</v>
@@ -6865,7 +6865,7 @@
         <v>51</v>
       </c>
       <c r="G224" t="n">
-        <v>44.706844329834</v>
+        <v>44.7068367004395</v>
       </c>
       <c r="H224" t="n">
         <v>144844</v>
@@ -6894,7 +6894,7 @@
         <v>51</v>
       </c>
       <c r="G225" t="n">
-        <v>44.706844329834</v>
+        <v>44.7068367004395</v>
       </c>
       <c r="H225" t="n">
         <v>74954</v>
@@ -6952,7 +6952,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H227" t="n">
         <v>99562</v>
@@ -6981,7 +6981,7 @@
         <v>52.25</v>
       </c>
       <c r="G228" t="n">
-        <v>45.8025932312012</v>
+        <v>45.8025970458984</v>
       </c>
       <c r="H228" t="n">
         <v>99489</v>
@@ -7010,7 +7010,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>45.4081192016602</v>
+        <v>45.4081230163574</v>
       </c>
       <c r="H229" t="n">
         <v>76726</v>
@@ -7039,7 +7039,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G230" t="n">
-        <v>45.3204612731934</v>
+        <v>45.3204574584961</v>
       </c>
       <c r="H230" t="n">
         <v>74885</v>
@@ -7068,7 +7068,7 @@
         <v>51.25</v>
       </c>
       <c r="G231" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259910583496</v>
       </c>
       <c r="H231" t="n">
         <v>72155</v>
@@ -7097,7 +7097,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>45.2766342163086</v>
+        <v>45.2766304016113</v>
       </c>
       <c r="H232" t="n">
         <v>43249</v>
@@ -7126,7 +7126,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>45.7149314880371</v>
+        <v>45.7149391174316</v>
       </c>
       <c r="H233" t="n">
         <v>26119</v>
@@ -7184,7 +7184,7 @@
         <v>51.5</v>
       </c>
       <c r="G235" t="n">
-        <v>45.1451416015625</v>
+        <v>45.1451377868652</v>
       </c>
       <c r="H235" t="n">
         <v>125607</v>
@@ -7242,7 +7242,7 @@
         <v>51.25</v>
       </c>
       <c r="G237" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259910583496</v>
       </c>
       <c r="H237" t="n">
         <v>109858</v>
@@ -7300,7 +7300,7 @@
         <v>51.25</v>
       </c>
       <c r="G239" t="n">
-        <v>44.9259948730469</v>
+        <v>44.9259910583496</v>
       </c>
       <c r="H239" t="n">
         <v>58604</v>
@@ -7329,7 +7329,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H240" t="n">
         <v>63619</v>
@@ -7358,7 +7358,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>45.6711044311523</v>
+        <v>45.6710968017578</v>
       </c>
       <c r="H241" t="n">
         <v>108454</v>
@@ -7387,7 +7387,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G242" t="n">
-        <v>45.6711044311523</v>
+        <v>45.6710968017578</v>
       </c>
       <c r="H242" t="n">
         <v>106069</v>
@@ -7416,7 +7416,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>45.7149314880371</v>
+        <v>45.7149391174316</v>
       </c>
       <c r="H243" t="n">
         <v>96572</v>
@@ -7445,7 +7445,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G244" t="n">
-        <v>46.0655746459961</v>
+        <v>46.0655784606934</v>
       </c>
       <c r="H244" t="n">
         <v>65574</v>
@@ -7474,7 +7474,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>45.4081192016602</v>
+        <v>45.4081230163574</v>
       </c>
       <c r="H245" t="n">
         <v>73074</v>
@@ -7503,7 +7503,7 @@
         <v>51.8499984741211</v>
       </c>
       <c r="G246" t="n">
-        <v>45.4519538879395</v>
+        <v>45.4519462585449</v>
       </c>
       <c r="H246" t="n">
         <v>76582</v>
@@ -7532,7 +7532,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>46.3723945617676</v>
+        <v>46.372386932373</v>
       </c>
       <c r="H247" t="n">
         <v>104815</v>
@@ -7619,7 +7619,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>48.3009185791016</v>
+        <v>48.300910949707</v>
       </c>
       <c r="H250" t="n">
         <v>168307</v>
@@ -7677,7 +7677,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>49.046028137207</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H252" t="n">
         <v>158003</v>
@@ -7706,7 +7706,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G253" t="n">
-        <v>48.5639038085938</v>
+        <v>48.5638999938965</v>
       </c>
       <c r="H253" t="n">
         <v>91984</v>
@@ -7735,7 +7735,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G254" t="n">
-        <v>49.440502166748</v>
+        <v>49.4405097961426</v>
       </c>
       <c r="H254" t="n">
         <v>21800</v>
@@ -7764,7 +7764,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>49.2651901245117</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H255" t="n">
         <v>41254</v>
@@ -7880,7 +7880,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>50.3171081542969</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H259" t="n">
         <v>95026</v>
@@ -7938,7 +7938,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>50.5800857543945</v>
+        <v>50.5800933837891</v>
       </c>
       <c r="H261" t="n">
         <v>43639</v>
@@ -7967,7 +7967,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G262" t="n">
-        <v>51.1937141418457</v>
+        <v>51.193717956543</v>
       </c>
       <c r="H262" t="n">
         <v>44010</v>
@@ -8141,7 +8141,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>49.7911376953125</v>
+        <v>49.791145324707</v>
       </c>
       <c r="H268" t="n">
         <v>46171</v>
@@ -8170,7 +8170,7 @@
         <v>57</v>
       </c>
       <c r="G269" t="n">
-        <v>49.9664688110352</v>
+        <v>49.9664611816406</v>
       </c>
       <c r="H269" t="n">
         <v>89699</v>
@@ -8199,7 +8199,7 @@
         <v>57</v>
       </c>
       <c r="G270" t="n">
-        <v>49.9664688110352</v>
+        <v>49.9664611816406</v>
       </c>
       <c r="H270" t="n">
         <v>70741</v>
@@ -8228,7 +8228,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>49.7911376953125</v>
+        <v>49.791145324707</v>
       </c>
       <c r="H271" t="n">
         <v>35621</v>
@@ -8257,7 +8257,7 @@
         <v>56</v>
       </c>
       <c r="G272" t="n">
-        <v>49.0898551940918</v>
+        <v>49.0898590087891</v>
       </c>
       <c r="H272" t="n">
         <v>41651</v>
@@ -8315,7 +8315,7 @@
         <v>55</v>
       </c>
       <c r="G274" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H274" t="n">
         <v>183138</v>
@@ -8344,7 +8344,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G275" t="n">
-        <v>47.6872940063477</v>
+        <v>47.6873054504395</v>
       </c>
       <c r="H275" t="n">
         <v>90413</v>
@@ -8373,7 +8373,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G276" t="n">
-        <v>47.9502754211426</v>
+        <v>47.9502716064453</v>
       </c>
       <c r="H276" t="n">
         <v>115124</v>
@@ -8402,7 +8402,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>48.6953811645508</v>
+        <v>48.6953887939453</v>
       </c>
       <c r="H277" t="n">
         <v>99818</v>
@@ -8489,7 +8489,7 @@
         <v>56</v>
       </c>
       <c r="G280" t="n">
-        <v>49.0898551940918</v>
+        <v>49.0898590087891</v>
       </c>
       <c r="H280" t="n">
         <v>70892</v>
@@ -8518,7 +8518,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>51.1937141418457</v>
+        <v>51.193717956543</v>
       </c>
       <c r="H281" t="n">
         <v>176623</v>
@@ -8547,7 +8547,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>50.7992401123047</v>
+        <v>50.799243927002</v>
       </c>
       <c r="H282" t="n">
         <v>58562</v>
@@ -8576,7 +8576,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>49.6596603393555</v>
+        <v>49.6596527099609</v>
       </c>
       <c r="H283" t="n">
         <v>55901</v>
@@ -8605,7 +8605,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G284" t="n">
-        <v>49.2651901245117</v>
+        <v>49.2651863098145</v>
       </c>
       <c r="H284" t="n">
         <v>60368</v>
@@ -8634,7 +8634,7 @@
         <v>57</v>
       </c>
       <c r="G285" t="n">
-        <v>49.9664688110352</v>
+        <v>49.9664611816406</v>
       </c>
       <c r="H285" t="n">
         <v>64846</v>
@@ -8692,7 +8692,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G287" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102920532227</v>
       </c>
       <c r="H287" t="n">
         <v>68947</v>
@@ -8721,7 +8721,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>50.0102958679199</v>
+        <v>50.0102920532227</v>
       </c>
       <c r="H288" t="n">
         <v>33003</v>
@@ -8750,7 +8750,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>50.6677436828613</v>
+        <v>50.6677474975586</v>
       </c>
       <c r="H289" t="n">
         <v>47641</v>
@@ -8808,7 +8808,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G291" t="n">
-        <v>50.7992401123047</v>
+        <v>50.799243927002</v>
       </c>
       <c r="H291" t="n">
         <v>101762</v>
@@ -8837,7 +8837,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G292" t="n">
-        <v>49.8788108825684</v>
+        <v>49.8788070678711</v>
       </c>
       <c r="H292" t="n">
         <v>84201</v>
@@ -8866,7 +8866,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>50.3171081542969</v>
+        <v>50.3171157836914</v>
       </c>
       <c r="H293" t="n">
         <v>68398</v>
@@ -8924,7 +8924,7 @@
         <v>59</v>
       </c>
       <c r="G295" t="n">
-        <v>51.7196769714355</v>
+        <v>51.7196731567383</v>
       </c>
       <c r="H295" t="n">
         <v>116359</v>
@@ -8953,7 +8953,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>51.1060562133789</v>
+        <v>51.1060485839844</v>
       </c>
       <c r="H296" t="n">
         <v>80368</v>
@@ -8982,7 +8982,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>51.2375450134277</v>
+        <v>51.2375411987305</v>
       </c>
       <c r="H297" t="n">
         <v>126567</v>
@@ -9069,7 +9069,7 @@
         <v>60</v>
       </c>
       <c r="G300" t="n">
-        <v>52.5962753295898</v>
+        <v>52.5962791442871</v>
       </c>
       <c r="H300" t="n">
         <v>115569</v>
@@ -9098,7 +9098,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>52.4209594726562</v>
+        <v>52.4209632873535</v>
       </c>
       <c r="H301" t="n">
         <v>69522</v>
@@ -9127,7 +9127,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>52.4209594726562</v>
+        <v>52.4209632873535</v>
       </c>
       <c r="H302" t="n">
         <v>60828</v>
@@ -9156,7 +9156,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G303" t="n">
-        <v>52.4647903442383</v>
+        <v>52.464786529541</v>
       </c>
       <c r="H303" t="n">
         <v>87140</v>
@@ -9185,7 +9185,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G304" t="n">
-        <v>52.6839408874512</v>
+        <v>52.6839370727539</v>
       </c>
       <c r="H304" t="n">
         <v>94608</v>
@@ -9214,7 +9214,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>51.5443534851074</v>
+        <v>51.5443496704102</v>
       </c>
       <c r="H305" t="n">
         <v>154357</v>
@@ -9243,7 +9243,7 @@
         <v>59.25</v>
       </c>
       <c r="G306" t="n">
-        <v>51.9388236999512</v>
+        <v>51.9388275146484</v>
       </c>
       <c r="H306" t="n">
         <v>85958</v>
@@ -9272,7 +9272,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>52.2894668579102</v>
+        <v>52.2894744873047</v>
       </c>
       <c r="H307" t="n">
         <v>78202</v>
@@ -9301,7 +9301,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>51.5443534851074</v>
+        <v>51.5443496704102</v>
       </c>
       <c r="H308" t="n">
         <v>103451</v>
@@ -9330,7 +9330,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>52.4647903442383</v>
+        <v>52.464786529541</v>
       </c>
       <c r="H309" t="n">
         <v>105806</v>
@@ -9388,7 +9388,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>53.7796974182129</v>
+        <v>53.7796897888184</v>
       </c>
       <c r="H311" t="n">
         <v>99357</v>
@@ -9417,7 +9417,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>53.7796974182129</v>
+        <v>53.7796897888184</v>
       </c>
       <c r="H312" t="n">
         <v>90388</v>
@@ -9446,7 +9446,7 @@
         <v>62.25</v>
       </c>
       <c r="G313" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H313" t="n">
         <v>168323</v>
@@ -9504,7 +9504,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>54.4809799194336</v>
+        <v>54.4809837341309</v>
       </c>
       <c r="H315" t="n">
         <v>94164</v>
@@ -9533,7 +9533,7 @@
         <v>63</v>
       </c>
       <c r="G316" t="n">
-        <v>55.2260971069336</v>
+        <v>55.2260932922363</v>
       </c>
       <c r="H316" t="n">
         <v>83517</v>
@@ -9591,7 +9591,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>54.612476348877</v>
+        <v>54.6124687194824</v>
       </c>
       <c r="H318" t="n">
         <v>58897</v>
@@ -9649,7 +9649,7 @@
         <v>62.25</v>
       </c>
       <c r="G320" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H320" t="n">
         <v>73391</v>
@@ -9678,7 +9678,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G321" t="n">
-        <v>55.7520561218262</v>
+        <v>55.7520523071289</v>
       </c>
       <c r="H321" t="n">
         <v>85289</v>
@@ -9794,7 +9794,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G325" t="n">
-        <v>56.3656883239746</v>
+        <v>56.3656845092773</v>
       </c>
       <c r="H325" t="n">
         <v>54692</v>
@@ -9823,7 +9823,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>56.278018951416</v>
+        <v>56.2780151367188</v>
       </c>
       <c r="H326" t="n">
         <v>93016</v>
@@ -9852,7 +9852,7 @@
         <v>65</v>
       </c>
       <c r="G327" t="n">
-        <v>56.979305267334</v>
+        <v>56.9793090820312</v>
       </c>
       <c r="H327" t="n">
         <v>61355</v>
@@ -9881,7 +9881,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G328" t="n">
-        <v>57.8120803833008</v>
+        <v>57.8120727539062</v>
       </c>
       <c r="H328" t="n">
         <v>105326</v>
@@ -9910,7 +9910,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G329" t="n">
-        <v>57.9435691833496</v>
+        <v>57.9435653686523</v>
       </c>
       <c r="H329" t="n">
         <v>88839</v>
@@ -9997,7 +9997,7 @@
         <v>64</v>
       </c>
       <c r="G332" t="n">
-        <v>56.1027030944824</v>
+        <v>56.1026954650879</v>
       </c>
       <c r="H332" t="n">
         <v>205806</v>
@@ -10055,7 +10055,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G334" t="n">
-        <v>57.9435691833496</v>
+        <v>57.9435653686523</v>
       </c>
       <c r="H334" t="n">
         <v>121496</v>
@@ -10084,7 +10084,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G335" t="n">
-        <v>57.5052642822266</v>
+        <v>57.5052680969238</v>
       </c>
       <c r="H335" t="n">
         <v>103682</v>
@@ -10113,7 +10113,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G336" t="n">
-        <v>58.907829284668</v>
+        <v>58.9078330993652</v>
       </c>
       <c r="H336" t="n">
         <v>121938</v>
@@ -10142,7 +10142,7 @@
         <v>66</v>
       </c>
       <c r="G337" t="n">
-        <v>57.8559112548828</v>
+        <v>57.8559074401855</v>
       </c>
       <c r="H337" t="n">
         <v>107496</v>
@@ -10171,7 +10171,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G338" t="n">
-        <v>58.2065467834473</v>
+        <v>58.2065505981445</v>
       </c>
       <c r="H338" t="n">
         <v>84175</v>
@@ -10200,7 +10200,7 @@
         <v>67.5</v>
       </c>
       <c r="G339" t="n">
-        <v>59.1708106994629</v>
+        <v>59.1708183288574</v>
       </c>
       <c r="H339" t="n">
         <v>87020</v>
@@ -10229,7 +10229,7 @@
         <v>68.8000030517578</v>
       </c>
       <c r="G340" t="n">
-        <v>60.3104057312012</v>
+        <v>60.3104095458984</v>
       </c>
       <c r="H340" t="n">
         <v>93918</v>
@@ -10258,7 +10258,7 @@
         <v>71</v>
       </c>
       <c r="G341" t="n">
-        <v>62.2389373779297</v>
+        <v>62.2389335632324</v>
       </c>
       <c r="H341" t="n">
         <v>130581</v>
@@ -10316,7 +10316,7 @@
         <v>69</v>
       </c>
       <c r="G343" t="n">
-        <v>60.4857139587402</v>
+        <v>60.4857292175293</v>
       </c>
       <c r="H343" t="n">
         <v>124118</v>
@@ -10345,7 +10345,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G344" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H344" t="n">
         <v>113418</v>
@@ -10374,7 +10374,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G345" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H345" t="n">
         <v>142132</v>
@@ -10403,7 +10403,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G346" t="n">
-        <v>61.6691284179688</v>
+        <v>61.6691360473633</v>
       </c>
       <c r="H346" t="n">
         <v>203289</v>
@@ -10519,7 +10519,7 @@
         <v>70</v>
       </c>
       <c r="G350" t="n">
-        <v>61.3623161315918</v>
+        <v>61.3623199462891</v>
       </c>
       <c r="H350" t="n">
         <v>67704</v>
@@ -10548,7 +10548,7 @@
         <v>70</v>
       </c>
       <c r="G351" t="n">
-        <v>61.3623161315918</v>
+        <v>61.3623199462891</v>
       </c>
       <c r="H351" t="n">
         <v>93071</v>
@@ -10635,7 +10635,7 @@
         <v>68.25</v>
       </c>
       <c r="G354" t="n">
-        <v>59.8282699584961</v>
+        <v>59.8282661437988</v>
       </c>
       <c r="H354" t="n">
         <v>78001</v>
@@ -10664,7 +10664,7 @@
         <v>68.25</v>
       </c>
       <c r="G355" t="n">
-        <v>60.5378646850586</v>
+        <v>60.5378684997559</v>
       </c>
       <c r="H355" t="n">
         <v>58161</v>
@@ -10693,7 +10693,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G356" t="n">
-        <v>60.8039741516113</v>
+        <v>60.8039665222168</v>
       </c>
       <c r="H356" t="n">
         <v>86355</v>
@@ -10722,7 +10722,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G357" t="n">
-        <v>60.9370155334473</v>
+        <v>60.9370193481445</v>
       </c>
       <c r="H357" t="n">
         <v>85485</v>
@@ -10809,7 +10809,7 @@
         <v>68.0500030517578</v>
       </c>
       <c r="G360" t="n">
-        <v>60.3604698181152</v>
+        <v>60.3604736328125</v>
       </c>
       <c r="H360" t="n">
         <v>44961</v>
@@ -10838,7 +10838,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G361" t="n">
-        <v>60.9370155334473</v>
+        <v>60.9370193481445</v>
       </c>
       <c r="H361" t="n">
         <v>92493</v>
@@ -10896,7 +10896,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G363" t="n">
-        <v>62.2675323486328</v>
+        <v>62.2675170898438</v>
       </c>
       <c r="H363" t="n">
         <v>76993</v>
@@ -11012,7 +11012,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>62.8884239196777</v>
+        <v>62.8884162902832</v>
       </c>
       <c r="H367" t="n">
         <v>88768</v>
@@ -11041,7 +11041,7 @@
         <v>71.75</v>
       </c>
       <c r="G368" t="n">
-        <v>63.6423873901367</v>
+        <v>63.6423759460449</v>
       </c>
       <c r="H368" t="n">
         <v>78174</v>
@@ -11099,7 +11099,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014381408691</v>
       </c>
       <c r="H370" t="n">
         <v>126134</v>
@@ -11128,7 +11128,7 @@
         <v>69.75</v>
       </c>
       <c r="G371" t="n">
-        <v>61.8683700561523</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H371" t="n">
         <v>83211</v>
@@ -11186,7 +11186,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G373" t="n">
-        <v>62.7110176086426</v>
+        <v>62.7110328674316</v>
       </c>
       <c r="H373" t="n">
         <v>62075</v>
@@ -11244,7 +11244,7 @@
         <v>71.1500015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>63.1101722717285</v>
+        <v>63.1101684570312</v>
       </c>
       <c r="H375" t="n">
         <v>41602</v>
@@ -11273,7 +11273,7 @@
         <v>71</v>
       </c>
       <c r="G376" t="n">
-        <v>62.9771156311035</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H376" t="n">
         <v>55189</v>
@@ -11331,7 +11331,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G378" t="n">
-        <v>62.2675323486328</v>
+        <v>62.2675170898438</v>
       </c>
       <c r="H378" t="n">
         <v>44527</v>
@@ -11418,7 +11418,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014381408691</v>
       </c>
       <c r="H381" t="n">
         <v>151026</v>
@@ -11476,7 +11476,7 @@
         <v>66</v>
       </c>
       <c r="G383" t="n">
-        <v>58.5421180725098</v>
+        <v>58.5421142578125</v>
       </c>
       <c r="H383" t="n">
         <v>152369</v>
@@ -11505,7 +11505,7 @@
         <v>67.25</v>
       </c>
       <c r="G384" t="n">
-        <v>59.65087890625</v>
+        <v>59.6508750915527</v>
       </c>
       <c r="H384" t="n">
         <v>94522</v>
@@ -11534,7 +11534,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G385" t="n">
-        <v>59.0743179321289</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H385" t="n">
         <v>79441</v>
@@ -11563,7 +11563,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G386" t="n">
-        <v>59.0743179321289</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H386" t="n">
         <v>35043</v>
@@ -11592,7 +11592,7 @@
         <v>67.25</v>
       </c>
       <c r="G387" t="n">
-        <v>59.65087890625</v>
+        <v>59.6508750915527</v>
       </c>
       <c r="H387" t="n">
         <v>75320</v>
@@ -11621,7 +11621,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G388" t="n">
-        <v>59.0743179321289</v>
+        <v>59.0743141174316</v>
       </c>
       <c r="H388" t="n">
         <v>68536</v>
@@ -11650,7 +11650,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G389" t="n">
-        <v>59.6952209472656</v>
+        <v>59.6952323913574</v>
       </c>
       <c r="H389" t="n">
         <v>31158</v>
@@ -11679,7 +11679,7 @@
         <v>67</v>
       </c>
       <c r="G390" t="n">
-        <v>59.4291191101074</v>
+        <v>59.4291152954102</v>
       </c>
       <c r="H390" t="n">
         <v>83527</v>
@@ -11708,7 +11708,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>58.5864677429199</v>
+        <v>58.5864753723145</v>
       </c>
       <c r="H391" t="n">
         <v>60337</v>
@@ -11737,7 +11737,7 @@
         <v>67</v>
       </c>
       <c r="G392" t="n">
-        <v>59.4291191101074</v>
+        <v>59.4291152954102</v>
       </c>
       <c r="H392" t="n">
         <v>65587</v>
@@ -11766,7 +11766,7 @@
         <v>67.0999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>59.5178070068359</v>
+        <v>59.5178184509277</v>
       </c>
       <c r="H393" t="n">
         <v>54381</v>
@@ -11795,7 +11795,7 @@
         <v>68</v>
       </c>
       <c r="G394" t="n">
-        <v>60.3161239624023</v>
+        <v>60.3161201477051</v>
       </c>
       <c r="H394" t="n">
         <v>59621</v>
@@ -11824,7 +11824,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G395" t="n">
-        <v>61.2474784851074</v>
+        <v>61.2474708557129</v>
       </c>
       <c r="H395" t="n">
         <v>74590</v>
@@ -11853,7 +11853,7 @@
         <v>69.75</v>
       </c>
       <c r="G396" t="n">
-        <v>61.8683700561523</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H396" t="n">
         <v>106303</v>
@@ -11882,7 +11882,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G397" t="n">
-        <v>62.045768737793</v>
+        <v>62.0457725524902</v>
       </c>
       <c r="H397" t="n">
         <v>56355</v>
@@ -11911,7 +11911,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>62.4005661010742</v>
+        <v>62.4005699157715</v>
       </c>
       <c r="H398" t="n">
         <v>82183</v>
@@ -11940,7 +11940,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G399" t="n">
-        <v>62.2231712341309</v>
+        <v>62.2231864929199</v>
       </c>
       <c r="H399" t="n">
         <v>53923</v>
@@ -12027,7 +12027,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G402" t="n">
-        <v>65.0172348022461</v>
+        <v>65.0172424316406</v>
       </c>
       <c r="H402" t="n">
         <v>200681</v>
@@ -12056,7 +12056,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>65.5494537353516</v>
+        <v>65.5494384765625</v>
       </c>
       <c r="H403" t="n">
         <v>98784</v>
@@ -12085,7 +12085,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G404" t="n">
-        <v>64.7954711914062</v>
+        <v>64.7954940795898</v>
       </c>
       <c r="H404" t="n">
         <v>67694</v>
@@ -12114,7 +12114,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>65.2833251953125</v>
+        <v>65.283332824707</v>
       </c>
       <c r="H405" t="n">
         <v>62565</v>
@@ -12172,7 +12172,7 @@
         <v>73</v>
       </c>
       <c r="G407" t="n">
-        <v>64.7511291503906</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H407" t="n">
         <v>66371</v>
@@ -12201,7 +12201,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>64.7954711914062</v>
+        <v>64.7954940795898</v>
       </c>
       <c r="H408" t="n">
         <v>127324</v>
@@ -12259,7 +12259,7 @@
         <v>72.5999984741211</v>
       </c>
       <c r="G410" t="n">
-        <v>64.3963165283203</v>
+        <v>64.3963241577148</v>
       </c>
       <c r="H410" t="n">
         <v>118089</v>
@@ -12288,7 +12288,7 @@
         <v>71.9499969482422</v>
       </c>
       <c r="G411" t="n">
-        <v>63.8197708129883</v>
+        <v>63.8197631835938</v>
       </c>
       <c r="H411" t="n">
         <v>175766</v>
@@ -12375,7 +12375,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G414" t="n">
-        <v>62.7110176086426</v>
+        <v>62.7110328674316</v>
       </c>
       <c r="H414" t="n">
         <v>53923</v>
@@ -12404,7 +12404,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>63.5536804199219</v>
+        <v>63.5536727905273</v>
       </c>
       <c r="H415" t="n">
         <v>58212</v>
@@ -12462,7 +12462,7 @@
         <v>71.6999969482422</v>
       </c>
       <c r="G417" t="n">
-        <v>63.5980262756348</v>
+        <v>63.5980110168457</v>
       </c>
       <c r="H417" t="n">
         <v>60605</v>
@@ -12520,7 +12520,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H419" t="n">
         <v>32790</v>
@@ -12578,7 +12578,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G421" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H421" t="n">
         <v>54279</v>
@@ -12607,7 +12607,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G422" t="n">
-        <v>62.7997207641602</v>
+        <v>62.7997360229492</v>
       </c>
       <c r="H422" t="n">
         <v>37097</v>
@@ -12665,7 +12665,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>62.1344795227051</v>
+        <v>62.1344757080078</v>
       </c>
       <c r="H424" t="n">
         <v>69545</v>
@@ -12694,7 +12694,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G425" t="n">
-        <v>62.045768737793</v>
+        <v>62.0457725524902</v>
       </c>
       <c r="H425" t="n">
         <v>96037</v>
@@ -12723,7 +12723,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>63.2875709533691</v>
+        <v>63.2875785827637</v>
       </c>
       <c r="H426" t="n">
         <v>67312</v>
@@ -12752,7 +12752,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>64.2189254760742</v>
+        <v>64.2189331054688</v>
       </c>
       <c r="H427" t="n">
         <v>125587</v>
@@ -12839,7 +12839,7 @@
         <v>73</v>
       </c>
       <c r="G430" t="n">
-        <v>64.7511291503906</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H430" t="n">
         <v>68493</v>
@@ -12868,7 +12868,7 @@
         <v>73.3499984741211</v>
       </c>
       <c r="G431" t="n">
-        <v>65.0615768432617</v>
+        <v>65.0615844726562</v>
       </c>
       <c r="H431" t="n">
         <v>79399</v>
@@ -12897,7 +12897,7 @@
         <v>73.6999969482422</v>
       </c>
       <c r="G432" t="n">
-        <v>65.3720397949219</v>
+        <v>65.3720245361328</v>
       </c>
       <c r="H432" t="n">
         <v>96313</v>
@@ -12926,7 +12926,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G433" t="n">
-        <v>65.2389755249023</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H433" t="n">
         <v>52881</v>
@@ -12955,7 +12955,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>65.5494537353516</v>
+        <v>65.5494384765625</v>
       </c>
       <c r="H434" t="n">
         <v>63832</v>
@@ -12984,7 +12984,7 @@
         <v>73</v>
       </c>
       <c r="G435" t="n">
-        <v>64.7511291503906</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H435" t="n">
         <v>68517</v>
@@ -13013,7 +13013,7 @@
         <v>74</v>
       </c>
       <c r="G436" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H436" t="n">
         <v>59046</v>
@@ -13042,7 +13042,7 @@
         <v>74</v>
       </c>
       <c r="G437" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H437" t="n">
         <v>38905</v>
@@ -13071,7 +13071,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>64.8398284912109</v>
+        <v>64.8398361206055</v>
       </c>
       <c r="H438" t="n">
         <v>73428</v>
@@ -13100,7 +13100,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G439" t="n">
-        <v>65.1502838134766</v>
+        <v>65.150276184082</v>
       </c>
       <c r="H439" t="n">
         <v>48041</v>
@@ -13129,7 +13129,7 @@
         <v>74</v>
       </c>
       <c r="G440" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H440" t="n">
         <v>47098</v>
@@ -13303,7 +13303,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G446" t="n">
-        <v>66.6138153076172</v>
+        <v>66.6138305664062</v>
       </c>
       <c r="H446" t="n">
         <v>162554</v>
@@ -13361,7 +13361,7 @@
         <v>75.4499969482422</v>
       </c>
       <c r="G448" t="n">
-        <v>66.9242858886719</v>
+        <v>66.9242782592773</v>
       </c>
       <c r="H448" t="n">
         <v>113939</v>
@@ -13419,7 +13419,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G450" t="n">
-        <v>69.0087280273438</v>
+        <v>69.0087356567383</v>
       </c>
       <c r="H450" t="n">
         <v>70572</v>
@@ -13477,7 +13477,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496810913086</v>
       </c>
       <c r="H452" t="n">
         <v>107042</v>
@@ -13506,7 +13506,7 @@
         <v>79</v>
       </c>
       <c r="G453" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731506347656</v>
       </c>
       <c r="H453" t="n">
         <v>44675</v>
@@ -13564,7 +13564,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G455" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409317016602</v>
       </c>
       <c r="H455" t="n">
         <v>59456</v>
@@ -13593,7 +13593,7 @@
         <v>78.75</v>
       </c>
       <c r="G456" t="n">
-        <v>69.8513870239258</v>
+        <v>69.8513946533203</v>
       </c>
       <c r="H456" t="n">
         <v>105461</v>
@@ -13622,7 +13622,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G457" t="n">
-        <v>71.4479904174805</v>
+        <v>71.4480056762695</v>
       </c>
       <c r="H457" t="n">
         <v>165700</v>
@@ -13651,7 +13651,7 @@
         <v>78.75</v>
       </c>
       <c r="G458" t="n">
-        <v>69.8513870239258</v>
+        <v>69.8513946533203</v>
       </c>
       <c r="H458" t="n">
         <v>206055</v>
@@ -13680,7 +13680,7 @@
         <v>79</v>
       </c>
       <c r="G459" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731506347656</v>
       </c>
       <c r="H459" t="n">
         <v>72167</v>
@@ -13709,7 +13709,7 @@
         <v>79</v>
       </c>
       <c r="G460" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731506347656</v>
       </c>
       <c r="H460" t="n">
         <v>72203</v>
@@ -13738,7 +13738,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G461" t="n">
-        <v>69.5852813720703</v>
+        <v>69.5852737426758</v>
       </c>
       <c r="H461" t="n">
         <v>88886</v>
@@ -13767,7 +13767,7 @@
         <v>77.75</v>
       </c>
       <c r="G462" t="n">
-        <v>68.9643936157227</v>
+        <v>68.9643859863281</v>
       </c>
       <c r="H462" t="n">
         <v>79077</v>
@@ -13796,7 +13796,7 @@
         <v>77.8499984741211</v>
       </c>
       <c r="G463" t="n">
-        <v>69.0530776977539</v>
+        <v>69.0530853271484</v>
       </c>
       <c r="H463" t="n">
         <v>68100</v>
@@ -13825,7 +13825,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G464" t="n">
-        <v>69.0087280273438</v>
+        <v>69.0087356567383</v>
       </c>
       <c r="H464" t="n">
         <v>68089</v>
@@ -13854,7 +13854,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G465" t="n">
-        <v>69.2304840087891</v>
+        <v>69.2304916381836</v>
       </c>
       <c r="H465" t="n">
         <v>102722</v>
@@ -13970,7 +13970,7 @@
         <v>78</v>
       </c>
       <c r="G469" t="n">
-        <v>69.1861343383789</v>
+        <v>69.1861267089844</v>
       </c>
       <c r="H469" t="n">
         <v>75889</v>
@@ -13999,7 +13999,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G470" t="n">
-        <v>69.2748336791992</v>
+        <v>69.2748413085938</v>
       </c>
       <c r="H470" t="n">
         <v>74903</v>
@@ -14028,7 +14028,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G471" t="n">
-        <v>70.0287857055664</v>
+        <v>70.0287780761719</v>
       </c>
       <c r="H471" t="n">
         <v>89387</v>
@@ -14086,7 +14086,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G473" t="n">
-        <v>70.2505416870117</v>
+        <v>70.2505340576172</v>
       </c>
       <c r="H473" t="n">
         <v>98034</v>
@@ -14115,7 +14115,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G474" t="n">
-        <v>69.6739883422852</v>
+        <v>69.6739959716797</v>
       </c>
       <c r="H474" t="n">
         <v>75930</v>
@@ -14144,7 +14144,7 @@
         <v>78.25</v>
       </c>
       <c r="G475" t="n">
-        <v>69.4078826904297</v>
+        <v>69.4079055786133</v>
       </c>
       <c r="H475" t="n">
         <v>56037</v>
@@ -14173,7 +14173,7 @@
         <v>77.75</v>
       </c>
       <c r="G476" t="n">
-        <v>68.9643936157227</v>
+        <v>68.9643859863281</v>
       </c>
       <c r="H476" t="n">
         <v>111473</v>
@@ -14289,7 +14289,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>66.2146759033203</v>
+        <v>66.2146911621094</v>
       </c>
       <c r="H480" t="n">
         <v>137194</v>
@@ -14318,7 +14318,7 @@
         <v>74</v>
       </c>
       <c r="G481" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H481" t="n">
         <v>60994</v>
@@ -14376,7 +14376,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G483" t="n">
-        <v>66.5694885253906</v>
+        <v>66.5694808959961</v>
       </c>
       <c r="H483" t="n">
         <v>31199</v>
@@ -14405,7 +14405,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>67.9886856079102</v>
+        <v>67.9887084960938</v>
       </c>
       <c r="H484" t="n">
         <v>41631</v>
@@ -14550,7 +14550,7 @@
         <v>75.6500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>67.1016845703125</v>
+        <v>67.1016998291016</v>
       </c>
       <c r="H489" t="n">
         <v>55696</v>
@@ -14608,7 +14608,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G491" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999862670898</v>
       </c>
       <c r="H491" t="n">
         <v>52899</v>
@@ -14666,7 +14666,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G493" t="n">
-        <v>69.2304840087891</v>
+        <v>69.2304916381836</v>
       </c>
       <c r="H493" t="n">
         <v>131555</v>
@@ -14695,7 +14695,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>68.8756866455078</v>
+        <v>68.8756790161133</v>
       </c>
       <c r="H494" t="n">
         <v>87616</v>
@@ -14724,7 +14724,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409317016602</v>
       </c>
       <c r="H495" t="n">
         <v>55937</v>
@@ -14753,7 +14753,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G496" t="n">
-        <v>69.5852813720703</v>
+        <v>69.5852737426758</v>
       </c>
       <c r="H496" t="n">
         <v>53005</v>
@@ -14782,7 +14782,7 @@
         <v>79.5500030517578</v>
       </c>
       <c r="G497" t="n">
-        <v>70.5609893798828</v>
+        <v>70.5610046386719</v>
       </c>
       <c r="H497" t="n">
         <v>66956</v>
@@ -14811,7 +14811,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G498" t="n">
-        <v>71.4479904174805</v>
+        <v>71.4480056762695</v>
       </c>
       <c r="H498" t="n">
         <v>114724</v>
@@ -14840,7 +14840,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G499" t="n">
-        <v>71.2705917358398</v>
+        <v>71.2705841064453</v>
       </c>
       <c r="H499" t="n">
         <v>61927</v>
@@ -14869,7 +14869,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>69.6739883422852</v>
+        <v>69.6739959716797</v>
       </c>
       <c r="H500" t="n">
         <v>78057</v>
@@ -14898,7 +14898,7 @@
         <v>77.3499984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>68.6095809936523</v>
+        <v>68.6095886230469</v>
       </c>
       <c r="H501" t="n">
         <v>77973</v>
@@ -14956,7 +14956,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G503" t="n">
-        <v>67.2347412109375</v>
+        <v>67.234733581543</v>
       </c>
       <c r="H503" t="n">
         <v>98841</v>
@@ -15014,7 +15014,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G505" t="n">
-        <v>66.5694885253906</v>
+        <v>66.5694808959961</v>
       </c>
       <c r="H505" t="n">
         <v>78401</v>
@@ -15043,7 +15043,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G506" t="n">
-        <v>67.1460418701172</v>
+        <v>67.1460342407227</v>
       </c>
       <c r="H506" t="n">
         <v>111441</v>
@@ -15101,7 +15101,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G508" t="n">
-        <v>66.0372924804688</v>
+        <v>66.0372772216797</v>
       </c>
       <c r="H508" t="n">
         <v>31305</v>
@@ -15130,7 +15130,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G509" t="n">
-        <v>66.2146759033203</v>
+        <v>66.2146911621094</v>
       </c>
       <c r="H509" t="n">
         <v>49015</v>
@@ -15188,7 +15188,7 @@
         <v>74</v>
       </c>
       <c r="G511" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H511" t="n">
         <v>37851</v>
@@ -15246,7 +15246,7 @@
         <v>74.8499984741211</v>
       </c>
       <c r="G513" t="n">
-        <v>66.3920822143555</v>
+        <v>66.3920745849609</v>
       </c>
       <c r="H513" t="n">
         <v>58114</v>
@@ -15304,7 +15304,7 @@
         <v>76.8000030517578</v>
       </c>
       <c r="G515" t="n">
-        <v>68.1217346191406</v>
+        <v>68.1217422485352</v>
       </c>
       <c r="H515" t="n">
         <v>65184</v>
@@ -15449,7 +15449,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G520" t="n">
-        <v>70.6940383911133</v>
+        <v>70.6940307617188</v>
       </c>
       <c r="H520" t="n">
         <v>91810</v>
@@ -15478,7 +15478,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G521" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496810913086</v>
       </c>
       <c r="H521" t="n">
         <v>32110</v>
@@ -15507,7 +15507,7 @@
         <v>79.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>70.3835906982422</v>
+        <v>70.3835830688477</v>
       </c>
       <c r="H522" t="n">
         <v>38884</v>
@@ -15536,7 +15536,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>70.6496963500977</v>
+        <v>70.6496810913086</v>
       </c>
       <c r="H523" t="n">
         <v>44134</v>
@@ -15623,7 +15623,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G526" t="n">
-        <v>70.1618423461914</v>
+        <v>70.1618347167969</v>
       </c>
       <c r="H526" t="n">
         <v>32335</v>
@@ -15652,7 +15652,7 @@
         <v>79.0500030517578</v>
       </c>
       <c r="G527" t="n">
-        <v>70.1174926757812</v>
+        <v>70.1175003051758</v>
       </c>
       <c r="H527" t="n">
         <v>54775</v>
@@ -15681,7 +15681,7 @@
         <v>79</v>
       </c>
       <c r="G528" t="n">
-        <v>70.0731353759766</v>
+        <v>70.0731506347656</v>
       </c>
       <c r="H528" t="n">
         <v>24694</v>
@@ -15710,7 +15710,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409317016602</v>
       </c>
       <c r="H529" t="n">
         <v>38771</v>
@@ -15855,7 +15855,7 @@
         <v>79.4000015258789</v>
       </c>
       <c r="G534" t="n">
-        <v>70.4279403686523</v>
+        <v>70.4279479980469</v>
       </c>
       <c r="H534" t="n">
         <v>92393</v>
@@ -15884,7 +15884,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G535" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999862670898</v>
       </c>
       <c r="H535" t="n">
         <v>80635</v>
@@ -15913,7 +15913,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>66.8355865478516</v>
+        <v>66.8355941772461</v>
       </c>
       <c r="H536" t="n">
         <v>74286</v>
@@ -15942,7 +15942,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G537" t="n">
-        <v>65.1502838134766</v>
+        <v>65.150276184082</v>
       </c>
       <c r="H537" t="n">
         <v>108860</v>
@@ -15971,7 +15971,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G538" t="n">
-        <v>67.1460418701172</v>
+        <v>67.1460342407227</v>
       </c>
       <c r="H538" t="n">
         <v>141070</v>
@@ -16000,7 +16000,7 @@
         <v>74.0999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>65.7268295288086</v>
+        <v>65.7268218994141</v>
       </c>
       <c r="H539" t="n">
         <v>74319</v>
@@ -16029,7 +16029,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G540" t="n">
-        <v>61.690975189209</v>
+        <v>61.6909713745117</v>
       </c>
       <c r="H540" t="n">
         <v>177993</v>
@@ -16087,7 +16087,7 @@
         <v>71</v>
       </c>
       <c r="G542" t="n">
-        <v>62.9771156311035</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H542" t="n">
         <v>60963</v>
@@ -16116,7 +16116,7 @@
         <v>70</v>
       </c>
       <c r="G543" t="n">
-        <v>62.0901374816895</v>
+        <v>62.0901145935059</v>
       </c>
       <c r="H543" t="n">
         <v>98122</v>
@@ -16145,7 +16145,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G544" t="n">
-        <v>62.4449272155762</v>
+        <v>62.4449310302734</v>
       </c>
       <c r="H544" t="n">
         <v>107264</v>
@@ -16203,7 +16203,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014381408691</v>
       </c>
       <c r="H546" t="n">
         <v>100665</v>
@@ -16232,7 +16232,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G547" t="n">
-        <v>61.690975189209</v>
+        <v>61.6909713745117</v>
       </c>
       <c r="H547" t="n">
         <v>113369</v>
@@ -16261,7 +16261,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G548" t="n">
-        <v>61.912727355957</v>
+        <v>61.9127311706543</v>
       </c>
       <c r="H548" t="n">
         <v>73072</v>
@@ -16290,7 +16290,7 @@
         <v>69.6500015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>61.7796745300293</v>
+        <v>61.7796821594238</v>
       </c>
       <c r="H549" t="n">
         <v>58126</v>
@@ -16319,7 +16319,7 @@
         <v>69.75</v>
       </c>
       <c r="G550" t="n">
-        <v>61.8683700561523</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H550" t="n">
         <v>130511</v>
@@ -16377,7 +16377,7 @@
         <v>68.5</v>
       </c>
       <c r="G552" t="n">
-        <v>60.7596244812012</v>
+        <v>60.7596130371094</v>
       </c>
       <c r="H552" t="n">
         <v>106726</v>
@@ -16406,7 +16406,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>59.8282699584961</v>
+        <v>59.8282623291016</v>
       </c>
       <c r="H553" t="n">
         <v>167258</v>
@@ -16435,7 +16435,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>58.8969268798828</v>
+        <v>58.8969192504883</v>
       </c>
       <c r="H554" t="n">
         <v>163250</v>
@@ -16464,7 +16464,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>58.6308212280273</v>
+        <v>58.6308135986328</v>
       </c>
       <c r="H555" t="n">
         <v>140188</v>
@@ -16493,7 +16493,7 @@
         <v>67.3499984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>59.7395706176758</v>
+        <v>59.7395629882812</v>
       </c>
       <c r="H556" t="n">
         <v>65605</v>
@@ -16522,7 +16522,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>60.6709327697754</v>
+        <v>60.6709251403809</v>
       </c>
       <c r="H557" t="n">
         <v>96155</v>
@@ -16551,7 +16551,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G558" t="n">
-        <v>62.6223258972168</v>
+        <v>62.6223220825195</v>
       </c>
       <c r="H558" t="n">
         <v>201361</v>
@@ -16580,7 +16580,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G559" t="n">
-        <v>65.2389755249023</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H559" t="n">
         <v>157061</v>
@@ -16638,7 +16638,7 @@
         <v>73.8499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>65.5050735473633</v>
+        <v>65.5050888061523</v>
       </c>
       <c r="H561" t="n">
         <v>178088</v>
@@ -16667,7 +16667,7 @@
         <v>74</v>
       </c>
       <c r="G562" t="n">
-        <v>65.6381301879883</v>
+        <v>65.6381378173828</v>
       </c>
       <c r="H562" t="n">
         <v>122457</v>
@@ -16725,7 +16725,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G564" t="n">
-        <v>64.7954711914062</v>
+        <v>64.7954940795898</v>
       </c>
       <c r="H564" t="n">
         <v>119834</v>
@@ -16754,7 +16754,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G565" t="n">
-        <v>64.0415344238281</v>
+        <v>64.0415191650391</v>
       </c>
       <c r="H565" t="n">
         <v>111591</v>
@@ -16870,7 +16870,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G569" t="n">
-        <v>64.4406890869141</v>
+        <v>64.440673828125</v>
       </c>
       <c r="H569" t="n">
         <v>112305</v>
@@ -16899,7 +16899,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>63.5536804199219</v>
+        <v>63.5536727905273</v>
       </c>
       <c r="H570" t="n">
         <v>72259</v>
@@ -16928,7 +16928,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G571" t="n">
-        <v>62.4005661010742</v>
+        <v>62.4005699157715</v>
       </c>
       <c r="H571" t="n">
         <v>80142</v>
@@ -16957,7 +16957,7 @@
         <v>72.6500015258789</v>
       </c>
       <c r="G572" t="n">
-        <v>64.4406890869141</v>
+        <v>64.440673828125</v>
       </c>
       <c r="H572" t="n">
         <v>116056</v>
@@ -17015,7 +17015,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>64.8398284912109</v>
+        <v>64.8398361206055</v>
       </c>
       <c r="H574" t="n">
         <v>52352</v>
@@ -17073,7 +17073,7 @@
         <v>71.75</v>
       </c>
       <c r="G576" t="n">
-        <v>63.6423873901367</v>
+        <v>63.6423759460449</v>
       </c>
       <c r="H576" t="n">
         <v>105782</v>
@@ -17131,7 +17131,7 @@
         <v>73.8499984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>65.5050735473633</v>
+        <v>65.5050888061523</v>
       </c>
       <c r="H578" t="n">
         <v>90582</v>
@@ -17160,7 +17160,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>64.7954711914062</v>
+        <v>64.7954940795898</v>
       </c>
       <c r="H579" t="n">
         <v>99543</v>
@@ -17189,7 +17189,7 @@
         <v>73</v>
       </c>
       <c r="G580" t="n">
-        <v>64.7511291503906</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H580" t="n">
         <v>91866</v>
@@ -17247,7 +17247,7 @@
         <v>73.5</v>
       </c>
       <c r="G582" t="n">
-        <v>65.1946334838867</v>
+        <v>65.1946258544922</v>
       </c>
       <c r="H582" t="n">
         <v>45972</v>
@@ -17276,7 +17276,7 @@
         <v>73.5</v>
       </c>
       <c r="G583" t="n">
-        <v>65.1946334838867</v>
+        <v>65.1946258544922</v>
       </c>
       <c r="H583" t="n">
         <v>44775</v>
@@ -17305,7 +17305,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G584" t="n">
-        <v>66.8355865478516</v>
+        <v>66.8355941772461</v>
       </c>
       <c r="H584" t="n">
         <v>90831</v>
@@ -17334,7 +17334,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G585" t="n">
-        <v>67.0129928588867</v>
+        <v>67.0129852294922</v>
       </c>
       <c r="H585" t="n">
         <v>77497</v>
@@ -17363,7 +17363,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>68.8313217163086</v>
+        <v>68.8313293457031</v>
       </c>
       <c r="H586" t="n">
         <v>170948</v>
@@ -17450,7 +17450,7 @@
         <v>76.1999969482422</v>
       </c>
       <c r="G589" t="n">
-        <v>67.5895385742188</v>
+        <v>67.5895309448242</v>
       </c>
       <c r="H589" t="n">
         <v>77037</v>
@@ -17479,7 +17479,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409317016602</v>
       </c>
       <c r="H590" t="n">
         <v>130725</v>
@@ -17508,7 +17508,7 @@
         <v>77.3000030517578</v>
       </c>
       <c r="G591" t="n">
-        <v>68.5652389526367</v>
+        <v>68.5652542114258</v>
       </c>
       <c r="H591" t="n">
         <v>67536</v>
@@ -17537,7 +17537,7 @@
         <v>78.1500015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>69.3191909790039</v>
+        <v>69.3191833496094</v>
       </c>
       <c r="H592" t="n">
         <v>49026</v>
@@ -17566,7 +17566,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409317016602</v>
       </c>
       <c r="H593" t="n">
         <v>58135</v>
@@ -17624,7 +17624,7 @@
         <v>78.6999969482422</v>
       </c>
       <c r="G595" t="n">
-        <v>69.8070373535156</v>
+        <v>69.8070220947266</v>
       </c>
       <c r="H595" t="n">
         <v>103931</v>
@@ -17653,7 +17653,7 @@
         <v>78</v>
       </c>
       <c r="G596" t="n">
-        <v>69.1861343383789</v>
+        <v>69.1861267089844</v>
       </c>
       <c r="H596" t="n">
         <v>101024</v>
@@ -17682,7 +17682,7 @@
         <v>78.6500015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>69.7627029418945</v>
+        <v>69.7626876831055</v>
       </c>
       <c r="H597" t="n">
         <v>54121</v>
@@ -17769,7 +17769,7 @@
         <v>80.4000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>71.31494140625</v>
+        <v>71.3149337768555</v>
       </c>
       <c r="H600" t="n">
         <v>84989</v>
@@ -17798,7 +17798,7 @@
         <v>81.5500030517578</v>
       </c>
       <c r="G601" t="n">
-        <v>72.3349914550781</v>
+        <v>72.3349990844727</v>
       </c>
       <c r="H601" t="n">
         <v>110542</v>
@@ -17885,7 +17885,7 @@
         <v>81</v>
       </c>
       <c r="G604" t="n">
-        <v>71.8471450805664</v>
+        <v>71.8471374511719</v>
       </c>
       <c r="H604" t="n">
         <v>84633</v>
@@ -17914,7 +17914,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G605" t="n">
-        <v>72.024543762207</v>
+        <v>72.0245361328125</v>
       </c>
       <c r="H605" t="n">
         <v>98632</v>
@@ -17943,7 +17943,7 @@
         <v>82.6500015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>73.3106994628906</v>
+        <v>73.3106918334961</v>
       </c>
       <c r="H606" t="n">
         <v>90912</v>
@@ -18001,7 +18001,7 @@
         <v>81.25</v>
       </c>
       <c r="G608" t="n">
-        <v>72.8294067382812</v>
+        <v>72.8293991088867</v>
       </c>
       <c r="H608" t="n">
         <v>62147</v>
@@ -18030,7 +18030,7 @@
         <v>81.9000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>73.4120407104492</v>
+        <v>73.4120330810547</v>
       </c>
       <c r="H609" t="n">
         <v>82870</v>
@@ -18088,7 +18088,7 @@
         <v>82.0500030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>73.5464859008789</v>
+        <v>73.5464935302734</v>
       </c>
       <c r="H611" t="n">
         <v>73748</v>
@@ -18146,7 +18146,7 @@
         <v>83</v>
       </c>
       <c r="G613" t="n">
-        <v>74.3980331420898</v>
+        <v>74.3980255126953</v>
       </c>
       <c r="H613" t="n">
         <v>81300</v>
@@ -18175,7 +18175,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G614" t="n">
-        <v>72.7845764160156</v>
+        <v>72.7845687866211</v>
       </c>
       <c r="H614" t="n">
         <v>180565</v>
@@ -18204,7 +18204,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G615" t="n">
-        <v>75.8322067260742</v>
+        <v>75.8321990966797</v>
       </c>
       <c r="H615" t="n">
         <v>139846</v>
@@ -18262,7 +18262,7 @@
         <v>85.5</v>
       </c>
       <c r="G617" t="n">
-        <v>76.6389312744141</v>
+        <v>76.6389389038086</v>
       </c>
       <c r="H617" t="n">
         <v>117653</v>
@@ -18320,7 +18320,7 @@
         <v>88.25</v>
       </c>
       <c r="G619" t="n">
-        <v>79.1039352416992</v>
+        <v>79.1039199829102</v>
       </c>
       <c r="H619" t="n">
         <v>91300</v>
@@ -18349,7 +18349,7 @@
         <v>88</v>
       </c>
       <c r="G620" t="n">
-        <v>78.8798446655273</v>
+        <v>78.8798370361328</v>
       </c>
       <c r="H620" t="n">
         <v>90647</v>
@@ -18465,7 +18465,7 @@
         <v>91</v>
       </c>
       <c r="G624" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H624" t="n">
         <v>130037</v>
@@ -18523,7 +18523,7 @@
         <v>93.3499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>83.6753768920898</v>
+        <v>83.6753692626953</v>
       </c>
       <c r="H626" t="n">
         <v>69385</v>
@@ -18552,7 +18552,7 @@
         <v>93</v>
       </c>
       <c r="G627" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H627" t="n">
         <v>96749</v>
@@ -18610,7 +18610,7 @@
         <v>90.9499969482422</v>
       </c>
       <c r="G629" t="n">
-        <v>81.5241088867188</v>
+        <v>81.5241012573242</v>
       </c>
       <c r="H629" t="n">
         <v>123549</v>
@@ -18639,7 +18639,7 @@
         <v>89.5</v>
       </c>
       <c r="G630" t="n">
-        <v>80.2243728637695</v>
+        <v>80.2243881225586</v>
       </c>
       <c r="H630" t="n">
         <v>107271</v>
@@ -18668,7 +18668,7 @@
         <v>89.1500015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>79.9106674194336</v>
+        <v>79.9106597900391</v>
       </c>
       <c r="H631" t="n">
         <v>85755</v>
@@ -18697,7 +18697,7 @@
         <v>96</v>
       </c>
       <c r="G632" t="n">
-        <v>86.0507431030273</v>
+        <v>86.0507354736328</v>
       </c>
       <c r="H632" t="n">
         <v>142895</v>
@@ -18755,7 +18755,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G634" t="n">
-        <v>85.7818298339844</v>
+        <v>85.7818222045898</v>
       </c>
       <c r="H634" t="n">
         <v>55163</v>
@@ -18813,7 +18813,7 @@
         <v>96.3499984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>86.3644561767578</v>
+        <v>86.3644638061523</v>
       </c>
       <c r="H636" t="n">
         <v>136400</v>
@@ -18958,7 +18958,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>85.6473846435547</v>
+        <v>85.6473770141602</v>
       </c>
       <c r="H641" t="n">
         <v>108916</v>
@@ -18987,7 +18987,7 @@
         <v>96</v>
       </c>
       <c r="G642" t="n">
-        <v>86.0507431030273</v>
+        <v>86.0507354736328</v>
       </c>
       <c r="H642" t="n">
         <v>86861</v>
@@ -19016,7 +19016,7 @@
         <v>95.8000030517578</v>
       </c>
       <c r="G643" t="n">
-        <v>85.871467590332</v>
+        <v>85.8714828491211</v>
       </c>
       <c r="H643" t="n">
         <v>46270</v>
@@ -19045,7 +19045,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G644" t="n">
-        <v>85.9611053466797</v>
+        <v>85.9610977172852</v>
       </c>
       <c r="H644" t="n">
         <v>45786</v>
@@ -19132,7 +19132,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>87.5297241210938</v>
+        <v>87.5297470092773</v>
       </c>
       <c r="H647" t="n">
         <v>29778</v>
@@ -19161,7 +19161,7 @@
         <v>97.9000015258789</v>
       </c>
       <c r="G648" t="n">
-        <v>87.7538146972656</v>
+        <v>87.7538070678711</v>
       </c>
       <c r="H648" t="n">
         <v>36696</v>
@@ -19219,7 +19219,7 @@
         <v>95.9499969482422</v>
       </c>
       <c r="G650" t="n">
-        <v>86.0059051513672</v>
+        <v>86.0059127807617</v>
       </c>
       <c r="H650" t="n">
         <v>65806</v>
@@ -19364,7 +19364,7 @@
         <v>94.3499984741211</v>
       </c>
       <c r="G655" t="n">
-        <v>84.5717315673828</v>
+        <v>84.5717468261719</v>
       </c>
       <c r="H655" t="n">
         <v>105068</v>
@@ -19393,7 +19393,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G656" t="n">
-        <v>82.8686370849609</v>
+        <v>82.8686447143555</v>
       </c>
       <c r="H656" t="n">
         <v>119477</v>
@@ -19422,7 +19422,7 @@
         <v>93</v>
       </c>
       <c r="G657" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H657" t="n">
         <v>92816</v>
@@ -19451,7 +19451,7 @@
         <v>92.5</v>
       </c>
       <c r="G658" t="n">
-        <v>82.9134674072266</v>
+        <v>82.913459777832</v>
       </c>
       <c r="H658" t="n">
         <v>79668</v>
@@ -19509,7 +19509,7 @@
         <v>93</v>
       </c>
       <c r="G660" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616409301758</v>
       </c>
       <c r="H660" t="n">
         <v>69462</v>
@@ -19654,7 +19654,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>78.7453842163086</v>
+        <v>78.7453765869141</v>
       </c>
       <c r="H665" t="n">
         <v>107411</v>
@@ -19683,7 +19683,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>78.969482421875</v>
+        <v>78.9694747924805</v>
       </c>
       <c r="H666" t="n">
         <v>78905</v>
@@ -19712,7 +19712,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>78.7453842163086</v>
+        <v>78.7453765869141</v>
       </c>
       <c r="H667" t="n">
         <v>58890</v>
@@ -19741,7 +19741,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>77.8938446044922</v>
+        <v>77.8938522338867</v>
       </c>
       <c r="H668" t="n">
         <v>42176</v>
@@ -19770,7 +19770,7 @@
         <v>88.1500015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>79.014289855957</v>
+        <v>79.0142974853516</v>
       </c>
       <c r="H669" t="n">
         <v>48700</v>
@@ -19799,7 +19799,7 @@
         <v>86.5500030517578</v>
       </c>
       <c r="G670" t="n">
-        <v>77.5801162719727</v>
+        <v>77.5801239013672</v>
       </c>
       <c r="H670" t="n">
         <v>73123</v>
@@ -19857,7 +19857,7 @@
         <v>93.1999969482422</v>
       </c>
       <c r="G672" t="n">
-        <v>83.5409164428711</v>
+        <v>83.5409240722656</v>
       </c>
       <c r="H672" t="n">
         <v>124136</v>
@@ -19886,7 +19886,7 @@
         <v>93.75</v>
       </c>
       <c r="G673" t="n">
-        <v>84.0339126586914</v>
+        <v>84.0339202880859</v>
       </c>
       <c r="H673" t="n">
         <v>153238</v>
@@ -19915,7 +19915,7 @@
         <v>91.5</v>
       </c>
       <c r="G674" t="n">
-        <v>82.0170974731445</v>
+        <v>82.0171127319336</v>
       </c>
       <c r="H674" t="n">
         <v>117256</v>
@@ -20002,7 +20002,7 @@
         <v>91.1500015258789</v>
       </c>
       <c r="G677" t="n">
-        <v>81.7033843994141</v>
+        <v>81.7033767700195</v>
       </c>
       <c r="H677" t="n">
         <v>62973</v>
@@ -20060,7 +20060,7 @@
         <v>92.9000015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>83.2720108032227</v>
+        <v>83.2720031738281</v>
       </c>
       <c r="H679" t="n">
         <v>59481</v>
@@ -20089,7 +20089,7 @@
         <v>93.8000030517578</v>
       </c>
       <c r="G680" t="n">
-        <v>84.078742980957</v>
+        <v>84.078727722168</v>
       </c>
       <c r="H680" t="n">
         <v>57437</v>
@@ -20118,7 +20118,7 @@
         <v>93.8000030517578</v>
       </c>
       <c r="G681" t="n">
-        <v>84.078742980957</v>
+        <v>84.078727722168</v>
       </c>
       <c r="H681" t="n">
         <v>52413</v>
@@ -20147,7 +20147,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G682" t="n">
-        <v>82.8686370849609</v>
+        <v>82.8686447143555</v>
       </c>
       <c r="H682" t="n">
         <v>33661</v>
@@ -20176,7 +20176,7 @@
         <v>92.3499984741211</v>
       </c>
       <c r="G683" t="n">
-        <v>82.7790145874023</v>
+        <v>82.7790069580078</v>
       </c>
       <c r="H683" t="n">
         <v>59883</v>
@@ -20379,7 +20379,7 @@
         <v>89.5</v>
       </c>
       <c r="G690" t="n">
-        <v>80.2243728637695</v>
+        <v>80.2243881225586</v>
       </c>
       <c r="H690" t="n">
         <v>37780</v>
@@ -20408,7 +20408,7 @@
         <v>89</v>
       </c>
       <c r="G691" t="n">
-        <v>79.7761917114258</v>
+        <v>79.7761993408203</v>
       </c>
       <c r="H691" t="n">
         <v>27813</v>
@@ -20466,7 +20466,7 @@
         <v>93.75</v>
       </c>
       <c r="G693" t="n">
-        <v>84.0339126586914</v>
+        <v>84.0339202880859</v>
       </c>
       <c r="H693" t="n">
         <v>162492</v>
@@ -20524,7 +20524,7 @@
         <v>97.1999969482422</v>
       </c>
       <c r="G695" t="n">
-        <v>87.1263656616211</v>
+        <v>87.1263580322266</v>
       </c>
       <c r="H695" t="n">
         <v>153783</v>
@@ -20553,7 +20553,7 @@
         <v>92.25</v>
       </c>
       <c r="G696" t="n">
-        <v>82.6893692016602</v>
+        <v>82.6893844604492</v>
       </c>
       <c r="H696" t="n">
         <v>661740</v>
@@ -20582,7 +20582,7 @@
         <v>91.5</v>
       </c>
       <c r="G697" t="n">
-        <v>82.0170974731445</v>
+        <v>82.0171127319336</v>
       </c>
       <c r="H697" t="n">
         <v>122508</v>
@@ -20611,7 +20611,7 @@
         <v>93.0999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>83.451286315918</v>
+        <v>83.4512786865234</v>
       </c>
       <c r="H698" t="n">
         <v>72943</v>
@@ -20669,7 +20669,7 @@
         <v>91</v>
       </c>
       <c r="G700" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H700" t="n">
         <v>78519</v>
@@ -20698,7 +20698,7 @@
         <v>90.5999984741211</v>
       </c>
       <c r="G701" t="n">
-        <v>81.2103805541992</v>
+        <v>81.2103729248047</v>
       </c>
       <c r="H701" t="n">
         <v>145913</v>
@@ -20727,7 +20727,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G702" t="n">
-        <v>81.8378372192383</v>
+        <v>81.8378448486328</v>
       </c>
       <c r="H702" t="n">
         <v>82540</v>
@@ -20756,7 +20756,7 @@
         <v>91</v>
       </c>
       <c r="G703" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H703" t="n">
         <v>65461</v>
@@ -20785,7 +20785,7 @@
         <v>90.5999984741211</v>
       </c>
       <c r="G704" t="n">
-        <v>81.2103805541992</v>
+        <v>81.2103729248047</v>
       </c>
       <c r="H704" t="n">
         <v>37461</v>
@@ -20843,7 +20843,7 @@
         <v>86.8000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>77.8042068481445</v>
+        <v>77.8042144775391</v>
       </c>
       <c r="H706" t="n">
         <v>256998</v>
@@ -20872,7 +20872,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G707" t="n">
-        <v>73.7705841064453</v>
+        <v>73.7705764770508</v>
       </c>
       <c r="H707" t="n">
         <v>126590</v>
@@ -20901,7 +20901,7 @@
         <v>81.5</v>
       </c>
       <c r="G708" t="n">
-        <v>73.0534820556641</v>
+        <v>73.0534896850586</v>
       </c>
       <c r="H708" t="n">
         <v>106072</v>
@@ -20959,7 +20959,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G710" t="n">
-        <v>71.4400405883789</v>
+        <v>71.4400329589844</v>
       </c>
       <c r="H710" t="n">
         <v>100334</v>
@@ -21017,7 +21017,7 @@
         <v>79.5</v>
       </c>
       <c r="G712" t="n">
-        <v>71.2607650756836</v>
+        <v>71.2607574462891</v>
       </c>
       <c r="H712" t="n">
         <v>87671</v>
@@ -21046,7 +21046,7 @@
         <v>79.8499984741211</v>
       </c>
       <c r="G713" t="n">
-        <v>71.5744934082031</v>
+        <v>71.5744857788086</v>
       </c>
       <c r="H713" t="n">
         <v>121176</v>
@@ -21104,7 +21104,7 @@
         <v>82</v>
       </c>
       <c r="G715" t="n">
-        <v>73.5016632080078</v>
+        <v>73.5016708374023</v>
       </c>
       <c r="H715" t="n">
         <v>86910</v>
@@ -21133,7 +21133,7 @@
         <v>82.4000015258789</v>
       </c>
       <c r="G716" t="n">
-        <v>73.860221862793</v>
+        <v>73.8602294921875</v>
       </c>
       <c r="H716" t="n">
         <v>56700</v>
@@ -21220,7 +21220,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G719" t="n">
-        <v>72.2019424438477</v>
+        <v>72.2019577026367</v>
       </c>
       <c r="H719" t="n">
         <v>39216</v>
@@ -21365,7 +21365,7 @@
         <v>83.8000030517578</v>
       </c>
       <c r="G724" t="n">
-        <v>75.115119934082</v>
+        <v>75.1151275634766</v>
       </c>
       <c r="H724" t="n">
         <v>192896</v>
@@ -21394,7 +21394,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G725" t="n">
-        <v>77.8938446044922</v>
+        <v>77.8938522338867</v>
       </c>
       <c r="H725" t="n">
         <v>101199</v>
@@ -21423,7 +21423,7 @@
         <v>86.5500030517578</v>
       </c>
       <c r="G726" t="n">
-        <v>77.5801162719727</v>
+        <v>77.5801239013672</v>
       </c>
       <c r="H726" t="n">
         <v>89277</v>
@@ -21452,7 +21452,7 @@
         <v>87.5500030517578</v>
       </c>
       <c r="G727" t="n">
-        <v>78.4764862060547</v>
+        <v>78.4764785766602</v>
       </c>
       <c r="H727" t="n">
         <v>78626</v>
@@ -21626,7 +21626,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G733" t="n">
-        <v>73.7705841064453</v>
+        <v>73.7705764770508</v>
       </c>
       <c r="H733" t="n">
         <v>77523</v>
@@ -21713,7 +21713,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G736" t="n">
-        <v>72.7845764160156</v>
+        <v>72.7845687866211</v>
       </c>
       <c r="H736" t="n">
         <v>43768</v>
@@ -21829,7 +21829,7 @@
         <v>77.8499984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>69.7817535400391</v>
+        <v>69.7817687988281</v>
       </c>
       <c r="H740" t="n">
         <v>60230</v>
@@ -21858,7 +21858,7 @@
         <v>78.8000030517578</v>
       </c>
       <c r="G741" t="n">
-        <v>70.6333084106445</v>
+        <v>70.6333236694336</v>
       </c>
       <c r="H741" t="n">
         <v>77805</v>
@@ -21887,7 +21887,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G742" t="n">
-        <v>71.7537612915039</v>
+        <v>71.7537689208984</v>
       </c>
       <c r="H742" t="n">
         <v>109282</v>
@@ -21916,7 +21916,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G743" t="n">
-        <v>70.9918518066406</v>
+        <v>70.9918441772461</v>
       </c>
       <c r="H743" t="n">
         <v>95288</v>
@@ -21945,7 +21945,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G744" t="n">
-        <v>69.736946105957</v>
+        <v>69.7369537353516</v>
       </c>
       <c r="H744" t="n">
         <v>92402</v>
@@ -22003,7 +22003,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G746" t="n">
-        <v>67.3167572021484</v>
+        <v>67.316764831543</v>
       </c>
       <c r="H746" t="n">
         <v>166307</v>
@@ -22032,7 +22032,7 @@
         <v>75</v>
       </c>
       <c r="G747" t="n">
-        <v>67.2271347045898</v>
+        <v>67.2271270751953</v>
       </c>
       <c r="H747" t="n">
         <v>640044</v>
@@ -22061,7 +22061,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>67.5856857299805</v>
+        <v>67.5856781005859</v>
       </c>
       <c r="H748" t="n">
         <v>271330</v>
@@ -22090,7 +22090,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>70.0058517456055</v>
+        <v>70.005859375</v>
       </c>
       <c r="H749" t="n">
         <v>206228</v>
@@ -22119,7 +22119,7 @@
         <v>73.1500015258789</v>
       </c>
       <c r="G750" t="n">
-        <v>65.5688705444336</v>
+        <v>65.5688629150391</v>
       </c>
       <c r="H750" t="n">
         <v>439461</v>
@@ -22206,7 +22206,7 @@
         <v>72.9499969482422</v>
       </c>
       <c r="G753" t="n">
-        <v>65.3895874023438</v>
+        <v>65.3895797729492</v>
       </c>
       <c r="H753" t="n">
         <v>81159</v>
@@ -22235,7 +22235,7 @@
         <v>74</v>
       </c>
       <c r="G754" t="n">
-        <v>66.3307723999023</v>
+        <v>66.3307800292969</v>
       </c>
       <c r="H754" t="n">
         <v>138111</v>
@@ -22293,7 +22293,7 @@
         <v>71.75</v>
       </c>
       <c r="G756" t="n">
-        <v>64.3139724731445</v>
+        <v>64.31396484375</v>
       </c>
       <c r="H756" t="n">
         <v>131555</v>
@@ -22380,7 +22380,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>63.103874206543</v>
+        <v>63.1038703918457</v>
       </c>
       <c r="H759" t="n">
         <v>136498</v>
@@ -22409,7 +22409,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G760" t="n">
-        <v>63.5968742370605</v>
+        <v>63.596866607666</v>
       </c>
       <c r="H760" t="n">
         <v>142583</v>
@@ -22467,7 +22467,7 @@
         <v>69.3499984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>63.7464599609375</v>
+        <v>63.746452331543</v>
       </c>
       <c r="H762" t="n">
         <v>134941</v>
@@ -22496,7 +22496,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G763" t="n">
-        <v>64.9873657226562</v>
+        <v>64.9873809814453</v>
       </c>
       <c r="H763" t="n">
         <v>53669</v>
@@ -22525,7 +22525,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G764" t="n">
-        <v>65.4469528198242</v>
+        <v>65.4469680786133</v>
       </c>
       <c r="H764" t="n">
         <v>92132</v>
@@ -22641,7 +22641,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G768" t="n">
-        <v>67.928825378418</v>
+        <v>67.9288101196289</v>
       </c>
       <c r="H768" t="n">
         <v>155662</v>
@@ -22670,7 +22670,7 @@
         <v>74.3499984741211</v>
       </c>
       <c r="G769" t="n">
-        <v>68.3424453735352</v>
+        <v>68.3424377441406</v>
       </c>
       <c r="H769" t="n">
         <v>129576</v>
@@ -22728,7 +22728,7 @@
         <v>74.9000015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>68.8479995727539</v>
+        <v>68.848014831543</v>
       </c>
       <c r="H771" t="n">
         <v>58124</v>
@@ -22757,7 +22757,7 @@
         <v>74.5</v>
       </c>
       <c r="G772" t="n">
-        <v>68.4803314208984</v>
+        <v>68.4803237915039</v>
       </c>
       <c r="H772" t="n">
         <v>50241</v>
@@ -22844,7 +22844,7 @@
         <v>78</v>
       </c>
       <c r="G775" t="n">
-        <v>71.6975250244141</v>
+        <v>71.6975173950195</v>
       </c>
       <c r="H775" t="n">
         <v>84212</v>
@@ -22873,7 +22873,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G776" t="n">
-        <v>73.8576354980469</v>
+        <v>73.8576431274414</v>
       </c>
       <c r="H776" t="n">
         <v>145820</v>
@@ -22931,7 +22931,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G778" t="n">
-        <v>73.5818786621094</v>
+        <v>73.5818939208984</v>
       </c>
       <c r="H778" t="n">
         <v>152719</v>
@@ -22960,7 +22960,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G779" t="n">
-        <v>73.2141952514648</v>
+        <v>73.2142028808594</v>
       </c>
       <c r="H779" t="n">
         <v>139876</v>
@@ -23018,7 +23018,7 @@
         <v>80.4000015258789</v>
       </c>
       <c r="G781" t="n">
-        <v>73.9036026000977</v>
+        <v>73.9035949707031</v>
       </c>
       <c r="H781" t="n">
         <v>72255</v>
@@ -23047,7 +23047,7 @@
         <v>79.75</v>
       </c>
       <c r="G782" t="n">
-        <v>73.3061370849609</v>
+        <v>73.3061218261719</v>
       </c>
       <c r="H782" t="n">
         <v>62554</v>
@@ -23076,7 +23076,7 @@
         <v>81.75</v>
       </c>
       <c r="G783" t="n">
-        <v>75.1445083618164</v>
+        <v>75.1445236206055</v>
       </c>
       <c r="H783" t="n">
         <v>104802</v>
@@ -23105,7 +23105,7 @@
         <v>81.3000030517578</v>
       </c>
       <c r="G784" t="n">
-        <v>74.7308959960938</v>
+        <v>74.7308883666992</v>
       </c>
       <c r="H784" t="n">
         <v>123024</v>
@@ -23134,7 +23134,7 @@
         <v>79.9499969482422</v>
       </c>
       <c r="G785" t="n">
-        <v>73.4899520874023</v>
+        <v>73.4899673461914</v>
       </c>
       <c r="H785" t="n">
         <v>91066</v>
@@ -23163,7 +23163,7 @@
         <v>82.0999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>75.4662399291992</v>
+        <v>75.4662322998047</v>
       </c>
       <c r="H786" t="n">
         <v>190749</v>
@@ -23192,7 +23192,7 @@
         <v>82.1999969482422</v>
       </c>
       <c r="G787" t="n">
-        <v>75.5581512451172</v>
+        <v>75.5581588745117</v>
       </c>
       <c r="H787" t="n">
         <v>150444</v>
@@ -23221,7 +23221,7 @@
         <v>84.0500030517578</v>
       </c>
       <c r="G788" t="n">
-        <v>77.2586822509766</v>
+        <v>77.2586898803711</v>
       </c>
       <c r="H788" t="n">
         <v>88125</v>
@@ -23250,7 +23250,7 @@
         <v>83.9499969482422</v>
       </c>
       <c r="G789" t="n">
-        <v>77.1667633056641</v>
+        <v>77.166748046875</v>
       </c>
       <c r="H789" t="n">
         <v>89975</v>
@@ -23337,7 +23337,7 @@
         <v>85</v>
       </c>
       <c r="G792" t="n">
-        <v>78.1319198608398</v>
+        <v>78.1319274902344</v>
       </c>
       <c r="H792" t="n">
         <v>60802</v>
@@ -23366,7 +23366,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G793" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H793" t="n">
         <v>114380</v>
@@ -23395,7 +23395,7 @@
         <v>85</v>
       </c>
       <c r="G794" t="n">
-        <v>78.1319198608398</v>
+        <v>78.1319274902344</v>
       </c>
       <c r="H794" t="n">
         <v>83750</v>
@@ -23424,7 +23424,7 @@
         <v>84.8000030517578</v>
       </c>
       <c r="G795" t="n">
-        <v>77.9480819702148</v>
+        <v>77.9480895996094</v>
       </c>
       <c r="H795" t="n">
         <v>81092</v>
@@ -23453,7 +23453,7 @@
         <v>85.1999969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>78.3157501220703</v>
+        <v>78.3157424926758</v>
       </c>
       <c r="H796" t="n">
         <v>100025</v>
@@ -23482,7 +23482,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G797" t="n">
-        <v>78.5455551147461</v>
+        <v>78.545539855957</v>
       </c>
       <c r="H797" t="n">
         <v>105022</v>
@@ -23511,7 +23511,7 @@
         <v>84.4000015258789</v>
       </c>
       <c r="G798" t="n">
-        <v>77.5804061889648</v>
+        <v>77.5803985595703</v>
       </c>
       <c r="H798" t="n">
         <v>86893</v>
@@ -23540,7 +23540,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H799" t="n">
         <v>72446</v>
@@ -23627,7 +23627,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642364501953</v>
       </c>
       <c r="H802" t="n">
         <v>78894</v>
@@ -23714,7 +23714,7 @@
         <v>86.25</v>
       </c>
       <c r="G805" t="n">
-        <v>79.2809066772461</v>
+        <v>79.2809143066406</v>
       </c>
       <c r="H805" t="n">
         <v>103167</v>
@@ -23772,7 +23772,7 @@
         <v>87.25</v>
       </c>
       <c r="G807" t="n">
-        <v>80.2001190185547</v>
+        <v>80.2001113891602</v>
       </c>
       <c r="H807" t="n">
         <v>71430</v>
@@ -23888,7 +23888,7 @@
         <v>86.75</v>
       </c>
       <c r="G811" t="n">
-        <v>79.7405242919922</v>
+        <v>79.7405166625977</v>
       </c>
       <c r="H811" t="n">
         <v>82074</v>
@@ -23917,7 +23917,7 @@
         <v>86.75</v>
       </c>
       <c r="G812" t="n">
-        <v>79.7405242919922</v>
+        <v>79.7405166625977</v>
       </c>
       <c r="H812" t="n">
         <v>53324</v>
@@ -23946,7 +23946,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G813" t="n">
-        <v>80.7056884765625</v>
+        <v>80.705680847168</v>
       </c>
       <c r="H813" t="n">
         <v>67619</v>
@@ -24091,7 +24091,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G818" t="n">
-        <v>80.7516326904297</v>
+        <v>80.7516250610352</v>
       </c>
       <c r="H818" t="n">
         <v>157322</v>
@@ -24149,7 +24149,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G820" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4869918823242</v>
       </c>
       <c r="H820" t="n">
         <v>70750</v>
@@ -24236,7 +24236,7 @@
         <v>89.3499984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>82.1304473876953</v>
+        <v>82.1304321289062</v>
       </c>
       <c r="H823" t="n">
         <v>108948</v>
@@ -24265,7 +24265,7 @@
         <v>88.5999984741211</v>
       </c>
       <c r="G824" t="n">
-        <v>81.441032409668</v>
+        <v>81.4410247802734</v>
       </c>
       <c r="H824" t="n">
         <v>119152</v>
@@ -24294,7 +24294,7 @@
         <v>89.75</v>
       </c>
       <c r="G825" t="n">
-        <v>82.4981079101562</v>
+        <v>82.4981155395508</v>
       </c>
       <c r="H825" t="n">
         <v>86069</v>
@@ -24323,7 +24323,7 @@
         <v>89.6999969482422</v>
       </c>
       <c r="G826" t="n">
-        <v>82.4521636962891</v>
+        <v>82.4521484375</v>
       </c>
       <c r="H826" t="n">
         <v>78107</v>
@@ -24352,7 +24352,7 @@
         <v>90.5500030517578</v>
       </c>
       <c r="G827" t="n">
-        <v>83.2334747314453</v>
+        <v>83.2334823608398</v>
       </c>
       <c r="H827" t="n">
         <v>113522</v>
@@ -24439,7 +24439,7 @@
         <v>92</v>
       </c>
       <c r="G830" t="n">
-        <v>84.5663070678711</v>
+        <v>84.5663146972656</v>
       </c>
       <c r="H830" t="n">
         <v>129196</v>
@@ -24468,7 +24468,7 @@
         <v>92</v>
       </c>
       <c r="G831" t="n">
-        <v>84.5663070678711</v>
+        <v>84.5663146972656</v>
       </c>
       <c r="H831" t="n">
         <v>97582</v>
@@ -24526,7 +24526,7 @@
         <v>91.5</v>
       </c>
       <c r="G833" t="n">
-        <v>84.1067123413086</v>
+        <v>84.1067199707031</v>
       </c>
       <c r="H833" t="n">
         <v>83242</v>
@@ -24555,7 +24555,7 @@
         <v>91</v>
       </c>
       <c r="G834" t="n">
-        <v>83.6471176147461</v>
+        <v>83.6471252441406</v>
       </c>
       <c r="H834" t="n">
         <v>103560</v>
@@ -24584,7 +24584,7 @@
         <v>91</v>
       </c>
       <c r="G835" t="n">
-        <v>83.6471176147461</v>
+        <v>83.6471252441406</v>
       </c>
       <c r="H835" t="n">
         <v>103343</v>
@@ -24613,7 +24613,7 @@
         <v>90.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>83.5551910400391</v>
+        <v>83.5551986694336</v>
       </c>
       <c r="H836" t="n">
         <v>121451</v>
@@ -24642,7 +24642,7 @@
         <v>91.4499969482422</v>
       </c>
       <c r="G837" t="n">
-        <v>84.0607528686523</v>
+        <v>84.0607376098633</v>
       </c>
       <c r="H837" t="n">
         <v>76099</v>
@@ -24671,7 +24671,7 @@
         <v>91</v>
       </c>
       <c r="G838" t="n">
-        <v>83.6471176147461</v>
+        <v>83.6471252441406</v>
       </c>
       <c r="H838" t="n">
         <v>74992</v>
@@ -24700,7 +24700,7 @@
         <v>87.6500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>80.5677947998047</v>
+        <v>80.5678176879883</v>
       </c>
       <c r="H839" t="n">
         <v>196520</v>
@@ -24758,7 +24758,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G841" t="n">
-        <v>80.7056884765625</v>
+        <v>80.705680847168</v>
       </c>
       <c r="H841" t="n">
         <v>122041</v>
@@ -24816,7 +24816,7 @@
         <v>85.1500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>78.2697982788086</v>
+        <v>78.2698059082031</v>
       </c>
       <c r="H843" t="n">
         <v>80115</v>
@@ -24874,7 +24874,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>80.0622406005859</v>
+        <v>80.0622253417969</v>
       </c>
       <c r="H845" t="n">
         <v>103640</v>
@@ -24903,7 +24903,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G846" t="n">
-        <v>80.0622406005859</v>
+        <v>80.0622253417969</v>
       </c>
       <c r="H846" t="n">
         <v>116286</v>
@@ -24932,7 +24932,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G847" t="n">
-        <v>80.0622406005859</v>
+        <v>80.0622253417969</v>
       </c>
       <c r="H847" t="n">
         <v>87670</v>
@@ -24961,7 +24961,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G848" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4869918823242</v>
       </c>
       <c r="H848" t="n">
         <v>104300</v>
@@ -24990,7 +24990,7 @@
         <v>87.4000015258789</v>
       </c>
       <c r="G849" t="n">
-        <v>80.3379821777344</v>
+        <v>80.338005065918</v>
       </c>
       <c r="H849" t="n">
         <v>43250</v>
@@ -25019,7 +25019,7 @@
         <v>89.5</v>
       </c>
       <c r="G850" t="n">
-        <v>82.268310546875</v>
+        <v>82.2683181762695</v>
       </c>
       <c r="H850" t="n">
         <v>211859</v>
@@ -25048,7 +25048,7 @@
         <v>89.9000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>82.635986328125</v>
+        <v>82.6359939575195</v>
       </c>
       <c r="H851" t="n">
         <v>95610</v>
@@ -25077,7 +25077,7 @@
         <v>90</v>
       </c>
       <c r="G852" t="n">
-        <v>82.7279205322266</v>
+        <v>82.727912902832</v>
       </c>
       <c r="H852" t="n">
         <v>97652</v>
@@ -25106,7 +25106,7 @@
         <v>91.0999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>83.7390365600586</v>
+        <v>83.7390289306641</v>
       </c>
       <c r="H853" t="n">
         <v>91325</v>
@@ -25135,7 +25135,7 @@
         <v>91.5</v>
       </c>
       <c r="G854" t="n">
-        <v>84.1067123413086</v>
+        <v>84.1067199707031</v>
       </c>
       <c r="H854" t="n">
         <v>90352</v>
@@ -25164,7 +25164,7 @@
         <v>94.1500015258789</v>
       </c>
       <c r="G855" t="n">
-        <v>86.542594909668</v>
+        <v>86.5426025390625</v>
       </c>
       <c r="H855" t="n">
         <v>167962</v>
@@ -25193,7 +25193,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G856" t="n">
-        <v>87.8294830322266</v>
+        <v>87.829475402832</v>
       </c>
       <c r="H856" t="n">
         <v>153602</v>
@@ -25222,7 +25222,7 @@
         <v>97.4499969482422</v>
       </c>
       <c r="G857" t="n">
-        <v>89.5759429931641</v>
+        <v>89.5759353637695</v>
       </c>
       <c r="H857" t="n">
         <v>106349</v>
@@ -25280,7 +25280,7 @@
         <v>97</v>
       </c>
       <c r="G859" t="n">
-        <v>89.9938735961914</v>
+        <v>89.9938812255859</v>
       </c>
       <c r="H859" t="n">
         <v>90354</v>
@@ -25338,7 +25338,7 @@
         <v>97.5</v>
       </c>
       <c r="G861" t="n">
-        <v>90.4577560424805</v>
+        <v>90.457763671875</v>
       </c>
       <c r="H861" t="n">
         <v>91444</v>
@@ -25396,7 +25396,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>89.1588745117188</v>
+        <v>89.1588821411133</v>
       </c>
       <c r="H863" t="n">
         <v>80875</v>
@@ -25425,7 +25425,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>88.9269332885742</v>
+        <v>88.9269409179688</v>
       </c>
       <c r="H864" t="n">
         <v>34520</v>
@@ -25483,7 +25483,7 @@
         <v>93.4499969482422</v>
       </c>
       <c r="G866" t="n">
-        <v>86.7002792358398</v>
+        <v>86.7002868652344</v>
       </c>
       <c r="H866" t="n">
         <v>108738</v>
@@ -25541,7 +25541,7 @@
         <v>91.5500030517578</v>
       </c>
       <c r="G868" t="n">
-        <v>84.9375228881836</v>
+        <v>84.9375305175781</v>
       </c>
       <c r="H868" t="n">
         <v>138252</v>
@@ -25570,7 +25570,7 @@
         <v>95.3000030517578</v>
       </c>
       <c r="G869" t="n">
-        <v>88.4166717529297</v>
+        <v>88.4166641235352</v>
       </c>
       <c r="H869" t="n">
         <v>177997</v>
@@ -25599,7 +25599,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>89.6691513061523</v>
+        <v>89.6691589355469</v>
       </c>
       <c r="H870" t="n">
         <v>197967</v>
@@ -25628,7 +25628,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G871" t="n">
-        <v>90.2722091674805</v>
+        <v>90.272216796875</v>
       </c>
       <c r="H871" t="n">
         <v>173154</v>
@@ -25657,7 +25657,7 @@
         <v>98.5</v>
       </c>
       <c r="G872" t="n">
-        <v>91.3855209350586</v>
+        <v>91.3855285644531</v>
       </c>
       <c r="H872" t="n">
         <v>105393</v>
@@ -25715,7 +25715,7 @@
         <v>102</v>
       </c>
       <c r="G874" t="n">
-        <v>94.6327438354492</v>
+        <v>94.6327285766602</v>
       </c>
       <c r="H874" t="n">
         <v>88957</v>
@@ -25744,7 +25744,7 @@
         <v>98.5</v>
       </c>
       <c r="G875" t="n">
-        <v>91.3855209350586</v>
+        <v>91.3855285644531</v>
       </c>
       <c r="H875" t="n">
         <v>346930</v>
@@ -25831,7 +25831,7 @@
         <v>103.5</v>
       </c>
       <c r="G878" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H878" t="n">
         <v>247114</v>
@@ -25889,7 +25889,7 @@
         <v>107.199996948242</v>
       </c>
       <c r="G880" t="n">
-        <v>99.4571380615234</v>
+        <v>99.457145690918</v>
       </c>
       <c r="H880" t="n">
         <v>204977</v>
@@ -25918,7 +25918,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G881" t="n">
-        <v>96.8593826293945</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H881" t="n">
         <v>280147</v>
@@ -26005,7 +26005,7 @@
         <v>103.300003051758</v>
       </c>
       <c r="G884" t="n">
-        <v>95.8388442993164</v>
+        <v>95.8388366699219</v>
       </c>
       <c r="H884" t="n">
         <v>90227</v>
@@ -26034,7 +26034,7 @@
         <v>102</v>
       </c>
       <c r="G885" t="n">
-        <v>94.6327438354492</v>
+        <v>94.6327285766602</v>
       </c>
       <c r="H885" t="n">
         <v>62348</v>
@@ -26092,7 +26092,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G887" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399627685547</v>
       </c>
       <c r="H887" t="n">
         <v>51072</v>
@@ -26121,7 +26121,7 @@
         <v>102.099998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>94.7255020141602</v>
+        <v>94.7255172729492</v>
       </c>
       <c r="H888" t="n">
         <v>120137</v>
@@ -26208,7 +26208,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G891" t="n">
-        <v>97.6943893432617</v>
+        <v>97.6943969726562</v>
       </c>
       <c r="H891" t="n">
         <v>134615</v>
@@ -26237,7 +26237,7 @@
         <v>104</v>
       </c>
       <c r="G892" t="n">
-        <v>96.4882888793945</v>
+        <v>96.48828125</v>
       </c>
       <c r="H892" t="n">
         <v>83587</v>
@@ -26266,7 +26266,7 @@
         <v>103</v>
       </c>
       <c r="G893" t="n">
-        <v>95.5605087280273</v>
+        <v>95.5605010986328</v>
       </c>
       <c r="H893" t="n">
         <v>66201</v>
@@ -26295,7 +26295,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G894" t="n">
-        <v>96.3955001831055</v>
+        <v>96.3954925537109</v>
       </c>
       <c r="H894" t="n">
         <v>59104</v>
@@ -26382,7 +26382,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G897" t="n">
-        <v>95.7460556030273</v>
+        <v>95.7460479736328</v>
       </c>
       <c r="H897" t="n">
         <v>98550</v>
@@ -26440,7 +26440,7 @@
         <v>103</v>
       </c>
       <c r="G899" t="n">
-        <v>95.5605087280273</v>
+        <v>95.5605010986328</v>
       </c>
       <c r="H899" t="n">
         <v>49645</v>
@@ -26469,7 +26469,7 @@
         <v>101.800003051758</v>
       </c>
       <c r="G900" t="n">
-        <v>94.4471969604492</v>
+        <v>94.4471893310547</v>
       </c>
       <c r="H900" t="n">
         <v>114464</v>
@@ -26498,7 +26498,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399627685547</v>
       </c>
       <c r="H901" t="n">
         <v>87010</v>
@@ -26556,7 +26556,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G903" t="n">
-        <v>93.9832992553711</v>
+        <v>93.9832916259766</v>
       </c>
       <c r="H903" t="n">
         <v>64496</v>
@@ -26614,7 +26614,7 @@
         <v>102</v>
       </c>
       <c r="G905" t="n">
-        <v>94.6327438354492</v>
+        <v>94.6327285766602</v>
       </c>
       <c r="H905" t="n">
         <v>60880</v>
@@ -26701,7 +26701,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G908" t="n">
-        <v>94.5399551391602</v>
+        <v>94.5399627685547</v>
       </c>
       <c r="H908" t="n">
         <v>73250</v>
@@ -26730,7 +26730,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>95.0038528442383</v>
+        <v>95.0038452148438</v>
       </c>
       <c r="H909" t="n">
         <v>87642</v>
@@ -26759,7 +26759,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G910" t="n">
-        <v>93.9832992553711</v>
+        <v>93.9832916259766</v>
       </c>
       <c r="H910" t="n">
         <v>229110</v>
@@ -26875,7 +26875,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>96.3955001831055</v>
+        <v>96.3954925537109</v>
       </c>
       <c r="H914" t="n">
         <v>137806</v>
@@ -26904,7 +26904,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G915" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H915" t="n">
         <v>120067</v>
@@ -26962,7 +26962,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G917" t="n">
-        <v>99.9210433959961</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H917" t="n">
         <v>127807</v>
@@ -26991,7 +26991,7 @@
         <v>106.5</v>
       </c>
       <c r="G918" t="n">
-        <v>98.8077087402344</v>
+        <v>98.8077011108398</v>
       </c>
       <c r="H918" t="n">
         <v>120718</v>
@@ -27020,7 +27020,7 @@
         <v>105.900001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>98.2510452270508</v>
+        <v>98.2510528564453</v>
       </c>
       <c r="H919" t="n">
         <v>51100</v>
@@ -27136,7 +27136,7 @@
         <v>108.300003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>100.47770690918</v>
+        <v>100.477714538574</v>
       </c>
       <c r="H923" t="n">
         <v>125584</v>
@@ -27165,7 +27165,7 @@
         <v>108.099998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>100.292152404785</v>
+        <v>100.292144775391</v>
       </c>
       <c r="H924" t="n">
         <v>67236</v>
@@ -27194,7 +27194,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G925" t="n">
-        <v>101.869354248047</v>
+        <v>101.869361877441</v>
       </c>
       <c r="H925" t="n">
         <v>82352</v>
@@ -27223,7 +27223,7 @@
         <v>109</v>
       </c>
       <c r="G926" t="n">
-        <v>101.127143859863</v>
+        <v>101.127128601074</v>
       </c>
       <c r="H926" t="n">
         <v>61146</v>
@@ -27281,7 +27281,7 @@
         <v>107</v>
       </c>
       <c r="G928" t="n">
-        <v>99.2715911865234</v>
+        <v>99.271598815918</v>
       </c>
       <c r="H928" t="n">
         <v>134579</v>
@@ -27310,7 +27310,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>99.9210433959961</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H929" t="n">
         <v>92387</v>
@@ -27339,7 +27339,7 @@
         <v>106.5</v>
       </c>
       <c r="G930" t="n">
-        <v>98.8077087402344</v>
+        <v>98.8077011108398</v>
       </c>
       <c r="H930" t="n">
         <v>90528</v>
@@ -27368,7 +27368,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G931" t="n">
-        <v>99.8282470703125</v>
+        <v>99.828254699707</v>
       </c>
       <c r="H931" t="n">
         <v>120053</v>
@@ -27397,7 +27397,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G932" t="n">
-        <v>99.9210433959961</v>
+        <v>99.921028137207</v>
       </c>
       <c r="H932" t="n">
         <v>95300</v>
@@ -27426,7 +27426,7 @@
         <v>109.699996948242</v>
       </c>
       <c r="G933" t="n">
-        <v>101.776580810547</v>
+        <v>101.776573181152</v>
       </c>
       <c r="H933" t="n">
         <v>101448</v>
@@ -27484,7 +27484,7 @@
         <v>108.900001525879</v>
       </c>
       <c r="G935" t="n">
-        <v>101.034362792969</v>
+        <v>101.034355163574</v>
       </c>
       <c r="H935" t="n">
         <v>99027</v>
@@ -27513,7 +27513,7 @@
         <v>107</v>
       </c>
       <c r="G936" t="n">
-        <v>99.2715911865234</v>
+        <v>99.271598815918</v>
       </c>
       <c r="H936" t="n">
         <v>223566</v>
@@ -27629,7 +27629,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G940" t="n">
-        <v>94.9110641479492</v>
+        <v>94.9110717773438</v>
       </c>
       <c r="H940" t="n">
         <v>272397</v>
@@ -27687,7 +27687,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G942" t="n">
-        <v>95.0038528442383</v>
+        <v>95.0038452148438</v>
       </c>
       <c r="H942" t="n">
         <v>140833</v>
@@ -27774,7 +27774,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G945" t="n">
-        <v>96.3955001831055</v>
+        <v>96.3954925537109</v>
       </c>
       <c r="H945" t="n">
         <v>103885</v>
@@ -27861,7 +27861,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G948" t="n">
-        <v>96.8593826293945</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H948" t="n">
         <v>58835</v>
@@ -27890,7 +27890,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G949" t="n">
-        <v>99.0860366821289</v>
+        <v>99.0860443115234</v>
       </c>
       <c r="H949" t="n">
         <v>112018</v>
@@ -27919,7 +27919,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G950" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H950" t="n">
         <v>121403</v>
@@ -27948,7 +27948,7 @@
         <v>106.099998474121</v>
       </c>
       <c r="G951" t="n">
-        <v>98.4365921020508</v>
+        <v>98.4365844726562</v>
       </c>
       <c r="H951" t="n">
         <v>72020</v>
@@ -28035,7 +28035,7 @@
         <v>105.400001525879</v>
       </c>
       <c r="G954" t="n">
-        <v>97.7871551513672</v>
+        <v>97.7871627807617</v>
       </c>
       <c r="H954" t="n">
         <v>147656</v>
@@ -28180,7 +28180,7 @@
         <v>99.9000015258789</v>
       </c>
       <c r="G959" t="n">
-        <v>92.6844100952148</v>
+        <v>92.6844253540039</v>
       </c>
       <c r="H959" t="n">
         <v>476496</v>
@@ -28209,7 +28209,7 @@
         <v>100.199996948242</v>
       </c>
       <c r="G960" t="n">
-        <v>92.9627456665039</v>
+        <v>92.9627380371094</v>
       </c>
       <c r="H960" t="n">
         <v>162480</v>
@@ -28238,7 +28238,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G961" t="n">
-        <v>92.1277465820312</v>
+        <v>92.1277542114258</v>
       </c>
       <c r="H961" t="n">
         <v>113845</v>
@@ -28296,7 +28296,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G963" t="n">
-        <v>92.3597030639648</v>
+        <v>92.3597106933594</v>
       </c>
       <c r="H963" t="n">
         <v>106414</v>
@@ -28354,7 +28354,7 @@
         <v>100.099998474121</v>
       </c>
       <c r="G965" t="n">
-        <v>92.8699645996094</v>
+        <v>92.8699569702148</v>
       </c>
       <c r="H965" t="n">
         <v>139914</v>
@@ -28383,7 +28383,7 @@
         <v>100</v>
       </c>
       <c r="G966" t="n">
-        <v>92.7771911621094</v>
+        <v>92.7771835327148</v>
       </c>
       <c r="H966" t="n">
         <v>134395</v>
@@ -28412,7 +28412,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G967" t="n">
-        <v>92.3597030639648</v>
+        <v>92.3597106933594</v>
       </c>
       <c r="H967" t="n">
         <v>128135</v>
@@ -28441,7 +28441,7 @@
         <v>96.9499969482422</v>
       </c>
       <c r="G968" t="n">
-        <v>89.9474792480469</v>
+        <v>89.9474868774414</v>
       </c>
       <c r="H968" t="n">
         <v>145555</v>
@@ -28470,7 +28470,7 @@
         <v>97.6999969482422</v>
       </c>
       <c r="G969" t="n">
-        <v>90.6433029174805</v>
+        <v>90.643310546875</v>
       </c>
       <c r="H969" t="n">
         <v>208459</v>
@@ -28499,7 +28499,7 @@
         <v>96.5999984741211</v>
       </c>
       <c r="G970" t="n">
-        <v>89.6227645874023</v>
+        <v>89.6227569580078</v>
       </c>
       <c r="H970" t="n">
         <v>108199</v>
@@ -28528,7 +28528,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>90.596923828125</v>
+        <v>90.5969314575195</v>
       </c>
       <c r="H971" t="n">
         <v>91441</v>
@@ -28557,7 +28557,7 @@
         <v>97.0500030517578</v>
       </c>
       <c r="G972" t="n">
-        <v>90.0402679443359</v>
+        <v>90.0402603149414</v>
       </c>
       <c r="H972" t="n">
         <v>70641</v>
@@ -28586,7 +28586,7 @@
         <v>97.3499984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>90.3185958862305</v>
+        <v>90.3185806274414</v>
       </c>
       <c r="H973" t="n">
         <v>106448</v>
@@ -28644,7 +28644,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G975" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H975" t="n">
         <v>180644</v>
@@ -28731,7 +28731,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G978" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H978" t="n">
         <v>85549</v>
@@ -28818,7 +28818,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G981" t="n">
-        <v>96.3955001831055</v>
+        <v>96.3954925537109</v>
       </c>
       <c r="H981" t="n">
         <v>198362</v>
@@ -28847,7 +28847,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G982" t="n">
-        <v>97.0449371337891</v>
+        <v>97.0449447631836</v>
       </c>
       <c r="H982" t="n">
         <v>265653</v>
@@ -28876,7 +28876,7 @@
         <v>103.5</v>
       </c>
       <c r="G983" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H983" t="n">
         <v>123220</v>
@@ -28905,7 +28905,7 @@
         <v>103.599998474121</v>
       </c>
       <c r="G984" t="n">
-        <v>96.1171569824219</v>
+        <v>96.1171646118164</v>
       </c>
       <c r="H984" t="n">
         <v>142262</v>
@@ -28934,7 +28934,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G985" t="n">
-        <v>98.9004821777344</v>
+        <v>98.9004745483398</v>
       </c>
       <c r="H985" t="n">
         <v>152430</v>
@@ -28963,7 +28963,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G986" t="n">
-        <v>101.219917297363</v>
+        <v>101.219909667969</v>
       </c>
       <c r="H986" t="n">
         <v>313302</v>
@@ -28992,7 +28992,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G987" t="n">
-        <v>102.70435333252</v>
+        <v>102.704345703125</v>
       </c>
       <c r="H987" t="n">
         <v>195641</v>
@@ -29050,7 +29050,7 @@
         <v>114.5</v>
       </c>
       <c r="G989" t="n">
-        <v>106.229881286621</v>
+        <v>106.229873657227</v>
       </c>
       <c r="H989" t="n">
         <v>207841</v>
@@ -29079,7 +29079,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>105.673217773438</v>
+        <v>105.673233032227</v>
       </c>
       <c r="H990" t="n">
         <v>252377</v>
@@ -29137,7 +29137,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G992" t="n">
-        <v>110.497634887695</v>
+        <v>110.497627258301</v>
       </c>
       <c r="H992" t="n">
         <v>336887</v>
@@ -29166,7 +29166,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G993" t="n">
-        <v>110.497634887695</v>
+        <v>110.497627258301</v>
       </c>
       <c r="H993" t="n">
         <v>190913</v>
@@ -29195,7 +29195,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G994" t="n">
-        <v>111.703735351562</v>
+        <v>111.703742980957</v>
       </c>
       <c r="H994" t="n">
         <v>169221</v>
@@ -29224,7 +29224,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G995" t="n">
-        <v>111.147079467773</v>
+        <v>111.147087097168</v>
       </c>
       <c r="H995" t="n">
         <v>177628</v>
@@ -29253,7 +29253,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G996" t="n">
-        <v>111.425399780273</v>
+        <v>111.425407409668</v>
       </c>
       <c r="H996" t="n">
         <v>122685</v>
@@ -29282,7 +29282,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>112.538726806641</v>
+        <v>112.53874206543</v>
       </c>
       <c r="H997" t="n">
         <v>150216</v>
@@ -29311,7 +29311,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G998" t="n">
-        <v>109.755424499512</v>
+        <v>109.755416870117</v>
       </c>
       <c r="H998" t="n">
         <v>150330</v>
@@ -29340,7 +29340,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G999" t="n">
-        <v>112.817047119141</v>
+        <v>112.817054748535</v>
       </c>
       <c r="H999" t="n">
         <v>250127</v>
@@ -29369,7 +29369,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G1000" t="n">
-        <v>113.837608337402</v>
+        <v>113.837600708008</v>
       </c>
       <c r="H1000" t="n">
         <v>300033</v>
@@ -29456,7 +29456,7 @@
         <v>122</v>
       </c>
       <c r="G1003" t="n">
-        <v>113.188163757324</v>
+        <v>113.188179016113</v>
       </c>
       <c r="H1003" t="n">
         <v>152129</v>
@@ -29485,7 +29485,7 @@
         <v>122</v>
       </c>
       <c r="G1004" t="n">
-        <v>113.188163757324</v>
+        <v>113.188179016113</v>
       </c>
       <c r="H1004" t="n">
         <v>164174</v>
@@ -29543,7 +29543,7 @@
         <v>120</v>
       </c>
       <c r="G1006" t="n">
-        <v>111.332618713379</v>
+        <v>111.332626342773</v>
       </c>
       <c r="H1006" t="n">
         <v>171715</v>
@@ -29601,7 +29601,7 @@
         <v>117.699996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>109.198753356934</v>
+        <v>109.198745727539</v>
       </c>
       <c r="H1008" t="n">
         <v>113611</v>
@@ -29688,7 +29688,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1011" t="n">
-        <v>109.105979919434</v>
+        <v>109.105964660645</v>
       </c>
       <c r="H1011" t="n">
         <v>118695</v>
@@ -29717,7 +29717,7 @@
         <v>118.199996948242</v>
       </c>
       <c r="G1012" t="n">
-        <v>109.662635803223</v>
+        <v>109.662643432617</v>
       </c>
       <c r="H1012" t="n">
         <v>199369</v>
@@ -29833,7 +29833,7 @@
         <v>116.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>108.085418701172</v>
+        <v>108.085433959961</v>
       </c>
       <c r="H1016" t="n">
         <v>166980</v>
@@ -29862,7 +29862,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1017" t="n">
-        <v>107.807090759277</v>
+        <v>107.807083129883</v>
       </c>
       <c r="H1017" t="n">
         <v>83294</v>
@@ -29891,7 +29891,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>106.50821685791</v>
+        <v>106.508232116699</v>
       </c>
       <c r="H1018" t="n">
         <v>93251</v>
@@ -29978,7 +29978,7 @@
         <v>119.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>110.86873626709</v>
+        <v>110.868743896484</v>
       </c>
       <c r="H1021" t="n">
         <v>83655</v>
@@ -30007,7 +30007,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1022" t="n">
-        <v>108.82763671875</v>
+        <v>108.827644348145</v>
       </c>
       <c r="H1022" t="n">
         <v>132761</v>
@@ -30123,7 +30123,7 @@
         <v>113.699996948242</v>
       </c>
       <c r="G1026" t="n">
-        <v>105.487663269043</v>
+        <v>105.487670898438</v>
       </c>
       <c r="H1026" t="n">
         <v>131679</v>
@@ -30152,7 +30152,7 @@
         <v>116.900001525879</v>
       </c>
       <c r="G1027" t="n">
-        <v>108.456535339355</v>
+        <v>108.45654296875</v>
       </c>
       <c r="H1027" t="n">
         <v>134188</v>
@@ -30181,7 +30181,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1028" t="n">
-        <v>106.50821685791</v>
+        <v>106.508232116699</v>
       </c>
       <c r="H1028" t="n">
         <v>114599</v>
@@ -30210,7 +30210,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>106.044319152832</v>
+        <v>106.044326782227</v>
       </c>
       <c r="H1029" t="n">
         <v>142027</v>
@@ -30268,7 +30268,7 @@
         <v>114.099998474121</v>
       </c>
       <c r="G1031" t="n">
-        <v>105.858764648438</v>
+        <v>105.858772277832</v>
       </c>
       <c r="H1031" t="n">
         <v>134155</v>
@@ -30326,7 +30326,7 @@
         <v>112.599998474121</v>
       </c>
       <c r="G1033" t="n">
-        <v>104.46711730957</v>
+        <v>104.467109680176</v>
       </c>
       <c r="H1033" t="n">
         <v>133869</v>
@@ -30355,7 +30355,7 @@
         <v>115.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>107.157661437988</v>
+        <v>107.157653808594</v>
       </c>
       <c r="H1034" t="n">
         <v>122572</v>
@@ -30413,7 +30413,7 @@
         <v>113.199996948242</v>
       </c>
       <c r="G1036" t="n">
-        <v>105.023780822754</v>
+        <v>105.023773193359</v>
       </c>
       <c r="H1036" t="n">
         <v>82899</v>
@@ -30442,7 +30442,7 @@
         <v>111</v>
       </c>
       <c r="G1037" t="n">
-        <v>102.982681274414</v>
+        <v>102.982688903809</v>
       </c>
       <c r="H1037" t="n">
         <v>159706</v>
@@ -30471,7 +30471,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>103.817680358887</v>
+        <v>103.817672729492</v>
       </c>
       <c r="H1038" t="n">
         <v>118544</v>
@@ -30500,7 +30500,7 @@
         <v>114</v>
       </c>
       <c r="G1039" t="n">
-        <v>105.766006469727</v>
+        <v>105.765998840332</v>
       </c>
       <c r="H1039" t="n">
         <v>100652</v>
@@ -30529,7 +30529,7 @@
         <v>113.699996948242</v>
       </c>
       <c r="G1040" t="n">
-        <v>105.487663269043</v>
+        <v>105.487670898438</v>
       </c>
       <c r="H1040" t="n">
         <v>112259</v>
@@ -30558,7 +30558,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1041" t="n">
-        <v>106.50821685791</v>
+        <v>106.508232116699</v>
       </c>
       <c r="H1041" t="n">
         <v>270734</v>
@@ -30587,7 +30587,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1042" t="n">
-        <v>106.044319152832</v>
+        <v>106.044326782227</v>
       </c>
       <c r="H1042" t="n">
         <v>76827</v>
@@ -30674,7 +30674,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>106.50821685791</v>
+        <v>106.508232116699</v>
       </c>
       <c r="H1045" t="n">
         <v>108233</v>
@@ -30732,7 +30732,7 @@
         <v>116.599998474121</v>
       </c>
       <c r="G1047" t="n">
-        <v>108.178215026855</v>
+        <v>108.178199768066</v>
       </c>
       <c r="H1047" t="n">
         <v>76277</v>
@@ -30761,7 +30761,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>108.82763671875</v>
+        <v>108.827644348145</v>
       </c>
       <c r="H1048" t="n">
         <v>49235</v>
@@ -30877,7 +30877,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>107.899871826172</v>
+        <v>107.899887084961</v>
       </c>
       <c r="H1052" t="n">
         <v>119025</v>
@@ -30964,7 +30964,7 @@
         <v>107.199996948242</v>
       </c>
       <c r="G1055" t="n">
-        <v>99.4571380615234</v>
+        <v>99.457145690918</v>
       </c>
       <c r="H1055" t="n">
         <v>335606</v>
@@ -31051,7 +31051,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G1058" t="n">
-        <v>94.9110641479492</v>
+        <v>94.9110717773438</v>
       </c>
       <c r="H1058" t="n">
         <v>235831</v>
@@ -31080,7 +31080,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G1059" t="n">
-        <v>97.6943893432617</v>
+        <v>97.6943969726562</v>
       </c>
       <c r="H1059" t="n">
         <v>294872</v>
@@ -31109,7 +31109,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G1060" t="n">
-        <v>97.3232650756836</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H1060" t="n">
         <v>258453</v>
@@ -31138,7 +31138,7 @@
         <v>104.5</v>
       </c>
       <c r="G1061" t="n">
-        <v>96.9521636962891</v>
+        <v>96.9521713256836</v>
       </c>
       <c r="H1061" t="n">
         <v>141963</v>
@@ -31225,7 +31225,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G1064" t="n">
-        <v>96.8593826293945</v>
+        <v>96.8593902587891</v>
       </c>
       <c r="H1064" t="n">
         <v>945948</v>
@@ -31254,7 +31254,7 @@
         <v>113</v>
       </c>
       <c r="G1065" t="n">
-        <v>104.838226318359</v>
+        <v>104.838218688965</v>
       </c>
       <c r="H1065" t="n">
         <v>732508</v>
@@ -31283,7 +31283,7 @@
         <v>103</v>
       </c>
       <c r="G1066" t="n">
-        <v>95.5605087280273</v>
+        <v>95.5605010986328</v>
       </c>
       <c r="H1066" t="n">
         <v>656130</v>
@@ -31370,7 +31370,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G1069" t="n">
-        <v>97.9727020263672</v>
+        <v>97.9727096557617</v>
       </c>
       <c r="H1069" t="n">
         <v>414448</v>
@@ -31399,7 +31399,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>99.0860366821289</v>
+        <v>99.0860443115234</v>
       </c>
       <c r="H1070" t="n">
         <v>216222</v>
@@ -31457,7 +31457,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1072" t="n">
-        <v>103.539344787598</v>
+        <v>103.539337158203</v>
       </c>
       <c r="H1072" t="n">
         <v>822715</v>
@@ -31486,7 +31486,7 @@
         <v>116.800003051758</v>
       </c>
       <c r="G1073" t="n">
-        <v>108.36376953125</v>
+        <v>108.363761901855</v>
       </c>
       <c r="H1073" t="n">
         <v>409710</v>
@@ -31515,7 +31515,7 @@
         <v>115.199996948242</v>
       </c>
       <c r="G1074" t="n">
-        <v>106.879325866699</v>
+        <v>106.879318237305</v>
       </c>
       <c r="H1074" t="n">
         <v>401583</v>
@@ -31631,7 +31631,7 @@
         <v>116.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>108.085418701172</v>
+        <v>108.085433959961</v>
       </c>
       <c r="H1078" t="n">
         <v>271381</v>
@@ -31660,7 +31660,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G1079" t="n">
-        <v>111.982070922852</v>
+        <v>111.982063293457</v>
       </c>
       <c r="H1079" t="n">
         <v>297859</v>
@@ -31689,7 +31689,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G1080" t="n">
-        <v>109.755424499512</v>
+        <v>109.755416870117</v>
       </c>
       <c r="H1080" t="n">
         <v>157506</v>
@@ -31718,7 +31718,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>109.755424499512</v>
+        <v>109.755416870117</v>
       </c>
       <c r="H1081" t="n">
         <v>184324</v>
@@ -31747,7 +31747,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1082" t="n">
-        <v>109.105979919434</v>
+        <v>109.105964660645</v>
       </c>
       <c r="H1082" t="n">
         <v>167694</v>
@@ -31776,7 +31776,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1083" t="n">
-        <v>109.569862365723</v>
+        <v>109.569854736328</v>
       </c>
       <c r="H1083" t="n">
         <v>144071</v>
@@ -31805,7 +31805,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G1084" t="n">
-        <v>115.878715515137</v>
+        <v>115.878723144531</v>
       </c>
       <c r="H1084" t="n">
         <v>503694</v>
@@ -31834,7 +31834,7 @@
         <v>129.399993896484</v>
       </c>
       <c r="G1085" t="n">
-        <v>120.053665161133</v>
+        <v>120.053657531738</v>
       </c>
       <c r="H1085" t="n">
         <v>344567</v>
@@ -31921,7 +31921,7 @@
         <v>149.800003051758</v>
       </c>
       <c r="G1088" t="n">
-        <v>138.980224609375</v>
+        <v>138.980239868164</v>
       </c>
       <c r="H1088" t="n">
         <v>518157</v>
@@ -31950,7 +31950,7 @@
         <v>150.100006103516</v>
       </c>
       <c r="G1089" t="n">
-        <v>139.258590698242</v>
+        <v>139.258560180664</v>
       </c>
       <c r="H1089" t="n">
         <v>581970</v>
@@ -32037,7 +32037,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G1092" t="n">
-        <v>141.577987670898</v>
+        <v>141.578002929688</v>
       </c>
       <c r="H1092" t="n">
         <v>324414</v>
@@ -32066,7 +32066,7 @@
         <v>165</v>
       </c>
       <c r="G1093" t="n">
-        <v>153.08235168457</v>
+        <v>153.082366943359</v>
       </c>
       <c r="H1093" t="n">
         <v>447472</v>
@@ -32095,7 +32095,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1094" t="n">
-        <v>147.608505249023</v>
+        <v>147.608520507812</v>
       </c>
       <c r="H1094" t="n">
         <v>583928</v>
@@ -32124,7 +32124,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1095" t="n">
-        <v>150.855697631836</v>
+        <v>150.855728149414</v>
       </c>
       <c r="H1095" t="n">
         <v>300403</v>
@@ -32182,7 +32182,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1097" t="n">
-        <v>155.030685424805</v>
+        <v>155.030700683594</v>
       </c>
       <c r="H1097" t="n">
         <v>282090</v>
@@ -32269,7 +32269,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1100" t="n">
-        <v>144.175765991211</v>
+        <v>144.175735473633</v>
       </c>
       <c r="H1100" t="n">
         <v>232643</v>
@@ -32327,7 +32327,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G1102" t="n">
-        <v>141.856307983398</v>
+        <v>141.856323242188</v>
       </c>
       <c r="H1102" t="n">
         <v>153280</v>
@@ -32356,7 +32356,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1103" t="n">
-        <v>143.619079589844</v>
+        <v>143.619110107422</v>
       </c>
       <c r="H1103" t="n">
         <v>130241</v>
@@ -32385,7 +32385,7 @@
         <v>156.199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>144.917984008789</v>
+        <v>144.91796875</v>
       </c>
       <c r="H1104" t="n">
         <v>70987</v>
@@ -32414,7 +32414,7 @@
         <v>162.5</v>
       </c>
       <c r="G1105" t="n">
-        <v>150.762924194336</v>
+        <v>150.762939453125</v>
       </c>
       <c r="H1105" t="n">
         <v>267464</v>
@@ -32443,7 +32443,7 @@
         <v>160.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>148.90739440918</v>
+        <v>148.907379150391</v>
       </c>
       <c r="H1106" t="n">
         <v>258847</v>
@@ -32617,7 +32617,7 @@
         <v>189.199996948242</v>
       </c>
       <c r="G1112" t="n">
-        <v>175.534454345703</v>
+        <v>175.534439086914</v>
       </c>
       <c r="H1112" t="n">
         <v>486038</v>
@@ -32733,7 +32733,7 @@
         <v>197</v>
       </c>
       <c r="G1116" t="n">
-        <v>182.771041870117</v>
+        <v>182.771057128906</v>
       </c>
       <c r="H1116" t="n">
         <v>684856</v>
@@ -32762,7 +32762,7 @@
         <v>173</v>
       </c>
       <c r="G1117" t="n">
-        <v>160.504531860352</v>
+        <v>160.504547119141</v>
       </c>
       <c r="H1117" t="n">
         <v>1004392</v>
@@ -32820,7 +32820,7 @@
         <v>188.5</v>
       </c>
       <c r="G1119" t="n">
-        <v>174.885025024414</v>
+        <v>174.885009765625</v>
       </c>
       <c r="H1119" t="n">
         <v>2999027</v>
@@ -32849,7 +32849,7 @@
         <v>181.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>168.390609741211</v>
+        <v>168.390625</v>
       </c>
       <c r="H1120" t="n">
         <v>427520</v>
@@ -32878,7 +32878,7 @@
         <v>178.899993896484</v>
       </c>
       <c r="G1121" t="n">
-        <v>165.978393554688</v>
+        <v>165.978378295898</v>
       </c>
       <c r="H1121" t="n">
         <v>418839</v>
@@ -32936,7 +32936,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1123" t="n">
-        <v>161.617874145508</v>
+        <v>161.61784362793</v>
       </c>
       <c r="H1123" t="n">
         <v>528586</v>
@@ -32965,7 +32965,7 @@
         <v>166</v>
       </c>
       <c r="G1124" t="n">
-        <v>154.010131835938</v>
+        <v>154.010116577148</v>
       </c>
       <c r="H1124" t="n">
         <v>573423</v>
@@ -32994,7 +32994,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G1125" t="n">
-        <v>148.072402954102</v>
+        <v>148.072418212891</v>
       </c>
       <c r="H1125" t="n">
         <v>584751</v>
@@ -33023,7 +33023,7 @@
         <v>161.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>149.835189819336</v>
+        <v>149.835174560547</v>
       </c>
       <c r="H1126" t="n">
         <v>684242</v>
@@ -33052,7 +33052,7 @@
         <v>164</v>
       </c>
       <c r="G1127" t="n">
-        <v>152.154586791992</v>
+        <v>152.154602050781</v>
       </c>
       <c r="H1127" t="n">
         <v>361385</v>
@@ -33081,7 +33081,7 @@
         <v>167.800003051758</v>
       </c>
       <c r="G1128" t="n">
-        <v>155.680130004883</v>
+        <v>155.680145263672</v>
       </c>
       <c r="H1128" t="n">
         <v>357835</v>
@@ -33110,7 +33110,7 @@
         <v>167</v>
       </c>
       <c r="G1129" t="n">
-        <v>154.937881469727</v>
+        <v>154.937896728516</v>
       </c>
       <c r="H1129" t="n">
         <v>331932</v>
@@ -33168,7 +33168,7 @@
         <v>170.800003051758</v>
       </c>
       <c r="G1131" t="n">
-        <v>159.370056152344</v>
+        <v>159.370040893555</v>
       </c>
       <c r="H1131" t="n">
         <v>304851</v>
@@ -33197,7 +33197,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1132" t="n">
-        <v>158.90348815918</v>
+        <v>158.903503417969</v>
       </c>
       <c r="H1132" t="n">
         <v>216573</v>
@@ -33226,7 +33226,7 @@
         <v>169.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>158.157028198242</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1133" t="n">
         <v>188475</v>
@@ -33342,7 +33342,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1137" t="n">
-        <v>158.90348815918</v>
+        <v>158.903503417969</v>
       </c>
       <c r="H1137" t="n">
         <v>165364</v>
@@ -33400,7 +33400,7 @@
         <v>171.399993896484</v>
       </c>
       <c r="G1139" t="n">
-        <v>159.929885864258</v>
+        <v>159.929870605469</v>
       </c>
       <c r="H1139" t="n">
         <v>220915</v>
@@ -33429,7 +33429,7 @@
         <v>169.699996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>158.343627929688</v>
+        <v>158.343643188477</v>
       </c>
       <c r="H1140" t="n">
         <v>197091</v>
@@ -33458,7 +33458,7 @@
         <v>170.399993896484</v>
       </c>
       <c r="G1141" t="n">
-        <v>158.996795654297</v>
+        <v>158.996780395508</v>
       </c>
       <c r="H1141" t="n">
         <v>215907</v>
@@ -33516,7 +33516,7 @@
         <v>171.300003051758</v>
       </c>
       <c r="G1143" t="n">
-        <v>159.83659362793</v>
+        <v>159.836578369141</v>
       </c>
       <c r="H1143" t="n">
         <v>289763</v>
@@ -33545,7 +33545,7 @@
         <v>171.100006103516</v>
       </c>
       <c r="G1144" t="n">
-        <v>159.649963378906</v>
+        <v>159.649978637695</v>
       </c>
       <c r="H1144" t="n">
         <v>119973</v>
@@ -33603,7 +33603,7 @@
         <v>178.5</v>
       </c>
       <c r="G1146" t="n">
-        <v>166.554748535156</v>
+        <v>166.554763793945</v>
       </c>
       <c r="H1146" t="n">
         <v>235569</v>
@@ -33661,7 +33661,7 @@
         <v>171.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>160.023178100586</v>
+        <v>160.023193359375</v>
       </c>
       <c r="H1148" t="n">
         <v>273837</v>
@@ -33690,7 +33690,7 @@
         <v>172.899993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>161.329513549805</v>
+        <v>161.329498291016</v>
       </c>
       <c r="H1149" t="n">
         <v>160523</v>
@@ -33748,7 +33748,7 @@
         <v>173.199996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>161.609436035156</v>
+        <v>161.609420776367</v>
       </c>
       <c r="H1151" t="n">
         <v>170112</v>
@@ -33951,7 +33951,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1158" t="n">
-        <v>157.970413208008</v>
+        <v>157.970428466797</v>
       </c>
       <c r="H1158" t="n">
         <v>446703</v>
@@ -34009,7 +34009,7 @@
         <v>170.800003051758</v>
       </c>
       <c r="G1160" t="n">
-        <v>159.370056152344</v>
+        <v>159.370040893555</v>
       </c>
       <c r="H1160" t="n">
         <v>161960</v>
@@ -34038,7 +34038,7 @@
         <v>170.600006103516</v>
       </c>
       <c r="G1161" t="n">
-        <v>159.183410644531</v>
+        <v>159.18342590332</v>
       </c>
       <c r="H1161" t="n">
         <v>116037</v>
@@ -34183,7 +34183,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G1166" t="n">
-        <v>149.852615356445</v>
+        <v>149.852630615234</v>
       </c>
       <c r="H1166" t="n">
         <v>203712</v>
@@ -34299,7 +34299,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>142.574584960938</v>
+        <v>142.574600219727</v>
       </c>
       <c r="H1170" t="n">
         <v>182163</v>
@@ -34328,7 +34328,7 @@
         <v>157.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>146.960083007812</v>
+        <v>146.960052490234</v>
       </c>
       <c r="H1171" t="n">
         <v>181402</v>
@@ -34357,7 +34357,7 @@
         <v>160.199996948242</v>
       </c>
       <c r="G1172" t="n">
-        <v>149.479385375977</v>
+        <v>149.479370117188</v>
       </c>
       <c r="H1172" t="n">
         <v>133270</v>
@@ -34415,7 +34415,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1174" t="n">
-        <v>145.653762817383</v>
+        <v>145.653778076172</v>
       </c>
       <c r="H1174" t="n">
         <v>177264</v>
@@ -34502,7 +34502,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1177" t="n">
-        <v>151.34553527832</v>
+        <v>151.345550537109</v>
       </c>
       <c r="H1177" t="n">
         <v>111771</v>
@@ -34531,7 +34531,7 @@
         <v>162.899993896484</v>
       </c>
       <c r="G1178" t="n">
-        <v>151.99870300293</v>
+        <v>151.998687744141</v>
       </c>
       <c r="H1178" t="n">
         <v>102684</v>
@@ -34560,7 +34560,7 @@
         <v>163</v>
       </c>
       <c r="G1179" t="n">
-        <v>152.092010498047</v>
+        <v>152.092025756836</v>
       </c>
       <c r="H1179" t="n">
         <v>117685</v>
@@ -34618,7 +34618,7 @@
         <v>163.899993896484</v>
       </c>
       <c r="G1181" t="n">
-        <v>152.931777954102</v>
+        <v>152.931762695312</v>
       </c>
       <c r="H1181" t="n">
         <v>93665</v>
@@ -34676,7 +34676,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1183" t="n">
-        <v>142.947830200195</v>
+        <v>142.947845458984</v>
       </c>
       <c r="H1183" t="n">
         <v>513169</v>
@@ -34705,7 +34705,7 @@
         <v>145.800003051758</v>
       </c>
       <c r="G1184" t="n">
-        <v>136.043045043945</v>
+        <v>136.043060302734</v>
       </c>
       <c r="H1184" t="n">
         <v>460285</v>
@@ -34763,7 +34763,7 @@
         <v>152.100006103516</v>
       </c>
       <c r="G1186" t="n">
-        <v>141.921417236328</v>
+        <v>141.921447753906</v>
       </c>
       <c r="H1186" t="n">
         <v>212429</v>
@@ -34792,7 +34792,7 @@
         <v>151</v>
       </c>
       <c r="G1187" t="n">
-        <v>140.895050048828</v>
+        <v>140.895065307617</v>
       </c>
       <c r="H1187" t="n">
         <v>125409</v>
@@ -34966,7 +34966,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G1193" t="n">
-        <v>140.615112304688</v>
+        <v>140.615127563477</v>
       </c>
       <c r="H1193" t="n">
         <v>173029</v>
@@ -34995,7 +34995,7 @@
         <v>154.699996948242</v>
       </c>
       <c r="G1194" t="n">
-        <v>144.347442626953</v>
+        <v>144.347457885742</v>
       </c>
       <c r="H1194" t="n">
         <v>131020</v>
@@ -35024,7 +35024,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1195" t="n">
-        <v>145.000610351562</v>
+        <v>145.000595092773</v>
       </c>
       <c r="H1195" t="n">
         <v>120422</v>
@@ -35053,7 +35053,7 @@
         <v>157</v>
       </c>
       <c r="G1196" t="n">
-        <v>146.493560791016</v>
+        <v>146.493545532227</v>
       </c>
       <c r="H1196" t="n">
         <v>108163</v>
@@ -35082,7 +35082,7 @@
         <v>160.899993896484</v>
       </c>
       <c r="G1197" t="n">
-        <v>150.132537841797</v>
+        <v>150.132522583008</v>
       </c>
       <c r="H1197" t="n">
         <v>252082</v>
@@ -35111,7 +35111,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1198" t="n">
-        <v>147.613220214844</v>
+        <v>147.613204956055</v>
       </c>
       <c r="H1198" t="n">
         <v>101347</v>
@@ -35169,7 +35169,7 @@
         <v>169.399993896484</v>
       </c>
       <c r="G1200" t="n">
-        <v>158.063720703125</v>
+        <v>158.063705444336</v>
       </c>
       <c r="H1200" t="n">
         <v>546780</v>
@@ -35227,7 +35227,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1202" t="n">
-        <v>157.970413208008</v>
+        <v>157.970428466797</v>
       </c>
       <c r="H1202" t="n">
         <v>215161</v>
@@ -35314,7 +35314,7 @@
         <v>170.199996948242</v>
       </c>
       <c r="G1205" t="n">
-        <v>158.810180664062</v>
+        <v>158.810195922852</v>
       </c>
       <c r="H1205" t="n">
         <v>146129</v>
@@ -35575,7 +35575,7 @@
         <v>188</v>
       </c>
       <c r="G1214" t="n">
-        <v>175.419006347656</v>
+        <v>175.418991088867</v>
       </c>
       <c r="H1214" t="n">
         <v>141353</v>
@@ -35604,7 +35604,7 @@
         <v>190.100006103516</v>
       </c>
       <c r="G1215" t="n">
-        <v>177.378479003906</v>
+        <v>177.378494262695</v>
       </c>
       <c r="H1215" t="n">
         <v>149173</v>
@@ -35633,7 +35633,7 @@
         <v>187.5</v>
       </c>
       <c r="G1216" t="n">
-        <v>174.95246887207</v>
+        <v>174.952453613281</v>
       </c>
       <c r="H1216" t="n">
         <v>125251</v>
@@ -35662,7 +35662,7 @@
         <v>191.300003051758</v>
       </c>
       <c r="G1217" t="n">
-        <v>178.498153686523</v>
+        <v>178.498184204102</v>
       </c>
       <c r="H1217" t="n">
         <v>183967</v>
@@ -35691,7 +35691,7 @@
         <v>189</v>
       </c>
       <c r="G1218" t="n">
-        <v>176.352096557617</v>
+        <v>176.352081298828</v>
       </c>
       <c r="H1218" t="n">
         <v>203551</v>
@@ -35720,7 +35720,7 @@
         <v>194.600006103516</v>
       </c>
       <c r="G1219" t="n">
-        <v>181.577331542969</v>
+        <v>181.577346801758</v>
       </c>
       <c r="H1219" t="n">
         <v>229813</v>
@@ -35778,7 +35778,7 @@
         <v>191.100006103516</v>
       </c>
       <c r="G1221" t="n">
-        <v>178.311569213867</v>
+        <v>178.311553955078</v>
       </c>
       <c r="H1221" t="n">
         <v>152123</v>
@@ -35836,7 +35836,7 @@
         <v>192.600006103516</v>
       </c>
       <c r="G1223" t="n">
-        <v>179.711166381836</v>
+        <v>179.711181640625</v>
       </c>
       <c r="H1223" t="n">
         <v>139931</v>
@@ -35865,7 +35865,7 @@
         <v>188</v>
       </c>
       <c r="G1224" t="n">
-        <v>175.419006347656</v>
+        <v>175.418991088867</v>
       </c>
       <c r="H1224" t="n">
         <v>159068</v>
@@ -35894,7 +35894,7 @@
         <v>189</v>
       </c>
       <c r="G1225" t="n">
-        <v>176.352096557617</v>
+        <v>176.352081298828</v>
       </c>
       <c r="H1225" t="n">
         <v>159604</v>
@@ -35923,7 +35923,7 @@
         <v>191</v>
       </c>
       <c r="G1226" t="n">
-        <v>178.21826171875</v>
+        <v>178.218246459961</v>
       </c>
       <c r="H1226" t="n">
         <v>227774</v>
@@ -35952,7 +35952,7 @@
         <v>188.600006103516</v>
       </c>
       <c r="G1227" t="n">
-        <v>175.978866577148</v>
+        <v>175.978881835938</v>
       </c>
       <c r="H1227" t="n">
         <v>269042</v>
@@ -35981,7 +35981,7 @@
         <v>187.300003051758</v>
       </c>
       <c r="G1228" t="n">
-        <v>174.765853881836</v>
+        <v>174.765838623047</v>
       </c>
       <c r="H1228" t="n">
         <v>154872</v>
@@ -36155,7 +36155,7 @@
         <v>201.199996948242</v>
       </c>
       <c r="G1234" t="n">
-        <v>187.73567199707</v>
+        <v>187.735641479492</v>
       </c>
       <c r="H1234" t="n">
         <v>192061</v>
@@ -36184,7 +36184,7 @@
         <v>168</v>
       </c>
       <c r="G1235" t="n">
-        <v>156.757415771484</v>
+        <v>156.757431030273</v>
       </c>
       <c r="H1235" t="n">
         <v>663868</v>
@@ -36242,7 +36242,7 @@
         <v>172.399993896484</v>
       </c>
       <c r="G1237" t="n">
-        <v>160.862976074219</v>
+        <v>160.862945556641</v>
       </c>
       <c r="H1237" t="n">
         <v>458040</v>
@@ -36503,7 +36503,7 @@
         <v>165.100006103516</v>
       </c>
       <c r="G1246" t="n">
-        <v>154.051483154297</v>
+        <v>154.051498413086</v>
       </c>
       <c r="H1246" t="n">
         <v>527334</v>
@@ -36590,7 +36590,7 @@
         <v>172.800003051758</v>
       </c>
       <c r="G1249" t="n">
-        <v>161.236206054688</v>
+        <v>161.236190795898</v>
       </c>
       <c r="H1249" t="n">
         <v>221273</v>
@@ -36648,7 +36648,7 @@
         <v>172.199996948242</v>
       </c>
       <c r="G1251" t="n">
-        <v>160.676345825195</v>
+        <v>160.676330566406</v>
       </c>
       <c r="H1251" t="n">
         <v>216284</v>
@@ -36706,7 +36706,7 @@
         <v>170</v>
       </c>
       <c r="G1253" t="n">
-        <v>158.623565673828</v>
+        <v>158.623580932617</v>
       </c>
       <c r="H1253" t="n">
         <v>131920</v>
@@ -36764,7 +36764,7 @@
         <v>170</v>
       </c>
       <c r="G1255" t="n">
-        <v>158.623565673828</v>
+        <v>158.623580932617</v>
       </c>
       <c r="H1255" t="n">
         <v>181130</v>
@@ -36793,7 +36793,7 @@
         <v>171.199996948242</v>
       </c>
       <c r="G1256" t="n">
-        <v>159.743270874023</v>
+        <v>159.743255615234</v>
       </c>
       <c r="H1256" t="n">
         <v>119035</v>
@@ -36822,7 +36822,7 @@
         <v>168.5</v>
       </c>
       <c r="G1257" t="n">
-        <v>157.223937988281</v>
+        <v>157.22395324707</v>
       </c>
       <c r="H1257" t="n">
         <v>141131</v>
@@ -36851,7 +36851,7 @@
         <v>169.699996948242</v>
       </c>
       <c r="G1258" t="n">
-        <v>158.343627929688</v>
+        <v>158.343643188477</v>
       </c>
       <c r="H1258" t="n">
         <v>237469</v>
@@ -36996,7 +36996,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1263" t="n">
-        <v>155.91764831543</v>
+        <v>155.917663574219</v>
       </c>
       <c r="H1263" t="n">
         <v>126302</v>
@@ -37054,7 +37054,7 @@
         <v>171.699996948242</v>
       </c>
       <c r="G1265" t="n">
-        <v>160.209823608398</v>
+        <v>160.209808349609</v>
       </c>
       <c r="H1265" t="n">
         <v>179244</v>
@@ -37083,7 +37083,7 @@
         <v>170.199996948242</v>
       </c>
       <c r="G1266" t="n">
-        <v>158.810180664062</v>
+        <v>158.810195922852</v>
       </c>
       <c r="H1266" t="n">
         <v>104034</v>
@@ -37170,7 +37170,7 @@
         <v>167.899993896484</v>
       </c>
       <c r="G1269" t="n">
-        <v>156.664108276367</v>
+        <v>156.664093017578</v>
       </c>
       <c r="H1269" t="n">
         <v>99428</v>
@@ -37199,7 +37199,7 @@
         <v>170.100006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>158.716873168945</v>
+        <v>158.716888427734</v>
       </c>
       <c r="H1270" t="n">
         <v>144762</v>
@@ -37228,7 +37228,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1271" t="n">
-        <v>158.250335693359</v>
+        <v>158.250350952148</v>
       </c>
       <c r="H1271" t="n">
         <v>241069</v>
@@ -37257,7 +37257,7 @@
         <v>168.5</v>
       </c>
       <c r="G1272" t="n">
-        <v>157.223937988281</v>
+        <v>157.22395324707</v>
       </c>
       <c r="H1272" t="n">
         <v>122959</v>
@@ -37286,7 +37286,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1273" t="n">
-        <v>150.972320556641</v>
+        <v>150.97233581543</v>
       </c>
       <c r="H1273" t="n">
         <v>290237</v>
@@ -37344,7 +37344,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>150.972320556641</v>
+        <v>150.97233581543</v>
       </c>
       <c r="H1275" t="n">
         <v>186516</v>
@@ -37402,7 +37402,7 @@
         <v>159.399993896484</v>
       </c>
       <c r="G1277" t="n">
-        <v>148.732925415039</v>
+        <v>148.73291015625</v>
       </c>
       <c r="H1277" t="n">
         <v>170407</v>
@@ -37489,7 +37489,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1280" t="n">
-        <v>151.718780517578</v>
+        <v>151.718811035156</v>
       </c>
       <c r="H1280" t="n">
         <v>185002</v>
@@ -37518,7 +37518,7 @@
         <v>166.199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>155.077850341797</v>
+        <v>155.077865600586</v>
       </c>
       <c r="H1281" t="n">
         <v>196955</v>
@@ -37547,7 +37547,7 @@
         <v>171.199996948242</v>
       </c>
       <c r="G1282" t="n">
-        <v>159.743270874023</v>
+        <v>159.743255615234</v>
       </c>
       <c r="H1282" t="n">
         <v>340902</v>
@@ -37576,7 +37576,7 @@
         <v>171.100006103516</v>
       </c>
       <c r="G1283" t="n">
-        <v>159.649963378906</v>
+        <v>159.649978637695</v>
       </c>
       <c r="H1283" t="n">
         <v>153567</v>
@@ -37663,7 +37663,7 @@
         <v>179.699996948242</v>
       </c>
       <c r="G1286" t="n">
-        <v>167.674453735352</v>
+        <v>167.674438476562</v>
       </c>
       <c r="H1286" t="n">
         <v>272557</v>
@@ -37750,7 +37750,7 @@
         <v>177.699996948242</v>
       </c>
       <c r="G1289" t="n">
-        <v>165.808288574219</v>
+        <v>165.80827331543</v>
       </c>
       <c r="H1289" t="n">
         <v>293150</v>
@@ -37779,7 +37779,7 @@
         <v>180.600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>168.514221191406</v>
+        <v>168.514205932617</v>
       </c>
       <c r="H1290" t="n">
         <v>265167</v>
@@ -37808,7 +37808,7 @@
         <v>180</v>
       </c>
       <c r="G1291" t="n">
-        <v>167.954360961914</v>
+        <v>167.954376220703</v>
       </c>
       <c r="H1291" t="n">
         <v>201666</v>
@@ -37837,7 +37837,7 @@
         <v>179.399993896484</v>
       </c>
       <c r="G1292" t="n">
-        <v>167.394515991211</v>
+        <v>167.39453125</v>
       </c>
       <c r="H1292" t="n">
         <v>187484</v>
@@ -37895,7 +37895,7 @@
         <v>176.199996948242</v>
       </c>
       <c r="G1294" t="n">
-        <v>164.408676147461</v>
+        <v>164.408660888672</v>
       </c>
       <c r="H1294" t="n">
         <v>132358</v>
@@ -37953,7 +37953,7 @@
         <v>177.699996948242</v>
       </c>
       <c r="G1296" t="n">
-        <v>165.808288574219</v>
+        <v>165.80827331543</v>
       </c>
       <c r="H1296" t="n">
         <v>123175</v>
@@ -38011,7 +38011,7 @@
         <v>182.199996948242</v>
       </c>
       <c r="G1298" t="n">
-        <v>170.007141113281</v>
+        <v>170.007125854492</v>
       </c>
       <c r="H1298" t="n">
         <v>157335</v>
@@ -38040,7 +38040,7 @@
         <v>184.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>172.153213500977</v>
+        <v>172.153228759766</v>
       </c>
       <c r="H1299" t="n">
         <v>101763</v>
@@ -38098,7 +38098,7 @@
         <v>185.300003051758</v>
       </c>
       <c r="G1301" t="n">
-        <v>172.899688720703</v>
+        <v>172.899703979492</v>
       </c>
       <c r="H1301" t="n">
         <v>107967</v>
@@ -38156,7 +38156,7 @@
         <v>183.5</v>
       </c>
       <c r="G1303" t="n">
-        <v>171.220138549805</v>
+        <v>171.220153808594</v>
       </c>
       <c r="H1303" t="n">
         <v>100354</v>
@@ -38214,7 +38214,7 @@
         <v>169.5</v>
       </c>
       <c r="G1305" t="n">
-        <v>158.157028198242</v>
+        <v>158.157043457031</v>
       </c>
       <c r="H1305" t="n">
         <v>234314</v>
@@ -38301,7 +38301,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1308" t="n">
-        <v>147.613220214844</v>
+        <v>147.613204956055</v>
       </c>
       <c r="H1308" t="n">
         <v>193734</v>
@@ -38330,7 +38330,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1309" t="n">
-        <v>153.118408203125</v>
+        <v>153.118423461914</v>
       </c>
       <c r="H1309" t="n">
         <v>351753</v>
@@ -38359,7 +38359,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1310" t="n">
-        <v>151.532165527344</v>
+        <v>151.532150268555</v>
       </c>
       <c r="H1310" t="n">
         <v>218095</v>
@@ -38446,7 +38446,7 @@
         <v>161.800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>150.972320556641</v>
+        <v>150.97233581543</v>
       </c>
       <c r="H1313" t="n">
         <v>186263</v>
@@ -38475,7 +38475,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G1314" t="n">
-        <v>153.118408203125</v>
+        <v>153.118423461914</v>
       </c>
       <c r="H1314" t="n">
         <v>159342</v>
@@ -38504,7 +38504,7 @@
         <v>162</v>
       </c>
       <c r="G1315" t="n">
-        <v>151.158935546875</v>
+        <v>151.158905029297</v>
       </c>
       <c r="H1315" t="n">
         <v>144663</v>
@@ -38533,7 +38533,7 @@
         <v>158</v>
       </c>
       <c r="G1316" t="n">
-        <v>147.426635742188</v>
+        <v>147.426620483398</v>
       </c>
       <c r="H1316" t="n">
         <v>225610</v>
@@ -38591,7 +38591,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1318" t="n">
-        <v>144.44075012207</v>
+        <v>144.440780639648</v>
       </c>
       <c r="H1318" t="n">
         <v>257428</v>
@@ -38678,7 +38678,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1321" t="n">
-        <v>132.590667724609</v>
+        <v>132.59065246582</v>
       </c>
       <c r="H1321" t="n">
         <v>295438</v>
@@ -38707,7 +38707,7 @@
         <v>145.899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>136.136337280273</v>
+        <v>136.136322021484</v>
       </c>
       <c r="H1322" t="n">
         <v>350628</v>
@@ -38736,7 +38736,7 @@
         <v>142</v>
       </c>
       <c r="G1323" t="n">
-        <v>132.497360229492</v>
+        <v>132.497344970703</v>
       </c>
       <c r="H1323" t="n">
         <v>223928</v>
@@ -38794,7 +38794,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>133.523727416992</v>
+        <v>133.523742675781</v>
       </c>
       <c r="H1325" t="n">
         <v>319389</v>
@@ -38823,7 +38823,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>130.817779541016</v>
+        <v>130.817794799805</v>
       </c>
       <c r="H1326" t="n">
         <v>268900</v>
@@ -38968,7 +38968,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>128.111846923828</v>
+        <v>128.111862182617</v>
       </c>
       <c r="H1331" t="n">
         <v>287517</v>
@@ -38997,7 +38997,7 @@
         <v>137.699996948242</v>
       </c>
       <c r="G1332" t="n">
-        <v>128.485092163086</v>
+        <v>128.485076904297</v>
       </c>
       <c r="H1332" t="n">
         <v>167009</v>
@@ -39084,7 +39084,7 @@
         <v>142.5</v>
       </c>
       <c r="G1335" t="n">
-        <v>132.963897705078</v>
+        <v>132.963882446289</v>
       </c>
       <c r="H1335" t="n">
         <v>292456</v>
@@ -39113,7 +39113,7 @@
         <v>140.149993896484</v>
       </c>
       <c r="G1336" t="n">
-        <v>130.771133422852</v>
+        <v>130.771118164062</v>
       </c>
       <c r="H1336" t="n">
         <v>193898</v>
@@ -39258,7 +39258,7 @@
         <v>149.149993896484</v>
       </c>
       <c r="G1341" t="n">
-        <v>139.168853759766</v>
+        <v>139.168838500977</v>
       </c>
       <c r="H1341" t="n">
         <v>183651</v>
@@ -39287,7 +39287,7 @@
         <v>151</v>
       </c>
       <c r="G1342" t="n">
-        <v>140.895050048828</v>
+        <v>140.895065307617</v>
       </c>
       <c r="H1342" t="n">
         <v>192282</v>
@@ -39316,7 +39316,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1343" t="n">
-        <v>142.947830200195</v>
+        <v>142.947845458984</v>
       </c>
       <c r="H1343" t="n">
         <v>281536</v>
@@ -39519,7 +39519,7 @@
         <v>144.100006103516</v>
       </c>
       <c r="G1350" t="n">
-        <v>134.456817626953</v>
+        <v>134.456802368164</v>
       </c>
       <c r="H1350" t="n">
         <v>415633</v>
@@ -39548,7 +39548,7 @@
         <v>143.899993896484</v>
       </c>
       <c r="G1351" t="n">
-        <v>134.27018737793</v>
+        <v>134.270172119141</v>
       </c>
       <c r="H1351" t="n">
         <v>449860</v>
@@ -39577,7 +39577,7 @@
         <v>140.25</v>
       </c>
       <c r="G1352" t="n">
-        <v>130.864440917969</v>
+        <v>130.864456176758</v>
       </c>
       <c r="H1352" t="n">
         <v>342812</v>
@@ -39635,7 +39635,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1354" t="n">
-        <v>131.42431640625</v>
+        <v>131.424301147461</v>
       </c>
       <c r="H1354" t="n">
         <v>111270</v>
@@ -39664,7 +39664,7 @@
         <v>137.699996948242</v>
       </c>
       <c r="G1355" t="n">
-        <v>128.485092163086</v>
+        <v>128.485076904297</v>
       </c>
       <c r="H1355" t="n">
         <v>200790</v>
@@ -39693,7 +39693,7 @@
         <v>141.199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>131.750885009766</v>
+        <v>131.750869750977</v>
       </c>
       <c r="H1356" t="n">
         <v>146704</v>
@@ -39722,7 +39722,7 @@
         <v>138.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>129.231552124023</v>
+        <v>129.231536865234</v>
       </c>
       <c r="H1357" t="n">
         <v>219957</v>
@@ -39780,7 +39780,7 @@
         <v>142.649993896484</v>
       </c>
       <c r="G1359" t="n">
-        <v>133.10383605957</v>
+        <v>133.103820800781</v>
       </c>
       <c r="H1359" t="n">
         <v>234905</v>
@@ -39867,7 +39867,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G1362" t="n">
-        <v>129.044921875</v>
+        <v>129.044937133789</v>
       </c>
       <c r="H1362" t="n">
         <v>196626</v>
@@ -39896,7 +39896,7 @@
         <v>138</v>
       </c>
       <c r="G1363" t="n">
-        <v>128.765029907227</v>
+        <v>128.765045166016</v>
       </c>
       <c r="H1363" t="n">
         <v>226020</v>
@@ -39925,7 +39925,7 @@
         <v>140.850006103516</v>
       </c>
       <c r="G1364" t="n">
-        <v>131.42431640625</v>
+        <v>131.424301147461</v>
       </c>
       <c r="H1364" t="n">
         <v>267732</v>
@@ -39983,7 +39983,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1366" t="n">
-        <v>132.590667724609</v>
+        <v>132.59065246582</v>
       </c>
       <c r="H1366" t="n">
         <v>140516</v>
@@ -40041,7 +40041,7 @@
         <v>144.149993896484</v>
       </c>
       <c r="G1368" t="n">
-        <v>134.503463745117</v>
+        <v>134.503448486328</v>
       </c>
       <c r="H1368" t="n">
         <v>262530</v>
@@ -40070,7 +40070,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1369" t="n">
-        <v>134.456481933594</v>
+        <v>134.456497192383</v>
       </c>
       <c r="H1369" t="n">
         <v>99816</v>
@@ -40157,7 +40157,7 @@
         <v>143.949996948242</v>
       </c>
       <c r="G1372" t="n">
-        <v>135.255111694336</v>
+        <v>135.255142211914</v>
       </c>
       <c r="H1372" t="n">
         <v>290807</v>
@@ -40244,7 +40244,7 @@
         <v>142.050003051758</v>
       </c>
       <c r="G1375" t="n">
-        <v>133.46989440918</v>
+        <v>133.469909667969</v>
       </c>
       <c r="H1375" t="n">
         <v>381977</v>
@@ -40389,7 +40389,7 @@
         <v>143.649993896484</v>
       </c>
       <c r="G1380" t="n">
-        <v>134.973251342773</v>
+        <v>134.973236083984</v>
       </c>
       <c r="H1380" t="n">
         <v>323282</v>
@@ -40418,7 +40418,7 @@
         <v>144.850006103516</v>
       </c>
       <c r="G1381" t="n">
-        <v>136.100784301758</v>
+        <v>136.100769042969</v>
       </c>
       <c r="H1381" t="n">
         <v>125399</v>
@@ -40505,7 +40505,7 @@
         <v>150.75</v>
       </c>
       <c r="G1384" t="n">
-        <v>141.644409179688</v>
+        <v>141.644393920898</v>
       </c>
       <c r="H1384" t="n">
         <v>122474</v>
@@ -40563,7 +40563,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1386" t="n">
-        <v>143.570556640625</v>
+        <v>143.570571899414</v>
       </c>
       <c r="H1386" t="n">
         <v>163521</v>
@@ -40650,7 +40650,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G1389" t="n">
-        <v>144.134323120117</v>
+        <v>144.134307861328</v>
       </c>
       <c r="H1389" t="n">
         <v>95596</v>
@@ -40708,7 +40708,7 @@
         <v>149.800003051758</v>
       </c>
       <c r="G1391" t="n">
-        <v>140.75178527832</v>
+        <v>140.751800537109</v>
       </c>
       <c r="H1391" t="n">
         <v>134474</v>
@@ -40737,7 +40737,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G1392" t="n">
-        <v>145.261840820312</v>
+        <v>145.261856079102</v>
       </c>
       <c r="H1392" t="n">
         <v>295841</v>
@@ -40766,7 +40766,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1393" t="n">
-        <v>146.671249389648</v>
+        <v>146.671264648438</v>
       </c>
       <c r="H1393" t="n">
         <v>119203</v>
@@ -40795,7 +40795,7 @@
         <v>157</v>
       </c>
       <c r="G1394" t="n">
-        <v>147.516906738281</v>
+        <v>147.516891479492</v>
       </c>
       <c r="H1394" t="n">
         <v>115959</v>
@@ -40882,7 +40882,7 @@
         <v>157.5</v>
       </c>
       <c r="G1397" t="n">
-        <v>147.986709594727</v>
+        <v>147.986679077148</v>
       </c>
       <c r="H1397" t="n">
         <v>157413</v>
@@ -40998,7 +40998,7 @@
         <v>163.300003051758</v>
       </c>
       <c r="G1401" t="n">
-        <v>153.43635559082</v>
+        <v>153.436370849609</v>
       </c>
       <c r="H1401" t="n">
         <v>158512</v>
@@ -41085,7 +41085,7 @@
         <v>162.050003051758</v>
       </c>
       <c r="G1404" t="n">
-        <v>152.261856079102</v>
+        <v>152.261871337891</v>
       </c>
       <c r="H1404" t="n">
         <v>212038</v>
@@ -41114,7 +41114,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1405" t="n">
-        <v>152.590728759766</v>
+        <v>152.590713500977</v>
       </c>
       <c r="H1405" t="n">
         <v>329836</v>
@@ -41172,7 +41172,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1407" t="n">
-        <v>152.778625488281</v>
+        <v>152.778656005859</v>
       </c>
       <c r="H1407" t="n">
         <v>120303</v>
@@ -41201,7 +41201,7 @@
         <v>163.050003051758</v>
       </c>
       <c r="G1408" t="n">
-        <v>153.201461791992</v>
+        <v>153.201446533203</v>
       </c>
       <c r="H1408" t="n">
         <v>133417</v>
@@ -41288,7 +41288,7 @@
         <v>169.449996948242</v>
       </c>
       <c r="G1411" t="n">
-        <v>159.214874267578</v>
+        <v>159.214889526367</v>
       </c>
       <c r="H1411" t="n">
         <v>302805</v>
@@ -41346,7 +41346,7 @@
         <v>172.350006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>161.939712524414</v>
+        <v>161.939727783203</v>
       </c>
       <c r="H1413" t="n">
         <v>141959</v>
@@ -41375,7 +41375,7 @@
         <v>168.949996948242</v>
       </c>
       <c r="G1414" t="n">
-        <v>158.745071411133</v>
+        <v>158.745086669922</v>
       </c>
       <c r="H1414" t="n">
         <v>164215</v>
@@ -41404,7 +41404,7 @@
         <v>168.100006103516</v>
       </c>
       <c r="G1415" t="n">
-        <v>157.946426391602</v>
+        <v>157.946441650391</v>
       </c>
       <c r="H1415" t="n">
         <v>126581</v>
@@ -41433,7 +41433,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1416" t="n">
-        <v>159.355819702148</v>
+        <v>159.355834960938</v>
       </c>
       <c r="H1416" t="n">
         <v>97378</v>
@@ -41520,7 +41520,7 @@
         <v>176.449996948242</v>
       </c>
       <c r="G1419" t="n">
-        <v>165.792068481445</v>
+        <v>165.792053222656</v>
       </c>
       <c r="H1419" t="n">
         <v>223351</v>
@@ -41549,7 +41549,7 @@
         <v>171.949996948242</v>
       </c>
       <c r="G1420" t="n">
-        <v>161.563888549805</v>
+        <v>161.563873291016</v>
       </c>
       <c r="H1420" t="n">
         <v>178590</v>
@@ -41665,7 +41665,7 @@
         <v>176.199996948242</v>
       </c>
       <c r="G1424" t="n">
-        <v>165.557174682617</v>
+        <v>165.557159423828</v>
       </c>
       <c r="H1424" t="n">
         <v>142117</v>
@@ -41694,7 +41694,7 @@
         <v>175.850006103516</v>
       </c>
       <c r="G1425" t="n">
-        <v>165.228317260742</v>
+        <v>165.228332519531</v>
       </c>
       <c r="H1425" t="n">
         <v>127422</v>
@@ -41752,7 +41752,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1427" t="n">
-        <v>168.000137329102</v>
+        <v>168.000122070312</v>
       </c>
       <c r="H1427" t="n">
         <v>109222</v>
@@ -41781,7 +41781,7 @@
         <v>177.850006103516</v>
       </c>
       <c r="G1428" t="n">
-        <v>167.107498168945</v>
+        <v>167.107528686523</v>
       </c>
       <c r="H1428" t="n">
         <v>103150</v>
@@ -41868,7 +41868,7 @@
         <v>184.850006103516</v>
       </c>
       <c r="G1431" t="n">
-        <v>173.684692382812</v>
+        <v>173.684707641602</v>
       </c>
       <c r="H1431" t="n">
         <v>119649</v>
@@ -41897,7 +41897,7 @@
         <v>185.050003051758</v>
       </c>
       <c r="G1432" t="n">
-        <v>173.872619628906</v>
+        <v>173.872604370117</v>
       </c>
       <c r="H1432" t="n">
         <v>176783</v>
@@ -41955,7 +41955,7 @@
         <v>187.550003051758</v>
       </c>
       <c r="G1434" t="n">
-        <v>176.221603393555</v>
+        <v>176.221618652344</v>
       </c>
       <c r="H1434" t="n">
         <v>124411</v>
@@ -42129,7 +42129,7 @@
         <v>193.25</v>
       </c>
       <c r="G1440" t="n">
-        <v>181.57731628418</v>
+        <v>181.577301025391</v>
       </c>
       <c r="H1440" t="n">
         <v>168673</v>
@@ -42274,7 +42274,7 @@
         <v>200.199996948242</v>
       </c>
       <c r="G1445" t="n">
-        <v>188.107513427734</v>
+        <v>188.107528686523</v>
       </c>
       <c r="H1445" t="n">
         <v>166966</v>
@@ -42390,7 +42390,7 @@
         <v>196.699996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>184.818939208984</v>
+        <v>184.818923950195</v>
       </c>
       <c r="H1449" t="n">
         <v>244088</v>
@@ -42448,7 +42448,7 @@
         <v>198.850006103516</v>
       </c>
       <c r="G1451" t="n">
-        <v>186.839080810547</v>
+        <v>186.839065551758</v>
       </c>
       <c r="H1451" t="n">
         <v>143244</v>
@@ -42477,7 +42477,7 @@
         <v>200.600006103516</v>
       </c>
       <c r="G1452" t="n">
-        <v>188.483367919922</v>
+        <v>188.483383178711</v>
       </c>
       <c r="H1452" t="n">
         <v>69766</v>
@@ -42506,7 +42506,7 @@
         <v>202.600006103516</v>
       </c>
       <c r="G1453" t="n">
-        <v>190.362579345703</v>
+        <v>190.362564086914</v>
       </c>
       <c r="H1453" t="n">
         <v>195621</v>
@@ -42535,7 +42535,7 @@
         <v>200.199996948242</v>
       </c>
       <c r="G1454" t="n">
-        <v>188.107513427734</v>
+        <v>188.107528686523</v>
       </c>
       <c r="H1454" t="n">
         <v>121231</v>
@@ -42651,7 +42651,7 @@
         <v>195.850006103516</v>
       </c>
       <c r="G1458" t="n">
-        <v>184.020294189453</v>
+        <v>184.020278930664</v>
       </c>
       <c r="H1458" t="n">
         <v>168457</v>
@@ -42680,7 +42680,7 @@
         <v>188.600006103516</v>
       </c>
       <c r="G1459" t="n">
-        <v>177.208190917969</v>
+        <v>177.208206176758</v>
       </c>
       <c r="H1459" t="n">
         <v>211297</v>
@@ -42709,7 +42709,7 @@
         <v>182.800003051758</v>
       </c>
       <c r="G1460" t="n">
-        <v>171.758529663086</v>
+        <v>171.758514404297</v>
       </c>
       <c r="H1460" t="n">
         <v>253079</v>
@@ -42767,7 +42767,7 @@
         <v>181.350006103516</v>
       </c>
       <c r="G1462" t="n">
-        <v>170.396102905273</v>
+        <v>170.396087646484</v>
       </c>
       <c r="H1462" t="n">
         <v>121586</v>
@@ -42825,7 +42825,7 @@
         <v>171.850006103516</v>
       </c>
       <c r="G1464" t="n">
-        <v>161.469924926758</v>
+        <v>161.469940185547</v>
       </c>
       <c r="H1464" t="n">
         <v>148532</v>
@@ -42854,7 +42854,7 @@
         <v>172.850006103516</v>
       </c>
       <c r="G1465" t="n">
-        <v>162.409530639648</v>
+        <v>162.409515380859</v>
       </c>
       <c r="H1465" t="n">
         <v>167873</v>
@@ -42941,7 +42941,7 @@
         <v>172.100006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>161.704833984375</v>
+        <v>161.704818725586</v>
       </c>
       <c r="H1468" t="n">
         <v>110991</v>
@@ -42999,7 +42999,7 @@
         <v>173.949996948242</v>
       </c>
       <c r="G1470" t="n">
-        <v>163.443054199219</v>
+        <v>163.443069458008</v>
       </c>
       <c r="H1470" t="n">
         <v>303280</v>
@@ -43028,7 +43028,7 @@
         <v>178.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>167.718246459961</v>
+        <v>167.71826171875</v>
       </c>
       <c r="H1471" t="n">
         <v>158372</v>
@@ -43086,7 +43086,7 @@
         <v>180.100006103516</v>
       </c>
       <c r="G1473" t="n">
-        <v>169.221618652344</v>
+        <v>169.221633911133</v>
       </c>
       <c r="H1473" t="n">
         <v>104846</v>
@@ -43260,7 +43260,7 @@
         <v>191.050003051758</v>
       </c>
       <c r="G1479" t="n">
-        <v>179.510192871094</v>
+        <v>179.510208129883</v>
       </c>
       <c r="H1479" t="n">
         <v>81861</v>
@@ -43289,7 +43289,7 @@
         <v>191</v>
       </c>
       <c r="G1480" t="n">
-        <v>179.463226318359</v>
+        <v>179.46321105957</v>
       </c>
       <c r="H1480" t="n">
         <v>119081</v>
@@ -43347,7 +43347,7 @@
         <v>195.449996948242</v>
       </c>
       <c r="G1482" t="n">
-        <v>183.644439697266</v>
+        <v>183.644409179688</v>
       </c>
       <c r="H1482" t="n">
         <v>233069</v>
@@ -43405,7 +43405,7 @@
         <v>197.149993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>185.241760253906</v>
+        <v>185.241744995117</v>
       </c>
       <c r="H1484" t="n">
         <v>97845</v>
@@ -43550,7 +43550,7 @@
         <v>184.100006103516</v>
       </c>
       <c r="G1489" t="n">
-        <v>172.979995727539</v>
+        <v>172.980010986328</v>
       </c>
       <c r="H1489" t="n">
         <v>196667</v>
@@ -43579,7 +43579,7 @@
         <v>182.800003051758</v>
       </c>
       <c r="G1490" t="n">
-        <v>171.758529663086</v>
+        <v>171.758514404297</v>
       </c>
       <c r="H1490" t="n">
         <v>102792</v>
@@ -43608,7 +43608,7 @@
         <v>183.399993896484</v>
       </c>
       <c r="G1491" t="n">
-        <v>172.322265625</v>
+        <v>172.322280883789</v>
       </c>
       <c r="H1491" t="n">
         <v>147063</v>
@@ -43666,7 +43666,7 @@
         <v>188</v>
       </c>
       <c r="G1493" t="n">
-        <v>176.644424438477</v>
+        <v>176.644409179688</v>
       </c>
       <c r="H1493" t="n">
         <v>181928</v>
@@ -43695,7 +43695,7 @@
         <v>188.949996948242</v>
       </c>
       <c r="G1494" t="n">
-        <v>177.537033081055</v>
+        <v>177.537048339844</v>
       </c>
       <c r="H1494" t="n">
         <v>122784</v>
@@ -43724,7 +43724,7 @@
         <v>191.699996948242</v>
       </c>
       <c r="G1495" t="n">
-        <v>180.12092590332</v>
+        <v>180.120941162109</v>
       </c>
       <c r="H1495" t="n">
         <v>162483</v>
@@ -43782,7 +43782,7 @@
         <v>184.5</v>
       </c>
       <c r="G1497" t="n">
-        <v>173.355819702148</v>
+        <v>173.355834960938</v>
       </c>
       <c r="H1497" t="n">
         <v>108994</v>
@@ -43898,7 +43898,7 @@
         <v>177.449996948242</v>
       </c>
       <c r="G1501" t="n">
-        <v>166.731658935547</v>
+        <v>166.731674194336</v>
       </c>
       <c r="H1501" t="n">
         <v>153592</v>
@@ -43927,7 +43927,7 @@
         <v>177.449996948242</v>
       </c>
       <c r="G1502" t="n">
-        <v>166.731658935547</v>
+        <v>166.731674194336</v>
       </c>
       <c r="H1502" t="n">
         <v>75392</v>
@@ -43956,7 +43956,7 @@
         <v>187.300003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>175.986709594727</v>
+        <v>175.986694335938</v>
       </c>
       <c r="H1503" t="n">
         <v>372294</v>
@@ -43985,7 +43985,7 @@
         <v>185.100006103516</v>
       </c>
       <c r="G1504" t="n">
-        <v>173.919586181641</v>
+        <v>173.91960144043</v>
       </c>
       <c r="H1504" t="n">
         <v>205053</v>
@@ -44014,7 +44014,7 @@
         <v>188.75</v>
       </c>
       <c r="G1505" t="n">
-        <v>177.34912109375</v>
+        <v>177.349105834961</v>
       </c>
       <c r="H1505" t="n">
         <v>359394</v>
@@ -44101,7 +44101,7 @@
         <v>176.699996948242</v>
       </c>
       <c r="G1508" t="n">
-        <v>166.026962280273</v>
+        <v>166.026977539062</v>
       </c>
       <c r="H1508" t="n">
         <v>117673</v>
@@ -44188,7 +44188,7 @@
         <v>174.949996948242</v>
       </c>
       <c r="G1511" t="n">
-        <v>164.382675170898</v>
+        <v>164.382659912109</v>
       </c>
       <c r="H1511" t="n">
         <v>188909</v>
@@ -44217,7 +44217,7 @@
         <v>178</v>
       </c>
       <c r="G1512" t="n">
-        <v>167.248428344727</v>
+        <v>167.248443603516</v>
       </c>
       <c r="H1512" t="n">
         <v>123846</v>
@@ -44246,7 +44246,7 @@
         <v>180</v>
       </c>
       <c r="G1513" t="n">
-        <v>169.127639770508</v>
+        <v>169.127655029297</v>
       </c>
       <c r="H1513" t="n">
         <v>163104</v>
@@ -44304,7 +44304,7 @@
         <v>176.300003051758</v>
       </c>
       <c r="G1515" t="n">
-        <v>165.651138305664</v>
+        <v>165.651153564453</v>
       </c>
       <c r="H1515" t="n">
         <v>157321</v>
@@ -44362,7 +44362,7 @@
         <v>178.149993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>167.389389038086</v>
+        <v>167.389373779297</v>
       </c>
       <c r="H1517" t="n">
         <v>197009</v>
@@ -44391,7 +44391,7 @@
         <v>158.850006103516</v>
       </c>
       <c r="G1518" t="n">
-        <v>149.255142211914</v>
+        <v>149.255172729492</v>
       </c>
       <c r="H1518" t="n">
         <v>852382</v>
@@ -44420,7 +44420,7 @@
         <v>160.550003051758</v>
       </c>
       <c r="G1519" t="n">
-        <v>150.852447509766</v>
+        <v>150.852462768555</v>
       </c>
       <c r="H1519" t="n">
         <v>332357</v>
@@ -44478,7 +44478,7 @@
         <v>161.850006103516</v>
       </c>
       <c r="G1521" t="n">
-        <v>152.073928833008</v>
+        <v>152.073959350586</v>
       </c>
       <c r="H1521" t="n">
         <v>173529</v>
@@ -44507,7 +44507,7 @@
         <v>161.649993896484</v>
       </c>
       <c r="G1522" t="n">
-        <v>151.886016845703</v>
+        <v>151.886001586914</v>
       </c>
       <c r="H1522" t="n">
         <v>99903</v>
@@ -44594,7 +44594,7 @@
         <v>165</v>
       </c>
       <c r="G1525" t="n">
-        <v>155.033660888672</v>
+        <v>155.033676147461</v>
       </c>
       <c r="H1525" t="n">
         <v>89536</v>
@@ -44623,7 +44623,7 @@
         <v>167.449996948242</v>
       </c>
       <c r="G1526" t="n">
-        <v>157.335678100586</v>
+        <v>157.335693359375</v>
       </c>
       <c r="H1526" t="n">
         <v>110574</v>
@@ -44681,7 +44681,7 @@
         <v>158.949996948242</v>
       </c>
       <c r="G1528" t="n">
-        <v>149.349090576172</v>
+        <v>149.349105834961</v>
       </c>
       <c r="H1528" t="n">
         <v>312211</v>
@@ -44710,7 +44710,7 @@
         <v>160.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>150.805480957031</v>
+        <v>150.805465698242</v>
       </c>
       <c r="H1529" t="n">
         <v>187469</v>
@@ -44739,7 +44739,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1530" t="n">
-        <v>146.671249389648</v>
+        <v>146.671264648438</v>
       </c>
       <c r="H1530" t="n">
         <v>220701</v>
@@ -44768,7 +44768,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1531" t="n">
-        <v>145.449768066406</v>
+        <v>145.449798583984</v>
       </c>
       <c r="H1531" t="n">
         <v>146624</v>
@@ -44797,7 +44797,7 @@
         <v>148.100006103516</v>
       </c>
       <c r="G1532" t="n">
-        <v>139.154479980469</v>
+        <v>139.15446472168</v>
       </c>
       <c r="H1532" t="n">
         <v>298395</v>
@@ -44913,7 +44913,7 @@
         <v>146.100006103516</v>
       </c>
       <c r="G1536" t="n">
-        <v>137.275299072266</v>
+        <v>137.275283813477</v>
       </c>
       <c r="H1536" t="n">
         <v>192588</v>
@@ -45029,7 +45029,7 @@
         <v>147</v>
       </c>
       <c r="G1540" t="n">
-        <v>138.12092590332</v>
+        <v>138.120895385742</v>
       </c>
       <c r="H1540" t="n">
         <v>200365</v>
@@ -45087,7 +45087,7 @@
         <v>134.699996948242</v>
       </c>
       <c r="G1542" t="n">
-        <v>126.563858032227</v>
+        <v>126.563842773438</v>
       </c>
       <c r="H1542" t="n">
         <v>258264</v>
@@ -45116,7 +45116,7 @@
         <v>132.550003051758</v>
       </c>
       <c r="G1543" t="n">
-        <v>124.543701171875</v>
+        <v>124.543724060059</v>
       </c>
       <c r="H1543" t="n">
         <v>238575</v>
@@ -45145,7 +45145,7 @@
         <v>134.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>126.610847473145</v>
+        <v>126.610832214355</v>
       </c>
       <c r="H1544" t="n">
         <v>138490</v>
@@ -45232,7 +45232,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G1547" t="n">
-        <v>128.630950927734</v>
+        <v>128.630966186523</v>
       </c>
       <c r="H1547" t="n">
         <v>116999</v>
@@ -45290,7 +45290,7 @@
         <v>137.899993896484</v>
       </c>
       <c r="G1549" t="n">
-        <v>129.570541381836</v>
+        <v>129.570556640625</v>
       </c>
       <c r="H1549" t="n">
         <v>114556</v>
@@ -45319,7 +45319,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1550" t="n">
-        <v>125.342361450195</v>
+        <v>125.342353820801</v>
       </c>
       <c r="H1550" t="n">
         <v>164718</v>
@@ -45348,7 +45348,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G1551" t="n">
-        <v>123.65111541748</v>
+        <v>123.651107788086</v>
       </c>
       <c r="H1551" t="n">
         <v>134476</v>
@@ -45377,7 +45377,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>118.295402526855</v>
+        <v>118.295387268066</v>
       </c>
       <c r="H1552" t="n">
         <v>327942</v>
@@ -45522,7 +45522,7 @@
         <v>119.75</v>
       </c>
       <c r="G1557" t="n">
-        <v>112.51685333252</v>
+        <v>112.516860961914</v>
       </c>
       <c r="H1557" t="n">
         <v>221947</v>
@@ -45551,7 +45551,7 @@
         <v>122.300003051758</v>
       </c>
       <c r="G1558" t="n">
-        <v>114.912841796875</v>
+        <v>114.91284942627</v>
       </c>
       <c r="H1558" t="n">
         <v>150998</v>
@@ -45638,7 +45638,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1561" t="n">
-        <v>110.21484375</v>
+        <v>110.214851379395</v>
       </c>
       <c r="H1561" t="n">
         <v>208572</v>
@@ -45667,7 +45667,7 @@
         <v>117.449996948242</v>
       </c>
       <c r="G1562" t="n">
-        <v>110.35578918457</v>
+        <v>110.355781555176</v>
       </c>
       <c r="H1562" t="n">
         <v>122923</v>
@@ -45812,7 +45812,7 @@
         <v>133.649993896484</v>
       </c>
       <c r="G1567" t="n">
-        <v>125.577270507812</v>
+        <v>125.577262878418</v>
       </c>
       <c r="H1567" t="n">
         <v>224735</v>
@@ -45841,7 +45841,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G1568" t="n">
-        <v>124.778617858887</v>
+        <v>124.778625488281</v>
       </c>
       <c r="H1568" t="n">
         <v>211077</v>
@@ -45870,7 +45870,7 @@
         <v>129.300003051758</v>
       </c>
       <c r="G1569" t="n">
-        <v>121.490020751953</v>
+        <v>121.490028381348</v>
       </c>
       <c r="H1569" t="n">
         <v>217124</v>
@@ -45899,7 +45899,7 @@
         <v>128.649993896484</v>
       </c>
       <c r="G1570" t="n">
-        <v>120.879272460938</v>
+        <v>120.879280090332</v>
       </c>
       <c r="H1570" t="n">
         <v>92715</v>
@@ -45986,7 +45986,7 @@
         <v>122.75</v>
       </c>
       <c r="G1573" t="n">
-        <v>115.335655212402</v>
+        <v>115.335647583008</v>
       </c>
       <c r="H1573" t="n">
         <v>240923</v>
@@ -46015,7 +46015,7 @@
         <v>126.199996948242</v>
       </c>
       <c r="G1574" t="n">
-        <v>118.577262878418</v>
+        <v>118.577270507812</v>
       </c>
       <c r="H1574" t="n">
         <v>237226</v>
@@ -46102,7 +46102,7 @@
         <v>127.300003051758</v>
       </c>
       <c r="G1577" t="n">
-        <v>119.610832214355</v>
+        <v>119.61083984375</v>
       </c>
       <c r="H1577" t="n">
         <v>113985</v>
@@ -46131,7 +46131,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1578" t="n">
-        <v>118.295402526855</v>
+        <v>118.295387268066</v>
       </c>
       <c r="H1578" t="n">
         <v>103471</v>
@@ -46218,7 +46218,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G1581" t="n">
-        <v>129.852416992188</v>
+        <v>129.852432250977</v>
       </c>
       <c r="H1581" t="n">
         <v>241443</v>
@@ -46247,7 +46247,7 @@
         <v>132.350006103516</v>
       </c>
       <c r="G1582" t="n">
-        <v>124.355804443359</v>
+        <v>124.355812072754</v>
       </c>
       <c r="H1582" t="n">
         <v>141438</v>
@@ -46276,7 +46276,7 @@
         <v>132.25</v>
       </c>
       <c r="G1583" t="n">
-        <v>124.261825561523</v>
+        <v>124.261833190918</v>
       </c>
       <c r="H1583" t="n">
         <v>127989</v>
@@ -46305,7 +46305,7 @@
         <v>130.850006103516</v>
       </c>
       <c r="G1584" t="n">
-        <v>122.946411132812</v>
+        <v>122.946418762207</v>
       </c>
       <c r="H1584" t="n">
         <v>118635</v>
@@ -46334,7 +46334,7 @@
         <v>129.75</v>
       </c>
       <c r="G1585" t="n">
-        <v>121.91283416748</v>
+        <v>121.91284942627</v>
       </c>
       <c r="H1585" t="n">
         <v>95622</v>
@@ -46363,7 +46363,7 @@
         <v>128.649993896484</v>
       </c>
       <c r="G1586" t="n">
-        <v>120.879272460938</v>
+        <v>120.879280090332</v>
       </c>
       <c r="H1586" t="n">
         <v>94605</v>
@@ -46421,7 +46421,7 @@
         <v>139.800003051758</v>
       </c>
       <c r="G1588" t="n">
-        <v>131.35578918457</v>
+        <v>131.355819702148</v>
       </c>
       <c r="H1588" t="n">
         <v>258823</v>
@@ -46479,7 +46479,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G1590" t="n">
-        <v>133.328948974609</v>
+        <v>133.32893371582</v>
       </c>
       <c r="H1590" t="n">
         <v>129411</v>
@@ -46508,7 +46508,7 @@
         <v>145.550003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>136.758483886719</v>
+        <v>136.758499145508</v>
       </c>
       <c r="H1591" t="n">
         <v>167885</v>
@@ -46653,7 +46653,7 @@
         <v>141.300003051758</v>
       </c>
       <c r="G1596" t="n">
-        <v>132.765197753906</v>
+        <v>132.765213012695</v>
       </c>
       <c r="H1596" t="n">
         <v>104501</v>
@@ -46682,7 +46682,7 @@
         <v>138.550003051758</v>
       </c>
       <c r="G1597" t="n">
-        <v>130.181304931641</v>
+        <v>130.18132019043</v>
       </c>
       <c r="H1597" t="n">
         <v>115375</v>
@@ -46740,7 +46740,7 @@
         <v>134.850006103516</v>
       </c>
       <c r="G1599" t="n">
-        <v>126.704818725586</v>
+        <v>126.704803466797</v>
       </c>
       <c r="H1599" t="n">
         <v>114281</v>
@@ -46769,7 +46769,7 @@
         <v>134.300003051758</v>
       </c>
       <c r="G1600" t="n">
-        <v>126.188018798828</v>
+        <v>126.188026428223</v>
       </c>
       <c r="H1600" t="n">
         <v>82429</v>
@@ -46798,7 +46798,7 @@
         <v>134.149993896484</v>
       </c>
       <c r="G1601" t="n">
-        <v>126.047065734863</v>
+        <v>126.047058105469</v>
       </c>
       <c r="H1601" t="n">
         <v>133305</v>
@@ -46827,7 +46827,7 @@
         <v>132.100006103516</v>
       </c>
       <c r="G1602" t="n">
-        <v>124.120903015137</v>
+        <v>124.120910644531</v>
       </c>
       <c r="H1602" t="n">
         <v>105461</v>
@@ -46885,7 +46885,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G1604" t="n">
-        <v>118.765190124512</v>
+        <v>118.765197753906</v>
       </c>
       <c r="H1604" t="n">
         <v>210078</v>
@@ -46972,7 +46972,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G1607" t="n">
-        <v>113.127593994141</v>
+        <v>113.127601623535</v>
       </c>
       <c r="H1607" t="n">
         <v>146131</v>
@@ -47001,7 +47001,7 @@
         <v>123.949996948242</v>
       </c>
       <c r="G1608" t="n">
-        <v>116.463165283203</v>
+        <v>116.463172912598</v>
       </c>
       <c r="H1608" t="n">
         <v>144335</v>
@@ -47030,7 +47030,7 @@
         <v>125.050003051758</v>
       </c>
       <c r="G1609" t="n">
-        <v>117.496726989746</v>
+        <v>117.496734619141</v>
       </c>
       <c r="H1609" t="n">
         <v>222303</v>
@@ -47059,7 +47059,7 @@
         <v>123.449996948242</v>
       </c>
       <c r="G1610" t="n">
-        <v>115.993377685547</v>
+        <v>115.993362426758</v>
       </c>
       <c r="H1610" t="n">
         <v>157455</v>
@@ -47088,7 +47088,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G1611" t="n">
-        <v>115.476600646973</v>
+        <v>115.476593017578</v>
       </c>
       <c r="H1611" t="n">
         <v>126786</v>
@@ -47117,7 +47117,7 @@
         <v>119.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>112.281951904297</v>
+        <v>112.281959533691</v>
       </c>
       <c r="H1612" t="n">
         <v>160766</v>
@@ -47146,7 +47146,7 @@
         <v>119.949996948242</v>
       </c>
       <c r="G1613" t="n">
-        <v>112.704772949219</v>
+        <v>112.704765319824</v>
       </c>
       <c r="H1613" t="n">
         <v>156486</v>
@@ -47204,7 +47204,7 @@
         <v>114.150001525879</v>
       </c>
       <c r="G1615" t="n">
-        <v>107.25511932373</v>
+        <v>107.255111694336</v>
       </c>
       <c r="H1615" t="n">
         <v>216195</v>
@@ -47262,7 +47262,7 @@
         <v>114.550003051758</v>
       </c>
       <c r="G1617" t="n">
-        <v>107.630950927734</v>
+        <v>107.630958557129</v>
       </c>
       <c r="H1617" t="n">
         <v>153090</v>
@@ -47291,7 +47291,7 @@
         <v>111.949996948242</v>
       </c>
       <c r="G1618" t="n">
-        <v>105.188003540039</v>
+        <v>105.187995910645</v>
       </c>
       <c r="H1618" t="n">
         <v>218244</v>
@@ -47349,7 +47349,7 @@
         <v>120</v>
       </c>
       <c r="G1620" t="n">
-        <v>112.751754760742</v>
+        <v>112.751762390137</v>
       </c>
       <c r="H1620" t="n">
         <v>140871</v>
@@ -47581,7 +47581,7 @@
         <v>117.400001525879</v>
       </c>
       <c r="G1628" t="n">
-        <v>111.289543151855</v>
+        <v>111.289535522461</v>
       </c>
       <c r="H1628" t="n">
         <v>65440</v>
@@ -47668,7 +47668,7 @@
         <v>122.5</v>
       </c>
       <c r="G1631" t="n">
-        <v>116.124092102051</v>
+        <v>116.124084472656</v>
       </c>
       <c r="H1631" t="n">
         <v>507793</v>
@@ -47726,7 +47726,7 @@
         <v>124.050003051758</v>
       </c>
       <c r="G1633" t="n">
-        <v>117.593414306641</v>
+        <v>117.593421936035</v>
       </c>
       <c r="H1633" t="n">
         <v>89748</v>
@@ -47784,7 +47784,7 @@
         <v>122.449996948242</v>
       </c>
       <c r="G1635" t="n">
-        <v>116.076690673828</v>
+        <v>116.076683044434</v>
       </c>
       <c r="H1635" t="n">
         <v>84303</v>
@@ -47900,7 +47900,7 @@
         <v>115.75</v>
       </c>
       <c r="G1639" t="n">
-        <v>109.725425720215</v>
+        <v>109.72541809082</v>
       </c>
       <c r="H1639" t="n">
         <v>163450</v>
@@ -48016,7 +48016,7 @@
         <v>113.800003051758</v>
       </c>
       <c r="G1643" t="n">
-        <v>107.876907348633</v>
+        <v>107.876914978027</v>
       </c>
       <c r="H1643" t="n">
         <v>153710</v>
@@ -48161,7 +48161,7 @@
         <v>124.449996948242</v>
       </c>
       <c r="G1648" t="n">
-        <v>117.972595214844</v>
+        <v>117.972587585449</v>
       </c>
       <c r="H1648" t="n">
         <v>207628</v>
@@ -48248,7 +48248,7 @@
         <v>126.949996948242</v>
       </c>
       <c r="G1651" t="n">
-        <v>120.342483520508</v>
+        <v>120.342475891113</v>
       </c>
       <c r="H1651" t="n">
         <v>62222</v>
@@ -48277,7 +48277,7 @@
         <v>125.150001525879</v>
       </c>
       <c r="G1652" t="n">
-        <v>118.636169433594</v>
+        <v>118.636161804199</v>
       </c>
       <c r="H1652" t="n">
         <v>73306</v>
@@ -48306,7 +48306,7 @@
         <v>125.199996948242</v>
       </c>
       <c r="G1653" t="n">
-        <v>118.683563232422</v>
+        <v>118.683555603027</v>
       </c>
       <c r="H1653" t="n">
         <v>103732</v>
@@ -48538,7 +48538,7 @@
         <v>130.050003051758</v>
       </c>
       <c r="G1661" t="n">
-        <v>123.281127929688</v>
+        <v>123.281135559082</v>
       </c>
       <c r="H1661" t="n">
         <v>130171</v>
@@ -48596,7 +48596,7 @@
         <v>129.399993896484</v>
       </c>
       <c r="G1663" t="n">
-        <v>122.664947509766</v>
+        <v>122.664939880371</v>
       </c>
       <c r="H1663" t="n">
         <v>60705</v>
@@ -48625,7 +48625,7 @@
         <v>132.449996948242</v>
       </c>
       <c r="G1664" t="n">
-        <v>125.556213378906</v>
+        <v>125.556198120117</v>
       </c>
       <c r="H1664" t="n">
         <v>52174</v>
@@ -48857,7 +48857,7 @@
         <v>130.399993896484</v>
       </c>
       <c r="G1672" t="n">
-        <v>123.612915039062</v>
+        <v>123.612899780273</v>
       </c>
       <c r="H1672" t="n">
         <v>149687</v>
@@ -48886,7 +48886,7 @@
         <v>134.850006103516</v>
       </c>
       <c r="G1673" t="n">
-        <v>127.83129119873</v>
+        <v>127.83130645752</v>
       </c>
       <c r="H1673" t="n">
         <v>98365</v>
@@ -48915,7 +48915,7 @@
         <v>135.600006103516</v>
       </c>
       <c r="G1674" t="n">
-        <v>128.542251586914</v>
+        <v>128.542266845703</v>
       </c>
       <c r="H1674" t="n">
         <v>89785</v>
@@ -48973,7 +48973,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G1676" t="n">
-        <v>126.267181396484</v>
+        <v>126.267166137695</v>
       </c>
       <c r="H1676" t="n">
         <v>115753</v>
@@ -49118,7 +49118,7 @@
         <v>135.550003051758</v>
       </c>
       <c r="G1681" t="n">
-        <v>128.494857788086</v>
+        <v>128.494873046875</v>
       </c>
       <c r="H1681" t="n">
         <v>84588</v>
@@ -49205,7 +49205,7 @@
         <v>139.899993896484</v>
       </c>
       <c r="G1684" t="n">
-        <v>132.618453979492</v>
+        <v>132.618438720703</v>
       </c>
       <c r="H1684" t="n">
         <v>103334</v>
@@ -49234,7 +49234,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G1685" t="n">
-        <v>130.438171386719</v>
+        <v>130.438186645508</v>
       </c>
       <c r="H1685" t="n">
         <v>127100</v>
@@ -49350,7 +49350,7 @@
         <v>136.699996948242</v>
       </c>
       <c r="G1689" t="n">
-        <v>129.585006713867</v>
+        <v>129.584991455078</v>
       </c>
       <c r="H1689" t="n">
         <v>84380</v>
@@ -49408,7 +49408,7 @@
         <v>136.149993896484</v>
       </c>
       <c r="G1691" t="n">
-        <v>129.06364440918</v>
+        <v>129.063629150391</v>
       </c>
       <c r="H1691" t="n">
         <v>71598</v>
@@ -49495,7 +49495,7 @@
         <v>131</v>
       </c>
       <c r="G1694" t="n">
-        <v>124.181671142578</v>
+        <v>124.181686401367</v>
       </c>
       <c r="H1694" t="n">
         <v>82745</v>
@@ -49524,7 +49524,7 @@
         <v>132.399993896484</v>
       </c>
       <c r="G1695" t="n">
-        <v>125.508819580078</v>
+        <v>125.508804321289</v>
       </c>
       <c r="H1695" t="n">
         <v>51143</v>
@@ -49582,7 +49582,7 @@
         <v>130.350006103516</v>
       </c>
       <c r="G1697" t="n">
-        <v>123.565505981445</v>
+        <v>123.565521240234</v>
       </c>
       <c r="H1697" t="n">
         <v>116161</v>
@@ -49611,7 +49611,7 @@
         <v>133.75</v>
       </c>
       <c r="G1698" t="n">
-        <v>126.788543701172</v>
+        <v>126.788558959961</v>
       </c>
       <c r="H1698" t="n">
         <v>88755</v>
@@ -49756,7 +49756,7 @@
         <v>134.600006103516</v>
       </c>
       <c r="G1703" t="n">
-        <v>127.594314575195</v>
+        <v>127.594329833984</v>
       </c>
       <c r="H1703" t="n">
         <v>64863</v>
@@ -49843,7 +49843,7 @@
         <v>132.399993896484</v>
       </c>
       <c r="G1706" t="n">
-        <v>125.508819580078</v>
+        <v>125.508804321289</v>
       </c>
       <c r="H1706" t="n">
         <v>102539</v>
@@ -49872,7 +49872,7 @@
         <v>129.550003051758</v>
       </c>
       <c r="G1707" t="n">
-        <v>122.807151794434</v>
+        <v>122.807159423828</v>
       </c>
       <c r="H1707" t="n">
         <v>102263</v>
@@ -49901,7 +49901,7 @@
         <v>127.849998474121</v>
       </c>
       <c r="G1708" t="n">
-        <v>121.195640563965</v>
+        <v>121.19563293457</v>
       </c>
       <c r="H1708" t="n">
         <v>124471</v>
@@ -50162,7 +50162,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>105.79141998291</v>
+        <v>105.791412353516</v>
       </c>
       <c r="H1717" t="n">
         <v>70187</v>
@@ -50191,7 +50191,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1718" t="n">
-        <v>108.824867248535</v>
+        <v>108.82487487793</v>
       </c>
       <c r="H1718" t="n">
         <v>102634</v>
@@ -50220,7 +50220,7 @@
         <v>114</v>
       </c>
       <c r="G1719" t="n">
-        <v>108.066505432129</v>
+        <v>108.066497802734</v>
       </c>
       <c r="H1719" t="n">
         <v>86168</v>
@@ -50365,7 +50365,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1724" t="n">
-        <v>108.824867248535</v>
+        <v>108.82487487793</v>
       </c>
       <c r="H1724" t="n">
         <v>54205</v>
@@ -50423,7 +50423,7 @@
         <v>112.349998474121</v>
       </c>
       <c r="G1726" t="n">
-        <v>106.502380371094</v>
+        <v>106.502372741699</v>
       </c>
       <c r="H1726" t="n">
         <v>55996</v>
@@ -50481,7 +50481,7 @@
         <v>119.050003051758</v>
       </c>
       <c r="G1728" t="n">
-        <v>112.853668212891</v>
+        <v>112.853660583496</v>
       </c>
       <c r="H1728" t="n">
         <v>168448</v>
@@ -50539,7 +50539,7 @@
         <v>128.149993896484</v>
       </c>
       <c r="G1730" t="n">
-        <v>121.480010986328</v>
+        <v>121.480018615723</v>
       </c>
       <c r="H1730" t="n">
         <v>149505</v>
@@ -50626,7 +50626,7 @@
         <v>130.100006103516</v>
       </c>
       <c r="G1733" t="n">
-        <v>123.32852935791</v>
+        <v>123.328536987305</v>
       </c>
       <c r="H1733" t="n">
         <v>127721</v>
@@ -50800,7 +50800,7 @@
         <v>132.300003051758</v>
       </c>
       <c r="G1739" t="n">
-        <v>125.414009094238</v>
+        <v>125.414024353027</v>
       </c>
       <c r="H1739" t="n">
         <v>132414</v>
@@ -50829,7 +50829,7 @@
         <v>131.149993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>124.323875427246</v>
+        <v>124.323860168457</v>
       </c>
       <c r="H1740" t="n">
         <v>67021</v>
@@ -50858,7 +50858,7 @@
         <v>129.350006103516</v>
       </c>
       <c r="G1741" t="n">
-        <v>122.617576599121</v>
+        <v>122.617568969727</v>
       </c>
       <c r="H1741" t="n">
         <v>74446</v>
@@ -50887,7 +50887,7 @@
         <v>126.650001525879</v>
       </c>
       <c r="G1742" t="n">
-        <v>120.058090209961</v>
+        <v>120.058097839355</v>
       </c>
       <c r="H1742" t="n">
         <v>61920</v>
@@ -51003,7 +51003,7 @@
         <v>133.149993896484</v>
       </c>
       <c r="G1746" t="n">
-        <v>126.219779968262</v>
+        <v>126.219764709473</v>
       </c>
       <c r="H1746" t="n">
         <v>85892</v>
@@ -51090,7 +51090,7 @@
         <v>135.399993896484</v>
       </c>
       <c r="G1749" t="n">
-        <v>128.352676391602</v>
+        <v>128.352661132812</v>
       </c>
       <c r="H1749" t="n">
         <v>96025</v>
@@ -51264,7 +51264,7 @@
         <v>132.449996948242</v>
       </c>
       <c r="G1755" t="n">
-        <v>125.556213378906</v>
+        <v>125.556198120117</v>
       </c>
       <c r="H1755" t="n">
         <v>61112</v>
@@ -51293,7 +51293,7 @@
         <v>132.449996948242</v>
       </c>
       <c r="G1756" t="n">
-        <v>125.556213378906</v>
+        <v>125.556198120117</v>
       </c>
       <c r="H1756" t="n">
         <v>58710</v>
@@ -51322,7 +51322,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G1757" t="n">
-        <v>126.267181396484</v>
+        <v>126.267166137695</v>
       </c>
       <c r="H1757" t="n">
         <v>69501</v>
@@ -51380,7 +51380,7 @@
         <v>131.550003051758</v>
       </c>
       <c r="G1759" t="n">
-        <v>124.703048706055</v>
+        <v>124.703063964844</v>
       </c>
       <c r="H1759" t="n">
         <v>136045</v>
@@ -51438,7 +51438,7 @@
         <v>126.949996948242</v>
       </c>
       <c r="G1761" t="n">
-        <v>120.342483520508</v>
+        <v>120.342475891113</v>
       </c>
       <c r="H1761" t="n">
         <v>630814</v>
@@ -51496,7 +51496,7 @@
         <v>133.899993896484</v>
       </c>
       <c r="G1763" t="n">
-        <v>126.93074798584</v>
+        <v>126.930732727051</v>
       </c>
       <c r="H1763" t="n">
         <v>108132</v>
@@ -51554,7 +51554,7 @@
         <v>128.149993896484</v>
       </c>
       <c r="G1765" t="n">
-        <v>121.480010986328</v>
+        <v>121.480018615723</v>
       </c>
       <c r="H1765" t="n">
         <v>123530</v>
@@ -51583,7 +51583,7 @@
         <v>129.350006103516</v>
       </c>
       <c r="G1766" t="n">
-        <v>122.617576599121</v>
+        <v>122.617568969727</v>
       </c>
       <c r="H1766" t="n">
         <v>78122</v>
@@ -51612,7 +51612,7 @@
         <v>129.699996948242</v>
       </c>
       <c r="G1767" t="n">
-        <v>122.949348449707</v>
+        <v>122.949340820312</v>
       </c>
       <c r="H1767" t="n">
         <v>131451</v>
@@ -51670,7 +51670,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G1769" t="n">
-        <v>127.120330810547</v>
+        <v>127.120346069336</v>
       </c>
       <c r="H1769" t="n">
         <v>89506</v>
@@ -51699,7 +51699,7 @@
         <v>136.350006103516</v>
       </c>
       <c r="G1770" t="n">
-        <v>129.253219604492</v>
+        <v>129.253234863281</v>
       </c>
       <c r="H1770" t="n">
         <v>102434</v>
@@ -51728,7 +51728,7 @@
         <v>139.199996948242</v>
       </c>
       <c r="G1771" t="n">
-        <v>131.954895019531</v>
+        <v>131.954879760742</v>
       </c>
       <c r="H1771" t="n">
         <v>131704</v>
@@ -51757,7 +51757,7 @@
         <v>134.449996948242</v>
       </c>
       <c r="G1772" t="n">
-        <v>127.452117919922</v>
+        <v>127.452102661133</v>
       </c>
       <c r="H1772" t="n">
         <v>196752</v>
@@ -51815,7 +51815,7 @@
         <v>128.149993896484</v>
       </c>
       <c r="G1774" t="n">
-        <v>121.480010986328</v>
+        <v>121.480018615723</v>
       </c>
       <c r="H1774" t="n">
         <v>49669</v>
@@ -51873,7 +51873,7 @@
         <v>127.800003051758</v>
       </c>
       <c r="G1776" t="n">
-        <v>121.148231506348</v>
+        <v>121.148239135742</v>
       </c>
       <c r="H1776" t="n">
         <v>113826</v>
@@ -51960,7 +51960,7 @@
         <v>127.400001525879</v>
       </c>
       <c r="G1779" t="n">
-        <v>120.769050598145</v>
+        <v>120.769058227539</v>
       </c>
       <c r="H1779" t="n">
         <v>54658</v>
@@ -52047,7 +52047,7 @@
         <v>130.399993896484</v>
       </c>
       <c r="G1782" t="n">
-        <v>123.612915039062</v>
+        <v>123.612899780273</v>
       </c>
       <c r="H1782" t="n">
         <v>62523</v>
@@ -52076,7 +52076,7 @@
         <v>129.550003051758</v>
       </c>
       <c r="G1783" t="n">
-        <v>122.807151794434</v>
+        <v>122.807159423828</v>
       </c>
       <c r="H1783" t="n">
         <v>64504</v>
@@ -52134,7 +52134,7 @@
         <v>129.850006103516</v>
       </c>
       <c r="G1785" t="n">
-        <v>123.09154510498</v>
+        <v>123.091552734375</v>
       </c>
       <c r="H1785" t="n">
         <v>72350</v>
@@ -52163,7 +52163,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G1786" t="n">
-        <v>120.579467773438</v>
+        <v>120.579460144043</v>
       </c>
       <c r="H1786" t="n">
         <v>123183</v>
@@ -52221,7 +52221,7 @@
         <v>127.599998474121</v>
       </c>
       <c r="G1788" t="n">
-        <v>120.958648681641</v>
+        <v>120.958641052246</v>
       </c>
       <c r="H1788" t="n">
         <v>115090</v>
@@ -52250,7 +52250,7 @@
         <v>126.199996948242</v>
       </c>
       <c r="G1789" t="n">
-        <v>119.63151550293</v>
+        <v>119.631507873535</v>
       </c>
       <c r="H1789" t="n">
         <v>94760</v>
@@ -52337,7 +52337,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G1792" t="n">
-        <v>120.579467773438</v>
+        <v>120.579460144043</v>
       </c>
       <c r="H1792" t="n">
         <v>202885</v>
@@ -52395,7 +52395,7 @@
         <v>130.399993896484</v>
       </c>
       <c r="G1794" t="n">
-        <v>123.612915039062</v>
+        <v>123.612899780273</v>
       </c>
       <c r="H1794" t="n">
         <v>133529</v>
@@ -52424,7 +52424,7 @@
         <v>129.850006103516</v>
       </c>
       <c r="G1795" t="n">
-        <v>123.09154510498</v>
+        <v>123.091552734375</v>
       </c>
       <c r="H1795" t="n">
         <v>98709</v>
@@ -52482,7 +52482,7 @@
         <v>125.199996948242</v>
       </c>
       <c r="G1797" t="n">
-        <v>118.683563232422</v>
+        <v>118.683555603027</v>
       </c>
       <c r="H1797" t="n">
         <v>141913</v>
@@ -52540,7 +52540,7 @@
         <v>124.75</v>
       </c>
       <c r="G1799" t="n">
-        <v>118.256973266602</v>
+        <v>118.256980895996</v>
       </c>
       <c r="H1799" t="n">
         <v>71284</v>
@@ -52627,7 +52627,7 @@
         <v>124.449996948242</v>
       </c>
       <c r="G1802" t="n">
-        <v>117.972595214844</v>
+        <v>117.972587585449</v>
       </c>
       <c r="H1802" t="n">
         <v>55617</v>
@@ -52859,7 +52859,7 @@
         <v>121.050003051758</v>
       </c>
       <c r="G1810" t="n">
-        <v>114.749557495117</v>
+        <v>114.749565124512</v>
       </c>
       <c r="H1810" t="n">
         <v>83984</v>
@@ -52946,7 +52946,7 @@
         <v>117.25</v>
       </c>
       <c r="G1813" t="n">
-        <v>111.147346496582</v>
+        <v>111.147354125977</v>
       </c>
       <c r="H1813" t="n">
         <v>128871</v>
@@ -53004,7 +53004,7 @@
         <v>115.75</v>
       </c>
       <c r="G1815" t="n">
-        <v>109.725425720215</v>
+        <v>109.72541809082</v>
       </c>
       <c r="H1815" t="n">
         <v>109875</v>
@@ -53062,7 +53062,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1817" t="n">
-        <v>110.246795654297</v>
+        <v>110.246803283691</v>
       </c>
       <c r="H1817" t="n">
         <v>133277</v>
@@ -53236,7 +53236,7 @@
         <v>115</v>
       </c>
       <c r="G1823" t="n">
-        <v>109.014457702637</v>
+        <v>109.014450073242</v>
       </c>
       <c r="H1823" t="n">
         <v>77314</v>
@@ -53323,7 +53323,7 @@
         <v>109.949996948242</v>
       </c>
       <c r="G1826" t="n">
-        <v>104.227294921875</v>
+        <v>104.22728729248</v>
       </c>
       <c r="H1826" t="n">
         <v>141015</v>
@@ -53381,7 +53381,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1828" t="n">
-        <v>106.834167480469</v>
+        <v>106.834159851074</v>
       </c>
       <c r="H1828" t="n">
         <v>69502</v>
@@ -53410,7 +53410,7 @@
         <v>111.949996948242</v>
       </c>
       <c r="G1829" t="n">
-        <v>106.123199462891</v>
+        <v>106.123191833496</v>
       </c>
       <c r="H1829" t="n">
         <v>122024</v>
@@ -53642,7 +53642,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G1837" t="n">
-        <v>100.198501586914</v>
+        <v>100.19849395752</v>
       </c>
       <c r="H1837" t="n">
         <v>202368</v>
@@ -53700,7 +53700,7 @@
         <v>102.449996948242</v>
       </c>
       <c r="G1839" t="n">
-        <v>97.1176605224609</v>
+        <v>97.1176528930664</v>
       </c>
       <c r="H1839" t="n">
         <v>151769</v>
@@ -53729,7 +53729,7 @@
         <v>101.050003051758</v>
       </c>
       <c r="G1840" t="n">
-        <v>95.79052734375</v>
+        <v>95.7905349731445</v>
       </c>
       <c r="H1840" t="n">
         <v>97952</v>
@@ -53787,7 +53787,7 @@
         <v>102.050003051758</v>
       </c>
       <c r="G1842" t="n">
-        <v>96.7384796142578</v>
+        <v>96.7384872436523</v>
       </c>
       <c r="H1842" t="n">
         <v>327140</v>
@@ -53903,7 +53903,7 @@
         <v>98.4400024414062</v>
       </c>
       <c r="G1846" t="n">
-        <v>93.3163757324219</v>
+        <v>93.3163681030273</v>
       </c>
       <c r="H1846" t="n">
         <v>102963</v>
@@ -53961,7 +53961,7 @@
         <v>97</v>
       </c>
       <c r="G1848" t="n">
-        <v>91.9513168334961</v>
+        <v>91.9513244628906</v>
       </c>
       <c r="H1848" t="n">
         <v>163589</v>
@@ -54077,7 +54077,7 @@
         <v>99.620002746582</v>
       </c>
       <c r="G1852" t="n">
-        <v>94.4349594116211</v>
+        <v>94.4349517822266</v>
       </c>
       <c r="H1852" t="n">
         <v>218716</v>
@@ -54106,7 +54106,7 @@
         <v>99.1800003051758</v>
       </c>
       <c r="G1853" t="n">
-        <v>94.0178527832031</v>
+        <v>94.0178604125977</v>
       </c>
       <c r="H1853" t="n">
         <v>223489</v>
@@ -54135,7 +54135,7 @@
         <v>99.0999984741211</v>
       </c>
       <c r="G1854" t="n">
-        <v>93.942024230957</v>
+        <v>93.9420166015625</v>
       </c>
       <c r="H1854" t="n">
         <v>126162</v>
@@ -54164,7 +54164,7 @@
         <v>97.3199996948242</v>
       </c>
       <c r="G1855" t="n">
-        <v>92.2546691894531</v>
+        <v>92.2546615600586</v>
       </c>
       <c r="H1855" t="n">
         <v>133943</v>
@@ -54193,7 +54193,7 @@
         <v>96.8399963378906</v>
       </c>
       <c r="G1856" t="n">
-        <v>91.7996520996094</v>
+        <v>91.7996444702148</v>
       </c>
       <c r="H1856" t="n">
         <v>130994</v>
@@ -54222,7 +54222,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G1857" t="n">
-        <v>92.235710144043</v>
+        <v>92.2357177734375</v>
       </c>
       <c r="H1857" t="n">
         <v>196632</v>
@@ -54280,7 +54280,7 @@
         <v>97.1600036621094</v>
       </c>
       <c r="G1859" t="n">
-        <v>92.1029968261719</v>
+        <v>92.1030044555664</v>
       </c>
       <c r="H1859" t="n">
         <v>86372</v>
@@ -54338,7 +54338,7 @@
         <v>99.3600006103516</v>
       </c>
       <c r="G1861" t="n">
-        <v>94.1884918212891</v>
+        <v>94.1884841918945</v>
       </c>
       <c r="H1861" t="n">
         <v>106627</v>
@@ -54367,7 +54367,7 @@
         <v>97.5199966430664</v>
       </c>
       <c r="G1862" t="n">
-        <v>92.4442443847656</v>
+        <v>92.4442520141602</v>
       </c>
       <c r="H1862" t="n">
         <v>168893</v>
@@ -54425,7 +54425,7 @@
         <v>97.3199996948242</v>
       </c>
       <c r="G1864" t="n">
-        <v>92.2546691894531</v>
+        <v>92.2546615600586</v>
       </c>
       <c r="H1864" t="n">
         <v>96353</v>
@@ -54483,7 +54483,7 @@
         <v>97.7200012207031</v>
       </c>
       <c r="G1866" t="n">
-        <v>92.6338500976562</v>
+        <v>92.6338424682617</v>
       </c>
       <c r="H1866" t="n">
         <v>103866</v>
@@ -54599,7 +54599,7 @@
         <v>102.050003051758</v>
       </c>
       <c r="G1870" t="n">
-        <v>96.7384796142578</v>
+        <v>96.7384872436523</v>
       </c>
       <c r="H1870" t="n">
         <v>168493</v>
@@ -54628,7 +54628,7 @@
         <v>102.199996948242</v>
       </c>
       <c r="G1871" t="n">
-        <v>96.8806686401367</v>
+        <v>96.8806610107422</v>
       </c>
       <c r="H1871" t="n">
         <v>478838</v>
@@ -54715,7 +54715,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G1874" t="n">
-        <v>100.103706359863</v>
+        <v>100.103698730469</v>
       </c>
       <c r="H1874" t="n">
         <v>229715</v>
@@ -54744,7 +54744,7 @@
         <v>105.050003051758</v>
       </c>
       <c r="G1875" t="n">
-        <v>99.5823287963867</v>
+        <v>99.5823364257812</v>
       </c>
       <c r="H1875" t="n">
         <v>108965</v>
@@ -80067,6 +80067,35 @@
         <v>151184</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>79.0599975585938</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>79.0400009155273</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>79.7200012207031</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>79.7200012207031</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>165324</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>48.1800003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>41.7114105224609</v>
+        <v>41.7114067077637</v>
       </c>
       <c r="H2" t="n">
         <v>50491</v>
@@ -456,7 +456,7 @@
         <v>49.0900001525879</v>
       </c>
       <c r="G3" t="n">
-        <v>42.4992332458496</v>
+        <v>42.4992294311523</v>
       </c>
       <c r="H3" t="n">
         <v>89363</v>
@@ -485,7 +485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G4" t="n">
-        <v>42.248161315918</v>
+        <v>42.2481651306152</v>
       </c>
       <c r="H4" t="n">
         <v>42997</v>
@@ -543,7 +543,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>42.0317344665527</v>
+        <v>42.0317306518555</v>
       </c>
       <c r="H6" t="n">
         <v>111815</v>
@@ -572,7 +572,7 @@
         <v>47.7900009155273</v>
       </c>
       <c r="G7" t="n">
-        <v>41.3737754821777</v>
+        <v>41.3737716674805</v>
       </c>
       <c r="H7" t="n">
         <v>75682</v>
@@ -630,7 +630,7 @@
         <v>47.310001373291</v>
       </c>
       <c r="G9" t="n">
-        <v>40.9582099914551</v>
+        <v>40.9582176208496</v>
       </c>
       <c r="H9" t="n">
         <v>75050</v>
@@ -659,7 +659,7 @@
         <v>46.810001373291</v>
       </c>
       <c r="G10" t="n">
-        <v>40.5253410339355</v>
+        <v>40.5253448486328</v>
       </c>
       <c r="H10" t="n">
         <v>44094</v>
@@ -775,7 +775,7 @@
         <v>42.9000015258789</v>
       </c>
       <c r="G14" t="n">
-        <v>37.1403007507324</v>
+        <v>37.1402931213379</v>
       </c>
       <c r="H14" t="n">
         <v>131326</v>
@@ -804,7 +804,7 @@
         <v>42.6800003051758</v>
       </c>
       <c r="G15" t="n">
-        <v>36.9498291015625</v>
+        <v>36.9498329162598</v>
       </c>
       <c r="H15" t="n">
         <v>170667</v>
@@ -862,7 +862,7 @@
         <v>45.6399993896484</v>
       </c>
       <c r="G17" t="n">
-        <v>39.5124320983887</v>
+        <v>39.5124282836914</v>
       </c>
       <c r="H17" t="n">
         <v>218430</v>
@@ -891,7 +891,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G18" t="n">
-        <v>40.4993667602539</v>
+        <v>40.4993743896484</v>
       </c>
       <c r="H18" t="n">
         <v>171711</v>
@@ -920,7 +920,7 @@
         <v>47.6800003051758</v>
       </c>
       <c r="G19" t="n">
-        <v>41.2785415649414</v>
+        <v>41.2785377502441</v>
       </c>
       <c r="H19" t="n">
         <v>97163</v>
@@ -949,7 +949,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G20" t="n">
-        <v>40.6032562255859</v>
+        <v>40.6032600402832</v>
       </c>
       <c r="H20" t="n">
         <v>145072</v>
@@ -978,7 +978,7 @@
         <v>48.5</v>
       </c>
       <c r="G21" t="n">
-        <v>41.9884490966797</v>
+        <v>41.9884452819824</v>
       </c>
       <c r="H21" t="n">
         <v>102390</v>
@@ -1036,7 +1036,7 @@
         <v>48.75</v>
       </c>
       <c r="G23" t="n">
-        <v>42.2048797607422</v>
+        <v>42.2048759460449</v>
       </c>
       <c r="H23" t="n">
         <v>112008</v>
@@ -1065,7 +1065,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>41.1053810119629</v>
+        <v>41.1053886413574</v>
       </c>
       <c r="H24" t="n">
         <v>118381</v>
@@ -1094,7 +1094,7 @@
         <v>46.75</v>
       </c>
       <c r="G25" t="n">
-        <v>40.4734001159668</v>
+        <v>40.4733963012695</v>
       </c>
       <c r="H25" t="n">
         <v>58114</v>
@@ -1123,7 +1123,7 @@
         <v>44.689998626709</v>
       </c>
       <c r="G26" t="n">
-        <v>38.6899719238281</v>
+        <v>38.6899681091309</v>
       </c>
       <c r="H26" t="n">
         <v>47084</v>
@@ -1152,7 +1152,7 @@
         <v>42.810001373291</v>
       </c>
       <c r="G27" t="n">
-        <v>37.0623741149902</v>
+        <v>37.0623817443848</v>
       </c>
       <c r="H27" t="n">
         <v>79262</v>
@@ -1210,7 +1210,7 @@
         <v>43.75</v>
       </c>
       <c r="G29" t="n">
-        <v>37.8761749267578</v>
+        <v>37.8761787414551</v>
       </c>
       <c r="H29" t="n">
         <v>111628</v>
@@ -1239,7 +1239,7 @@
         <v>43.7700004577637</v>
       </c>
       <c r="G30" t="n">
-        <v>37.8934936523438</v>
+        <v>37.893482208252</v>
       </c>
       <c r="H30" t="n">
         <v>96253</v>
@@ -1268,7 +1268,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G31" t="n">
-        <v>37.6943702697754</v>
+        <v>37.6943664550781</v>
       </c>
       <c r="H31" t="n">
         <v>98162</v>
@@ -1297,7 +1297,7 @@
         <v>45.4900016784668</v>
       </c>
       <c r="G32" t="n">
-        <v>39.3825645446777</v>
+        <v>39.3825569152832</v>
       </c>
       <c r="H32" t="n">
         <v>72531</v>
@@ -1326,7 +1326,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G33" t="n">
-        <v>39.6509437561035</v>
+        <v>39.6509475708008</v>
       </c>
       <c r="H33" t="n">
         <v>45200</v>
@@ -1355,7 +1355,7 @@
         <v>45.9099998474121</v>
       </c>
       <c r="G34" t="n">
-        <v>39.7461738586426</v>
+        <v>39.7461700439453</v>
       </c>
       <c r="H34" t="n">
         <v>76568</v>
@@ -1384,7 +1384,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G35" t="n">
-        <v>40.6378936767578</v>
+        <v>40.6378860473633</v>
       </c>
       <c r="H35" t="n">
         <v>46426</v>
@@ -1413,7 +1413,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G36" t="n">
-        <v>40.4993667602539</v>
+        <v>40.4993743896484</v>
       </c>
       <c r="H36" t="n">
         <v>62588</v>
@@ -1442,7 +1442,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="G37" t="n">
-        <v>41.763355255127</v>
+        <v>41.7633476257324</v>
       </c>
       <c r="H37" t="n">
         <v>101109</v>
@@ -1500,7 +1500,7 @@
         <v>48.2900009155273</v>
       </c>
       <c r="G39" t="n">
-        <v>41.806640625</v>
+        <v>41.8066368103027</v>
       </c>
       <c r="H39" t="n">
         <v>92020</v>
@@ -1529,7 +1529,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G40" t="n">
-        <v>42.412654876709</v>
+        <v>42.4126625061035</v>
       </c>
       <c r="H40" t="n">
         <v>70387</v>
@@ -1587,7 +1587,7 @@
         <v>48.6399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>42.1096496582031</v>
+        <v>42.1096458435059</v>
       </c>
       <c r="H42" t="n">
         <v>26989</v>
@@ -1645,7 +1645,7 @@
         <v>48.25</v>
       </c>
       <c r="G44" t="n">
-        <v>41.7720069885254</v>
+        <v>41.7720108032227</v>
       </c>
       <c r="H44" t="n">
         <v>123106</v>
@@ -1703,7 +1703,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>41.858585357666</v>
+        <v>41.8585777282715</v>
       </c>
       <c r="H46" t="n">
         <v>41036</v>
@@ -1732,7 +1732,7 @@
         <v>48.4199981689453</v>
       </c>
       <c r="G47" t="n">
-        <v>41.9191856384277</v>
+        <v>41.9191818237305</v>
       </c>
       <c r="H47" t="n">
         <v>52500</v>
@@ -1790,7 +1790,7 @@
         <v>46.2099990844727</v>
       </c>
       <c r="G49" t="n">
-        <v>40.0058937072754</v>
+        <v>40.0059013366699</v>
       </c>
       <c r="H49" t="n">
         <v>135834</v>
@@ -1819,7 +1819,7 @@
         <v>45.75</v>
       </c>
       <c r="G50" t="n">
-        <v>39.6076622009277</v>
+        <v>39.6076583862305</v>
       </c>
       <c r="H50" t="n">
         <v>108080</v>
@@ -1848,7 +1848,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>39.2700119018555</v>
+        <v>39.27001953125</v>
       </c>
       <c r="H51" t="n">
         <v>118250</v>
@@ -1877,7 +1877,7 @@
         <v>46.6699981689453</v>
       </c>
       <c r="G52" t="n">
-        <v>40.4041366577148</v>
+        <v>40.4041328430176</v>
       </c>
       <c r="H52" t="n">
         <v>59686</v>
@@ -1906,7 +1906,7 @@
         <v>46</v>
       </c>
       <c r="G53" t="n">
-        <v>39.824089050293</v>
+        <v>39.8240852355957</v>
       </c>
       <c r="H53" t="n">
         <v>39106</v>
@@ -1964,7 +1964,7 @@
         <v>44.9199981689453</v>
       </c>
       <c r="G55" t="n">
-        <v>38.8890914916992</v>
+        <v>38.8890991210938</v>
       </c>
       <c r="H55" t="n">
         <v>53754</v>
@@ -1993,7 +1993,7 @@
         <v>45.4799995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>39.3739051818848</v>
+        <v>39.3739013671875</v>
       </c>
       <c r="H56" t="n">
         <v>99139</v>
@@ -2022,7 +2022,7 @@
         <v>45.6800003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>39.5470504760742</v>
+        <v>39.5470581054688</v>
       </c>
       <c r="H57" t="n">
         <v>62232</v>
@@ -2051,7 +2051,7 @@
         <v>45.1699981689453</v>
       </c>
       <c r="G58" t="n">
-        <v>39.1055221557617</v>
+        <v>39.105525970459</v>
       </c>
       <c r="H58" t="n">
         <v>71459</v>
@@ -2080,7 +2080,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>39.6509437561035</v>
+        <v>39.6509475708008</v>
       </c>
       <c r="H59" t="n">
         <v>54272</v>
@@ -2109,7 +2109,7 @@
         <v>45.5</v>
       </c>
       <c r="G60" t="n">
-        <v>39.3912162780762</v>
+        <v>39.3912200927734</v>
       </c>
       <c r="H60" t="n">
         <v>58510</v>
@@ -2138,7 +2138,7 @@
         <v>45.8800010681152</v>
       </c>
       <c r="G61" t="n">
-        <v>39.7202110290527</v>
+        <v>39.7201957702637</v>
       </c>
       <c r="H61" t="n">
         <v>48377</v>
@@ -2167,7 +2167,7 @@
         <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>43.287052154541</v>
+        <v>43.2870559692383</v>
       </c>
       <c r="H62" t="n">
         <v>415378</v>
@@ -2196,7 +2196,7 @@
         <v>50.75</v>
       </c>
       <c r="G63" t="n">
-        <v>43.9363594055176</v>
+        <v>43.9363670349121</v>
       </c>
       <c r="H63" t="n">
         <v>128937</v>
@@ -2225,7 +2225,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>44.4558029174805</v>
+        <v>44.4558067321777</v>
       </c>
       <c r="H64" t="n">
         <v>210539</v>
@@ -2283,7 +2283,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>44.5423889160156</v>
+        <v>44.5423774719238</v>
       </c>
       <c r="H66" t="n">
         <v>64536</v>
@@ -2312,7 +2312,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>44.8453941345215</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H67" t="n">
         <v>68564</v>
@@ -2341,7 +2341,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>45.9708518981934</v>
+        <v>45.9708480834961</v>
       </c>
       <c r="H68" t="n">
         <v>102885</v>
@@ -2370,7 +2370,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618324279785</v>
       </c>
       <c r="H69" t="n">
         <v>49881</v>
@@ -2428,7 +2428,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>44.8453941345215</v>
+        <v>44.8453903198242</v>
       </c>
       <c r="H71" t="n">
         <v>36065</v>
@@ -2486,7 +2486,7 @@
         <v>51.25</v>
       </c>
       <c r="G73" t="n">
-        <v>44.3692321777344</v>
+        <v>44.3692359924316</v>
       </c>
       <c r="H73" t="n">
         <v>51163</v>
@@ -2515,7 +2515,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G74" t="n">
-        <v>44.0662231445312</v>
+        <v>44.066234588623</v>
       </c>
       <c r="H74" t="n">
         <v>33163</v>
@@ -2544,7 +2544,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>44.1095161437988</v>
+        <v>44.1095123291016</v>
       </c>
       <c r="H75" t="n">
         <v>39623</v>
@@ -2573,7 +2573,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>44.4558029174805</v>
+        <v>44.4558067321777</v>
       </c>
       <c r="H76" t="n">
         <v>38314</v>
@@ -2660,7 +2660,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>43.9796485900879</v>
+        <v>43.9796447753906</v>
       </c>
       <c r="H79" t="n">
         <v>48596</v>
@@ -2747,7 +2747,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G82" t="n">
-        <v>43.9796485900879</v>
+        <v>43.9796447753906</v>
       </c>
       <c r="H82" t="n">
         <v>25530</v>
@@ -2776,7 +2776,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>44.4125175476074</v>
+        <v>44.412525177002</v>
       </c>
       <c r="H83" t="n">
         <v>50375</v>
@@ -2834,7 +2834,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G85" t="n">
-        <v>44.0229301452637</v>
+        <v>44.0229339599609</v>
       </c>
       <c r="H85" t="n">
         <v>34059</v>
@@ -2863,7 +2863,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>44.1095161437988</v>
+        <v>44.1095123291016</v>
       </c>
       <c r="H86" t="n">
         <v>35475</v>
@@ -2950,7 +2950,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G89" t="n">
-        <v>44.9752540588379</v>
+        <v>44.9752464294434</v>
       </c>
       <c r="H89" t="n">
         <v>44495</v>
@@ -2979,7 +2979,7 @@
         <v>52.5</v>
       </c>
       <c r="G90" t="n">
-        <v>45.4514122009277</v>
+        <v>45.4514083862305</v>
       </c>
       <c r="H90" t="n">
         <v>86395</v>
@@ -3008,7 +3008,7 @@
         <v>52.5</v>
       </c>
       <c r="G91" t="n">
-        <v>45.4514122009277</v>
+        <v>45.4514083862305</v>
       </c>
       <c r="H91" t="n">
         <v>38800</v>
@@ -3037,7 +3037,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G92" t="n">
-        <v>45.3215446472168</v>
+        <v>45.3215522766113</v>
       </c>
       <c r="H92" t="n">
         <v>34602</v>
@@ -3124,7 +3124,7 @@
         <v>52.25</v>
       </c>
       <c r="G95" t="n">
-        <v>45.2349700927734</v>
+        <v>45.2349739074707</v>
       </c>
       <c r="H95" t="n">
         <v>40512</v>
@@ -3153,7 +3153,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>45.061824798584</v>
+        <v>45.0618324279785</v>
       </c>
       <c r="H96" t="n">
         <v>56148</v>
@@ -3211,7 +3211,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>45.1484031677246</v>
+        <v>45.1483993530273</v>
       </c>
       <c r="H98" t="n">
         <v>38023</v>
@@ -3298,7 +3298,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>46.6353607177734</v>
+        <v>46.6353721618652</v>
       </c>
       <c r="H101" t="n">
         <v>108486</v>
@@ -3327,7 +3327,7 @@
         <v>52.75</v>
       </c>
       <c r="G102" t="n">
-        <v>46.2408981323242</v>
+        <v>46.240894317627</v>
       </c>
       <c r="H102" t="n">
         <v>149531</v>
@@ -3356,7 +3356,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G103" t="n">
-        <v>47.0298461914062</v>
+        <v>47.029842376709</v>
       </c>
       <c r="H103" t="n">
         <v>88124</v>
@@ -3414,7 +3414,7 @@
         <v>55</v>
       </c>
       <c r="G105" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H105" t="n">
         <v>139286</v>
@@ -3472,7 +3472,7 @@
         <v>55.5</v>
       </c>
       <c r="G107" t="n">
-        <v>48.6515655517578</v>
+        <v>48.6515579223633</v>
       </c>
       <c r="H107" t="n">
         <v>133330</v>
@@ -3501,7 +3501,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G108" t="n">
-        <v>48.7392158508301</v>
+        <v>48.7392196655273</v>
       </c>
       <c r="H108" t="n">
         <v>80155</v>
@@ -3530,7 +3530,7 @@
         <v>56.25</v>
       </c>
       <c r="G109" t="n">
-        <v>49.3090133666992</v>
+        <v>49.3090171813965</v>
       </c>
       <c r="H109" t="n">
         <v>116556</v>
@@ -3559,7 +3559,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G110" t="n">
-        <v>48.1694221496582</v>
+        <v>48.1694259643555</v>
       </c>
       <c r="H110" t="n">
         <v>65714</v>
@@ -3588,7 +3588,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>49.0460357666016</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H111" t="n">
         <v>91204</v>
@@ -3617,7 +3617,7 @@
         <v>55.0499992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>48.2570877075195</v>
+        <v>48.2570838928223</v>
       </c>
       <c r="H112" t="n">
         <v>83540</v>
@@ -3646,7 +3646,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G113" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H113" t="n">
         <v>93852</v>
@@ -3675,7 +3675,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G114" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H114" t="n">
         <v>71011</v>
@@ -3704,7 +3704,7 @@
         <v>53.25</v>
       </c>
       <c r="G115" t="n">
-        <v>46.6792030334473</v>
+        <v>46.67919921875</v>
       </c>
       <c r="H115" t="n">
         <v>44939</v>
@@ -3791,7 +3791,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H118" t="n">
         <v>92065</v>
@@ -3849,7 +3849,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>47.0298461914062</v>
+        <v>47.029842376709</v>
       </c>
       <c r="H120" t="n">
         <v>60433</v>
@@ -3878,7 +3878,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G121" t="n">
-        <v>47.2051696777344</v>
+        <v>47.2051620483398</v>
       </c>
       <c r="H121" t="n">
         <v>31799</v>
@@ -3907,7 +3907,7 @@
         <v>55.0499992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>48.2570877075195</v>
+        <v>48.2570838928223</v>
       </c>
       <c r="H122" t="n">
         <v>64222</v>
@@ -3965,7 +3965,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>45.3204612731934</v>
+        <v>45.3204574584961</v>
       </c>
       <c r="H124" t="n">
         <v>161426</v>
@@ -4023,7 +4023,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>45.1889686584473</v>
+        <v>45.1889724731445</v>
       </c>
       <c r="H126" t="n">
         <v>159639</v>
@@ -4081,7 +4081,7 @@
         <v>55</v>
       </c>
       <c r="G128" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H128" t="n">
         <v>131299</v>
@@ -4110,7 +4110,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>48.8268814086914</v>
+        <v>48.8268852233887</v>
       </c>
       <c r="H129" t="n">
         <v>140774</v>
@@ -4255,7 +4255,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>48.0379371643066</v>
+        <v>48.0379333496094</v>
       </c>
       <c r="H134" t="n">
         <v>26738</v>
@@ -4284,7 +4284,7 @@
         <v>55.6500015258789</v>
       </c>
       <c r="G135" t="n">
-        <v>48.7830581665039</v>
+        <v>48.7830543518066</v>
       </c>
       <c r="H135" t="n">
         <v>31502</v>
@@ -4313,7 +4313,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G136" t="n">
-        <v>48.9145431518555</v>
+        <v>48.9145393371582</v>
       </c>
       <c r="H136" t="n">
         <v>53508</v>
@@ -4342,7 +4342,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>49.0460357666016</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H137" t="n">
         <v>46872</v>
@@ -4371,7 +4371,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G138" t="n">
-        <v>48.8268814086914</v>
+        <v>48.8268852233887</v>
       </c>
       <c r="H138" t="n">
         <v>43251</v>
@@ -4429,7 +4429,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G140" t="n">
-        <v>49.6596641540527</v>
+        <v>49.6596565246582</v>
       </c>
       <c r="H140" t="n">
         <v>41122</v>
@@ -4458,7 +4458,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G141" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H141" t="n">
         <v>46628</v>
@@ -4487,7 +4487,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G142" t="n">
-        <v>50.3171043395996</v>
+        <v>50.3171081542969</v>
       </c>
       <c r="H142" t="n">
         <v>82201</v>
@@ -4516,7 +4516,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0102958679199</v>
       </c>
       <c r="H143" t="n">
         <v>17674</v>
@@ -4545,7 +4545,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G144" t="n">
-        <v>49.9226379394531</v>
+        <v>49.9226341247559</v>
       </c>
       <c r="H144" t="n">
         <v>47333</v>
@@ -4603,7 +4603,7 @@
         <v>58</v>
       </c>
       <c r="G146" t="n">
-        <v>50.8430671691895</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H146" t="n">
         <v>54221</v>
@@ -4661,7 +4661,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G148" t="n">
-        <v>49.8349761962891</v>
+        <v>49.8349723815918</v>
       </c>
       <c r="H148" t="n">
         <v>38494</v>
@@ -4690,7 +4690,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G149" t="n">
-        <v>49.3528442382812</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H149" t="n">
         <v>68662</v>
@@ -4719,7 +4719,7 @@
         <v>56.0499992370605</v>
       </c>
       <c r="G150" t="n">
-        <v>49.1336936950684</v>
+        <v>49.1336898803711</v>
       </c>
       <c r="H150" t="n">
         <v>54634</v>
@@ -4748,7 +4748,7 @@
         <v>55.8499984741211</v>
       </c>
       <c r="G151" t="n">
-        <v>48.9583702087402</v>
+        <v>48.958366394043</v>
       </c>
       <c r="H151" t="n">
         <v>64253</v>
@@ -4806,7 +4806,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G153" t="n">
-        <v>50.6677551269531</v>
+        <v>50.6677513122559</v>
       </c>
       <c r="H153" t="n">
         <v>128897</v>
@@ -4835,7 +4835,7 @@
         <v>60</v>
       </c>
       <c r="G154" t="n">
-        <v>52.5962829589844</v>
+        <v>52.5962867736816</v>
       </c>
       <c r="H154" t="n">
         <v>118253</v>
@@ -4864,7 +4864,7 @@
         <v>59.4500007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>52.1141471862793</v>
+        <v>52.114143371582</v>
       </c>
       <c r="H155" t="n">
         <v>66348</v>
@@ -4893,7 +4893,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G156" t="n">
-        <v>53.1660766601562</v>
+        <v>53.166072845459</v>
       </c>
       <c r="H156" t="n">
         <v>97868</v>
@@ -4922,7 +4922,7 @@
         <v>60.8499984741211</v>
       </c>
       <c r="G157" t="n">
-        <v>53.3413963317871</v>
+        <v>53.3413925170898</v>
       </c>
       <c r="H157" t="n">
         <v>76402</v>
@@ -4951,7 +4951,7 @@
         <v>62</v>
       </c>
       <c r="G158" t="n">
-        <v>54.349494934082</v>
+        <v>54.3494873046875</v>
       </c>
       <c r="H158" t="n">
         <v>84132</v>
@@ -4980,7 +4980,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G159" t="n">
-        <v>53.122241973877</v>
+        <v>53.1222381591797</v>
       </c>
       <c r="H159" t="n">
         <v>79159</v>
@@ -5009,7 +5009,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>51.1060447692871</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H160" t="n">
         <v>136886</v>
@@ -5038,7 +5038,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>51.1060447692871</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H161" t="n">
         <v>48119</v>
@@ -5067,7 +5067,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G162" t="n">
-        <v>50.7115821838379</v>
+        <v>50.7115859985352</v>
       </c>
       <c r="H162" t="n">
         <v>44205</v>
@@ -5212,7 +5212,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>49.703483581543</v>
+        <v>49.7034912109375</v>
       </c>
       <c r="H167" t="n">
         <v>44573</v>
@@ -5241,7 +5241,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G168" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0102958679199</v>
       </c>
       <c r="H168" t="n">
         <v>23183</v>
@@ -5270,7 +5270,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G169" t="n">
-        <v>49.8349761962891</v>
+        <v>49.8349723815918</v>
       </c>
       <c r="H169" t="n">
         <v>25900</v>
@@ -5299,7 +5299,7 @@
         <v>58.5</v>
       </c>
       <c r="G170" t="n">
-        <v>51.2813720703125</v>
+        <v>51.2813682556152</v>
       </c>
       <c r="H170" t="n">
         <v>113411</v>
@@ -5328,7 +5328,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H171" t="n">
         <v>74536</v>
@@ -5357,7 +5357,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>50.4924278259277</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H172" t="n">
         <v>76973</v>
@@ -5386,7 +5386,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G173" t="n">
-        <v>50.4924278259277</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H173" t="n">
         <v>41557</v>
@@ -5415,7 +5415,7 @@
         <v>57.5</v>
       </c>
       <c r="G174" t="n">
-        <v>50.4047698974609</v>
+        <v>50.4047737121582</v>
       </c>
       <c r="H174" t="n">
         <v>21292</v>
@@ -5444,7 +5444,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G175" t="n">
-        <v>50.3171043395996</v>
+        <v>50.3171081542969</v>
       </c>
       <c r="H175" t="n">
         <v>37130</v>
@@ -5473,7 +5473,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>50.9307327270508</v>
+        <v>50.9307250976562</v>
       </c>
       <c r="H176" t="n">
         <v>60405</v>
@@ -5502,7 +5502,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>50.141788482666</v>
+        <v>50.1417846679688</v>
       </c>
       <c r="H177" t="n">
         <v>42536</v>
@@ -5531,7 +5531,7 @@
         <v>56.5</v>
       </c>
       <c r="G178" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281677246094</v>
       </c>
       <c r="H178" t="n">
         <v>77478</v>
@@ -5560,7 +5560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G179" t="n">
-        <v>48.563907623291</v>
+        <v>48.5639038085938</v>
       </c>
       <c r="H179" t="n">
         <v>78987</v>
@@ -5589,7 +5589,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G180" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H180" t="n">
         <v>71976</v>
@@ -5647,7 +5647,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>48.0817680358887</v>
+        <v>48.0817642211914</v>
       </c>
       <c r="H182" t="n">
         <v>108065</v>
@@ -5676,7 +5676,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>49.9226379394531</v>
+        <v>49.9226341247559</v>
       </c>
       <c r="H183" t="n">
         <v>94123</v>
@@ -5763,7 +5763,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>51.0183944702148</v>
+        <v>51.0183906555176</v>
       </c>
       <c r="H186" t="n">
         <v>57040</v>
@@ -5792,7 +5792,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G187" t="n">
-        <v>51.5443496704102</v>
+        <v>51.544361114502</v>
       </c>
       <c r="H187" t="n">
         <v>46007</v>
@@ -5821,7 +5821,7 @@
         <v>59</v>
       </c>
       <c r="G188" t="n">
-        <v>51.7196769714355</v>
+        <v>51.7196846008301</v>
       </c>
       <c r="H188" t="n">
         <v>61805</v>
@@ -5850,7 +5850,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>50.5800857543945</v>
+        <v>50.5800933837891</v>
       </c>
       <c r="H189" t="n">
         <v>39531</v>
@@ -5908,7 +5908,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>50.4924278259277</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H191" t="n">
         <v>37966</v>
@@ -5937,7 +5937,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>50.4924278259277</v>
+        <v>50.492431640625</v>
       </c>
       <c r="H192" t="n">
         <v>35774</v>
@@ -5966,7 +5966,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G193" t="n">
-        <v>50.141788482666</v>
+        <v>50.1417846679688</v>
       </c>
       <c r="H193" t="n">
         <v>52407</v>
@@ -5995,7 +5995,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G194" t="n">
-        <v>51.3690299987793</v>
+        <v>51.3690338134766</v>
       </c>
       <c r="H194" t="n">
         <v>39864</v>
@@ -6053,7 +6053,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>51.3252067565918</v>
+        <v>51.3251991271973</v>
       </c>
       <c r="H196" t="n">
         <v>55058</v>
@@ -6111,7 +6111,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G198" t="n">
-        <v>51.0183944702148</v>
+        <v>51.0183906555176</v>
       </c>
       <c r="H198" t="n">
         <v>51975</v>
@@ -6140,7 +6140,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>51.3252067565918</v>
+        <v>51.3251991271973</v>
       </c>
       <c r="H199" t="n">
         <v>26888</v>
@@ -6169,7 +6169,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>51.0183944702148</v>
+        <v>51.0183906555176</v>
       </c>
       <c r="H200" t="n">
         <v>32999</v>
@@ -6198,7 +6198,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>51.1060447692871</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H201" t="n">
         <v>63932</v>
@@ -6256,7 +6256,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H203" t="n">
         <v>127773</v>
@@ -6314,7 +6314,7 @@
         <v>58</v>
       </c>
       <c r="G205" t="n">
-        <v>50.8430671691895</v>
+        <v>50.8430709838867</v>
       </c>
       <c r="H205" t="n">
         <v>40883</v>
@@ -6401,7 +6401,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H208" t="n">
         <v>37855</v>
@@ -6488,7 +6488,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G211" t="n">
-        <v>48.7392158508301</v>
+        <v>48.7392196655273</v>
       </c>
       <c r="H211" t="n">
         <v>60350</v>
@@ -6517,7 +6517,7 @@
         <v>56.25</v>
       </c>
       <c r="G212" t="n">
-        <v>49.3090133666992</v>
+        <v>49.3090171813965</v>
       </c>
       <c r="H212" t="n">
         <v>100530</v>
@@ -6575,7 +6575,7 @@
         <v>56</v>
       </c>
       <c r="G214" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H214" t="n">
         <v>44252</v>
@@ -6633,7 +6633,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>47.2051696777344</v>
+        <v>47.2051620483398</v>
       </c>
       <c r="H216" t="n">
         <v>141726</v>
@@ -6691,7 +6691,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G218" t="n">
-        <v>46.7668609619141</v>
+        <v>46.7668571472168</v>
       </c>
       <c r="H218" t="n">
         <v>69051</v>
@@ -6720,7 +6720,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>46.9421844482422</v>
+        <v>46.9421806335449</v>
       </c>
       <c r="H219" t="n">
         <v>45180</v>
@@ -6778,7 +6778,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>47.2051696777344</v>
+        <v>47.2051620483398</v>
       </c>
       <c r="H221" t="n">
         <v>237721</v>
@@ -6836,7 +6836,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>44.8821601867676</v>
+        <v>44.8821563720703</v>
       </c>
       <c r="H223" t="n">
         <v>156382</v>
@@ -6865,7 +6865,7 @@
         <v>51</v>
       </c>
       <c r="G224" t="n">
-        <v>44.7068405151367</v>
+        <v>44.706844329834</v>
       </c>
       <c r="H224" t="n">
         <v>144844</v>
@@ -6894,7 +6894,7 @@
         <v>51</v>
       </c>
       <c r="G225" t="n">
-        <v>44.7068405151367</v>
+        <v>44.706844329834</v>
       </c>
       <c r="H225" t="n">
         <v>74954</v>
@@ -6923,7 +6923,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G226" t="n">
-        <v>45.539608001709</v>
+        <v>45.5396156311035</v>
       </c>
       <c r="H226" t="n">
         <v>159762</v>
@@ -6952,7 +6952,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H227" t="n">
         <v>99562</v>
@@ -6981,7 +6981,7 @@
         <v>52.25</v>
       </c>
       <c r="G228" t="n">
-        <v>45.8025970458984</v>
+        <v>45.8026008605957</v>
       </c>
       <c r="H228" t="n">
         <v>99489</v>
@@ -7039,7 +7039,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G230" t="n">
-        <v>45.3204612731934</v>
+        <v>45.3204574584961</v>
       </c>
       <c r="H230" t="n">
         <v>74885</v>
@@ -7068,7 +7068,7 @@
         <v>51.25</v>
       </c>
       <c r="G231" t="n">
-        <v>44.9259910583496</v>
+        <v>44.9259872436523</v>
       </c>
       <c r="H231" t="n">
         <v>72155</v>
@@ -7097,7 +7097,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G232" t="n">
-        <v>45.2766227722168</v>
+        <v>45.2766304016113</v>
       </c>
       <c r="H232" t="n">
         <v>43249</v>
@@ -7126,7 +7126,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G233" t="n">
-        <v>45.7149353027344</v>
+        <v>45.7149429321289</v>
       </c>
       <c r="H233" t="n">
         <v>26119</v>
@@ -7184,7 +7184,7 @@
         <v>51.5</v>
       </c>
       <c r="G235" t="n">
-        <v>45.1451416015625</v>
+        <v>45.1451377868652</v>
       </c>
       <c r="H235" t="n">
         <v>125607</v>
@@ -7213,7 +7213,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>44.6191825866699</v>
+        <v>44.6191787719727</v>
       </c>
       <c r="H236" t="n">
         <v>77799</v>
@@ -7242,7 +7242,7 @@
         <v>51.25</v>
       </c>
       <c r="G237" t="n">
-        <v>44.9259910583496</v>
+        <v>44.9259872436523</v>
       </c>
       <c r="H237" t="n">
         <v>109858</v>
@@ -7271,7 +7271,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G238" t="n">
-        <v>44.8383293151855</v>
+        <v>44.8383331298828</v>
       </c>
       <c r="H238" t="n">
         <v>115772</v>
@@ -7300,7 +7300,7 @@
         <v>51.25</v>
       </c>
       <c r="G239" t="n">
-        <v>44.9259910583496</v>
+        <v>44.9259872436523</v>
       </c>
       <c r="H239" t="n">
         <v>58604</v>
@@ -7329,7 +7329,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>45.7587661743164</v>
+        <v>45.7587623596191</v>
       </c>
       <c r="H240" t="n">
         <v>63619</v>
@@ -7416,7 +7416,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G243" t="n">
-        <v>45.7149353027344</v>
+        <v>45.7149429321289</v>
       </c>
       <c r="H243" t="n">
         <v>96572</v>
@@ -7532,7 +7532,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>46.372386932373</v>
+        <v>46.3723907470703</v>
       </c>
       <c r="H247" t="n">
         <v>104815</v>
@@ -7561,7 +7561,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>46.5915451049805</v>
+        <v>46.5915412902832</v>
       </c>
       <c r="H248" t="n">
         <v>101275</v>
@@ -7590,7 +7590,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G249" t="n">
-        <v>47.0298461914062</v>
+        <v>47.029842376709</v>
       </c>
       <c r="H249" t="n">
         <v>109982</v>
@@ -7619,7 +7619,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>48.3009185791016</v>
+        <v>48.3009147644043</v>
       </c>
       <c r="H250" t="n">
         <v>168307</v>
@@ -7648,7 +7648,7 @@
         <v>56.5</v>
       </c>
       <c r="G251" t="n">
-        <v>49.5281639099121</v>
+        <v>49.5281677246094</v>
       </c>
       <c r="H251" t="n">
         <v>175588</v>
@@ -7677,7 +7677,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>49.0460357666016</v>
+        <v>49.0460319519043</v>
       </c>
       <c r="H252" t="n">
         <v>158003</v>
@@ -7706,7 +7706,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G253" t="n">
-        <v>48.563907623291</v>
+        <v>48.5639038085938</v>
       </c>
       <c r="H253" t="n">
         <v>91984</v>
@@ -7735,7 +7735,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G254" t="n">
-        <v>49.4405097961426</v>
+        <v>49.4405059814453</v>
       </c>
       <c r="H254" t="n">
         <v>21800</v>
@@ -7793,7 +7793,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>49.3528442382812</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H256" t="n">
         <v>18333</v>
@@ -7822,7 +7822,7 @@
         <v>56.25</v>
       </c>
       <c r="G257" t="n">
-        <v>49.3090133666992</v>
+        <v>49.3090171813965</v>
       </c>
       <c r="H257" t="n">
         <v>13680</v>
@@ -7880,7 +7880,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>50.3171043395996</v>
+        <v>50.3171081542969</v>
       </c>
       <c r="H259" t="n">
         <v>95026</v>
@@ -7938,7 +7938,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>50.5800857543945</v>
+        <v>50.5800933837891</v>
       </c>
       <c r="H261" t="n">
         <v>43639</v>
@@ -7967,7 +7967,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G262" t="n">
-        <v>51.1937141418457</v>
+        <v>51.1937103271484</v>
       </c>
       <c r="H262" t="n">
         <v>44010</v>
@@ -7996,7 +7996,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G263" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H263" t="n">
         <v>39353</v>
@@ -8054,7 +8054,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>49.5719985961914</v>
+        <v>49.5719947814941</v>
       </c>
       <c r="H265" t="n">
         <v>62485</v>
@@ -8083,7 +8083,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G266" t="n">
-        <v>50.2732810974121</v>
+        <v>50.2732734680176</v>
       </c>
       <c r="H266" t="n">
         <v>55893</v>
@@ -8112,7 +8112,7 @@
         <v>57.5</v>
       </c>
       <c r="G267" t="n">
-        <v>50.4047698974609</v>
+        <v>50.4047737121582</v>
       </c>
       <c r="H267" t="n">
         <v>35730</v>
@@ -8141,7 +8141,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H268" t="n">
         <v>46171</v>
@@ -8228,7 +8228,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>49.791145324707</v>
+        <v>49.7911491394043</v>
       </c>
       <c r="H271" t="n">
         <v>35621</v>
@@ -8257,7 +8257,7 @@
         <v>56</v>
       </c>
       <c r="G272" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H272" t="n">
         <v>41651</v>
@@ -8286,7 +8286,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>49.3528442382812</v>
+        <v>49.352840423584</v>
       </c>
       <c r="H273" t="n">
         <v>54452</v>
@@ -8315,7 +8315,7 @@
         <v>55</v>
       </c>
       <c r="G274" t="n">
-        <v>48.2132606506348</v>
+        <v>48.2132568359375</v>
       </c>
       <c r="H274" t="n">
         <v>183138</v>
@@ -8402,7 +8402,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>48.6953887939453</v>
+        <v>48.6954002380371</v>
       </c>
       <c r="H277" t="n">
         <v>99818</v>
@@ -8431,7 +8431,7 @@
         <v>55.5</v>
       </c>
       <c r="G278" t="n">
-        <v>48.6515655517578</v>
+        <v>48.6515579223633</v>
       </c>
       <c r="H278" t="n">
         <v>67978</v>
@@ -8489,7 +8489,7 @@
         <v>56</v>
       </c>
       <c r="G280" t="n">
-        <v>49.0898590087891</v>
+        <v>49.0898628234863</v>
       </c>
       <c r="H280" t="n">
         <v>70892</v>
@@ -8518,7 +8518,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>51.1937141418457</v>
+        <v>51.1937103271484</v>
       </c>
       <c r="H281" t="n">
         <v>176623</v>
@@ -8547,7 +8547,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H282" t="n">
         <v>58562</v>
@@ -8576,7 +8576,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>49.6596641540527</v>
+        <v>49.6596565246582</v>
       </c>
       <c r="H283" t="n">
         <v>55901</v>
@@ -8663,7 +8663,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>49.5719985961914</v>
+        <v>49.5719947814941</v>
       </c>
       <c r="H286" t="n">
         <v>42386</v>
@@ -8692,7 +8692,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G287" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0102958679199</v>
       </c>
       <c r="H287" t="n">
         <v>68947</v>
@@ -8721,7 +8721,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>50.0102996826172</v>
+        <v>50.0102958679199</v>
       </c>
       <c r="H288" t="n">
         <v>33003</v>
@@ -8750,7 +8750,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>50.6677551269531</v>
+        <v>50.6677513122559</v>
       </c>
       <c r="H289" t="n">
         <v>47641</v>
@@ -8779,7 +8779,7 @@
         <v>58.5</v>
       </c>
       <c r="G290" t="n">
-        <v>51.2813720703125</v>
+        <v>51.2813682556152</v>
       </c>
       <c r="H290" t="n">
         <v>101816</v>
@@ -8808,7 +8808,7 @@
         <v>57.9500007629395</v>
       </c>
       <c r="G291" t="n">
-        <v>50.799243927002</v>
+        <v>50.7992477416992</v>
       </c>
       <c r="H291" t="n">
         <v>101762</v>
@@ -8866,7 +8866,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>50.3171043395996</v>
+        <v>50.3171081542969</v>
       </c>
       <c r="H293" t="n">
         <v>68398</v>
@@ -8895,7 +8895,7 @@
         <v>57.25</v>
       </c>
       <c r="G294" t="n">
-        <v>50.1856155395508</v>
+        <v>50.185619354248</v>
       </c>
       <c r="H294" t="n">
         <v>121098</v>
@@ -8924,7 +8924,7 @@
         <v>59</v>
       </c>
       <c r="G295" t="n">
-        <v>51.7196769714355</v>
+        <v>51.7196846008301</v>
       </c>
       <c r="H295" t="n">
         <v>116359</v>
@@ -8953,7 +8953,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>51.1060447692871</v>
+        <v>51.1060523986816</v>
       </c>
       <c r="H296" t="n">
         <v>80368</v>
@@ -8982,7 +8982,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>51.237548828125</v>
+        <v>51.2375411987305</v>
       </c>
       <c r="H297" t="n">
         <v>126567</v>
@@ -9040,7 +9040,7 @@
         <v>59.75</v>
       </c>
       <c r="G299" t="n">
-        <v>52.3771324157715</v>
+        <v>52.3771286010742</v>
       </c>
       <c r="H299" t="n">
         <v>83441</v>
@@ -9069,7 +9069,7 @@
         <v>60</v>
       </c>
       <c r="G300" t="n">
-        <v>52.5962829589844</v>
+        <v>52.5962867736816</v>
       </c>
       <c r="H300" t="n">
         <v>115569</v>
@@ -9098,7 +9098,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>52.420955657959</v>
+        <v>52.4209671020508</v>
       </c>
       <c r="H301" t="n">
         <v>69522</v>
@@ -9127,7 +9127,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>52.420955657959</v>
+        <v>52.4209671020508</v>
       </c>
       <c r="H302" t="n">
         <v>60828</v>
@@ -9185,7 +9185,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G304" t="n">
-        <v>52.6839370727539</v>
+        <v>52.6839408874512</v>
       </c>
       <c r="H304" t="n">
         <v>94608</v>
@@ -9214,7 +9214,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>51.5443496704102</v>
+        <v>51.544361114502</v>
       </c>
       <c r="H305" t="n">
         <v>154357</v>
@@ -9243,7 +9243,7 @@
         <v>59.25</v>
       </c>
       <c r="G306" t="n">
-        <v>51.9388275146484</v>
+        <v>51.9388198852539</v>
       </c>
       <c r="H306" t="n">
         <v>85958</v>
@@ -9301,7 +9301,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>51.5443496704102</v>
+        <v>51.544361114502</v>
       </c>
       <c r="H308" t="n">
         <v>103451</v>
@@ -9359,7 +9359,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G310" t="n">
-        <v>52.859260559082</v>
+        <v>52.8592567443848</v>
       </c>
       <c r="H310" t="n">
         <v>99450</v>
@@ -9388,7 +9388,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>53.7796974182129</v>
+        <v>53.7796936035156</v>
       </c>
       <c r="H311" t="n">
         <v>99357</v>
@@ -9417,7 +9417,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G312" t="n">
-        <v>53.7796974182129</v>
+        <v>53.7796936035156</v>
       </c>
       <c r="H312" t="n">
         <v>90388</v>
@@ -9446,7 +9446,7 @@
         <v>62.25</v>
       </c>
       <c r="G313" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H313" t="n">
         <v>168323</v>
@@ -9475,7 +9475,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>54.3056640625</v>
+        <v>54.3056678771973</v>
       </c>
       <c r="H314" t="n">
         <v>112926</v>
@@ -9504,7 +9504,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G315" t="n">
-        <v>54.4809837341309</v>
+        <v>54.4809799194336</v>
       </c>
       <c r="H315" t="n">
         <v>94164</v>
@@ -9562,7 +9562,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>55.0946044921875</v>
+        <v>55.0946006774902</v>
       </c>
       <c r="H317" t="n">
         <v>93970</v>
@@ -9620,7 +9620,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G319" t="n">
-        <v>55.0946044921875</v>
+        <v>55.0946006774902</v>
       </c>
       <c r="H319" t="n">
         <v>86476</v>
@@ -9649,7 +9649,7 @@
         <v>62.25</v>
       </c>
       <c r="G320" t="n">
-        <v>54.5686454772949</v>
+        <v>54.5686416625977</v>
       </c>
       <c r="H320" t="n">
         <v>73391</v>
@@ -9736,7 +9736,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>55.9273834228516</v>
+        <v>55.927375793457</v>
       </c>
       <c r="H323" t="n">
         <v>63561</v>
@@ -9794,7 +9794,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G325" t="n">
-        <v>56.3656883239746</v>
+        <v>56.3656806945801</v>
       </c>
       <c r="H325" t="n">
         <v>54692</v>
@@ -9823,7 +9823,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G326" t="n">
-        <v>56.2780151367188</v>
+        <v>56.2780227661133</v>
       </c>
       <c r="H326" t="n">
         <v>93016</v>
@@ -9852,7 +9852,7 @@
         <v>65</v>
       </c>
       <c r="G327" t="n">
-        <v>56.9793014526367</v>
+        <v>56.9792976379395</v>
       </c>
       <c r="H327" t="n">
         <v>61355</v>
@@ -9881,7 +9881,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G328" t="n">
-        <v>57.8120765686035</v>
+        <v>57.8120727539062</v>
       </c>
       <c r="H328" t="n">
         <v>105326</v>
@@ -9939,7 +9939,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G330" t="n">
-        <v>57.680591583252</v>
+        <v>57.6805953979492</v>
       </c>
       <c r="H330" t="n">
         <v>61993</v>
@@ -9968,7 +9968,7 @@
         <v>65.0500030517578</v>
       </c>
       <c r="G331" t="n">
-        <v>57.023136138916</v>
+        <v>57.0231399536133</v>
       </c>
       <c r="H331" t="n">
         <v>95522</v>
@@ -9997,7 +9997,7 @@
         <v>64</v>
       </c>
       <c r="G332" t="n">
-        <v>56.1026954650879</v>
+        <v>56.1026916503906</v>
       </c>
       <c r="H332" t="n">
         <v>205806</v>
@@ -10084,7 +10084,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G335" t="n">
-        <v>57.5052642822266</v>
+        <v>57.5052719116211</v>
       </c>
       <c r="H335" t="n">
         <v>103682</v>
@@ -10113,7 +10113,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G336" t="n">
-        <v>58.9078369140625</v>
+        <v>58.907829284668</v>
       </c>
       <c r="H336" t="n">
         <v>121938</v>
@@ -10171,7 +10171,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G338" t="n">
-        <v>58.2065544128418</v>
+        <v>58.2065505981445</v>
       </c>
       <c r="H338" t="n">
         <v>84175</v>
@@ -10200,7 +10200,7 @@
         <v>67.5</v>
       </c>
       <c r="G339" t="n">
-        <v>59.1708221435547</v>
+        <v>59.1708183288574</v>
       </c>
       <c r="H339" t="n">
         <v>87020</v>
@@ -10229,7 +10229,7 @@
         <v>68.8000030517578</v>
       </c>
       <c r="G340" t="n">
-        <v>60.3104019165039</v>
+        <v>60.3103981018066</v>
       </c>
       <c r="H340" t="n">
         <v>93918</v>
@@ -10287,7 +10287,7 @@
         <v>69.5999984741211</v>
       </c>
       <c r="G342" t="n">
-        <v>61.0116806030273</v>
+        <v>61.0116920471191</v>
       </c>
       <c r="H342" t="n">
         <v>146465</v>
@@ -10316,7 +10316,7 @@
         <v>69</v>
       </c>
       <c r="G343" t="n">
-        <v>60.485725402832</v>
+        <v>60.4857139587402</v>
       </c>
       <c r="H343" t="n">
         <v>124118</v>
@@ -10345,7 +10345,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G344" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H344" t="n">
         <v>113418</v>
@@ -10374,7 +10374,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G345" t="n">
-        <v>60.748706817627</v>
+        <v>60.7487030029297</v>
       </c>
       <c r="H345" t="n">
         <v>142132</v>
@@ -10403,7 +10403,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G346" t="n">
-        <v>61.669132232666</v>
+        <v>61.6691513061523</v>
       </c>
       <c r="H346" t="n">
         <v>203289</v>
@@ -10432,7 +10432,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G347" t="n">
-        <v>61.5376434326172</v>
+        <v>61.5376396179199</v>
       </c>
       <c r="H347" t="n">
         <v>102736</v>
@@ -10461,7 +10461,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>61.2308387756348</v>
+        <v>61.2308311462402</v>
       </c>
       <c r="H348" t="n">
         <v>156756</v>
@@ -10490,7 +10490,7 @@
         <v>70.25</v>
       </c>
       <c r="G349" t="n">
-        <v>61.5814819335938</v>
+        <v>61.5814781188965</v>
       </c>
       <c r="H349" t="n">
         <v>91255</v>
@@ -10577,7 +10577,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>59.7406120300293</v>
+        <v>59.740608215332</v>
       </c>
       <c r="H352" t="n">
         <v>78818</v>
@@ -10606,7 +10606,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>59.0831642150879</v>
+        <v>59.0831604003906</v>
       </c>
       <c r="H353" t="n">
         <v>90559</v>
@@ -10635,7 +10635,7 @@
         <v>68.25</v>
       </c>
       <c r="G354" t="n">
-        <v>59.8282699584961</v>
+        <v>59.8282623291016</v>
       </c>
       <c r="H354" t="n">
         <v>78001</v>
@@ -10664,7 +10664,7 @@
         <v>68.25</v>
       </c>
       <c r="G355" t="n">
-        <v>60.5378723144531</v>
+        <v>60.5378684997559</v>
       </c>
       <c r="H355" t="n">
         <v>58161</v>
@@ -10751,7 +10751,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G358" t="n">
-        <v>61.1587715148926</v>
+        <v>61.158763885498</v>
       </c>
       <c r="H358" t="n">
         <v>54688</v>
@@ -10780,7 +10780,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G359" t="n">
-        <v>61.3805274963379</v>
+        <v>61.3805198669434</v>
       </c>
       <c r="H359" t="n">
         <v>69316</v>
@@ -10809,7 +10809,7 @@
         <v>68.0500030517578</v>
       </c>
       <c r="G360" t="n">
-        <v>60.3604774475098</v>
+        <v>60.360481262207</v>
       </c>
       <c r="H360" t="n">
         <v>44961</v>
@@ -10867,7 +10867,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G362" t="n">
-        <v>61.1587715148926</v>
+        <v>61.158763885498</v>
       </c>
       <c r="H362" t="n">
         <v>59736</v>
@@ -10896,7 +10896,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G363" t="n">
-        <v>62.2675170898438</v>
+        <v>62.2675132751465</v>
       </c>
       <c r="H363" t="n">
         <v>76993</v>
@@ -10954,7 +10954,7 @@
         <v>70.25</v>
       </c>
       <c r="G365" t="n">
-        <v>62.3118782043457</v>
+        <v>62.3118743896484</v>
       </c>
       <c r="H365" t="n">
         <v>50482</v>
@@ -10983,7 +10983,7 @@
         <v>71.4499969482422</v>
       </c>
       <c r="G366" t="n">
-        <v>63.376277923584</v>
+        <v>63.3762702941895</v>
       </c>
       <c r="H366" t="n">
         <v>85002</v>
@@ -11012,7 +11012,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G367" t="n">
-        <v>62.8884315490723</v>
+        <v>62.8884239196777</v>
       </c>
       <c r="H367" t="n">
         <v>88768</v>
@@ -11041,7 +11041,7 @@
         <v>71.75</v>
       </c>
       <c r="G368" t="n">
-        <v>63.6423835754395</v>
+        <v>63.6423873901367</v>
       </c>
       <c r="H368" t="n">
         <v>78174</v>
@@ -11070,7 +11070,7 @@
         <v>72.5</v>
       </c>
       <c r="G369" t="n">
-        <v>64.3076171875</v>
+        <v>64.3076400756836</v>
       </c>
       <c r="H369" t="n">
         <v>87422</v>
@@ -11099,7 +11099,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014305114746</v>
       </c>
       <c r="H370" t="n">
         <v>126134</v>
@@ -11128,7 +11128,7 @@
         <v>69.75</v>
       </c>
       <c r="G371" t="n">
-        <v>61.8683853149414</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H371" t="n">
         <v>83211</v>
@@ -11157,7 +11157,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G372" t="n">
-        <v>63.3319358825684</v>
+        <v>63.3319206237793</v>
       </c>
       <c r="H372" t="n">
         <v>68728</v>
@@ -11186,7 +11186,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G373" t="n">
-        <v>62.7110252380371</v>
+        <v>62.7110214233398</v>
       </c>
       <c r="H373" t="n">
         <v>62075</v>
@@ -11215,7 +11215,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G374" t="n">
-        <v>63.2432174682617</v>
+        <v>63.243221282959</v>
       </c>
       <c r="H374" t="n">
         <v>80009</v>
@@ -11244,7 +11244,7 @@
         <v>71.1500015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>63.1101760864258</v>
+        <v>63.1101837158203</v>
       </c>
       <c r="H375" t="n">
         <v>41602</v>
@@ -11273,7 +11273,7 @@
         <v>71</v>
       </c>
       <c r="G376" t="n">
-        <v>62.9771308898926</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H376" t="n">
         <v>55189</v>
@@ -11331,7 +11331,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G378" t="n">
-        <v>62.2675170898438</v>
+        <v>62.2675132751465</v>
       </c>
       <c r="H378" t="n">
         <v>44527</v>
@@ -11389,7 +11389,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G380" t="n">
-        <v>63.2432174682617</v>
+        <v>63.243221282959</v>
       </c>
       <c r="H380" t="n">
         <v>131749</v>
@@ -11418,7 +11418,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014305114746</v>
       </c>
       <c r="H381" t="n">
         <v>151026</v>
@@ -11534,7 +11534,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G385" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743103027344</v>
       </c>
       <c r="H385" t="n">
         <v>79441</v>
@@ -11563,7 +11563,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G386" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743103027344</v>
       </c>
       <c r="H386" t="n">
         <v>35043</v>
@@ -11621,7 +11621,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G388" t="n">
-        <v>59.0743217468262</v>
+        <v>59.0743103027344</v>
       </c>
       <c r="H388" t="n">
         <v>68536</v>
@@ -11650,7 +11650,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G389" t="n">
-        <v>59.6952209472656</v>
+        <v>59.6952247619629</v>
       </c>
       <c r="H389" t="n">
         <v>31158</v>
@@ -11679,7 +11679,7 @@
         <v>67</v>
       </c>
       <c r="G390" t="n">
-        <v>59.4291229248047</v>
+        <v>59.4291191101074</v>
       </c>
       <c r="H390" t="n">
         <v>83527</v>
@@ -11708,7 +11708,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>58.5864753723145</v>
+        <v>58.5864715576172</v>
       </c>
       <c r="H391" t="n">
         <v>60337</v>
@@ -11737,7 +11737,7 @@
         <v>67</v>
       </c>
       <c r="G392" t="n">
-        <v>59.4291229248047</v>
+        <v>59.4291191101074</v>
       </c>
       <c r="H392" t="n">
         <v>65587</v>
@@ -11766,7 +11766,7 @@
         <v>67.0999984741211</v>
       </c>
       <c r="G393" t="n">
-        <v>59.5178184509277</v>
+        <v>59.5178108215332</v>
       </c>
       <c r="H393" t="n">
         <v>54381</v>
@@ -11795,7 +11795,7 @@
         <v>68</v>
       </c>
       <c r="G394" t="n">
-        <v>60.3161163330078</v>
+        <v>60.3161239624023</v>
       </c>
       <c r="H394" t="n">
         <v>59621</v>
@@ -11853,7 +11853,7 @@
         <v>69.75</v>
       </c>
       <c r="G396" t="n">
-        <v>61.8683853149414</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H396" t="n">
         <v>106303</v>
@@ -11911,7 +11911,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>62.4005699157715</v>
+        <v>62.4005813598633</v>
       </c>
       <c r="H398" t="n">
         <v>82183</v>
@@ -12056,7 +12056,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>65.5494384765625</v>
+        <v>65.5494232177734</v>
       </c>
       <c r="H403" t="n">
         <v>98784</v>
@@ -12085,7 +12085,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G404" t="n">
-        <v>64.7954940795898</v>
+        <v>64.7954788208008</v>
       </c>
       <c r="H404" t="n">
         <v>67694</v>
@@ -12114,7 +12114,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>65.283332824707</v>
+        <v>65.2833251953125</v>
       </c>
       <c r="H405" t="n">
         <v>62565</v>
@@ -12143,7 +12143,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G406" t="n">
-        <v>65.1059265136719</v>
+        <v>65.1059341430664</v>
       </c>
       <c r="H406" t="n">
         <v>54364</v>
@@ -12172,7 +12172,7 @@
         <v>73</v>
       </c>
       <c r="G407" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H407" t="n">
         <v>66371</v>
@@ -12201,7 +12201,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G408" t="n">
-        <v>64.7954940795898</v>
+        <v>64.7954788208008</v>
       </c>
       <c r="H408" t="n">
         <v>127324</v>
@@ -12230,7 +12230,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>64.6624298095703</v>
+        <v>64.6624374389648</v>
       </c>
       <c r="H409" t="n">
         <v>63510</v>
@@ -12288,7 +12288,7 @@
         <v>71.9499969482422</v>
       </c>
       <c r="G411" t="n">
-        <v>63.8197784423828</v>
+        <v>63.8197631835938</v>
       </c>
       <c r="H411" t="n">
         <v>175766</v>
@@ -12317,7 +12317,7 @@
         <v>72.1500015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>63.9971771240234</v>
+        <v>63.997184753418</v>
       </c>
       <c r="H412" t="n">
         <v>138872</v>
@@ -12346,7 +12346,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G413" t="n">
-        <v>63.3319358825684</v>
+        <v>63.3319206237793</v>
       </c>
       <c r="H413" t="n">
         <v>52658</v>
@@ -12375,7 +12375,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G414" t="n">
-        <v>62.7110252380371</v>
+        <v>62.7110214233398</v>
       </c>
       <c r="H414" t="n">
         <v>53923</v>
@@ -12404,7 +12404,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>63.5536651611328</v>
+        <v>63.5536918640137</v>
       </c>
       <c r="H415" t="n">
         <v>58212</v>
@@ -12433,7 +12433,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>63.3319358825684</v>
+        <v>63.3319206237793</v>
       </c>
       <c r="H416" t="n">
         <v>73224</v>
@@ -12491,7 +12491,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G418" t="n">
-        <v>63.4649887084961</v>
+        <v>63.4649810791016</v>
       </c>
       <c r="H418" t="n">
         <v>57244</v>
@@ -12520,7 +12520,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>63.2875823974609</v>
+        <v>63.2875671386719</v>
       </c>
       <c r="H419" t="n">
         <v>32790</v>
@@ -12549,7 +12549,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>63.3319358825684</v>
+        <v>63.3319206237793</v>
       </c>
       <c r="H420" t="n">
         <v>52903</v>
@@ -12578,7 +12578,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G421" t="n">
-        <v>63.2875823974609</v>
+        <v>63.2875671386719</v>
       </c>
       <c r="H421" t="n">
         <v>54279</v>
@@ -12607,7 +12607,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G422" t="n">
-        <v>62.7997207641602</v>
+        <v>62.7997245788574</v>
       </c>
       <c r="H422" t="n">
         <v>37097</v>
@@ -12665,7 +12665,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G424" t="n">
-        <v>62.1344795227051</v>
+        <v>62.1344757080078</v>
       </c>
       <c r="H424" t="n">
         <v>69545</v>
@@ -12723,7 +12723,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G426" t="n">
-        <v>63.2875823974609</v>
+        <v>63.2875671386719</v>
       </c>
       <c r="H426" t="n">
         <v>67312</v>
@@ -12752,7 +12752,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G427" t="n">
-        <v>64.2189331054688</v>
+        <v>64.2189407348633</v>
       </c>
       <c r="H427" t="n">
         <v>125587</v>
@@ -12781,7 +12781,7 @@
         <v>72.4499969482422</v>
       </c>
       <c r="G428" t="n">
-        <v>64.2632751464844</v>
+        <v>64.2632675170898</v>
       </c>
       <c r="H428" t="n">
         <v>65641</v>
@@ -12810,7 +12810,7 @@
         <v>72.5</v>
       </c>
       <c r="G429" t="n">
-        <v>64.3076171875</v>
+        <v>64.3076400756836</v>
       </c>
       <c r="H429" t="n">
         <v>52398</v>
@@ -12839,7 +12839,7 @@
         <v>73</v>
       </c>
       <c r="G430" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H430" t="n">
         <v>68493</v>
@@ -12926,7 +12926,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G433" t="n">
-        <v>65.2389907836914</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H433" t="n">
         <v>52881</v>
@@ -12955,7 +12955,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>65.5494384765625</v>
+        <v>65.5494232177734</v>
       </c>
       <c r="H434" t="n">
         <v>63832</v>
@@ -12984,7 +12984,7 @@
         <v>73</v>
       </c>
       <c r="G435" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H435" t="n">
         <v>68517</v>
@@ -13013,7 +13013,7 @@
         <v>74</v>
       </c>
       <c r="G436" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H436" t="n">
         <v>59046</v>
@@ -13042,7 +13042,7 @@
         <v>74</v>
       </c>
       <c r="G437" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H437" t="n">
         <v>38905</v>
@@ -13071,7 +13071,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G438" t="n">
-        <v>64.8398361206055</v>
+        <v>64.8398208618164</v>
       </c>
       <c r="H438" t="n">
         <v>73428</v>
@@ -13129,7 +13129,7 @@
         <v>74</v>
       </c>
       <c r="G440" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H440" t="n">
         <v>47098</v>
@@ -13158,7 +13158,7 @@
         <v>74.25</v>
       </c>
       <c r="G441" t="n">
-        <v>65.8598709106445</v>
+        <v>65.8598785400391</v>
       </c>
       <c r="H441" t="n">
         <v>71180</v>
@@ -13245,7 +13245,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G444" t="n">
-        <v>67.2790908813477</v>
+        <v>67.2790756225586</v>
       </c>
       <c r="H444" t="n">
         <v>98607</v>
@@ -13303,7 +13303,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G446" t="n">
-        <v>66.6138381958008</v>
+        <v>66.6138458251953</v>
       </c>
       <c r="H446" t="n">
         <v>162554</v>
@@ -13361,7 +13361,7 @@
         <v>75.4499969482422</v>
       </c>
       <c r="G448" t="n">
-        <v>66.9242706298828</v>
+        <v>66.9242858886719</v>
       </c>
       <c r="H448" t="n">
         <v>113939</v>
@@ -13390,7 +13390,7 @@
         <v>76.5</v>
       </c>
       <c r="G449" t="n">
-        <v>67.8556289672852</v>
+        <v>67.8556365966797</v>
       </c>
       <c r="H449" t="n">
         <v>96594</v>
@@ -13448,7 +13448,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G451" t="n">
-        <v>69.0974578857422</v>
+        <v>69.0974426269531</v>
       </c>
       <c r="H451" t="n">
         <v>82960</v>
@@ -13506,7 +13506,7 @@
         <v>79</v>
       </c>
       <c r="G453" t="n">
-        <v>70.0731506347656</v>
+        <v>70.073127746582</v>
       </c>
       <c r="H453" t="n">
         <v>44675</v>
@@ -13564,7 +13564,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G455" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409393310547</v>
       </c>
       <c r="H455" t="n">
         <v>59456</v>
@@ -13622,7 +13622,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G457" t="n">
-        <v>71.4479904174805</v>
+        <v>71.447998046875</v>
       </c>
       <c r="H457" t="n">
         <v>165700</v>
@@ -13680,7 +13680,7 @@
         <v>79</v>
       </c>
       <c r="G459" t="n">
-        <v>70.0731506347656</v>
+        <v>70.073127746582</v>
       </c>
       <c r="H459" t="n">
         <v>72167</v>
@@ -13709,7 +13709,7 @@
         <v>79</v>
       </c>
       <c r="G460" t="n">
-        <v>70.0731506347656</v>
+        <v>70.073127746582</v>
       </c>
       <c r="H460" t="n">
         <v>72203</v>
@@ -13738,7 +13738,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G461" t="n">
-        <v>69.5852890014648</v>
+        <v>69.5852966308594</v>
       </c>
       <c r="H461" t="n">
         <v>88886</v>
@@ -13767,7 +13767,7 @@
         <v>77.75</v>
       </c>
       <c r="G462" t="n">
-        <v>68.9643936157227</v>
+        <v>68.9643859863281</v>
       </c>
       <c r="H462" t="n">
         <v>79077</v>
@@ -13883,7 +13883,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G466" t="n">
-        <v>69.0974578857422</v>
+        <v>69.0974426269531</v>
       </c>
       <c r="H466" t="n">
         <v>80881</v>
@@ -13912,7 +13912,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G467" t="n">
-        <v>69.4522399902344</v>
+        <v>69.4522476196289</v>
       </c>
       <c r="H467" t="n">
         <v>99295</v>
@@ -13970,7 +13970,7 @@
         <v>78</v>
       </c>
       <c r="G469" t="n">
-        <v>69.1861419677734</v>
+        <v>69.1861343383789</v>
       </c>
       <c r="H469" t="n">
         <v>75889</v>
@@ -14028,7 +14028,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G471" t="n">
-        <v>70.0287780761719</v>
+        <v>70.0287857055664</v>
       </c>
       <c r="H471" t="n">
         <v>89387</v>
@@ -14057,7 +14057,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G472" t="n">
-        <v>69.1417770385742</v>
+        <v>69.1417846679688</v>
       </c>
       <c r="H472" t="n">
         <v>67354</v>
@@ -14115,7 +14115,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G474" t="n">
-        <v>69.6739883422852</v>
+        <v>69.6739959716797</v>
       </c>
       <c r="H474" t="n">
         <v>75930</v>
@@ -14144,7 +14144,7 @@
         <v>78.25</v>
       </c>
       <c r="G475" t="n">
-        <v>69.4078826904297</v>
+        <v>69.4078979492188</v>
       </c>
       <c r="H475" t="n">
         <v>56037</v>
@@ -14173,7 +14173,7 @@
         <v>77.75</v>
       </c>
       <c r="G476" t="n">
-        <v>68.9643936157227</v>
+        <v>68.9643859863281</v>
       </c>
       <c r="H476" t="n">
         <v>111473</v>
@@ -14289,7 +14289,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G480" t="n">
-        <v>66.2146835327148</v>
+        <v>66.2146911621094</v>
       </c>
       <c r="H480" t="n">
         <v>137194</v>
@@ -14318,7 +14318,7 @@
         <v>74</v>
       </c>
       <c r="G481" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H481" t="n">
         <v>60994</v>
@@ -14405,7 +14405,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G484" t="n">
-        <v>67.9886932373047</v>
+        <v>67.9886856079102</v>
       </c>
       <c r="H484" t="n">
         <v>41631</v>
@@ -14434,7 +14434,7 @@
         <v>77.5</v>
       </c>
       <c r="G485" t="n">
-        <v>68.7426300048828</v>
+        <v>68.7426376342773</v>
       </c>
       <c r="H485" t="n">
         <v>61379</v>
@@ -14463,7 +14463,7 @@
         <v>77.1999969482422</v>
       </c>
       <c r="G486" t="n">
-        <v>68.4765396118164</v>
+        <v>68.4765319824219</v>
       </c>
       <c r="H486" t="n">
         <v>53142</v>
@@ -14492,7 +14492,7 @@
         <v>76.3499984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>67.7225875854492</v>
+        <v>67.7225799560547</v>
       </c>
       <c r="H487" t="n">
         <v>27994</v>
@@ -14521,7 +14521,7 @@
         <v>74.5</v>
       </c>
       <c r="G488" t="n">
-        <v>66.0816345214844</v>
+        <v>66.0816268920898</v>
       </c>
       <c r="H488" t="n">
         <v>87105</v>
@@ -14550,7 +14550,7 @@
         <v>75.6500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>67.1016845703125</v>
+        <v>67.1016693115234</v>
       </c>
       <c r="H489" t="n">
         <v>55696</v>
@@ -14579,7 +14579,7 @@
         <v>76.4000015258789</v>
       </c>
       <c r="G490" t="n">
-        <v>67.7669372558594</v>
+        <v>67.7669448852539</v>
       </c>
       <c r="H490" t="n">
         <v>69626</v>
@@ -14608,7 +14608,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G491" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999862670898</v>
       </c>
       <c r="H491" t="n">
         <v>52899</v>
@@ -14637,7 +14637,7 @@
         <v>77.4000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>68.6539306640625</v>
+        <v>68.6539459228516</v>
       </c>
       <c r="H492" t="n">
         <v>86207</v>
@@ -14695,7 +14695,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>68.8756942749023</v>
+        <v>68.8756866455078</v>
       </c>
       <c r="H494" t="n">
         <v>87616</v>
@@ -14724,7 +14724,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409393310547</v>
       </c>
       <c r="H495" t="n">
         <v>55937</v>
@@ -14753,7 +14753,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G496" t="n">
-        <v>69.5852890014648</v>
+        <v>69.5852966308594</v>
       </c>
       <c r="H496" t="n">
         <v>53005</v>
@@ -14782,7 +14782,7 @@
         <v>79.5500030517578</v>
       </c>
       <c r="G497" t="n">
-        <v>70.5609970092773</v>
+        <v>70.5609893798828</v>
       </c>
       <c r="H497" t="n">
         <v>66956</v>
@@ -14811,7 +14811,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G498" t="n">
-        <v>71.4479904174805</v>
+        <v>71.447998046875</v>
       </c>
       <c r="H498" t="n">
         <v>114724</v>
@@ -14869,7 +14869,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>69.6739883422852</v>
+        <v>69.6739959716797</v>
       </c>
       <c r="H500" t="n">
         <v>78057</v>
@@ -14927,7 +14927,7 @@
         <v>76.4000015258789</v>
       </c>
       <c r="G502" t="n">
-        <v>67.7669372558594</v>
+        <v>67.7669448852539</v>
       </c>
       <c r="H502" t="n">
         <v>94493</v>
@@ -14956,7 +14956,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G503" t="n">
-        <v>67.2347259521484</v>
+        <v>67.234733581543</v>
       </c>
       <c r="H503" t="n">
         <v>98841</v>
@@ -15101,7 +15101,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G508" t="n">
-        <v>66.0372772216797</v>
+        <v>66.0372848510742</v>
       </c>
       <c r="H508" t="n">
         <v>31305</v>
@@ -15130,7 +15130,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G509" t="n">
-        <v>66.2146835327148</v>
+        <v>66.2146911621094</v>
       </c>
       <c r="H509" t="n">
         <v>49015</v>
@@ -15188,7 +15188,7 @@
         <v>74</v>
       </c>
       <c r="G511" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H511" t="n">
         <v>37851</v>
@@ -15217,7 +15217,7 @@
         <v>74.5</v>
       </c>
       <c r="G512" t="n">
-        <v>66.0816345214844</v>
+        <v>66.0816268920898</v>
       </c>
       <c r="H512" t="n">
         <v>71254</v>
@@ -15275,7 +15275,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G514" t="n">
-        <v>67.2790908813477</v>
+        <v>67.2790756225586</v>
       </c>
       <c r="H514" t="n">
         <v>71685</v>
@@ -15304,7 +15304,7 @@
         <v>76.8000030517578</v>
       </c>
       <c r="G515" t="n">
-        <v>68.1217346191406</v>
+        <v>68.1217422485352</v>
       </c>
       <c r="H515" t="n">
         <v>65184</v>
@@ -15362,7 +15362,7 @@
         <v>79.4499969482422</v>
       </c>
       <c r="G517" t="n">
-        <v>70.472282409668</v>
+        <v>70.4722900390625</v>
       </c>
       <c r="H517" t="n">
         <v>80894</v>
@@ -15420,7 +15420,7 @@
         <v>79.5999984741211</v>
       </c>
       <c r="G519" t="n">
-        <v>70.6053314208984</v>
+        <v>70.6053466796875</v>
       </c>
       <c r="H519" t="n">
         <v>39031</v>
@@ -15449,7 +15449,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G520" t="n">
-        <v>70.6940383911133</v>
+        <v>70.6940460205078</v>
       </c>
       <c r="H520" t="n">
         <v>91810</v>
@@ -15507,7 +15507,7 @@
         <v>79.3499984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>70.3835906982422</v>
+        <v>70.3835830688477</v>
       </c>
       <c r="H522" t="n">
         <v>38884</v>
@@ -15623,7 +15623,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G526" t="n">
-        <v>70.1618270874023</v>
+        <v>70.1618423461914</v>
       </c>
       <c r="H526" t="n">
         <v>32335</v>
@@ -15652,7 +15652,7 @@
         <v>79.0500030517578</v>
       </c>
       <c r="G527" t="n">
-        <v>70.1174926757812</v>
+        <v>70.1174850463867</v>
       </c>
       <c r="H527" t="n">
         <v>54775</v>
@@ -15681,7 +15681,7 @@
         <v>79</v>
       </c>
       <c r="G528" t="n">
-        <v>70.0731506347656</v>
+        <v>70.073127746582</v>
       </c>
       <c r="H528" t="n">
         <v>24694</v>
@@ -15710,7 +15710,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409393310547</v>
       </c>
       <c r="H529" t="n">
         <v>38771</v>
@@ -15739,7 +15739,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G530" t="n">
-        <v>70.3392486572266</v>
+        <v>70.3392562866211</v>
       </c>
       <c r="H530" t="n">
         <v>38349</v>
@@ -15797,7 +15797,7 @@
         <v>77.25</v>
       </c>
       <c r="G532" t="n">
-        <v>68.520881652832</v>
+        <v>68.5208969116211</v>
       </c>
       <c r="H532" t="n">
         <v>56789</v>
@@ -15826,7 +15826,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G533" t="n">
-        <v>69.1417770385742</v>
+        <v>69.1417846679688</v>
       </c>
       <c r="H533" t="n">
         <v>79064</v>
@@ -15884,7 +15884,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G535" t="n">
-        <v>67.8999786376953</v>
+        <v>67.8999862670898</v>
       </c>
       <c r="H535" t="n">
         <v>80635</v>
@@ -15913,7 +15913,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G536" t="n">
-        <v>66.8355865478516</v>
+        <v>66.835578918457</v>
       </c>
       <c r="H536" t="n">
         <v>74286</v>
@@ -16058,7 +16058,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G541" t="n">
-        <v>63.1545143127441</v>
+        <v>63.1545219421387</v>
       </c>
       <c r="H541" t="n">
         <v>77364</v>
@@ -16087,7 +16087,7 @@
         <v>71</v>
       </c>
       <c r="G542" t="n">
-        <v>62.9771308898926</v>
+        <v>62.9771270751953</v>
       </c>
       <c r="H542" t="n">
         <v>60963</v>
@@ -16116,7 +16116,7 @@
         <v>70</v>
       </c>
       <c r="G543" t="n">
-        <v>62.0901298522949</v>
+        <v>62.0901260375977</v>
       </c>
       <c r="H543" t="n">
         <v>98122</v>
@@ -16145,7 +16145,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G544" t="n">
-        <v>62.4449272155762</v>
+        <v>62.4449195861816</v>
       </c>
       <c r="H544" t="n">
         <v>107264</v>
@@ -16174,7 +16174,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G545" t="n">
-        <v>63.2432174682617</v>
+        <v>63.243221282959</v>
       </c>
       <c r="H545" t="n">
         <v>109455</v>
@@ -16203,7 +16203,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>62.0014228820801</v>
+        <v>62.0014305114746</v>
       </c>
       <c r="H546" t="n">
         <v>100665</v>
@@ -16261,7 +16261,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G548" t="n">
-        <v>61.9127197265625</v>
+        <v>61.912727355957</v>
       </c>
       <c r="H548" t="n">
         <v>73072</v>
@@ -16319,7 +16319,7 @@
         <v>69.75</v>
       </c>
       <c r="G550" t="n">
-        <v>61.8683853149414</v>
+        <v>61.8683776855469</v>
       </c>
       <c r="H550" t="n">
         <v>130511</v>
@@ -16348,7 +16348,7 @@
         <v>69.4499969482422</v>
       </c>
       <c r="G551" t="n">
-        <v>61.6022720336914</v>
+        <v>61.6022644042969</v>
       </c>
       <c r="H551" t="n">
         <v>113786</v>
@@ -16377,7 +16377,7 @@
         <v>68.5</v>
       </c>
       <c r="G552" t="n">
-        <v>60.7596168518066</v>
+        <v>60.7596206665039</v>
       </c>
       <c r="H552" t="n">
         <v>106726</v>
@@ -16406,7 +16406,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G553" t="n">
-        <v>59.8282661437988</v>
+        <v>59.8282699584961</v>
       </c>
       <c r="H553" t="n">
         <v>167258</v>
@@ -16435,7 +16435,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>58.8969192504883</v>
+        <v>58.896915435791</v>
       </c>
       <c r="H554" t="n">
         <v>163250</v>
@@ -16464,7 +16464,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G555" t="n">
-        <v>58.6308174133301</v>
+        <v>58.6308212280273</v>
       </c>
       <c r="H555" t="n">
         <v>140188</v>
@@ -16522,7 +16522,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>60.6709213256836</v>
+        <v>60.6709327697754</v>
       </c>
       <c r="H557" t="n">
         <v>96155</v>
@@ -16580,7 +16580,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G559" t="n">
-        <v>65.2389907836914</v>
+        <v>65.2389831542969</v>
       </c>
       <c r="H559" t="n">
         <v>157061</v>
@@ -16609,7 +16609,7 @@
         <v>74.75</v>
       </c>
       <c r="G560" t="n">
-        <v>66.3033752441406</v>
+        <v>66.3033828735352</v>
       </c>
       <c r="H560" t="n">
         <v>162714</v>
@@ -16667,7 +16667,7 @@
         <v>74</v>
       </c>
       <c r="G562" t="n">
-        <v>65.6381378173828</v>
+        <v>65.6381301879883</v>
       </c>
       <c r="H562" t="n">
         <v>122457</v>
@@ -16696,7 +16696,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G563" t="n">
-        <v>64.6624298095703</v>
+        <v>64.6624374389648</v>
       </c>
       <c r="H563" t="n">
         <v>148882</v>
@@ -16725,7 +16725,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G564" t="n">
-        <v>64.7954940795898</v>
+        <v>64.7954788208008</v>
       </c>
       <c r="H564" t="n">
         <v>119834</v>
@@ -16783,7 +16783,7 @@
         <v>71.8000030517578</v>
       </c>
       <c r="G566" t="n">
-        <v>63.6867218017578</v>
+        <v>63.6867256164551</v>
       </c>
       <c r="H566" t="n">
         <v>464005</v>
@@ -16841,7 +16841,7 @@
         <v>72.5</v>
       </c>
       <c r="G568" t="n">
-        <v>64.3076171875</v>
+        <v>64.3076400756836</v>
       </c>
       <c r="H568" t="n">
         <v>157755</v>
@@ -16899,7 +16899,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>63.5536651611328</v>
+        <v>63.5536918640137</v>
       </c>
       <c r="H570" t="n">
         <v>72259</v>
@@ -16928,7 +16928,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G571" t="n">
-        <v>62.4005699157715</v>
+        <v>62.4005813598633</v>
       </c>
       <c r="H571" t="n">
         <v>80142</v>
@@ -16986,7 +16986,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>64.6624298095703</v>
+        <v>64.6624374389648</v>
       </c>
       <c r="H573" t="n">
         <v>80627</v>
@@ -17015,7 +17015,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G574" t="n">
-        <v>64.8398361206055</v>
+        <v>64.8398208618164</v>
       </c>
       <c r="H574" t="n">
         <v>52352</v>
@@ -17044,7 +17044,7 @@
         <v>72.5</v>
       </c>
       <c r="G575" t="n">
-        <v>64.3076171875</v>
+        <v>64.3076400756836</v>
       </c>
       <c r="H575" t="n">
         <v>56944</v>
@@ -17073,7 +17073,7 @@
         <v>71.75</v>
       </c>
       <c r="G576" t="n">
-        <v>63.6423835754395</v>
+        <v>63.6423873901367</v>
       </c>
       <c r="H576" t="n">
         <v>105782</v>
@@ -17102,7 +17102,7 @@
         <v>72.25</v>
       </c>
       <c r="G577" t="n">
-        <v>64.0858840942383</v>
+        <v>64.0858688354492</v>
       </c>
       <c r="H577" t="n">
         <v>101002</v>
@@ -17160,7 +17160,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G579" t="n">
-        <v>64.7954940795898</v>
+        <v>64.7954788208008</v>
       </c>
       <c r="H579" t="n">
         <v>99543</v>
@@ -17189,7 +17189,7 @@
         <v>73</v>
       </c>
       <c r="G580" t="n">
-        <v>64.7511215209961</v>
+        <v>64.7511367797852</v>
       </c>
       <c r="H580" t="n">
         <v>91866</v>
@@ -17305,7 +17305,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G584" t="n">
-        <v>66.8355865478516</v>
+        <v>66.835578918457</v>
       </c>
       <c r="H584" t="n">
         <v>90831</v>
@@ -17334,7 +17334,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G585" t="n">
-        <v>67.0129928588867</v>
+        <v>67.0129852294922</v>
       </c>
       <c r="H585" t="n">
         <v>77497</v>
@@ -17363,7 +17363,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>68.8313369750977</v>
+        <v>68.8313293457031</v>
       </c>
       <c r="H586" t="n">
         <v>170948</v>
@@ -17392,7 +17392,7 @@
         <v>74.75</v>
       </c>
       <c r="G587" t="n">
-        <v>66.3033752441406</v>
+        <v>66.3033828735352</v>
       </c>
       <c r="H587" t="n">
         <v>136648</v>
@@ -17450,7 +17450,7 @@
         <v>76.1999969482422</v>
       </c>
       <c r="G589" t="n">
-        <v>67.5895462036133</v>
+        <v>67.5895233154297</v>
       </c>
       <c r="H589" t="n">
         <v>77037</v>
@@ -17479,7 +17479,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409393310547</v>
       </c>
       <c r="H590" t="n">
         <v>130725</v>
@@ -17508,7 +17508,7 @@
         <v>77.3000030517578</v>
       </c>
       <c r="G591" t="n">
-        <v>68.5652465820312</v>
+        <v>68.5652389526367</v>
       </c>
       <c r="H591" t="n">
         <v>67536</v>
@@ -17537,7 +17537,7 @@
         <v>78.1500015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>69.3191909790039</v>
+        <v>69.3191757202148</v>
       </c>
       <c r="H592" t="n">
         <v>49026</v>
@@ -17566,7 +17566,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G593" t="n">
-        <v>69.5409469604492</v>
+        <v>69.5409393310547</v>
       </c>
       <c r="H593" t="n">
         <v>58135</v>
@@ -17624,7 +17624,7 @@
         <v>78.6999969482422</v>
       </c>
       <c r="G595" t="n">
-        <v>69.8070449829102</v>
+        <v>69.8070373535156</v>
       </c>
       <c r="H595" t="n">
         <v>103931</v>
@@ -17653,7 +17653,7 @@
         <v>78</v>
       </c>
       <c r="G596" t="n">
-        <v>69.1861419677734</v>
+        <v>69.1861343383789</v>
       </c>
       <c r="H596" t="n">
         <v>101024</v>
@@ -17682,7 +17682,7 @@
         <v>78.6500015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>69.7626876831055</v>
+        <v>69.7626953125</v>
       </c>
       <c r="H597" t="n">
         <v>54121</v>
@@ -17740,7 +17740,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G599" t="n">
-        <v>69.4522399902344</v>
+        <v>69.4522476196289</v>
       </c>
       <c r="H599" t="n">
         <v>102601</v>
@@ -17769,7 +17769,7 @@
         <v>80.4000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>71.3149490356445</v>
+        <v>71.31494140625</v>
       </c>
       <c r="H600" t="n">
         <v>84989</v>
@@ -17798,7 +17798,7 @@
         <v>81.5500030517578</v>
       </c>
       <c r="G601" t="n">
-        <v>72.3350067138672</v>
+        <v>72.3349990844727</v>
       </c>
       <c r="H601" t="n">
         <v>110542</v>
@@ -17827,7 +17827,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G602" t="n">
-        <v>71.1375427246094</v>
+        <v>71.1375350952148</v>
       </c>
       <c r="H602" t="n">
         <v>87659</v>
@@ -17943,7 +17943,7 @@
         <v>82.6500015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>73.3106994628906</v>
+        <v>73.3107070922852</v>
       </c>
       <c r="H606" t="n">
         <v>90912</v>
@@ -17972,7 +17972,7 @@
         <v>81.4000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>72.2019424438477</v>
+        <v>72.2019500732422</v>
       </c>
       <c r="H607" t="n">
         <v>113958</v>
@@ -18001,7 +18001,7 @@
         <v>81.25</v>
       </c>
       <c r="G608" t="n">
-        <v>72.8293991088867</v>
+        <v>72.8294067382812</v>
       </c>
       <c r="H608" t="n">
         <v>62147</v>
@@ -18088,7 +18088,7 @@
         <v>82.0500030517578</v>
       </c>
       <c r="G611" t="n">
-        <v>73.5464935302734</v>
+        <v>73.5464859008789</v>
       </c>
       <c r="H611" t="n">
         <v>73748</v>
@@ -18117,7 +18117,7 @@
         <v>84.1500015258789</v>
       </c>
       <c r="G612" t="n">
-        <v>75.4288330078125</v>
+        <v>75.4288482666016</v>
       </c>
       <c r="H612" t="n">
         <v>88022</v>
@@ -18146,7 +18146,7 @@
         <v>83</v>
       </c>
       <c r="G613" t="n">
-        <v>74.3980331420898</v>
+        <v>74.3980255126953</v>
       </c>
       <c r="H613" t="n">
         <v>81300</v>
@@ -18175,7 +18175,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G614" t="n">
-        <v>72.7845840454102</v>
+        <v>72.7845687866211</v>
       </c>
       <c r="H614" t="n">
         <v>180565</v>
@@ -18233,7 +18233,7 @@
         <v>82.5999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>74.0394744873047</v>
+        <v>74.0394821166992</v>
       </c>
       <c r="H616" t="n">
         <v>132486</v>
@@ -18262,7 +18262,7 @@
         <v>85.5</v>
       </c>
       <c r="G617" t="n">
-        <v>76.6389389038086</v>
+        <v>76.6389312744141</v>
       </c>
       <c r="H617" t="n">
         <v>117653</v>
@@ -18291,7 +18291,7 @@
         <v>87.5</v>
       </c>
       <c r="G618" t="n">
-        <v>78.4316558837891</v>
+        <v>78.4316635131836</v>
       </c>
       <c r="H618" t="n">
         <v>108629</v>
@@ -18349,7 +18349,7 @@
         <v>88</v>
       </c>
       <c r="G620" t="n">
-        <v>78.8798370361328</v>
+        <v>78.8798446655273</v>
       </c>
       <c r="H620" t="n">
         <v>90647</v>
@@ -18378,7 +18378,7 @@
         <v>88.4000015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>79.2383880615234</v>
+        <v>79.2383804321289</v>
       </c>
       <c r="H621" t="n">
         <v>84613</v>
@@ -18407,7 +18407,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G622" t="n">
-        <v>78.7901992797852</v>
+        <v>78.7902145385742</v>
       </c>
       <c r="H622" t="n">
         <v>109981</v>
@@ -18436,7 +18436,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>79.7313690185547</v>
+        <v>79.7313766479492</v>
       </c>
       <c r="H623" t="n">
         <v>42192</v>
@@ -18465,7 +18465,7 @@
         <v>91</v>
       </c>
       <c r="G624" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H624" t="n">
         <v>130037</v>
@@ -18494,7 +18494,7 @@
         <v>92.4000015258789</v>
       </c>
       <c r="G625" t="n">
-        <v>82.8238372802734</v>
+        <v>82.823844909668</v>
       </c>
       <c r="H625" t="n">
         <v>127436</v>
@@ -18523,7 +18523,7 @@
         <v>93.3499984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>83.6753845214844</v>
+        <v>83.6753692626953</v>
       </c>
       <c r="H626" t="n">
         <v>69385</v>
@@ -18552,7 +18552,7 @@
         <v>93</v>
       </c>
       <c r="G627" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616638183594</v>
       </c>
       <c r="H627" t="n">
         <v>96749</v>
@@ -18610,7 +18610,7 @@
         <v>90.9499969482422</v>
       </c>
       <c r="G629" t="n">
-        <v>81.5241012573242</v>
+        <v>81.5241165161133</v>
       </c>
       <c r="H629" t="n">
         <v>123549</v>
@@ -18639,7 +18639,7 @@
         <v>89.5</v>
       </c>
       <c r="G630" t="n">
-        <v>80.2243804931641</v>
+        <v>80.2243728637695</v>
       </c>
       <c r="H630" t="n">
         <v>107271</v>
@@ -18668,7 +18668,7 @@
         <v>89.1500015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>79.9106674194336</v>
+        <v>79.9106521606445</v>
       </c>
       <c r="H631" t="n">
         <v>85755</v>
@@ -18726,7 +18726,7 @@
         <v>95.0500030517578</v>
       </c>
       <c r="G633" t="n">
-        <v>85.1992034912109</v>
+        <v>85.1991958618164</v>
       </c>
       <c r="H633" t="n">
         <v>89260</v>
@@ -18755,7 +18755,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G634" t="n">
-        <v>85.7818222045898</v>
+        <v>85.7818069458008</v>
       </c>
       <c r="H634" t="n">
         <v>55163</v>
@@ -18784,7 +18784,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G635" t="n">
-        <v>87.2160034179688</v>
+        <v>87.2160186767578</v>
       </c>
       <c r="H635" t="n">
         <v>119198</v>
@@ -18929,7 +18929,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G640" t="n">
-        <v>86.4092788696289</v>
+        <v>86.4092864990234</v>
       </c>
       <c r="H640" t="n">
         <v>48560</v>
@@ -18958,7 +18958,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G641" t="n">
-        <v>85.6473693847656</v>
+        <v>85.6473770141602</v>
       </c>
       <c r="H641" t="n">
         <v>108916</v>
@@ -19016,7 +19016,7 @@
         <v>95.8000030517578</v>
       </c>
       <c r="G643" t="n">
-        <v>85.871467590332</v>
+        <v>85.8714599609375</v>
       </c>
       <c r="H643" t="n">
         <v>46270</v>
@@ -19045,7 +19045,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G644" t="n">
-        <v>85.9611053466797</v>
+        <v>85.9610977172852</v>
       </c>
       <c r="H644" t="n">
         <v>45786</v>
@@ -19074,7 +19074,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G645" t="n">
-        <v>86.1851959228516</v>
+        <v>86.185188293457</v>
       </c>
       <c r="H645" t="n">
         <v>49001</v>
@@ -19103,7 +19103,7 @@
         <v>98.1999969482422</v>
       </c>
       <c r="G646" t="n">
-        <v>88.0227203369141</v>
+        <v>88.0227279663086</v>
       </c>
       <c r="H646" t="n">
         <v>48947</v>
@@ -19161,7 +19161,7 @@
         <v>97.9000015258789</v>
       </c>
       <c r="G648" t="n">
-        <v>87.7538223266602</v>
+        <v>87.7538146972656</v>
       </c>
       <c r="H648" t="n">
         <v>36696</v>
@@ -19248,7 +19248,7 @@
         <v>96.75</v>
       </c>
       <c r="G651" t="n">
-        <v>86.7229995727539</v>
+        <v>86.723014831543</v>
       </c>
       <c r="H651" t="n">
         <v>73196</v>
@@ -19277,7 +19277,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G652" t="n">
-        <v>86.4092788696289</v>
+        <v>86.4092864990234</v>
       </c>
       <c r="H652" t="n">
         <v>50636</v>
@@ -19306,7 +19306,7 @@
         <v>94.5</v>
       </c>
       <c r="G653" t="n">
-        <v>84.7061996459961</v>
+        <v>84.7061920166016</v>
       </c>
       <c r="H653" t="n">
         <v>38381</v>
@@ -19364,7 +19364,7 @@
         <v>94.3499984741211</v>
       </c>
       <c r="G655" t="n">
-        <v>84.5717391967773</v>
+        <v>84.5717315673828</v>
       </c>
       <c r="H655" t="n">
         <v>105068</v>
@@ -19393,7 +19393,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G656" t="n">
-        <v>82.8686447143555</v>
+        <v>82.86865234375</v>
       </c>
       <c r="H656" t="n">
         <v>119477</v>
@@ -19422,7 +19422,7 @@
         <v>93</v>
       </c>
       <c r="G657" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616638183594</v>
       </c>
       <c r="H657" t="n">
         <v>92816</v>
@@ -19451,7 +19451,7 @@
         <v>92.5</v>
       </c>
       <c r="G658" t="n">
-        <v>82.9134750366211</v>
+        <v>82.9134674072266</v>
       </c>
       <c r="H658" t="n">
         <v>79668</v>
@@ -19509,7 +19509,7 @@
         <v>93</v>
       </c>
       <c r="G660" t="n">
-        <v>83.3616485595703</v>
+        <v>83.3616638183594</v>
       </c>
       <c r="H660" t="n">
         <v>69462</v>
@@ -19538,7 +19538,7 @@
         <v>85.0500030517578</v>
       </c>
       <c r="G661" t="n">
-        <v>76.2355880737305</v>
+        <v>76.2355728149414</v>
       </c>
       <c r="H661" t="n">
         <v>377231</v>
@@ -19567,7 +19567,7 @@
         <v>87.3499984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>78.2972106933594</v>
+        <v>78.2972030639648</v>
       </c>
       <c r="H662" t="n">
         <v>169305</v>
@@ -19596,7 +19596,7 @@
         <v>87.5</v>
       </c>
       <c r="G663" t="n">
-        <v>78.4316558837891</v>
+        <v>78.4316635131836</v>
       </c>
       <c r="H663" t="n">
         <v>89704</v>
@@ -19625,7 +19625,7 @@
         <v>88.75</v>
       </c>
       <c r="G664" t="n">
-        <v>79.5521087646484</v>
+        <v>79.5521240234375</v>
       </c>
       <c r="H664" t="n">
         <v>55443</v>
@@ -19683,7 +19683,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G666" t="n">
-        <v>78.9694671630859</v>
+        <v>78.9694747924805</v>
       </c>
       <c r="H666" t="n">
         <v>78905</v>
@@ -19741,7 +19741,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>77.8938446044922</v>
+        <v>77.8938369750977</v>
       </c>
       <c r="H668" t="n">
         <v>42176</v>
@@ -19770,7 +19770,7 @@
         <v>88.1500015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>79.0142974853516</v>
+        <v>79.0143051147461</v>
       </c>
       <c r="H669" t="n">
         <v>48700</v>
@@ -19799,7 +19799,7 @@
         <v>86.5500030517578</v>
       </c>
       <c r="G670" t="n">
-        <v>77.5801239013672</v>
+        <v>77.5801162719727</v>
       </c>
       <c r="H670" t="n">
         <v>73123</v>
@@ -19828,7 +19828,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G671" t="n">
-        <v>77.8490219116211</v>
+        <v>77.8490295410156</v>
       </c>
       <c r="H671" t="n">
         <v>30505</v>
@@ -19857,7 +19857,7 @@
         <v>93.1999969482422</v>
       </c>
       <c r="G672" t="n">
-        <v>83.5409240722656</v>
+        <v>83.5409317016602</v>
       </c>
       <c r="H672" t="n">
         <v>124136</v>
@@ -19886,7 +19886,7 @@
         <v>93.75</v>
       </c>
       <c r="G673" t="n">
-        <v>84.0339202880859</v>
+        <v>84.0339126586914</v>
       </c>
       <c r="H673" t="n">
         <v>153238</v>
@@ -19915,7 +19915,7 @@
         <v>91.5</v>
       </c>
       <c r="G674" t="n">
-        <v>82.0171127319336</v>
+        <v>82.0170974731445</v>
       </c>
       <c r="H674" t="n">
         <v>117256</v>
@@ -19973,7 +19973,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G676" t="n">
-        <v>82.1067276000977</v>
+        <v>82.1067352294922</v>
       </c>
       <c r="H676" t="n">
         <v>68752</v>
@@ -20002,7 +20002,7 @@
         <v>91.1500015258789</v>
       </c>
       <c r="G677" t="n">
-        <v>81.7033767700195</v>
+        <v>81.703369140625</v>
       </c>
       <c r="H677" t="n">
         <v>62973</v>
@@ -20031,7 +20031,7 @@
         <v>91.6999969482422</v>
       </c>
       <c r="G678" t="n">
-        <v>82.1963806152344</v>
+        <v>82.1963653564453</v>
       </c>
       <c r="H678" t="n">
         <v>53095</v>
@@ -20147,7 +20147,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G682" t="n">
-        <v>82.8686447143555</v>
+        <v>82.86865234375</v>
       </c>
       <c r="H682" t="n">
         <v>33661</v>
@@ -20176,7 +20176,7 @@
         <v>92.3499984741211</v>
       </c>
       <c r="G683" t="n">
-        <v>82.7790222167969</v>
+        <v>82.7790145874023</v>
       </c>
       <c r="H683" t="n">
         <v>59883</v>
@@ -20205,7 +20205,7 @@
         <v>89.4000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>80.1347503662109</v>
+        <v>80.1347427368164</v>
       </c>
       <c r="H684" t="n">
         <v>61358</v>
@@ -20234,7 +20234,7 @@
         <v>89.6999969482422</v>
       </c>
       <c r="G685" t="n">
-        <v>80.4036636352539</v>
+        <v>80.4036407470703</v>
       </c>
       <c r="H685" t="n">
         <v>34402</v>
@@ -20263,7 +20263,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>78.7901992797852</v>
+        <v>78.7902145385742</v>
       </c>
       <c r="H686" t="n">
         <v>66724</v>
@@ -20292,7 +20292,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G687" t="n">
-        <v>79.7313690185547</v>
+        <v>79.7313766479492</v>
       </c>
       <c r="H687" t="n">
         <v>31413</v>
@@ -20321,7 +20321,7 @@
         <v>88.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>79.2383880615234</v>
+        <v>79.2383804321289</v>
       </c>
       <c r="H688" t="n">
         <v>25769</v>
@@ -20350,7 +20350,7 @@
         <v>88.6999969482422</v>
       </c>
       <c r="G689" t="n">
-        <v>79.5073013305664</v>
+        <v>79.5072860717773</v>
       </c>
       <c r="H689" t="n">
         <v>31366</v>
@@ -20379,7 +20379,7 @@
         <v>89.5</v>
       </c>
       <c r="G690" t="n">
-        <v>80.2243804931641</v>
+        <v>80.2243728637695</v>
       </c>
       <c r="H690" t="n">
         <v>37780</v>
@@ -20408,7 +20408,7 @@
         <v>89</v>
       </c>
       <c r="G691" t="n">
-        <v>79.7761917114258</v>
+        <v>79.7761993408203</v>
       </c>
       <c r="H691" t="n">
         <v>27813</v>
@@ -20466,7 +20466,7 @@
         <v>93.75</v>
       </c>
       <c r="G693" t="n">
-        <v>84.0339202880859</v>
+        <v>84.0339126586914</v>
       </c>
       <c r="H693" t="n">
         <v>162492</v>
@@ -20495,7 +20495,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>85.9162750244141</v>
+        <v>85.9162826538086</v>
       </c>
       <c r="H694" t="n">
         <v>163806</v>
@@ -20524,7 +20524,7 @@
         <v>97.1999969482422</v>
       </c>
       <c r="G695" t="n">
-        <v>87.1263656616211</v>
+        <v>87.1263732910156</v>
       </c>
       <c r="H695" t="n">
         <v>153783</v>
@@ -20553,7 +20553,7 @@
         <v>92.25</v>
       </c>
       <c r="G696" t="n">
-        <v>82.6893692016602</v>
+        <v>82.6893844604492</v>
       </c>
       <c r="H696" t="n">
         <v>661740</v>
@@ -20582,7 +20582,7 @@
         <v>91.5</v>
       </c>
       <c r="G697" t="n">
-        <v>82.0171127319336</v>
+        <v>82.0170974731445</v>
       </c>
       <c r="H697" t="n">
         <v>122508</v>
@@ -20611,7 +20611,7 @@
         <v>93.0999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>83.4512786865234</v>
+        <v>83.4512939453125</v>
       </c>
       <c r="H698" t="n">
         <v>72943</v>
@@ -20640,7 +20640,7 @@
         <v>92.9499969482422</v>
       </c>
       <c r="G699" t="n">
-        <v>83.3168258666992</v>
+        <v>83.3168411254883</v>
       </c>
       <c r="H699" t="n">
         <v>72035</v>
@@ -20669,7 +20669,7 @@
         <v>91</v>
       </c>
       <c r="G700" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H700" t="n">
         <v>78519</v>
@@ -20756,7 +20756,7 @@
         <v>91</v>
       </c>
       <c r="G703" t="n">
-        <v>81.5689163208008</v>
+        <v>81.5689315795898</v>
       </c>
       <c r="H703" t="n">
         <v>65461</v>
@@ -20814,7 +20814,7 @@
         <v>89.1999969482422</v>
       </c>
       <c r="G705" t="n">
-        <v>79.9554748535156</v>
+        <v>79.9554672241211</v>
       </c>
       <c r="H705" t="n">
         <v>46485</v>
@@ -20843,7 +20843,7 @@
         <v>86.8000030517578</v>
       </c>
       <c r="G706" t="n">
-        <v>77.8042068481445</v>
+        <v>77.8042144775391</v>
       </c>
       <c r="H706" t="n">
         <v>256998</v>
@@ -20930,7 +20930,7 @@
         <v>80.3000030517578</v>
       </c>
       <c r="G709" t="n">
-        <v>71.9778594970703</v>
+        <v>71.9778671264648</v>
       </c>
       <c r="H709" t="n">
         <v>108422</v>
@@ -21017,7 +21017,7 @@
         <v>79.5</v>
       </c>
       <c r="G712" t="n">
-        <v>71.2607650756836</v>
+        <v>71.2607727050781</v>
       </c>
       <c r="H712" t="n">
         <v>87671</v>
@@ -21046,7 +21046,7 @@
         <v>79.8499984741211</v>
       </c>
       <c r="G713" t="n">
-        <v>71.5744934082031</v>
+        <v>71.5744705200195</v>
       </c>
       <c r="H713" t="n">
         <v>121176</v>
@@ -21075,7 +21075,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G714" t="n">
-        <v>73.1431121826172</v>
+        <v>73.1431198120117</v>
       </c>
       <c r="H714" t="n">
         <v>98720</v>
@@ -21104,7 +21104,7 @@
         <v>82</v>
       </c>
       <c r="G715" t="n">
-        <v>73.5016632080078</v>
+        <v>73.5016708374023</v>
       </c>
       <c r="H715" t="n">
         <v>86910</v>
@@ -21162,7 +21162,7 @@
         <v>83.6999969482422</v>
       </c>
       <c r="G717" t="n">
-        <v>75.0254745483398</v>
+        <v>75.0254898071289</v>
       </c>
       <c r="H717" t="n">
         <v>60661</v>
@@ -21191,7 +21191,7 @@
         <v>79.75</v>
       </c>
       <c r="G718" t="n">
-        <v>71.4848556518555</v>
+        <v>71.4848480224609</v>
       </c>
       <c r="H718" t="n">
         <v>148610</v>
@@ -21307,7 +21307,7 @@
         <v>81</v>
       </c>
       <c r="G722" t="n">
-        <v>72.6053085327148</v>
+        <v>72.6053009033203</v>
       </c>
       <c r="H722" t="n">
         <v>74067</v>
@@ -21365,7 +21365,7 @@
         <v>83.8000030517578</v>
       </c>
       <c r="G724" t="n">
-        <v>75.115119934082</v>
+        <v>75.1151275634766</v>
       </c>
       <c r="H724" t="n">
         <v>192896</v>
@@ -21394,7 +21394,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G725" t="n">
-        <v>77.8938446044922</v>
+        <v>77.8938369750977</v>
       </c>
       <c r="H725" t="n">
         <v>101199</v>
@@ -21423,7 +21423,7 @@
         <v>86.5500030517578</v>
       </c>
       <c r="G726" t="n">
-        <v>77.5801239013672</v>
+        <v>77.5801162719727</v>
       </c>
       <c r="H726" t="n">
         <v>89277</v>
@@ -21452,7 +21452,7 @@
         <v>87.5500030517578</v>
       </c>
       <c r="G727" t="n">
-        <v>78.4764785766602</v>
+        <v>78.4764709472656</v>
       </c>
       <c r="H727" t="n">
         <v>78626</v>
@@ -21481,7 +21481,7 @@
         <v>86.8499984741211</v>
       </c>
       <c r="G728" t="n">
-        <v>77.8490219116211</v>
+        <v>77.8490295410156</v>
       </c>
       <c r="H728" t="n">
         <v>95580</v>
@@ -21510,7 +21510,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G729" t="n">
-        <v>73.1431121826172</v>
+        <v>73.1431198120117</v>
       </c>
       <c r="H729" t="n">
         <v>248355</v>
@@ -21539,7 +21539,7 @@
         <v>82.5</v>
       </c>
       <c r="G730" t="n">
-        <v>73.9498596191406</v>
+        <v>73.9498519897461</v>
       </c>
       <c r="H730" t="n">
         <v>122029</v>
@@ -21655,7 +21655,7 @@
         <v>81.5999984741211</v>
       </c>
       <c r="G734" t="n">
-        <v>73.1431121826172</v>
+        <v>73.1431198120117</v>
       </c>
       <c r="H734" t="n">
         <v>49172</v>
@@ -21713,7 +21713,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G736" t="n">
-        <v>72.7845840454102</v>
+        <v>72.7845687866211</v>
       </c>
       <c r="H736" t="n">
         <v>43768</v>
@@ -21742,7 +21742,7 @@
         <v>81</v>
       </c>
       <c r="G737" t="n">
-        <v>72.6053085327148</v>
+        <v>72.6053009033203</v>
       </c>
       <c r="H737" t="n">
         <v>90532</v>
@@ -21771,7 +21771,7 @@
         <v>77.25</v>
       </c>
       <c r="G738" t="n">
-        <v>69.2439498901367</v>
+        <v>69.2439575195312</v>
       </c>
       <c r="H738" t="n">
         <v>126656</v>
@@ -21887,7 +21887,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G742" t="n">
-        <v>71.7537689208984</v>
+        <v>71.7537612915039</v>
       </c>
       <c r="H742" t="n">
         <v>109282</v>
@@ -21916,7 +21916,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G743" t="n">
-        <v>70.9918670654297</v>
+        <v>70.9918594360352</v>
       </c>
       <c r="H743" t="n">
         <v>95288</v>
@@ -21974,7 +21974,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G745" t="n">
-        <v>69.5576705932617</v>
+        <v>69.5576553344727</v>
       </c>
       <c r="H745" t="n">
         <v>105516</v>
@@ -22032,7 +22032,7 @@
         <v>75</v>
       </c>
       <c r="G747" t="n">
-        <v>67.2271347045898</v>
+        <v>67.2271423339844</v>
       </c>
       <c r="H747" t="n">
         <v>640044</v>
@@ -22061,7 +22061,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>67.5856781005859</v>
+        <v>67.5856704711914</v>
       </c>
       <c r="H748" t="n">
         <v>271330</v>
@@ -22090,7 +22090,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>70.0058517456055</v>
+        <v>70.005859375</v>
       </c>
       <c r="H749" t="n">
         <v>206228</v>
@@ -22119,7 +22119,7 @@
         <v>73.1500015258789</v>
       </c>
       <c r="G750" t="n">
-        <v>65.5688705444336</v>
+        <v>65.5688629150391</v>
       </c>
       <c r="H750" t="n">
         <v>439461</v>
@@ -22206,7 +22206,7 @@
         <v>72.9499969482422</v>
       </c>
       <c r="G753" t="n">
-        <v>65.3895797729492</v>
+        <v>65.3895950317383</v>
       </c>
       <c r="H753" t="n">
         <v>81159</v>
@@ -22235,7 +22235,7 @@
         <v>74</v>
       </c>
       <c r="G754" t="n">
-        <v>66.3307800292969</v>
+        <v>66.3307723999023</v>
       </c>
       <c r="H754" t="n">
         <v>138111</v>
@@ -22264,7 +22264,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G755" t="n">
-        <v>65.6136703491211</v>
+        <v>65.6136856079102</v>
       </c>
       <c r="H755" t="n">
         <v>136727</v>
@@ -22322,7 +22322,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G757" t="n">
-        <v>62.8349533081055</v>
+        <v>62.8349609375</v>
       </c>
       <c r="H757" t="n">
         <v>168734</v>
@@ -22351,7 +22351,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G758" t="n">
-        <v>63.2383422851562</v>
+        <v>63.2383308410645</v>
       </c>
       <c r="H758" t="n">
         <v>101363</v>
@@ -22380,7 +22380,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>63.103874206543</v>
+        <v>63.1038665771484</v>
       </c>
       <c r="H759" t="n">
         <v>136498</v>
@@ -22409,7 +22409,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G760" t="n">
-        <v>63.5968589782715</v>
+        <v>63.5968704223633</v>
       </c>
       <c r="H760" t="n">
         <v>142583</v>
@@ -22467,7 +22467,7 @@
         <v>69.3499984741211</v>
       </c>
       <c r="G762" t="n">
-        <v>63.746452331543</v>
+        <v>63.7464485168457</v>
       </c>
       <c r="H762" t="n">
         <v>134941</v>
@@ -22496,7 +22496,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G763" t="n">
-        <v>64.9873580932617</v>
+        <v>64.9873657226562</v>
       </c>
       <c r="H763" t="n">
         <v>53669</v>
@@ -22525,7 +22525,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G764" t="n">
-        <v>65.4469604492188</v>
+        <v>65.4469680786133</v>
       </c>
       <c r="H764" t="n">
         <v>92132</v>
@@ -22554,7 +22554,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G765" t="n">
-        <v>65.0792999267578</v>
+        <v>65.0792922973633</v>
       </c>
       <c r="H765" t="n">
         <v>195745</v>
@@ -22670,7 +22670,7 @@
         <v>74.3499984741211</v>
       </c>
       <c r="G769" t="n">
-        <v>68.3424453735352</v>
+        <v>68.3424530029297</v>
       </c>
       <c r="H769" t="n">
         <v>129576</v>
@@ -22699,7 +22699,7 @@
         <v>75.5500030517578</v>
       </c>
       <c r="G770" t="n">
-        <v>69.4454956054688</v>
+        <v>69.4454803466797</v>
       </c>
       <c r="H770" t="n">
         <v>69821</v>
@@ -22728,7 +22728,7 @@
         <v>74.9000015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>68.8480072021484</v>
+        <v>68.8479995727539</v>
       </c>
       <c r="H771" t="n">
         <v>58124</v>
@@ -22786,7 +22786,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G773" t="n">
-        <v>69.5833587646484</v>
+        <v>69.583366394043</v>
       </c>
       <c r="H773" t="n">
         <v>72777</v>
@@ -22815,7 +22815,7 @@
         <v>77.5</v>
       </c>
       <c r="G774" t="n">
-        <v>71.2379302978516</v>
+        <v>71.237922668457</v>
       </c>
       <c r="H774" t="n">
         <v>75923</v>
@@ -22844,7 +22844,7 @@
         <v>78</v>
       </c>
       <c r="G775" t="n">
-        <v>71.6975326538086</v>
+        <v>71.6975250244141</v>
       </c>
       <c r="H775" t="n">
         <v>84212</v>
@@ -22873,7 +22873,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G776" t="n">
-        <v>73.8576431274414</v>
+        <v>73.8576354980469</v>
       </c>
       <c r="H776" t="n">
         <v>145820</v>
@@ -22902,7 +22902,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G777" t="n">
-        <v>73.7197494506836</v>
+        <v>73.7197647094727</v>
       </c>
       <c r="H777" t="n">
         <v>75557</v>
@@ -22931,7 +22931,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G778" t="n">
-        <v>73.5818939208984</v>
+        <v>73.5818786621094</v>
       </c>
       <c r="H778" t="n">
         <v>152719</v>
@@ -22960,7 +22960,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G779" t="n">
-        <v>73.2142028808594</v>
+        <v>73.2142105102539</v>
       </c>
       <c r="H779" t="n">
         <v>139876</v>
@@ -22989,7 +22989,7 @@
         <v>80.1500015258789</v>
       </c>
       <c r="G780" t="n">
-        <v>73.6738128662109</v>
+        <v>73.6738052368164</v>
       </c>
       <c r="H780" t="n">
         <v>67535</v>
@@ -23018,7 +23018,7 @@
         <v>80.4000015258789</v>
       </c>
       <c r="G781" t="n">
-        <v>73.9036178588867</v>
+        <v>73.9035949707031</v>
       </c>
       <c r="H781" t="n">
         <v>72255</v>
@@ -23047,7 +23047,7 @@
         <v>79.75</v>
       </c>
       <c r="G782" t="n">
-        <v>73.3061218261719</v>
+        <v>73.3061141967773</v>
       </c>
       <c r="H782" t="n">
         <v>62554</v>
@@ -23076,7 +23076,7 @@
         <v>81.75</v>
       </c>
       <c r="G783" t="n">
-        <v>75.1445236206055</v>
+        <v>75.1445388793945</v>
       </c>
       <c r="H783" t="n">
         <v>104802</v>
@@ -23105,7 +23105,7 @@
         <v>81.3000030517578</v>
       </c>
       <c r="G784" t="n">
-        <v>74.7308959960938</v>
+        <v>74.7308807373047</v>
       </c>
       <c r="H784" t="n">
         <v>123024</v>
@@ -23134,7 +23134,7 @@
         <v>79.9499969482422</v>
       </c>
       <c r="G785" t="n">
-        <v>73.4899520874023</v>
+        <v>73.4899597167969</v>
       </c>
       <c r="H785" t="n">
         <v>91066</v>
@@ -23163,7 +23163,7 @@
         <v>82.0999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>75.4662322998047</v>
+        <v>75.4662399291992</v>
       </c>
       <c r="H786" t="n">
         <v>190749</v>
@@ -23192,7 +23192,7 @@
         <v>82.1999969482422</v>
       </c>
       <c r="G787" t="n">
-        <v>75.5581665039062</v>
+        <v>75.5581588745117</v>
       </c>
       <c r="H787" t="n">
         <v>150444</v>
@@ -23221,7 +23221,7 @@
         <v>84.0500030517578</v>
       </c>
       <c r="G788" t="n">
-        <v>77.2586975097656</v>
+        <v>77.2586898803711</v>
       </c>
       <c r="H788" t="n">
         <v>88125</v>
@@ -23250,7 +23250,7 @@
         <v>83.9499969482422</v>
       </c>
       <c r="G789" t="n">
-        <v>77.1667404174805</v>
+        <v>77.1667556762695</v>
       </c>
       <c r="H789" t="n">
         <v>89975</v>
@@ -23308,7 +23308,7 @@
         <v>84.6500015258789</v>
       </c>
       <c r="G791" t="n">
-        <v>77.8102111816406</v>
+        <v>77.8102035522461</v>
       </c>
       <c r="H791" t="n">
         <v>92807</v>
@@ -23337,7 +23337,7 @@
         <v>85</v>
       </c>
       <c r="G792" t="n">
-        <v>78.1319122314453</v>
+        <v>78.1319198608398</v>
       </c>
       <c r="H792" t="n">
         <v>60802</v>
@@ -23366,7 +23366,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G793" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642211914062</v>
       </c>
       <c r="H793" t="n">
         <v>114380</v>
@@ -23395,7 +23395,7 @@
         <v>85</v>
       </c>
       <c r="G794" t="n">
-        <v>78.1319122314453</v>
+        <v>78.1319198608398</v>
       </c>
       <c r="H794" t="n">
         <v>83750</v>
@@ -23424,7 +23424,7 @@
         <v>84.8000030517578</v>
       </c>
       <c r="G795" t="n">
-        <v>77.9480972290039</v>
+        <v>77.9480743408203</v>
       </c>
       <c r="H795" t="n">
         <v>81092</v>
@@ -23453,7 +23453,7 @@
         <v>85.1999969482422</v>
       </c>
       <c r="G796" t="n">
-        <v>78.3157501220703</v>
+        <v>78.3157577514648</v>
       </c>
       <c r="H796" t="n">
         <v>100025</v>
@@ -23482,7 +23482,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G797" t="n">
-        <v>78.5455474853516</v>
+        <v>78.5455551147461</v>
       </c>
       <c r="H797" t="n">
         <v>105022</v>
@@ -23511,7 +23511,7 @@
         <v>84.4000015258789</v>
       </c>
       <c r="G798" t="n">
-        <v>77.5804061889648</v>
+        <v>77.5803985595703</v>
       </c>
       <c r="H798" t="n">
         <v>86893</v>
@@ -23540,7 +23540,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G799" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642211914062</v>
       </c>
       <c r="H799" t="n">
         <v>72446</v>
@@ -23627,7 +23627,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G802" t="n">
-        <v>77.7642440795898</v>
+        <v>77.7642211914062</v>
       </c>
       <c r="H802" t="n">
         <v>78894</v>
@@ -23656,7 +23656,7 @@
         <v>86.1500015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>79.1890106201172</v>
+        <v>79.1889953613281</v>
       </c>
       <c r="H803" t="n">
         <v>109844</v>
@@ -23685,7 +23685,7 @@
         <v>85.75</v>
       </c>
       <c r="G804" t="n">
-        <v>78.8213119506836</v>
+        <v>78.8213272094727</v>
       </c>
       <c r="H804" t="n">
         <v>66682</v>
@@ -23714,7 +23714,7 @@
         <v>86.25</v>
       </c>
       <c r="G805" t="n">
-        <v>79.2809143066406</v>
+        <v>79.2809066772461</v>
       </c>
       <c r="H805" t="n">
         <v>103167</v>
@@ -23743,7 +23743,7 @@
         <v>87.5999984741211</v>
       </c>
       <c r="G806" t="n">
-        <v>80.5218276977539</v>
+        <v>80.5218353271484</v>
       </c>
       <c r="H806" t="n">
         <v>74388</v>
@@ -23772,7 +23772,7 @@
         <v>87.25</v>
       </c>
       <c r="G807" t="n">
-        <v>80.2001037597656</v>
+        <v>80.2001190185547</v>
       </c>
       <c r="H807" t="n">
         <v>71430</v>
@@ -23801,7 +23801,7 @@
         <v>86.9000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>79.8784103393555</v>
+        <v>79.8783874511719</v>
       </c>
       <c r="H808" t="n">
         <v>109186</v>
@@ -23975,7 +23975,7 @@
         <v>86.6500015258789</v>
       </c>
       <c r="G814" t="n">
-        <v>79.6486053466797</v>
+        <v>79.6485900878906</v>
       </c>
       <c r="H814" t="n">
         <v>92493</v>
@@ -24004,7 +24004,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G815" t="n">
-        <v>78.8672714233398</v>
+        <v>78.8672790527344</v>
       </c>
       <c r="H815" t="n">
         <v>202818</v>
@@ -24033,7 +24033,7 @@
         <v>85.4000015258789</v>
       </c>
       <c r="G816" t="n">
-        <v>78.4996032714844</v>
+        <v>78.4995956420898</v>
       </c>
       <c r="H816" t="n">
         <v>239707</v>
@@ -24062,7 +24062,7 @@
         <v>86.6500015258789</v>
       </c>
       <c r="G817" t="n">
-        <v>79.6486053466797</v>
+        <v>79.6485900878906</v>
       </c>
       <c r="H817" t="n">
         <v>154275</v>
@@ -24091,7 +24091,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G818" t="n">
-        <v>80.7516403198242</v>
+        <v>80.7516326904297</v>
       </c>
       <c r="H818" t="n">
         <v>157322</v>
@@ -24120,7 +24120,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G819" t="n">
-        <v>80.9814376831055</v>
+        <v>80.9814300537109</v>
       </c>
       <c r="H819" t="n">
         <v>135102</v>
@@ -24149,7 +24149,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G820" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4870071411133</v>
       </c>
       <c r="H820" t="n">
         <v>70750</v>
@@ -24236,7 +24236,7 @@
         <v>89.3499984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>82.1304397583008</v>
+        <v>82.1304321289062</v>
       </c>
       <c r="H823" t="n">
         <v>108948</v>
@@ -24294,7 +24294,7 @@
         <v>89.75</v>
       </c>
       <c r="G825" t="n">
-        <v>82.4981155395508</v>
+        <v>82.4981231689453</v>
       </c>
       <c r="H825" t="n">
         <v>86069</v>
@@ -24352,7 +24352,7 @@
         <v>90.5500030517578</v>
       </c>
       <c r="G827" t="n">
-        <v>83.2334823608398</v>
+        <v>83.2334747314453</v>
       </c>
       <c r="H827" t="n">
         <v>113522</v>
@@ -24381,7 +24381,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G828" t="n">
-        <v>84.1986389160156</v>
+        <v>84.1986236572266</v>
       </c>
       <c r="H828" t="n">
         <v>90311</v>
@@ -24410,7 +24410,7 @@
         <v>92.75</v>
       </c>
       <c r="G829" t="n">
-        <v>85.2557144165039</v>
+        <v>85.2557220458984</v>
       </c>
       <c r="H829" t="n">
         <v>126038</v>
@@ -24497,7 +24497,7 @@
         <v>91.6500015258789</v>
       </c>
       <c r="G832" t="n">
-        <v>84.2446060180664</v>
+        <v>84.2445983886719</v>
       </c>
       <c r="H832" t="n">
         <v>119763</v>
@@ -24555,7 +24555,7 @@
         <v>91</v>
       </c>
       <c r="G834" t="n">
-        <v>83.647102355957</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H834" t="n">
         <v>103560</v>
@@ -24584,7 +24584,7 @@
         <v>91</v>
       </c>
       <c r="G835" t="n">
-        <v>83.647102355957</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H835" t="n">
         <v>103343</v>
@@ -24613,7 +24613,7 @@
         <v>90.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>83.5551910400391</v>
+        <v>83.5551986694336</v>
       </c>
       <c r="H836" t="n">
         <v>121451</v>
@@ -24671,7 +24671,7 @@
         <v>91</v>
       </c>
       <c r="G838" t="n">
-        <v>83.647102355957</v>
+        <v>83.6471176147461</v>
       </c>
       <c r="H838" t="n">
         <v>74992</v>
@@ -24700,7 +24700,7 @@
         <v>87.6500015258789</v>
       </c>
       <c r="G839" t="n">
-        <v>80.5678024291992</v>
+        <v>80.5677947998047</v>
       </c>
       <c r="H839" t="n">
         <v>196520</v>
@@ -24787,7 +24787,7 @@
         <v>85.75</v>
       </c>
       <c r="G842" t="n">
-        <v>78.8213119506836</v>
+        <v>78.8213272094727</v>
       </c>
       <c r="H842" t="n">
         <v>129436</v>
@@ -24816,7 +24816,7 @@
         <v>85.1500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>78.2698059082031</v>
+        <v>78.2697982788086</v>
       </c>
       <c r="H843" t="n">
         <v>80115</v>
@@ -24845,7 +24845,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G844" t="n">
-        <v>78.7753601074219</v>
+        <v>78.7753524780273</v>
       </c>
       <c r="H844" t="n">
         <v>127253</v>
@@ -24874,7 +24874,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>80.0622253417969</v>
+        <v>80.0622329711914</v>
       </c>
       <c r="H845" t="n">
         <v>103640</v>
@@ -24903,7 +24903,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G846" t="n">
-        <v>80.0622253417969</v>
+        <v>80.0622329711914</v>
       </c>
       <c r="H846" t="n">
         <v>116286</v>
@@ -24932,7 +24932,7 @@
         <v>87.0999984741211</v>
       </c>
       <c r="G847" t="n">
-        <v>80.0622253417969</v>
+        <v>80.0622329711914</v>
       </c>
       <c r="H847" t="n">
         <v>87670</v>
@@ -24961,7 +24961,7 @@
         <v>88.6500015258789</v>
       </c>
       <c r="G848" t="n">
-        <v>81.4869995117188</v>
+        <v>81.4870071411133</v>
       </c>
       <c r="H848" t="n">
         <v>104300</v>
@@ -25048,7 +25048,7 @@
         <v>89.9000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>82.6360015869141</v>
+        <v>82.6359939575195</v>
       </c>
       <c r="H851" t="n">
         <v>95610</v>
@@ -25077,7 +25077,7 @@
         <v>90</v>
       </c>
       <c r="G852" t="n">
-        <v>82.7279205322266</v>
+        <v>82.7279052734375</v>
       </c>
       <c r="H852" t="n">
         <v>97652</v>
@@ -25193,7 +25193,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G856" t="n">
-        <v>87.8294830322266</v>
+        <v>87.829475402832</v>
       </c>
       <c r="H856" t="n">
         <v>153602</v>
@@ -25222,7 +25222,7 @@
         <v>97.4499969482422</v>
       </c>
       <c r="G857" t="n">
-        <v>89.5759353637695</v>
+        <v>89.5759429931641</v>
       </c>
       <c r="H857" t="n">
         <v>106349</v>
@@ -25338,7 +25338,7 @@
         <v>97.5</v>
       </c>
       <c r="G861" t="n">
-        <v>90.4577560424805</v>
+        <v>90.457763671875</v>
       </c>
       <c r="H861" t="n">
         <v>91444</v>
@@ -25367,7 +25367,7 @@
         <v>96.8499984741211</v>
       </c>
       <c r="G862" t="n">
-        <v>89.8547058105469</v>
+        <v>89.8547134399414</v>
       </c>
       <c r="H862" t="n">
         <v>74155</v>
@@ -25425,7 +25425,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>88.9269409179688</v>
+        <v>88.9269332885742</v>
       </c>
       <c r="H864" t="n">
         <v>34520</v>
@@ -25512,7 +25512,7 @@
         <v>93.9499969482422</v>
       </c>
       <c r="G867" t="n">
-        <v>87.1641540527344</v>
+        <v>87.1641693115234</v>
       </c>
       <c r="H867" t="n">
         <v>57035</v>
@@ -25570,7 +25570,7 @@
         <v>95.3000030517578</v>
       </c>
       <c r="G869" t="n">
-        <v>88.4166641235352</v>
+        <v>88.4166717529297</v>
       </c>
       <c r="H869" t="n">
         <v>177997</v>
@@ -25599,7 +25599,7 @@
         <v>96.6500015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>89.6691665649414</v>
+        <v>89.6691589355469</v>
       </c>
       <c r="H870" t="n">
         <v>197967</v>
@@ -25686,7 +25686,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>93.7977447509766</v>
+        <v>93.797737121582</v>
       </c>
       <c r="H873" t="n">
         <v>182843</v>
@@ -25715,7 +25715,7 @@
         <v>102</v>
       </c>
       <c r="G874" t="n">
-        <v>94.6327285766602</v>
+        <v>94.6327362060547</v>
       </c>
       <c r="H874" t="n">
         <v>88957</v>
@@ -25773,7 +25773,7 @@
         <v>99.25</v>
       </c>
       <c r="G876" t="n">
-        <v>92.0813674926758</v>
+        <v>92.0813598632812</v>
       </c>
       <c r="H876" t="n">
         <v>165579</v>
@@ -25831,7 +25831,7 @@
         <v>103.5</v>
       </c>
       <c r="G878" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H878" t="n">
         <v>247114</v>
@@ -25860,7 +25860,7 @@
         <v>105.099998474121</v>
       </c>
       <c r="G879" t="n">
-        <v>97.5088195800781</v>
+        <v>97.5088272094727</v>
       </c>
       <c r="H879" t="n">
         <v>246638</v>
@@ -25889,7 +25889,7 @@
         <v>107.199996948242</v>
       </c>
       <c r="G880" t="n">
-        <v>99.4571380615234</v>
+        <v>99.457145690918</v>
       </c>
       <c r="H880" t="n">
         <v>204977</v>
@@ -25947,7 +25947,7 @@
         <v>105</v>
       </c>
       <c r="G882" t="n">
-        <v>97.4160537719727</v>
+        <v>97.4160461425781</v>
       </c>
       <c r="H882" t="n">
         <v>115633</v>
@@ -25976,7 +25976,7 @@
         <v>102.5</v>
       </c>
       <c r="G883" t="n">
-        <v>95.0966262817383</v>
+        <v>95.0966110229492</v>
       </c>
       <c r="H883" t="n">
         <v>256349</v>
@@ -26005,7 +26005,7 @@
         <v>103.300003051758</v>
       </c>
       <c r="G884" t="n">
-        <v>95.8388442993164</v>
+        <v>95.8388290405273</v>
       </c>
       <c r="H884" t="n">
         <v>90227</v>
@@ -26034,7 +26034,7 @@
         <v>102</v>
       </c>
       <c r="G885" t="n">
-        <v>94.6327285766602</v>
+        <v>94.6327362060547</v>
       </c>
       <c r="H885" t="n">
         <v>62348</v>
@@ -26063,7 +26063,7 @@
         <v>101.5</v>
       </c>
       <c r="G886" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H886" t="n">
         <v>95822</v>
@@ -26121,7 +26121,7 @@
         <v>102.099998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>94.7255020141602</v>
+        <v>94.7255096435547</v>
       </c>
       <c r="H888" t="n">
         <v>120137</v>
@@ -26179,7 +26179,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G890" t="n">
-        <v>95.1893997192383</v>
+        <v>95.1893844604492</v>
       </c>
       <c r="H890" t="n">
         <v>59553</v>
@@ -26237,7 +26237,7 @@
         <v>104</v>
       </c>
       <c r="G892" t="n">
-        <v>96.4882736206055</v>
+        <v>96.48828125</v>
       </c>
       <c r="H892" t="n">
         <v>83587</v>
@@ -26295,7 +26295,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G894" t="n">
-        <v>96.3955078125</v>
+        <v>96.3955001831055</v>
       </c>
       <c r="H894" t="n">
         <v>59104</v>
@@ -26324,7 +26324,7 @@
         <v>102.800003051758</v>
       </c>
       <c r="G895" t="n">
-        <v>95.3749618530273</v>
+        <v>95.3749542236328</v>
       </c>
       <c r="H895" t="n">
         <v>100438</v>
@@ -26382,7 +26382,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G897" t="n">
-        <v>95.7460479736328</v>
+        <v>95.7460556030273</v>
       </c>
       <c r="H897" t="n">
         <v>98550</v>
@@ -26527,7 +26527,7 @@
         <v>102.5</v>
       </c>
       <c r="G902" t="n">
-        <v>95.0966262817383</v>
+        <v>95.0966110229492</v>
       </c>
       <c r="H902" t="n">
         <v>60591</v>
@@ -26614,7 +26614,7 @@
         <v>102</v>
       </c>
       <c r="G905" t="n">
-        <v>94.6327285766602</v>
+        <v>94.6327362060547</v>
       </c>
       <c r="H905" t="n">
         <v>60880</v>
@@ -26643,7 +26643,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G906" t="n">
-        <v>94.0760726928711</v>
+        <v>94.0760803222656</v>
       </c>
       <c r="H906" t="n">
         <v>114741</v>
@@ -26730,7 +26730,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>95.0038528442383</v>
+        <v>95.0038375854492</v>
       </c>
       <c r="H909" t="n">
         <v>87642</v>
@@ -26788,7 +26788,7 @@
         <v>105</v>
       </c>
       <c r="G911" t="n">
-        <v>97.4160537719727</v>
+        <v>97.4160461425781</v>
       </c>
       <c r="H911" t="n">
         <v>150127</v>
@@ -26846,7 +26846,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>98.6221618652344</v>
+        <v>98.6221542358398</v>
       </c>
       <c r="H913" t="n">
         <v>135800</v>
@@ -26875,7 +26875,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>96.3955078125</v>
+        <v>96.3955001831055</v>
       </c>
       <c r="H914" t="n">
         <v>137806</v>
@@ -26904,7 +26904,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G915" t="n">
-        <v>97.3232803344727</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H915" t="n">
         <v>120067</v>
@@ -26933,7 +26933,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G916" t="n">
-        <v>98.6221618652344</v>
+        <v>98.6221542358398</v>
       </c>
       <c r="H916" t="n">
         <v>122708</v>
@@ -27020,7 +27020,7 @@
         <v>105.900001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>98.2510604858398</v>
+        <v>98.2510528564453</v>
       </c>
       <c r="H919" t="n">
         <v>51100</v>
@@ -27049,7 +27049,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G920" t="n">
-        <v>98.0654754638672</v>
+        <v>98.0654983520508</v>
       </c>
       <c r="H920" t="n">
         <v>97185</v>
@@ -27078,7 +27078,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G921" t="n">
-        <v>96.5810623168945</v>
+        <v>96.5810546875</v>
       </c>
       <c r="H921" t="n">
         <v>93618</v>
@@ -27136,7 +27136,7 @@
         <v>108.300003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>100.47770690918</v>
+        <v>100.477699279785</v>
       </c>
       <c r="H923" t="n">
         <v>125584</v>
@@ -27165,7 +27165,7 @@
         <v>108.099998474121</v>
       </c>
       <c r="G924" t="n">
-        <v>100.292129516602</v>
+        <v>100.292144775391</v>
       </c>
       <c r="H924" t="n">
         <v>67236</v>
@@ -27194,7 +27194,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G925" t="n">
-        <v>101.869361877441</v>
+        <v>101.869354248047</v>
       </c>
       <c r="H925" t="n">
         <v>82352</v>
@@ -27223,7 +27223,7 @@
         <v>109</v>
       </c>
       <c r="G926" t="n">
-        <v>101.127128601074</v>
+        <v>101.127136230469</v>
       </c>
       <c r="H926" t="n">
         <v>61146</v>
@@ -27252,7 +27252,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G927" t="n">
-        <v>98.1582717895508</v>
+        <v>98.1582794189453</v>
       </c>
       <c r="H927" t="n">
         <v>215221</v>
@@ -27281,7 +27281,7 @@
         <v>107</v>
       </c>
       <c r="G928" t="n">
-        <v>99.271598815918</v>
+        <v>99.2715911865234</v>
       </c>
       <c r="H928" t="n">
         <v>134579</v>
@@ -27368,7 +27368,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G931" t="n">
-        <v>99.8282623291016</v>
+        <v>99.8282470703125</v>
       </c>
       <c r="H931" t="n">
         <v>120053</v>
@@ -27455,7 +27455,7 @@
         <v>109.5</v>
       </c>
       <c r="G934" t="n">
-        <v>101.591018676758</v>
+        <v>101.591026306152</v>
       </c>
       <c r="H934" t="n">
         <v>76800</v>
@@ -27513,7 +27513,7 @@
         <v>107</v>
       </c>
       <c r="G936" t="n">
-        <v>99.271598815918</v>
+        <v>99.2715911865234</v>
       </c>
       <c r="H936" t="n">
         <v>223566</v>
@@ -27629,7 +27629,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G940" t="n">
-        <v>94.9110717773438</v>
+        <v>94.9110794067383</v>
       </c>
       <c r="H940" t="n">
         <v>272397</v>
@@ -27687,7 +27687,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G942" t="n">
-        <v>95.0038528442383</v>
+        <v>95.0038375854492</v>
       </c>
       <c r="H942" t="n">
         <v>140833</v>
@@ -27716,7 +27716,7 @@
         <v>101.5</v>
       </c>
       <c r="G943" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H943" t="n">
         <v>110311</v>
@@ -27745,7 +27745,7 @@
         <v>102.599998474121</v>
       </c>
       <c r="G944" t="n">
-        <v>95.1893997192383</v>
+        <v>95.1893844604492</v>
       </c>
       <c r="H944" t="n">
         <v>137051</v>
@@ -27774,7 +27774,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G945" t="n">
-        <v>96.3955078125</v>
+        <v>96.3955001831055</v>
       </c>
       <c r="H945" t="n">
         <v>103885</v>
@@ -27832,7 +27832,7 @@
         <v>104.800003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>97.2304992675781</v>
+        <v>97.2304916381836</v>
       </c>
       <c r="H947" t="n">
         <v>105910</v>
@@ -27919,7 +27919,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G950" t="n">
-        <v>97.3232803344727</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H950" t="n">
         <v>121403</v>
@@ -27948,7 +27948,7 @@
         <v>106.099998474121</v>
       </c>
       <c r="G951" t="n">
-        <v>98.4365997314453</v>
+        <v>98.4365921020508</v>
       </c>
       <c r="H951" t="n">
         <v>72020</v>
@@ -28006,7 +28006,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G953" t="n">
-        <v>98.9932556152344</v>
+        <v>98.9932632446289</v>
       </c>
       <c r="H953" t="n">
         <v>107796</v>
@@ -28064,7 +28064,7 @@
         <v>101.5</v>
       </c>
       <c r="G955" t="n">
-        <v>94.1688461303711</v>
+        <v>94.1688537597656</v>
       </c>
       <c r="H955" t="n">
         <v>241544</v>
@@ -28122,7 +28122,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G957" t="n">
-        <v>98.9932556152344</v>
+        <v>98.9932632446289</v>
       </c>
       <c r="H957" t="n">
         <v>166516</v>
@@ -28238,7 +28238,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G961" t="n">
-        <v>92.1277618408203</v>
+        <v>92.1277542114258</v>
       </c>
       <c r="H961" t="n">
         <v>113845</v>
@@ -28267,7 +28267,7 @@
         <v>99.25</v>
       </c>
       <c r="G962" t="n">
-        <v>92.0813674926758</v>
+        <v>92.0813598632812</v>
       </c>
       <c r="H962" t="n">
         <v>141849</v>
@@ -28296,7 +28296,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G963" t="n">
-        <v>92.3596954345703</v>
+        <v>92.3597030639648</v>
       </c>
       <c r="H963" t="n">
         <v>106414</v>
@@ -28325,7 +28325,7 @@
         <v>99.75</v>
       </c>
       <c r="G964" t="n">
-        <v>92.5452423095703</v>
+        <v>92.5452499389648</v>
       </c>
       <c r="H964" t="n">
         <v>117390</v>
@@ -28383,7 +28383,7 @@
         <v>100</v>
       </c>
       <c r="G966" t="n">
-        <v>92.7771911621094</v>
+        <v>92.7771987915039</v>
       </c>
       <c r="H966" t="n">
         <v>134395</v>
@@ -28412,7 +28412,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G967" t="n">
-        <v>92.3596954345703</v>
+        <v>92.3597030639648</v>
       </c>
       <c r="H967" t="n">
         <v>128135</v>
@@ -28441,7 +28441,7 @@
         <v>96.9499969482422</v>
       </c>
       <c r="G968" t="n">
-        <v>89.9474716186523</v>
+        <v>89.9474868774414</v>
       </c>
       <c r="H968" t="n">
         <v>145555</v>
@@ -28470,7 +28470,7 @@
         <v>97.6999969482422</v>
       </c>
       <c r="G969" t="n">
-        <v>90.6433029174805</v>
+        <v>90.6433181762695</v>
       </c>
       <c r="H969" t="n">
         <v>208459</v>
@@ -28528,7 +28528,7 @@
         <v>97.6500015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>90.5969314575195</v>
+        <v>90.596923828125</v>
       </c>
       <c r="H971" t="n">
         <v>91441</v>
@@ -28557,7 +28557,7 @@
         <v>97.0500030517578</v>
       </c>
       <c r="G972" t="n">
-        <v>90.0402755737305</v>
+        <v>90.0402679443359</v>
       </c>
       <c r="H972" t="n">
         <v>70641</v>
@@ -28644,7 +28644,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G975" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H975" t="n">
         <v>180644</v>
@@ -28702,7 +28702,7 @@
         <v>101.099998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>93.7977447509766</v>
+        <v>93.797737121582</v>
       </c>
       <c r="H977" t="n">
         <v>61642</v>
@@ -28731,7 +28731,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G978" t="n">
-        <v>93.612190246582</v>
+        <v>93.6121826171875</v>
       </c>
       <c r="H978" t="n">
         <v>85549</v>
@@ -28760,7 +28760,7 @@
         <v>100.300003051758</v>
       </c>
       <c r="G979" t="n">
-        <v>93.0555267333984</v>
+        <v>93.0555191040039</v>
       </c>
       <c r="H979" t="n">
         <v>135989</v>
@@ -28818,7 +28818,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G981" t="n">
-        <v>96.3955078125</v>
+        <v>96.3955001831055</v>
       </c>
       <c r="H981" t="n">
         <v>198362</v>
@@ -28876,7 +28876,7 @@
         <v>103.5</v>
       </c>
       <c r="G983" t="n">
-        <v>96.0243988037109</v>
+        <v>96.0243911743164</v>
       </c>
       <c r="H983" t="n">
         <v>123220</v>
@@ -28905,7 +28905,7 @@
         <v>103.599998474121</v>
       </c>
       <c r="G984" t="n">
-        <v>96.1171722412109</v>
+        <v>96.1171646118164</v>
       </c>
       <c r="H984" t="n">
         <v>142262</v>
@@ -28934,7 +28934,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G985" t="n">
-        <v>98.9004821777344</v>
+        <v>98.9004745483398</v>
       </c>
       <c r="H985" t="n">
         <v>152430</v>
@@ -28963,7 +28963,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G986" t="n">
-        <v>101.219917297363</v>
+        <v>101.219902038574</v>
       </c>
       <c r="H986" t="n">
         <v>313302</v>
@@ -28992,7 +28992,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G987" t="n">
-        <v>102.70433807373</v>
+        <v>102.704345703125</v>
       </c>
       <c r="H987" t="n">
         <v>195641</v>
@@ -29021,7 +29021,7 @@
         <v>112.099998474121</v>
       </c>
       <c r="G988" t="n">
-        <v>104.003227233887</v>
+        <v>104.003234863281</v>
       </c>
       <c r="H988" t="n">
         <v>287822</v>
@@ -29079,7 +29079,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G990" t="n">
-        <v>105.673233032227</v>
+        <v>105.673225402832</v>
       </c>
       <c r="H990" t="n">
         <v>252377</v>
@@ -29195,7 +29195,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G994" t="n">
-        <v>111.703742980957</v>
+        <v>111.703735351562</v>
       </c>
       <c r="H994" t="n">
         <v>169221</v>
@@ -29282,7 +29282,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G997" t="n">
-        <v>112.53874206543</v>
+        <v>112.538726806641</v>
       </c>
       <c r="H997" t="n">
         <v>150216</v>
@@ -29311,7 +29311,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G998" t="n">
-        <v>109.755424499512</v>
+        <v>109.755409240723</v>
       </c>
       <c r="H998" t="n">
         <v>150330</v>
@@ -29398,7 +29398,7 @@
         <v>124</v>
       </c>
       <c r="G1001" t="n">
-        <v>115.04370880127</v>
+        <v>115.043716430664</v>
       </c>
       <c r="H1001" t="n">
         <v>148889</v>
@@ -29427,7 +29427,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G1002" t="n">
-        <v>114.858169555664</v>
+        <v>114.858177185059</v>
       </c>
       <c r="H1002" t="n">
         <v>113540</v>
@@ -29514,7 +29514,7 @@
         <v>121</v>
       </c>
       <c r="G1005" t="n">
-        <v>112.260391235352</v>
+        <v>112.260398864746</v>
       </c>
       <c r="H1005" t="n">
         <v>82885</v>
@@ -29543,7 +29543,7 @@
         <v>120</v>
       </c>
       <c r="G1006" t="n">
-        <v>111.332641601562</v>
+        <v>111.332626342773</v>
       </c>
       <c r="H1006" t="n">
         <v>171715</v>
@@ -29601,7 +29601,7 @@
         <v>117.699996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>109.198745727539</v>
+        <v>109.198753356934</v>
       </c>
       <c r="H1008" t="n">
         <v>113611</v>
@@ -29659,7 +29659,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1010" t="n">
-        <v>108.270973205566</v>
+        <v>108.270988464355</v>
       </c>
       <c r="H1010" t="n">
         <v>91707</v>
@@ -29746,7 +29746,7 @@
         <v>117.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>109.013191223145</v>
+        <v>109.013198852539</v>
       </c>
       <c r="H1013" t="n">
         <v>122460</v>
@@ -29833,7 +29833,7 @@
         <v>116.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>108.085433959961</v>
+        <v>108.085426330566</v>
       </c>
       <c r="H1016" t="n">
         <v>166980</v>
@@ -29891,7 +29891,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1018" t="n">
-        <v>106.508232116699</v>
+        <v>106.508209228516</v>
       </c>
       <c r="H1018" t="n">
         <v>93251</v>
@@ -29920,7 +29920,7 @@
         <v>118.400001525879</v>
       </c>
       <c r="G1019" t="n">
-        <v>109.848190307617</v>
+        <v>109.848197937012</v>
       </c>
       <c r="H1019" t="n">
         <v>169545</v>
@@ -29949,7 +29949,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G1020" t="n">
-        <v>110.219314575195</v>
+        <v>110.219299316406</v>
       </c>
       <c r="H1020" t="n">
         <v>72503</v>
@@ -29978,7 +29978,7 @@
         <v>119.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>110.86873626709</v>
+        <v>110.868743896484</v>
       </c>
       <c r="H1021" t="n">
         <v>83655</v>
@@ -30007,7 +30007,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1022" t="n">
-        <v>108.827651977539</v>
+        <v>108.827644348145</v>
       </c>
       <c r="H1022" t="n">
         <v>132761</v>
@@ -30036,7 +30036,7 @@
         <v>116.699996948242</v>
       </c>
       <c r="G1023" t="n">
-        <v>108.270973205566</v>
+        <v>108.270988464355</v>
       </c>
       <c r="H1023" t="n">
         <v>157652</v>
@@ -30181,7 +30181,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1028" t="n">
-        <v>106.508232116699</v>
+        <v>106.508209228516</v>
       </c>
       <c r="H1028" t="n">
         <v>114599</v>
@@ -30210,7 +30210,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>106.044326782227</v>
+        <v>106.044319152832</v>
       </c>
       <c r="H1029" t="n">
         <v>142027</v>
@@ -30268,7 +30268,7 @@
         <v>114.099998474121</v>
       </c>
       <c r="G1031" t="n">
-        <v>105.858779907227</v>
+        <v>105.858772277832</v>
       </c>
       <c r="H1031" t="n">
         <v>134155</v>
@@ -30297,7 +30297,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G1032" t="n">
-        <v>106.78653717041</v>
+        <v>106.786552429199</v>
       </c>
       <c r="H1032" t="n">
         <v>99553</v>
@@ -30384,7 +30384,7 @@
         <v>115.599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>107.250427246094</v>
+        <v>107.250442504883</v>
       </c>
       <c r="H1035" t="n">
         <v>79387</v>
@@ -30413,7 +30413,7 @@
         <v>113.199996948242</v>
       </c>
       <c r="G1036" t="n">
-        <v>105.023765563965</v>
+        <v>105.023780822754</v>
       </c>
       <c r="H1036" t="n">
         <v>82899</v>
@@ -30442,7 +30442,7 @@
         <v>111</v>
       </c>
       <c r="G1037" t="n">
-        <v>102.982681274414</v>
+        <v>102.982688903809</v>
       </c>
       <c r="H1037" t="n">
         <v>159706</v>
@@ -30471,7 +30471,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G1038" t="n">
-        <v>103.817680358887</v>
+        <v>103.817672729492</v>
       </c>
       <c r="H1038" t="n">
         <v>118544</v>
@@ -30500,7 +30500,7 @@
         <v>114</v>
       </c>
       <c r="G1039" t="n">
-        <v>105.765998840332</v>
+        <v>105.765991210938</v>
       </c>
       <c r="H1039" t="n">
         <v>100652</v>
@@ -30558,7 +30558,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1041" t="n">
-        <v>106.508232116699</v>
+        <v>106.508209228516</v>
       </c>
       <c r="H1041" t="n">
         <v>270734</v>
@@ -30587,7 +30587,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1042" t="n">
-        <v>106.044326782227</v>
+        <v>106.044319152832</v>
       </c>
       <c r="H1042" t="n">
         <v>76827</v>
@@ -30616,7 +30616,7 @@
         <v>114.699996948242</v>
       </c>
       <c r="G1043" t="n">
-        <v>106.415428161621</v>
+        <v>106.415435791016</v>
       </c>
       <c r="H1043" t="n">
         <v>54246</v>
@@ -30674,7 +30674,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>106.508232116699</v>
+        <v>106.508209228516</v>
       </c>
       <c r="H1045" t="n">
         <v>108233</v>
@@ -30703,7 +30703,7 @@
         <v>114.599998474121</v>
       </c>
       <c r="G1046" t="n">
-        <v>106.322654724121</v>
+        <v>106.322662353516</v>
       </c>
       <c r="H1046" t="n">
         <v>99356</v>
@@ -30732,7 +30732,7 @@
         <v>116.599998474121</v>
       </c>
       <c r="G1047" t="n">
-        <v>108.178199768066</v>
+        <v>108.178207397461</v>
       </c>
       <c r="H1047" t="n">
         <v>76277</v>
@@ -30761,7 +30761,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>108.827651977539</v>
+        <v>108.827644348145</v>
       </c>
       <c r="H1048" t="n">
         <v>49235</v>
@@ -30819,7 +30819,7 @@
         <v>121.099998474121</v>
       </c>
       <c r="G1050" t="n">
-        <v>112.353172302246</v>
+        <v>112.353179931641</v>
       </c>
       <c r="H1050" t="n">
         <v>90854</v>
@@ -30848,7 +30848,7 @@
         <v>117.5</v>
       </c>
       <c r="G1051" t="n">
-        <v>109.013191223145</v>
+        <v>109.013198852539</v>
       </c>
       <c r="H1051" t="n">
         <v>95823</v>
@@ -30877,7 +30877,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>107.899879455566</v>
+        <v>107.899871826172</v>
       </c>
       <c r="H1052" t="n">
         <v>119025</v>
@@ -30906,7 +30906,7 @@
         <v>110.599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>102.611572265625</v>
+        <v>102.61156463623</v>
       </c>
       <c r="H1053" t="n">
         <v>285849</v>
@@ -30935,7 +30935,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G1054" t="n">
-        <v>98.6221618652344</v>
+        <v>98.6221542358398</v>
       </c>
       <c r="H1054" t="n">
         <v>558664</v>
@@ -30964,7 +30964,7 @@
         <v>107.199996948242</v>
       </c>
       <c r="G1055" t="n">
-        <v>99.4571380615234</v>
+        <v>99.457145690918</v>
       </c>
       <c r="H1055" t="n">
         <v>335606</v>
@@ -31022,7 +31022,7 @@
         <v>102.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>95.0966262817383</v>
+        <v>95.0966110229492</v>
       </c>
       <c r="H1057" t="n">
         <v>355146</v>
@@ -31051,7 +31051,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G1058" t="n">
-        <v>94.9110717773438</v>
+        <v>94.9110794067383</v>
       </c>
       <c r="H1058" t="n">
         <v>235831</v>
@@ -31109,7 +31109,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G1060" t="n">
-        <v>97.3232803344727</v>
+        <v>97.3232727050781</v>
       </c>
       <c r="H1060" t="n">
         <v>258453</v>
@@ -31254,7 +31254,7 @@
         <v>113</v>
       </c>
       <c r="G1065" t="n">
-        <v>104.838233947754</v>
+        <v>104.838226318359</v>
       </c>
       <c r="H1065" t="n">
         <v>732508</v>
@@ -31312,7 +31312,7 @@
         <v>109.599998474121</v>
       </c>
       <c r="G1067" t="n">
-        <v>101.683807373047</v>
+        <v>101.683792114258</v>
       </c>
       <c r="H1067" t="n">
         <v>690760</v>
@@ -31341,7 +31341,7 @@
         <v>107.800003051758</v>
       </c>
       <c r="G1068" t="n">
-        <v>100.013824462891</v>
+        <v>100.013809204102</v>
       </c>
       <c r="H1068" t="n">
         <v>729991</v>
@@ -31428,7 +31428,7 @@
         <v>114.400001525879</v>
       </c>
       <c r="G1071" t="n">
-        <v>106.137115478516</v>
+        <v>106.137107849121</v>
       </c>
       <c r="H1071" t="n">
         <v>424579</v>
@@ -31457,7 +31457,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1072" t="n">
-        <v>103.539337158203</v>
+        <v>103.539344787598</v>
       </c>
       <c r="H1072" t="n">
         <v>822715</v>
@@ -31515,7 +31515,7 @@
         <v>115.199996948242</v>
       </c>
       <c r="G1074" t="n">
-        <v>106.87931060791</v>
+        <v>106.879325866699</v>
       </c>
       <c r="H1074" t="n">
         <v>401583</v>
@@ -31544,7 +31544,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1075" t="n">
-        <v>104.559883117676</v>
+        <v>104.559898376465</v>
       </c>
       <c r="H1075" t="n">
         <v>436837</v>
@@ -31631,7 +31631,7 @@
         <v>116.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>108.085433959961</v>
+        <v>108.085426330566</v>
       </c>
       <c r="H1078" t="n">
         <v>271381</v>
@@ -31660,7 +31660,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G1079" t="n">
-        <v>111.982063293457</v>
+        <v>111.982055664062</v>
       </c>
       <c r="H1079" t="n">
         <v>297859</v>
@@ -31689,7 +31689,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G1080" t="n">
-        <v>109.755424499512</v>
+        <v>109.755409240723</v>
       </c>
       <c r="H1080" t="n">
         <v>157506</v>
@@ -31718,7 +31718,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>109.755424499512</v>
+        <v>109.755409240723</v>
       </c>
       <c r="H1081" t="n">
         <v>184324</v>
@@ -31805,7 +31805,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G1084" t="n">
-        <v>115.878715515137</v>
+        <v>115.878707885742</v>
       </c>
       <c r="H1084" t="n">
         <v>503694</v>
@@ -31863,7 +31863,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1086" t="n">
-        <v>123.764755249023</v>
+        <v>123.764739990234</v>
       </c>
       <c r="H1086" t="n">
         <v>341308</v>
@@ -31950,7 +31950,7 @@
         <v>150.100006103516</v>
       </c>
       <c r="G1089" t="n">
-        <v>139.258590698242</v>
+        <v>139.258575439453</v>
       </c>
       <c r="H1089" t="n">
         <v>581970</v>
@@ -31979,7 +31979,7 @@
         <v>144.5</v>
       </c>
       <c r="G1090" t="n">
-        <v>134.063049316406</v>
+        <v>134.063034057617</v>
       </c>
       <c r="H1090" t="n">
         <v>962667</v>
@@ -32008,7 +32008,7 @@
         <v>153.5</v>
       </c>
       <c r="G1091" t="n">
-        <v>142.412979125977</v>
+        <v>142.412994384766</v>
       </c>
       <c r="H1091" t="n">
         <v>430197</v>
@@ -32037,7 +32037,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G1092" t="n">
-        <v>141.577987670898</v>
+        <v>141.578002929688</v>
       </c>
       <c r="H1092" t="n">
         <v>324414</v>
@@ -32066,7 +32066,7 @@
         <v>165</v>
       </c>
       <c r="G1093" t="n">
-        <v>153.08235168457</v>
+        <v>153.082382202148</v>
       </c>
       <c r="H1093" t="n">
         <v>447472</v>
@@ -32124,7 +32124,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1095" t="n">
-        <v>150.855728149414</v>
+        <v>150.855712890625</v>
       </c>
       <c r="H1095" t="n">
         <v>300403</v>
@@ -32153,7 +32153,7 @@
         <v>166.899993896484</v>
       </c>
       <c r="G1096" t="n">
-        <v>154.845108032227</v>
+        <v>154.845123291016</v>
       </c>
       <c r="H1096" t="n">
         <v>292389</v>
@@ -32182,7 +32182,7 @@
         <v>167.100006103516</v>
       </c>
       <c r="G1097" t="n">
-        <v>155.030715942383</v>
+        <v>155.030685424805</v>
       </c>
       <c r="H1097" t="n">
         <v>282090</v>
@@ -32240,7 +32240,7 @@
         <v>155.300003051758</v>
       </c>
       <c r="G1099" t="n">
-        <v>144.082992553711</v>
+        <v>144.082977294922</v>
       </c>
       <c r="H1099" t="n">
         <v>420377</v>
@@ -32269,7 +32269,7 @@
         <v>155.399993896484</v>
       </c>
       <c r="G1100" t="n">
-        <v>144.175735473633</v>
+        <v>144.175720214844</v>
       </c>
       <c r="H1100" t="n">
         <v>232643</v>
@@ -32356,7 +32356,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1103" t="n">
-        <v>143.619110107422</v>
+        <v>143.619094848633</v>
       </c>
       <c r="H1103" t="n">
         <v>130241</v>
@@ -32385,7 +32385,7 @@
         <v>156.199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>144.917953491211</v>
+        <v>144.91796875</v>
       </c>
       <c r="H1104" t="n">
         <v>70987</v>
@@ -32472,7 +32472,7 @@
         <v>172.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>160.040649414062</v>
+        <v>160.040634155273</v>
       </c>
       <c r="H1107" t="n">
         <v>441095</v>
@@ -32530,7 +32530,7 @@
         <v>184.199996948242</v>
       </c>
       <c r="G1109" t="n">
-        <v>170.895584106445</v>
+        <v>170.895568847656</v>
       </c>
       <c r="H1109" t="n">
         <v>355559</v>
@@ -32559,7 +32559,7 @@
         <v>184.800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>171.452270507812</v>
+        <v>171.452255249023</v>
       </c>
       <c r="H1110" t="n">
         <v>268101</v>
@@ -32617,7 +32617,7 @@
         <v>189.199996948242</v>
       </c>
       <c r="G1112" t="n">
-        <v>175.534439086914</v>
+        <v>175.534454345703</v>
       </c>
       <c r="H1112" t="n">
         <v>486038</v>
@@ -32646,7 +32646,7 @@
         <v>190.899993896484</v>
       </c>
       <c r="G1113" t="n">
-        <v>177.111633300781</v>
+        <v>177.11164855957</v>
       </c>
       <c r="H1113" t="n">
         <v>477801</v>
@@ -32675,7 +32675,7 @@
         <v>202.800003051758</v>
       </c>
       <c r="G1114" t="n">
-        <v>188.152145385742</v>
+        <v>188.152160644531</v>
       </c>
       <c r="H1114" t="n">
         <v>552568</v>
@@ -32704,7 +32704,7 @@
         <v>209.399993896484</v>
       </c>
       <c r="G1115" t="n">
-        <v>194.275405883789</v>
+        <v>194.275436401367</v>
       </c>
       <c r="H1115" t="n">
         <v>446507</v>
@@ -32791,7 +32791,7 @@
         <v>181.800003051758</v>
       </c>
       <c r="G1118" t="n">
-        <v>168.668930053711</v>
+        <v>168.6689453125</v>
       </c>
       <c r="H1118" t="n">
         <v>636785</v>
@@ -32849,7 +32849,7 @@
         <v>181.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>168.390609741211</v>
+        <v>168.390594482422</v>
       </c>
       <c r="H1120" t="n">
         <v>427520</v>
@@ -32936,7 +32936,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1123" t="n">
-        <v>161.617858886719</v>
+        <v>161.61784362793</v>
       </c>
       <c r="H1123" t="n">
         <v>528586</v>
@@ -32965,7 +32965,7 @@
         <v>166</v>
       </c>
       <c r="G1124" t="n">
-        <v>154.010147094727</v>
+        <v>154.010131835938</v>
       </c>
       <c r="H1124" t="n">
         <v>573423</v>
@@ -32994,7 +32994,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G1125" t="n">
-        <v>148.072402954102</v>
+        <v>148.072418212891</v>
       </c>
       <c r="H1125" t="n">
         <v>584751</v>
@@ -33023,7 +33023,7 @@
         <v>161.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>149.835174560547</v>
+        <v>149.835159301758</v>
       </c>
       <c r="H1126" t="n">
         <v>684242</v>
@@ -33052,7 +33052,7 @@
         <v>164</v>
       </c>
       <c r="G1127" t="n">
-        <v>152.154586791992</v>
+        <v>152.15461730957</v>
       </c>
       <c r="H1127" t="n">
         <v>361385</v>
@@ -33081,7 +33081,7 @@
         <v>167.800003051758</v>
       </c>
       <c r="G1128" t="n">
-        <v>155.680130004883</v>
+        <v>155.680145263672</v>
       </c>
       <c r="H1128" t="n">
         <v>357835</v>
@@ -33139,7 +33139,7 @@
         <v>169.899993896484</v>
       </c>
       <c r="G1130" t="n">
-        <v>158.5302734375</v>
+        <v>158.530242919922</v>
       </c>
       <c r="H1130" t="n">
         <v>309208</v>
@@ -33197,7 +33197,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1132" t="n">
-        <v>158.90348815918</v>
+        <v>158.903503417969</v>
       </c>
       <c r="H1132" t="n">
         <v>216573</v>
@@ -33226,7 +33226,7 @@
         <v>169.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>158.157012939453</v>
+        <v>158.157028198242</v>
       </c>
       <c r="H1133" t="n">
         <v>188475</v>
@@ -33255,7 +33255,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1134" t="n">
-        <v>156.197540283203</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1134" t="n">
         <v>359432</v>
@@ -33342,7 +33342,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1137" t="n">
-        <v>158.90348815918</v>
+        <v>158.903503417969</v>
       </c>
       <c r="H1137" t="n">
         <v>165364</v>
@@ -33371,7 +33371,7 @@
         <v>173</v>
       </c>
       <c r="G1138" t="n">
-        <v>161.422805786133</v>
+        <v>161.422821044922</v>
       </c>
       <c r="H1138" t="n">
         <v>266304</v>
@@ -33400,7 +33400,7 @@
         <v>171.399993896484</v>
       </c>
       <c r="G1139" t="n">
-        <v>159.929885864258</v>
+        <v>159.929870605469</v>
       </c>
       <c r="H1139" t="n">
         <v>220915</v>
@@ -33516,7 +33516,7 @@
         <v>171.300003051758</v>
       </c>
       <c r="G1143" t="n">
-        <v>159.836578369141</v>
+        <v>159.83659362793</v>
       </c>
       <c r="H1143" t="n">
         <v>289763</v>
@@ -33574,7 +33574,7 @@
         <v>174.699996948242</v>
       </c>
       <c r="G1145" t="n">
-        <v>163.009033203125</v>
+        <v>163.009048461914</v>
       </c>
       <c r="H1145" t="n">
         <v>148347</v>
@@ -33603,7 +33603,7 @@
         <v>178.5</v>
       </c>
       <c r="G1146" t="n">
-        <v>166.554733276367</v>
+        <v>166.554748535156</v>
       </c>
       <c r="H1146" t="n">
         <v>235569</v>
@@ -33632,7 +33632,7 @@
         <v>179.199996948242</v>
       </c>
       <c r="G1147" t="n">
-        <v>167.207901000977</v>
+        <v>167.207885742188</v>
       </c>
       <c r="H1147" t="n">
         <v>155301</v>
@@ -33661,7 +33661,7 @@
         <v>171.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>160.023178100586</v>
+        <v>160.023193359375</v>
       </c>
       <c r="H1148" t="n">
         <v>273837</v>
@@ -33690,7 +33690,7 @@
         <v>172.899993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>161.329483032227</v>
+        <v>161.329498291016</v>
       </c>
       <c r="H1149" t="n">
         <v>160523</v>
@@ -33719,7 +33719,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1150" t="n">
-        <v>162.075958251953</v>
+        <v>162.075973510742</v>
       </c>
       <c r="H1150" t="n">
         <v>162432</v>
@@ -33748,7 +33748,7 @@
         <v>173.199996948242</v>
       </c>
       <c r="G1151" t="n">
-        <v>161.609436035156</v>
+        <v>161.609420776367</v>
       </c>
       <c r="H1151" t="n">
         <v>170112</v>
@@ -33806,7 +33806,7 @@
         <v>178.100006103516</v>
       </c>
       <c r="G1153" t="n">
-        <v>166.181533813477</v>
+        <v>166.181503295898</v>
       </c>
       <c r="H1153" t="n">
         <v>116177</v>
@@ -33835,7 +33835,7 @@
         <v>178.199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>166.274810791016</v>
+        <v>166.274826049805</v>
       </c>
       <c r="H1154" t="n">
         <v>124171</v>
@@ -33864,7 +33864,7 @@
         <v>180.899993896484</v>
       </c>
       <c r="G1155" t="n">
-        <v>168.794128417969</v>
+        <v>168.794143676758</v>
       </c>
       <c r="H1155" t="n">
         <v>120776</v>
@@ -33893,7 +33893,7 @@
         <v>178.300003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>166.368148803711</v>
+        <v>166.368133544922</v>
       </c>
       <c r="H1156" t="n">
         <v>157218</v>
@@ -33922,7 +33922,7 @@
         <v>175</v>
       </c>
       <c r="G1157" t="n">
-        <v>163.288955688477</v>
+        <v>163.288970947266</v>
       </c>
       <c r="H1157" t="n">
         <v>250110</v>
@@ -33951,7 +33951,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1158" t="n">
-        <v>157.970428466797</v>
+        <v>157.970413208008</v>
       </c>
       <c r="H1158" t="n">
         <v>446703</v>
@@ -33980,7 +33980,7 @@
         <v>162.699996948242</v>
       </c>
       <c r="G1159" t="n">
-        <v>151.812072753906</v>
+        <v>151.812088012695</v>
       </c>
       <c r="H1159" t="n">
         <v>310608</v>
@@ -34067,7 +34067,7 @@
         <v>173.300003051758</v>
       </c>
       <c r="G1162" t="n">
-        <v>161.702743530273</v>
+        <v>161.702728271484</v>
       </c>
       <c r="H1162" t="n">
         <v>143977</v>
@@ -34183,7 +34183,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G1166" t="n">
-        <v>149.852630615234</v>
+        <v>149.852615356445</v>
       </c>
       <c r="H1166" t="n">
         <v>203712</v>
@@ -34212,7 +34212,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G1167" t="n">
-        <v>147.053405761719</v>
+        <v>147.053375244141</v>
       </c>
       <c r="H1167" t="n">
         <v>387121</v>
@@ -34270,7 +34270,7 @@
         <v>158.600006103516</v>
       </c>
       <c r="G1169" t="n">
-        <v>147.986450195312</v>
+        <v>147.986480712891</v>
       </c>
       <c r="H1169" t="n">
         <v>133127</v>
@@ -34299,7 +34299,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>142.574600219727</v>
+        <v>142.574615478516</v>
       </c>
       <c r="H1170" t="n">
         <v>182163</v>
@@ -34328,7 +34328,7 @@
         <v>157.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>146.960067749023</v>
+        <v>146.960083007812</v>
       </c>
       <c r="H1171" t="n">
         <v>181402</v>
@@ -34386,7 +34386,7 @@
         <v>159.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>148.826232910156</v>
+        <v>148.826217651367</v>
       </c>
       <c r="H1173" t="n">
         <v>147186</v>
@@ -34415,7 +34415,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1174" t="n">
-        <v>145.653778076172</v>
+        <v>145.653747558594</v>
       </c>
       <c r="H1174" t="n">
         <v>177264</v>
@@ -34473,7 +34473,7 @@
         <v>159.100006103516</v>
       </c>
       <c r="G1176" t="n">
-        <v>148.453018188477</v>
+        <v>148.452987670898</v>
       </c>
       <c r="H1176" t="n">
         <v>116736</v>
@@ -34502,7 +34502,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1177" t="n">
-        <v>151.34553527832</v>
+        <v>151.345550537109</v>
       </c>
       <c r="H1177" t="n">
         <v>111771</v>
@@ -34560,7 +34560,7 @@
         <v>163</v>
       </c>
       <c r="G1179" t="n">
-        <v>152.091995239258</v>
+        <v>152.092010498047</v>
       </c>
       <c r="H1179" t="n">
         <v>117685</v>
@@ -34589,7 +34589,7 @@
         <v>163.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>152.558547973633</v>
+        <v>152.558563232422</v>
       </c>
       <c r="H1180" t="n">
         <v>137900</v>
@@ -34647,7 +34647,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1182" t="n">
-        <v>156.477462768555</v>
+        <v>156.477478027344</v>
       </c>
       <c r="H1182" t="n">
         <v>150389</v>
@@ -34676,7 +34676,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1183" t="n">
-        <v>142.947814941406</v>
+        <v>142.947830200195</v>
       </c>
       <c r="H1183" t="n">
         <v>513169</v>
@@ -34734,7 +34734,7 @@
         <v>151.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>141.361602783203</v>
+        <v>141.361587524414</v>
       </c>
       <c r="H1185" t="n">
         <v>216448</v>
@@ -34763,7 +34763,7 @@
         <v>152.100006103516</v>
       </c>
       <c r="G1186" t="n">
-        <v>141.921463012695</v>
+        <v>141.921447753906</v>
       </c>
       <c r="H1186" t="n">
         <v>212429</v>
@@ -34792,7 +34792,7 @@
         <v>151</v>
       </c>
       <c r="G1187" t="n">
-        <v>140.895034790039</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1187" t="n">
         <v>125409</v>
@@ -34821,7 +34821,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G1188" t="n">
-        <v>133.057205200195</v>
+        <v>133.057189941406</v>
       </c>
       <c r="H1188" t="n">
         <v>237378</v>
@@ -34879,7 +34879,7 @@
         <v>144.5</v>
       </c>
       <c r="G1190" t="n">
-        <v>134.830032348633</v>
+        <v>134.830047607422</v>
       </c>
       <c r="H1190" t="n">
         <v>128302</v>
@@ -34937,7 +34937,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G1192" t="n">
-        <v>142.108047485352</v>
+        <v>142.108062744141</v>
       </c>
       <c r="H1192" t="n">
         <v>482399</v>
@@ -35053,7 +35053,7 @@
         <v>157</v>
       </c>
       <c r="G1196" t="n">
-        <v>146.493530273438</v>
+        <v>146.493545532227</v>
       </c>
       <c r="H1196" t="n">
         <v>108163</v>
@@ -35111,7 +35111,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1198" t="n">
-        <v>147.613220214844</v>
+        <v>147.613235473633</v>
       </c>
       <c r="H1198" t="n">
         <v>101347</v>
@@ -35140,7 +35140,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>156.197540283203</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1199" t="n">
         <v>404378</v>
@@ -35169,7 +35169,7 @@
         <v>169.399993896484</v>
       </c>
       <c r="G1200" t="n">
-        <v>158.063720703125</v>
+        <v>158.063735961914</v>
       </c>
       <c r="H1200" t="n">
         <v>546780</v>
@@ -35198,7 +35198,7 @@
         <v>169</v>
       </c>
       <c r="G1201" t="n">
-        <v>157.690475463867</v>
+        <v>157.690490722656</v>
       </c>
       <c r="H1201" t="n">
         <v>200006</v>
@@ -35227,7 +35227,7 @@
         <v>169.300003051758</v>
       </c>
       <c r="G1202" t="n">
-        <v>157.970428466797</v>
+        <v>157.970413208008</v>
       </c>
       <c r="H1202" t="n">
         <v>215161</v>
@@ -35256,7 +35256,7 @@
         <v>167.699996948242</v>
       </c>
       <c r="G1203" t="n">
-        <v>156.477462768555</v>
+        <v>156.477478027344</v>
       </c>
       <c r="H1203" t="n">
         <v>158623</v>
@@ -35285,7 +35285,7 @@
         <v>170.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>159.090118408203</v>
+        <v>159.090103149414</v>
       </c>
       <c r="H1204" t="n">
         <v>199198</v>
@@ -35343,7 +35343,7 @@
         <v>173.300003051758</v>
       </c>
       <c r="G1206" t="n">
-        <v>161.702743530273</v>
+        <v>161.702728271484</v>
       </c>
       <c r="H1206" t="n">
         <v>129529</v>
@@ -35401,7 +35401,7 @@
         <v>176.800003051758</v>
       </c>
       <c r="G1208" t="n">
-        <v>164.968521118164</v>
+        <v>164.968505859375</v>
       </c>
       <c r="H1208" t="n">
         <v>243269</v>
@@ -35430,7 +35430,7 @@
         <v>178.100006103516</v>
       </c>
       <c r="G1209" t="n">
-        <v>166.181533813477</v>
+        <v>166.181503295898</v>
       </c>
       <c r="H1209" t="n">
         <v>187053</v>
@@ -35488,7 +35488,7 @@
         <v>184.399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>172.059921264648</v>
+        <v>172.059906005859</v>
       </c>
       <c r="H1211" t="n">
         <v>377881</v>
@@ -35546,7 +35546,7 @@
         <v>182.5</v>
       </c>
       <c r="G1213" t="n">
-        <v>170.287063598633</v>
+        <v>170.287078857422</v>
       </c>
       <c r="H1213" t="n">
         <v>180435</v>
@@ -35604,7 +35604,7 @@
         <v>190.100006103516</v>
       </c>
       <c r="G1215" t="n">
-        <v>177.378479003906</v>
+        <v>177.378494262695</v>
       </c>
       <c r="H1215" t="n">
         <v>149173</v>
@@ -35633,7 +35633,7 @@
         <v>187.5</v>
       </c>
       <c r="G1216" t="n">
-        <v>174.952453613281</v>
+        <v>174.95246887207</v>
       </c>
       <c r="H1216" t="n">
         <v>125251</v>
@@ -35662,7 +35662,7 @@
         <v>191.300003051758</v>
       </c>
       <c r="G1217" t="n">
-        <v>178.498184204102</v>
+        <v>178.498168945312</v>
       </c>
       <c r="H1217" t="n">
         <v>183967</v>
@@ -35720,7 +35720,7 @@
         <v>194.600006103516</v>
       </c>
       <c r="G1219" t="n">
-        <v>181.577362060547</v>
+        <v>181.577331542969</v>
       </c>
       <c r="H1219" t="n">
         <v>229813</v>
@@ -35749,7 +35749,7 @@
         <v>193.600006103516</v>
       </c>
       <c r="G1220" t="n">
-        <v>180.644271850586</v>
+        <v>180.644241333008</v>
       </c>
       <c r="H1220" t="n">
         <v>144248</v>
@@ -35807,7 +35807,7 @@
         <v>194.899993896484</v>
       </c>
       <c r="G1222" t="n">
-        <v>181.85725402832</v>
+        <v>181.857238769531</v>
       </c>
       <c r="H1222" t="n">
         <v>201771</v>
@@ -35836,7 +35836,7 @@
         <v>192.600006103516</v>
       </c>
       <c r="G1223" t="n">
-        <v>179.711181640625</v>
+        <v>179.711166381836</v>
       </c>
       <c r="H1223" t="n">
         <v>139931</v>
@@ -35952,7 +35952,7 @@
         <v>188.600006103516</v>
       </c>
       <c r="G1227" t="n">
-        <v>175.978881835938</v>
+        <v>175.978866577148</v>
       </c>
       <c r="H1227" t="n">
         <v>269042</v>
@@ -36010,7 +36010,7 @@
         <v>188.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>175.885543823242</v>
+        <v>175.885559082031</v>
       </c>
       <c r="H1229" t="n">
         <v>103313</v>
@@ -36068,7 +36068,7 @@
         <v>187.100006103516</v>
       </c>
       <c r="G1231" t="n">
-        <v>174.579254150391</v>
+        <v>174.579238891602</v>
       </c>
       <c r="H1231" t="n">
         <v>175470</v>
@@ -36155,7 +36155,7 @@
         <v>201.199996948242</v>
       </c>
       <c r="G1234" t="n">
-        <v>187.735656738281</v>
+        <v>187.73567199707</v>
       </c>
       <c r="H1234" t="n">
         <v>192061</v>
@@ -36242,7 +36242,7 @@
         <v>172.399993896484</v>
       </c>
       <c r="G1237" t="n">
-        <v>160.862945556641</v>
+        <v>160.86296081543</v>
       </c>
       <c r="H1237" t="n">
         <v>458040</v>
@@ -36271,7 +36271,7 @@
         <v>173</v>
       </c>
       <c r="G1238" t="n">
-        <v>161.422805786133</v>
+        <v>161.422821044922</v>
       </c>
       <c r="H1238" t="n">
         <v>275182</v>
@@ -36329,7 +36329,7 @@
         <v>173.300003051758</v>
       </c>
       <c r="G1240" t="n">
-        <v>161.702743530273</v>
+        <v>161.702728271484</v>
       </c>
       <c r="H1240" t="n">
         <v>385690</v>
@@ -36358,7 +36358,7 @@
         <v>173.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>161.889358520508</v>
+        <v>161.889343261719</v>
       </c>
       <c r="H1241" t="n">
         <v>276931</v>
@@ -36387,7 +36387,7 @@
         <v>169.899993896484</v>
       </c>
       <c r="G1242" t="n">
-        <v>158.5302734375</v>
+        <v>158.530242919922</v>
       </c>
       <c r="H1242" t="n">
         <v>282758</v>
@@ -36416,7 +36416,7 @@
         <v>172.600006103516</v>
       </c>
       <c r="G1243" t="n">
-        <v>161.049591064453</v>
+        <v>161.049606323242</v>
       </c>
       <c r="H1243" t="n">
         <v>312144</v>
@@ -36445,7 +36445,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1244" t="n">
-        <v>162.075958251953</v>
+        <v>162.075973510742</v>
       </c>
       <c r="H1244" t="n">
         <v>161137</v>
@@ -36474,7 +36474,7 @@
         <v>173.5</v>
       </c>
       <c r="G1245" t="n">
-        <v>161.889358520508</v>
+        <v>161.889343261719</v>
       </c>
       <c r="H1245" t="n">
         <v>211014</v>
@@ -36561,7 +36561,7 @@
         <v>169.199996948242</v>
       </c>
       <c r="G1248" t="n">
-        <v>157.877105712891</v>
+        <v>157.877090454102</v>
       </c>
       <c r="H1248" t="n">
         <v>219685</v>
@@ -36590,7 +36590,7 @@
         <v>172.800003051758</v>
       </c>
       <c r="G1249" t="n">
-        <v>161.236206054688</v>
+        <v>161.236221313477</v>
       </c>
       <c r="H1249" t="n">
         <v>221273</v>
@@ -36619,7 +36619,7 @@
         <v>176.600006103516</v>
       </c>
       <c r="G1250" t="n">
-        <v>164.78190612793</v>
+        <v>164.781921386719</v>
       </c>
       <c r="H1250" t="n">
         <v>668936</v>
@@ -36648,7 +36648,7 @@
         <v>172.199996948242</v>
       </c>
       <c r="G1251" t="n">
-        <v>160.676330566406</v>
+        <v>160.676345825195</v>
       </c>
       <c r="H1251" t="n">
         <v>216284</v>
@@ -36735,7 +36735,7 @@
         <v>168.399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>157.130615234375</v>
+        <v>157.130645751953</v>
       </c>
       <c r="H1254" t="n">
         <v>168573</v>
@@ -36880,7 +36880,7 @@
         <v>170.5</v>
       </c>
       <c r="G1259" t="n">
-        <v>159.090118408203</v>
+        <v>159.090103149414</v>
       </c>
       <c r="H1259" t="n">
         <v>151664</v>
@@ -36967,7 +36967,7 @@
         <v>166.699996948242</v>
       </c>
       <c r="G1262" t="n">
-        <v>155.544418334961</v>
+        <v>155.544403076172</v>
       </c>
       <c r="H1262" t="n">
         <v>174714</v>
@@ -37054,7 +37054,7 @@
         <v>171.699996948242</v>
       </c>
       <c r="G1265" t="n">
-        <v>160.209808349609</v>
+        <v>160.209823608398</v>
       </c>
       <c r="H1265" t="n">
         <v>179244</v>
@@ -37112,7 +37112,7 @@
         <v>167.399993896484</v>
       </c>
       <c r="G1267" t="n">
-        <v>156.197540283203</v>
+        <v>156.197570800781</v>
       </c>
       <c r="H1267" t="n">
         <v>108593</v>
@@ -37141,7 +37141,7 @@
         <v>167.300003051758</v>
       </c>
       <c r="G1268" t="n">
-        <v>156.104263305664</v>
+        <v>156.104248046875</v>
       </c>
       <c r="H1268" t="n">
         <v>150546</v>
@@ -37199,7 +37199,7 @@
         <v>170.100006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>158.716903686523</v>
+        <v>158.716873168945</v>
       </c>
       <c r="H1270" t="n">
         <v>144762</v>
@@ -37228,7 +37228,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1271" t="n">
-        <v>158.250350952148</v>
+        <v>158.250335693359</v>
       </c>
       <c r="H1271" t="n">
         <v>241069</v>
@@ -37315,7 +37315,7 @@
         <v>160.800003051758</v>
       </c>
       <c r="G1274" t="n">
-        <v>150.03923034668</v>
+        <v>150.039245605469</v>
       </c>
       <c r="H1274" t="n">
         <v>204826</v>
@@ -37373,7 +37373,7 @@
         <v>159.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>148.826232910156</v>
+        <v>148.826217651367</v>
       </c>
       <c r="H1276" t="n">
         <v>140346</v>
@@ -37402,7 +37402,7 @@
         <v>159.399993896484</v>
       </c>
       <c r="G1277" t="n">
-        <v>148.732925415039</v>
+        <v>148.73291015625</v>
       </c>
       <c r="H1277" t="n">
         <v>170407</v>
@@ -37460,7 +37460,7 @@
         <v>162.5</v>
       </c>
       <c r="G1279" t="n">
-        <v>151.625473022461</v>
+        <v>151.62548828125</v>
       </c>
       <c r="H1279" t="n">
         <v>144704</v>
@@ -37518,7 +37518,7 @@
         <v>166.199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>155.077850341797</v>
+        <v>155.077865600586</v>
       </c>
       <c r="H1281" t="n">
         <v>196955</v>
@@ -37605,7 +37605,7 @@
         <v>173.699996948242</v>
       </c>
       <c r="G1284" t="n">
-        <v>162.075958251953</v>
+        <v>162.075973510742</v>
       </c>
       <c r="H1284" t="n">
         <v>157579</v>
@@ -37634,7 +37634,7 @@
         <v>175</v>
       </c>
       <c r="G1285" t="n">
-        <v>163.288955688477</v>
+        <v>163.288970947266</v>
       </c>
       <c r="H1285" t="n">
         <v>135763</v>
@@ -37692,7 +37692,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1287" t="n">
-        <v>166.834671020508</v>
+        <v>166.834655761719</v>
       </c>
       <c r="H1287" t="n">
         <v>153171</v>
@@ -37721,7 +37721,7 @@
         <v>188.300003051758</v>
       </c>
       <c r="G1288" t="n">
-        <v>175.698928833008</v>
+        <v>175.698913574219</v>
       </c>
       <c r="H1288" t="n">
         <v>443566</v>
@@ -37779,7 +37779,7 @@
         <v>180.600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>168.514221191406</v>
+        <v>168.514236450195</v>
       </c>
       <c r="H1290" t="n">
         <v>265167</v>
@@ -37808,7 +37808,7 @@
         <v>180</v>
       </c>
       <c r="G1291" t="n">
-        <v>167.954376220703</v>
+        <v>167.954360961914</v>
       </c>
       <c r="H1291" t="n">
         <v>201666</v>
@@ -37866,7 +37866,7 @@
         <v>176.5</v>
       </c>
       <c r="G1293" t="n">
-        <v>164.688598632812</v>
+        <v>164.688583374023</v>
       </c>
       <c r="H1293" t="n">
         <v>151624</v>
@@ -37895,7 +37895,7 @@
         <v>176.199996948242</v>
       </c>
       <c r="G1294" t="n">
-        <v>164.408676147461</v>
+        <v>164.408660888672</v>
       </c>
       <c r="H1294" t="n">
         <v>132358</v>
@@ -37924,7 +37924,7 @@
         <v>179.100006103516</v>
       </c>
       <c r="G1295" t="n">
-        <v>167.114608764648</v>
+        <v>167.114593505859</v>
       </c>
       <c r="H1295" t="n">
         <v>134646</v>
@@ -38011,7 +38011,7 @@
         <v>182.199996948242</v>
       </c>
       <c r="G1298" t="n">
-        <v>170.00715637207</v>
+        <v>170.007141113281</v>
       </c>
       <c r="H1298" t="n">
         <v>157335</v>
@@ -38069,7 +38069,7 @@
         <v>185.600006103516</v>
       </c>
       <c r="G1300" t="n">
-        <v>173.179626464844</v>
+        <v>173.179611206055</v>
       </c>
       <c r="H1300" t="n">
         <v>73799</v>
@@ -38127,7 +38127,7 @@
         <v>186.399993896484</v>
       </c>
       <c r="G1302" t="n">
-        <v>173.926071166992</v>
+        <v>173.926086425781</v>
       </c>
       <c r="H1302" t="n">
         <v>85448</v>
@@ -38185,7 +38185,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>166.834671020508</v>
+        <v>166.834655761719</v>
       </c>
       <c r="H1304" t="n">
         <v>176424</v>
@@ -38214,7 +38214,7 @@
         <v>169.5</v>
       </c>
       <c r="G1305" t="n">
-        <v>158.157012939453</v>
+        <v>158.157028198242</v>
       </c>
       <c r="H1305" t="n">
         <v>234314</v>
@@ -38301,7 +38301,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G1308" t="n">
-        <v>147.613220214844</v>
+        <v>147.613235473633</v>
       </c>
       <c r="H1308" t="n">
         <v>193734</v>
@@ -38359,7 +38359,7 @@
         <v>162.399993896484</v>
       </c>
       <c r="G1310" t="n">
-        <v>151.532150268555</v>
+        <v>151.532165527344</v>
       </c>
       <c r="H1310" t="n">
         <v>218095</v>
@@ -38388,7 +38388,7 @@
         <v>164</v>
       </c>
       <c r="G1311" t="n">
-        <v>153.02507019043</v>
+        <v>153.025085449219</v>
       </c>
       <c r="H1311" t="n">
         <v>236766</v>
@@ -38417,7 +38417,7 @@
         <v>165.300003051758</v>
       </c>
       <c r="G1312" t="n">
-        <v>154.23811340332</v>
+        <v>154.238098144531</v>
       </c>
       <c r="H1312" t="n">
         <v>182132</v>
@@ -38562,7 +38562,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G1317" t="n">
-        <v>146.306930541992</v>
+        <v>146.306915283203</v>
       </c>
       <c r="H1317" t="n">
         <v>285750</v>
@@ -38591,7 +38591,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1318" t="n">
-        <v>144.440765380859</v>
+        <v>144.44075012207</v>
       </c>
       <c r="H1318" t="n">
         <v>257428</v>
@@ -38649,7 +38649,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G1320" t="n">
-        <v>130.257965087891</v>
+        <v>130.257949829102</v>
       </c>
       <c r="H1320" t="n">
         <v>382652</v>
@@ -38678,7 +38678,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1321" t="n">
-        <v>132.59065246582</v>
+        <v>132.590667724609</v>
       </c>
       <c r="H1321" t="n">
         <v>295438</v>
@@ -38707,7 +38707,7 @@
         <v>145.899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>136.136337280273</v>
+        <v>136.136352539062</v>
       </c>
       <c r="H1322" t="n">
         <v>350628</v>
@@ -38736,7 +38736,7 @@
         <v>142</v>
       </c>
       <c r="G1323" t="n">
-        <v>132.497314453125</v>
+        <v>132.497329711914</v>
       </c>
       <c r="H1323" t="n">
         <v>223928</v>
@@ -38765,7 +38765,7 @@
         <v>140.100006103516</v>
       </c>
       <c r="G1324" t="n">
-        <v>130.724472045898</v>
+        <v>130.724487304688</v>
       </c>
       <c r="H1324" t="n">
         <v>246756</v>
@@ -38794,7 +38794,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>133.523727416992</v>
+        <v>133.523712158203</v>
       </c>
       <c r="H1325" t="n">
         <v>319389</v>
@@ -38823,7 +38823,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>130.817779541016</v>
+        <v>130.817794799805</v>
       </c>
       <c r="H1326" t="n">
         <v>268900</v>
@@ -38852,7 +38852,7 @@
         <v>141</v>
       </c>
       <c r="G1327" t="n">
-        <v>131.564270019531</v>
+        <v>131.564254760742</v>
       </c>
       <c r="H1327" t="n">
         <v>210537</v>
@@ -38881,7 +38881,7 @@
         <v>140</v>
       </c>
       <c r="G1328" t="n">
-        <v>130.63117980957</v>
+        <v>130.631164550781</v>
       </c>
       <c r="H1328" t="n">
         <v>233525</v>
@@ -38910,7 +38910,7 @@
         <v>142.300003051758</v>
       </c>
       <c r="G1329" t="n">
-        <v>132.777267456055</v>
+        <v>132.777252197266</v>
       </c>
       <c r="H1329" t="n">
         <v>161218</v>
@@ -38968,7 +38968,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>128.111862182617</v>
+        <v>128.111846923828</v>
       </c>
       <c r="H1331" t="n">
         <v>287517</v>
@@ -39113,7 +39113,7 @@
         <v>140.149993896484</v>
       </c>
       <c r="G1336" t="n">
-        <v>130.771118164062</v>
+        <v>130.771148681641</v>
       </c>
       <c r="H1336" t="n">
         <v>193898</v>
@@ -39171,7 +39171,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>130.257965087891</v>
+        <v>130.257949829102</v>
       </c>
       <c r="H1338" t="n">
         <v>161499</v>
@@ -39200,7 +39200,7 @@
         <v>153.050003051758</v>
       </c>
       <c r="G1339" t="n">
-        <v>142.807876586914</v>
+        <v>142.807861328125</v>
       </c>
       <c r="H1339" t="n">
         <v>892150</v>
@@ -39258,7 +39258,7 @@
         <v>149.149993896484</v>
       </c>
       <c r="G1341" t="n">
-        <v>139.168838500977</v>
+        <v>139.168853759766</v>
       </c>
       <c r="H1341" t="n">
         <v>183651</v>
@@ -39287,7 +39287,7 @@
         <v>151</v>
       </c>
       <c r="G1342" t="n">
-        <v>140.895034790039</v>
+        <v>140.895050048828</v>
       </c>
       <c r="H1342" t="n">
         <v>192282</v>
@@ -39316,7 +39316,7 @@
         <v>153.199996948242</v>
       </c>
       <c r="G1343" t="n">
-        <v>142.947814941406</v>
+        <v>142.947830200195</v>
       </c>
       <c r="H1343" t="n">
         <v>281536</v>
@@ -39374,7 +39374,7 @@
         <v>155.899993896484</v>
       </c>
       <c r="G1345" t="n">
-        <v>145.467132568359</v>
+        <v>145.467147827148</v>
       </c>
       <c r="H1345" t="n">
         <v>256549</v>
@@ -39432,7 +39432,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1347" t="n">
-        <v>143.600967407227</v>
+        <v>143.600997924805</v>
       </c>
       <c r="H1347" t="n">
         <v>202776</v>
@@ -39461,7 +39461,7 @@
         <v>152.550003051758</v>
       </c>
       <c r="G1348" t="n">
-        <v>142.341339111328</v>
+        <v>142.341323852539</v>
       </c>
       <c r="H1348" t="n">
         <v>115078</v>
@@ -39490,7 +39490,7 @@
         <v>152.399993896484</v>
       </c>
       <c r="G1349" t="n">
-        <v>142.201354980469</v>
+        <v>142.201370239258</v>
       </c>
       <c r="H1349" t="n">
         <v>89652</v>
@@ -39548,7 +39548,7 @@
         <v>143.899993896484</v>
       </c>
       <c r="G1351" t="n">
-        <v>134.270172119141</v>
+        <v>134.27018737793</v>
       </c>
       <c r="H1351" t="n">
         <v>449860</v>
@@ -39577,7 +39577,7 @@
         <v>140.25</v>
       </c>
       <c r="G1352" t="n">
-        <v>130.864456176758</v>
+        <v>130.864440917969</v>
       </c>
       <c r="H1352" t="n">
         <v>342812</v>
@@ -39606,7 +39606,7 @@
         <v>141.25</v>
       </c>
       <c r="G1353" t="n">
-        <v>131.797515869141</v>
+        <v>131.797546386719</v>
       </c>
       <c r="H1353" t="n">
         <v>160312</v>
@@ -39693,7 +39693,7 @@
         <v>141.199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>131.750869750977</v>
+        <v>131.750854492188</v>
       </c>
       <c r="H1356" t="n">
         <v>146704</v>
@@ -39722,7 +39722,7 @@
         <v>138.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>129.231536865234</v>
+        <v>129.231552124023</v>
       </c>
       <c r="H1357" t="n">
         <v>219957</v>
@@ -39751,7 +39751,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G1358" t="n">
-        <v>131.377639770508</v>
+        <v>131.377624511719</v>
       </c>
       <c r="H1358" t="n">
         <v>137020</v>
@@ -39780,7 +39780,7 @@
         <v>142.649993896484</v>
       </c>
       <c r="G1359" t="n">
-        <v>133.103805541992</v>
+        <v>133.103820800781</v>
       </c>
       <c r="H1359" t="n">
         <v>234905</v>
@@ -39838,7 +39838,7 @@
         <v>135</v>
       </c>
       <c r="G1361" t="n">
-        <v>125.965782165527</v>
+        <v>125.965766906738</v>
       </c>
       <c r="H1361" t="n">
         <v>256865</v>
@@ -39896,7 +39896,7 @@
         <v>138</v>
       </c>
       <c r="G1363" t="n">
-        <v>128.764999389648</v>
+        <v>128.765014648438</v>
       </c>
       <c r="H1363" t="n">
         <v>226020</v>
@@ -39954,7 +39954,7 @@
         <v>141.649993896484</v>
       </c>
       <c r="G1365" t="n">
-        <v>132.170745849609</v>
+        <v>132.170761108398</v>
       </c>
       <c r="H1365" t="n">
         <v>155991</v>
@@ -39983,7 +39983,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G1366" t="n">
-        <v>132.59065246582</v>
+        <v>132.590667724609</v>
       </c>
       <c r="H1366" t="n">
         <v>140516</v>
@@ -40012,7 +40012,7 @@
         <v>144</v>
       </c>
       <c r="G1367" t="n">
-        <v>134.363479614258</v>
+        <v>134.363494873047</v>
       </c>
       <c r="H1367" t="n">
         <v>182501</v>
@@ -40041,7 +40041,7 @@
         <v>144.149993896484</v>
       </c>
       <c r="G1368" t="n">
-        <v>134.503433227539</v>
+        <v>134.503448486328</v>
       </c>
       <c r="H1368" t="n">
         <v>262530</v>
@@ -40070,7 +40070,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G1369" t="n">
-        <v>134.456497192383</v>
+        <v>134.456481933594</v>
       </c>
       <c r="H1369" t="n">
         <v>99816</v>
@@ -40157,7 +40157,7 @@
         <v>143.949996948242</v>
       </c>
       <c r="G1372" t="n">
-        <v>135.255111694336</v>
+        <v>135.255126953125</v>
       </c>
       <c r="H1372" t="n">
         <v>290807</v>
@@ -40186,7 +40186,7 @@
         <v>144.25</v>
       </c>
       <c r="G1373" t="n">
-        <v>135.537002563477</v>
+        <v>135.537017822266</v>
       </c>
       <c r="H1373" t="n">
         <v>159915</v>
@@ -40215,7 +40215,7 @@
         <v>144.649993896484</v>
       </c>
       <c r="G1374" t="n">
-        <v>135.912841796875</v>
+        <v>135.912857055664</v>
       </c>
       <c r="H1374" t="n">
         <v>71449</v>
@@ -40244,7 +40244,7 @@
         <v>142.050003051758</v>
       </c>
       <c r="G1375" t="n">
-        <v>133.469909667969</v>
+        <v>133.46989440918</v>
       </c>
       <c r="H1375" t="n">
         <v>381977</v>
@@ -40302,7 +40302,7 @@
         <v>138.899993896484</v>
       </c>
       <c r="G1377" t="n">
-        <v>130.510147094727</v>
+        <v>130.510162353516</v>
       </c>
       <c r="H1377" t="n">
         <v>202943</v>
@@ -40360,7 +40360,7 @@
         <v>142.300003051758</v>
       </c>
       <c r="G1379" t="n">
-        <v>133.704818725586</v>
+        <v>133.704788208008</v>
       </c>
       <c r="H1379" t="n">
         <v>133594</v>
@@ -40389,7 +40389,7 @@
         <v>143.649993896484</v>
       </c>
       <c r="G1380" t="n">
-        <v>134.973251342773</v>
+        <v>134.973236083984</v>
       </c>
       <c r="H1380" t="n">
         <v>323282</v>
@@ -40418,7 +40418,7 @@
         <v>144.850006103516</v>
       </c>
       <c r="G1381" t="n">
-        <v>136.100799560547</v>
+        <v>136.100784301758</v>
       </c>
       <c r="H1381" t="n">
         <v>125399</v>
@@ -40621,7 +40621,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>144.604110717773</v>
+        <v>144.604125976562</v>
       </c>
       <c r="H1388" t="n">
         <v>291658</v>
@@ -40650,7 +40650,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G1389" t="n">
-        <v>144.134338378906</v>
+        <v>144.134323120117</v>
       </c>
       <c r="H1389" t="n">
         <v>95596</v>
@@ -40737,7 +40737,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G1392" t="n">
-        <v>145.261856079102</v>
+        <v>145.261871337891</v>
       </c>
       <c r="H1392" t="n">
         <v>295841</v>
@@ -40766,7 +40766,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1393" t="n">
-        <v>146.671264648438</v>
+        <v>146.671249389648</v>
       </c>
       <c r="H1393" t="n">
         <v>119203</v>
@@ -40824,7 +40824,7 @@
         <v>159.899993896484</v>
       </c>
       <c r="G1395" t="n">
-        <v>150.24169921875</v>
+        <v>150.241714477539</v>
       </c>
       <c r="H1395" t="n">
         <v>150338</v>
@@ -40853,7 +40853,7 @@
         <v>159.5</v>
       </c>
       <c r="G1396" t="n">
-        <v>149.86589050293</v>
+        <v>149.865875244141</v>
       </c>
       <c r="H1396" t="n">
         <v>208336</v>
@@ -40969,7 +40969,7 @@
         <v>160.75</v>
       </c>
       <c r="G1400" t="n">
-        <v>151.040390014648</v>
+        <v>151.040374755859</v>
       </c>
       <c r="H1400" t="n">
         <v>154432</v>
@@ -40998,7 +40998,7 @@
         <v>163.300003051758</v>
       </c>
       <c r="G1401" t="n">
-        <v>153.436370849609</v>
+        <v>153.43635559082</v>
       </c>
       <c r="H1401" t="n">
         <v>158512</v>
@@ -41027,7 +41027,7 @@
         <v>159.199996948242</v>
       </c>
       <c r="G1402" t="n">
-        <v>149.583999633789</v>
+        <v>149.584014892578</v>
       </c>
       <c r="H1402" t="n">
         <v>139339</v>
@@ -41172,7 +41172,7 @@
         <v>162.600006103516</v>
       </c>
       <c r="G1407" t="n">
-        <v>152.778656005859</v>
+        <v>152.77864074707</v>
       </c>
       <c r="H1407" t="n">
         <v>120303</v>
@@ -41201,7 +41201,7 @@
         <v>163.050003051758</v>
       </c>
       <c r="G1408" t="n">
-        <v>153.201477050781</v>
+        <v>153.201461791992</v>
       </c>
       <c r="H1408" t="n">
         <v>133417</v>
@@ -41230,7 +41230,7 @@
         <v>166</v>
       </c>
       <c r="G1409" t="n">
-        <v>155.973266601562</v>
+        <v>155.973281860352</v>
       </c>
       <c r="H1409" t="n">
         <v>167042</v>
@@ -41259,7 +41259,7 @@
         <v>167.300003051758</v>
       </c>
       <c r="G1410" t="n">
-        <v>157.194763183594</v>
+        <v>157.194747924805</v>
       </c>
       <c r="H1410" t="n">
         <v>201939</v>
@@ -41288,7 +41288,7 @@
         <v>169.449996948242</v>
       </c>
       <c r="G1411" t="n">
-        <v>159.214889526367</v>
+        <v>159.214874267578</v>
       </c>
       <c r="H1411" t="n">
         <v>302805</v>
@@ -41346,7 +41346,7 @@
         <v>172.350006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>161.939712524414</v>
+        <v>161.939743041992</v>
       </c>
       <c r="H1413" t="n">
         <v>141959</v>
@@ -41375,7 +41375,7 @@
         <v>168.949996948242</v>
       </c>
       <c r="G1414" t="n">
-        <v>158.745086669922</v>
+        <v>158.745071411133</v>
       </c>
       <c r="H1414" t="n">
         <v>164215</v>
@@ -41404,7 +41404,7 @@
         <v>168.100006103516</v>
       </c>
       <c r="G1415" t="n">
-        <v>157.946426391602</v>
+        <v>157.946441650391</v>
       </c>
       <c r="H1415" t="n">
         <v>126581</v>
@@ -41520,7 +41520,7 @@
         <v>176.449996948242</v>
       </c>
       <c r="G1419" t="n">
-        <v>165.792068481445</v>
+        <v>165.792053222656</v>
       </c>
       <c r="H1419" t="n">
         <v>223351</v>
@@ -41549,7 +41549,7 @@
         <v>171.949996948242</v>
       </c>
       <c r="G1420" t="n">
-        <v>161.563873291016</v>
+        <v>161.563858032227</v>
       </c>
       <c r="H1420" t="n">
         <v>178590</v>
@@ -41578,7 +41578,7 @@
         <v>175.649993896484</v>
       </c>
       <c r="G1421" t="n">
-        <v>165.040390014648</v>
+        <v>165.040374755859</v>
       </c>
       <c r="H1421" t="n">
         <v>140376</v>
@@ -41607,7 +41607,7 @@
         <v>176.399993896484</v>
       </c>
       <c r="G1422" t="n">
-        <v>165.745086669922</v>
+        <v>165.745071411133</v>
       </c>
       <c r="H1422" t="n">
         <v>184666</v>
@@ -41636,7 +41636,7 @@
         <v>173.449996948242</v>
       </c>
       <c r="G1423" t="n">
-        <v>162.973251342773</v>
+        <v>162.973266601562</v>
       </c>
       <c r="H1423" t="n">
         <v>138448</v>
@@ -41694,7 +41694,7 @@
         <v>175.850006103516</v>
       </c>
       <c r="G1425" t="n">
-        <v>165.228332519531</v>
+        <v>165.228317260742</v>
       </c>
       <c r="H1425" t="n">
         <v>127422</v>
@@ -41752,7 +41752,7 @@
         <v>178.800003051758</v>
       </c>
       <c r="G1427" t="n">
-        <v>168.000122070312</v>
+        <v>168.000137329102</v>
       </c>
       <c r="H1427" t="n">
         <v>109222</v>
@@ -41810,7 +41810,7 @@
         <v>179</v>
       </c>
       <c r="G1429" t="n">
-        <v>168.188064575195</v>
+        <v>168.188049316406</v>
       </c>
       <c r="H1429" t="n">
         <v>89980</v>
@@ -41868,7 +41868,7 @@
         <v>184.850006103516</v>
       </c>
       <c r="G1431" t="n">
-        <v>173.684692382812</v>
+        <v>173.684707641602</v>
       </c>
       <c r="H1431" t="n">
         <v>119649</v>
@@ -42071,7 +42071,7 @@
         <v>189.449996948242</v>
       </c>
       <c r="G1438" t="n">
-        <v>178.006820678711</v>
+        <v>178.0068359375</v>
       </c>
       <c r="H1438" t="n">
         <v>111929</v>
@@ -42100,7 +42100,7 @@
         <v>190.899993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>179.369247436523</v>
+        <v>179.369262695312</v>
       </c>
       <c r="H1439" t="n">
         <v>118983</v>
@@ -42245,7 +42245,7 @@
         <v>204.300003051758</v>
       </c>
       <c r="G1444" t="n">
-        <v>191.959899902344</v>
+        <v>191.959869384766</v>
       </c>
       <c r="H1444" t="n">
         <v>176720</v>
@@ -42361,7 +42361,7 @@
         <v>206.199996948242</v>
       </c>
       <c r="G1448" t="n">
-        <v>193.745086669922</v>
+        <v>193.745101928711</v>
       </c>
       <c r="H1448" t="n">
         <v>113142</v>
@@ -42419,7 +42419,7 @@
         <v>201.800003051758</v>
       </c>
       <c r="G1450" t="n">
-        <v>189.610885620117</v>
+        <v>189.610870361328</v>
       </c>
       <c r="H1450" t="n">
         <v>198969</v>
@@ -42593,7 +42593,7 @@
         <v>204.300003051758</v>
       </c>
       <c r="G1456" t="n">
-        <v>191.959899902344</v>
+        <v>191.959869384766</v>
       </c>
       <c r="H1456" t="n">
         <v>124690</v>
@@ -42622,7 +42622,7 @@
         <v>203.199996948242</v>
       </c>
       <c r="G1457" t="n">
-        <v>190.926315307617</v>
+        <v>190.926300048828</v>
       </c>
       <c r="H1457" t="n">
         <v>80616</v>
@@ -42738,7 +42738,7 @@
         <v>181.850006103516</v>
       </c>
       <c r="G1461" t="n">
-        <v>170.865921020508</v>
+        <v>170.865905761719</v>
       </c>
       <c r="H1461" t="n">
         <v>131167</v>
@@ -42767,7 +42767,7 @@
         <v>181.350006103516</v>
       </c>
       <c r="G1462" t="n">
-        <v>170.396118164062</v>
+        <v>170.396102905273</v>
       </c>
       <c r="H1462" t="n">
         <v>121586</v>
@@ -42825,7 +42825,7 @@
         <v>171.850006103516</v>
       </c>
       <c r="G1464" t="n">
-        <v>161.469924926758</v>
+        <v>161.469940185547</v>
       </c>
       <c r="H1464" t="n">
         <v>148532</v>
@@ -42883,7 +42883,7 @@
         <v>170.050003051758</v>
       </c>
       <c r="G1466" t="n">
-        <v>159.77864074707</v>
+        <v>159.778656005859</v>
       </c>
       <c r="H1466" t="n">
         <v>162410</v>
@@ -42912,7 +42912,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>160.389389038086</v>
+        <v>160.389373779297</v>
       </c>
       <c r="H1467" t="n">
         <v>126504</v>
@@ -42941,7 +42941,7 @@
         <v>172.100006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>161.704818725586</v>
+        <v>161.704833984375</v>
       </c>
       <c r="H1468" t="n">
         <v>110991</v>
@@ -42999,7 +42999,7 @@
         <v>173.949996948242</v>
       </c>
       <c r="G1470" t="n">
-        <v>163.443054199219</v>
+        <v>163.443084716797</v>
       </c>
       <c r="H1470" t="n">
         <v>303280</v>
@@ -43028,7 +43028,7 @@
         <v>178.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>167.718246459961</v>
+        <v>167.718231201172</v>
       </c>
       <c r="H1471" t="n">
         <v>158372</v>
@@ -43057,7 +43057,7 @@
         <v>178.899993896484</v>
       </c>
       <c r="G1472" t="n">
-        <v>168.094055175781</v>
+        <v>168.094085693359</v>
       </c>
       <c r="H1472" t="n">
         <v>116743</v>
@@ -43086,7 +43086,7 @@
         <v>180.100006103516</v>
       </c>
       <c r="G1473" t="n">
-        <v>169.221618652344</v>
+        <v>169.221603393555</v>
       </c>
       <c r="H1473" t="n">
         <v>104846</v>
@@ -43144,7 +43144,7 @@
         <v>181.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>170.537033081055</v>
+        <v>170.537048339844</v>
       </c>
       <c r="H1475" t="n">
         <v>126077</v>
@@ -43202,7 +43202,7 @@
         <v>189.550003051758</v>
       </c>
       <c r="G1477" t="n">
-        <v>178.100814819336</v>
+        <v>178.100799560547</v>
       </c>
       <c r="H1477" t="n">
         <v>137715</v>
@@ -43231,7 +43231,7 @@
         <v>188.899993896484</v>
       </c>
       <c r="G1478" t="n">
-        <v>177.49006652832</v>
+        <v>177.490036010742</v>
       </c>
       <c r="H1478" t="n">
         <v>61467</v>
@@ -43260,7 +43260,7 @@
         <v>191.050003051758</v>
       </c>
       <c r="G1479" t="n">
-        <v>179.510208129883</v>
+        <v>179.510223388672</v>
       </c>
       <c r="H1479" t="n">
         <v>81861</v>
@@ -43289,7 +43289,7 @@
         <v>191</v>
       </c>
       <c r="G1480" t="n">
-        <v>179.463226318359</v>
+        <v>179.46321105957</v>
       </c>
       <c r="H1480" t="n">
         <v>119081</v>
@@ -43318,7 +43318,7 @@
         <v>187.350006103516</v>
       </c>
       <c r="G1481" t="n">
-        <v>176.03369140625</v>
+        <v>176.033706665039</v>
       </c>
       <c r="H1481" t="n">
         <v>119429</v>
@@ -43347,7 +43347,7 @@
         <v>195.449996948242</v>
       </c>
       <c r="G1482" t="n">
-        <v>183.644439697266</v>
+        <v>183.644424438477</v>
       </c>
       <c r="H1482" t="n">
         <v>233069</v>
@@ -43376,7 +43376,7 @@
         <v>195.350006103516</v>
       </c>
       <c r="G1483" t="n">
-        <v>183.550476074219</v>
+        <v>183.550491333008</v>
       </c>
       <c r="H1483" t="n">
         <v>135461</v>
@@ -43405,7 +43405,7 @@
         <v>197.149993896484</v>
       </c>
       <c r="G1484" t="n">
-        <v>185.241729736328</v>
+        <v>185.241744995117</v>
       </c>
       <c r="H1484" t="n">
         <v>97845</v>
@@ -43434,7 +43434,7 @@
         <v>197.649993896484</v>
       </c>
       <c r="G1485" t="n">
-        <v>185.711517333984</v>
+        <v>185.711532592773</v>
       </c>
       <c r="H1485" t="n">
         <v>93144</v>
@@ -43463,7 +43463,7 @@
         <v>194.75</v>
       </c>
       <c r="G1486" t="n">
-        <v>182.986724853516</v>
+        <v>182.986709594727</v>
       </c>
       <c r="H1486" t="n">
         <v>308379</v>
@@ -43521,7 +43521,7 @@
         <v>182.5</v>
       </c>
       <c r="G1488" t="n">
-        <v>171.476623535156</v>
+        <v>171.476638793945</v>
       </c>
       <c r="H1488" t="n">
         <v>334448</v>
@@ -43550,7 +43550,7 @@
         <v>184.100006103516</v>
       </c>
       <c r="G1489" t="n">
-        <v>172.97998046875</v>
+        <v>172.980010986328</v>
       </c>
       <c r="H1489" t="n">
         <v>196667</v>
@@ -43695,7 +43695,7 @@
         <v>188.949996948242</v>
       </c>
       <c r="G1494" t="n">
-        <v>177.537033081055</v>
+        <v>177.537048339844</v>
       </c>
       <c r="H1494" t="n">
         <v>122784</v>
@@ -43753,7 +43753,7 @@
         <v>183.75</v>
       </c>
       <c r="G1496" t="n">
-        <v>172.651123046875</v>
+        <v>172.651138305664</v>
       </c>
       <c r="H1496" t="n">
         <v>239929</v>
@@ -43782,7 +43782,7 @@
         <v>184.5</v>
       </c>
       <c r="G1497" t="n">
-        <v>173.355819702148</v>
+        <v>173.355834960938</v>
       </c>
       <c r="H1497" t="n">
         <v>108994</v>
@@ -43811,7 +43811,7 @@
         <v>188.899993896484</v>
       </c>
       <c r="G1498" t="n">
-        <v>177.49006652832</v>
+        <v>177.490036010742</v>
       </c>
       <c r="H1498" t="n">
         <v>199445</v>
@@ -43840,7 +43840,7 @@
         <v>183.649993896484</v>
       </c>
       <c r="G1499" t="n">
-        <v>172.557174682617</v>
+        <v>172.557159423828</v>
       </c>
       <c r="H1499" t="n">
         <v>126554</v>
@@ -43956,7 +43956,7 @@
         <v>187.300003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>175.986740112305</v>
+        <v>175.986709594727</v>
       </c>
       <c r="H1503" t="n">
         <v>372294</v>
@@ -43985,7 +43985,7 @@
         <v>185.100006103516</v>
       </c>
       <c r="G1504" t="n">
-        <v>173.91960144043</v>
+        <v>173.919586181641</v>
       </c>
       <c r="H1504" t="n">
         <v>205053</v>
@@ -44014,7 +44014,7 @@
         <v>188.75</v>
       </c>
       <c r="G1505" t="n">
-        <v>177.34912109375</v>
+        <v>177.349136352539</v>
       </c>
       <c r="H1505" t="n">
         <v>359394</v>
@@ -44130,7 +44130,7 @@
         <v>172.300003051758</v>
       </c>
       <c r="G1509" t="n">
-        <v>161.892761230469</v>
+        <v>161.89274597168</v>
       </c>
       <c r="H1509" t="n">
         <v>139544</v>
@@ -44159,7 +44159,7 @@
         <v>176.399993896484</v>
       </c>
       <c r="G1510" t="n">
-        <v>165.745086669922</v>
+        <v>165.745071411133</v>
       </c>
       <c r="H1510" t="n">
         <v>123973</v>
@@ -44217,7 +44217,7 @@
         <v>178</v>
       </c>
       <c r="G1512" t="n">
-        <v>167.248458862305</v>
+        <v>167.248443603516</v>
       </c>
       <c r="H1512" t="n">
         <v>123846</v>
@@ -44246,7 +44246,7 @@
         <v>180</v>
       </c>
       <c r="G1513" t="n">
-        <v>169.127655029297</v>
+        <v>169.127639770508</v>
       </c>
       <c r="H1513" t="n">
         <v>163104</v>
@@ -44275,7 +44275,7 @@
         <v>180.649993896484</v>
       </c>
       <c r="G1514" t="n">
-        <v>169.738357543945</v>
+        <v>169.738372802734</v>
       </c>
       <c r="H1514" t="n">
         <v>140911</v>
@@ -44304,7 +44304,7 @@
         <v>176.300003051758</v>
       </c>
       <c r="G1515" t="n">
-        <v>165.651123046875</v>
+        <v>165.651138305664</v>
       </c>
       <c r="H1515" t="n">
         <v>157321</v>
@@ -44391,7 +44391,7 @@
         <v>158.850006103516</v>
       </c>
       <c r="G1518" t="n">
-        <v>149.255142211914</v>
+        <v>149.255157470703</v>
       </c>
       <c r="H1518" t="n">
         <v>852382</v>
@@ -44420,7 +44420,7 @@
         <v>160.550003051758</v>
       </c>
       <c r="G1519" t="n">
-        <v>150.852462768555</v>
+        <v>150.852447509766</v>
       </c>
       <c r="H1519" t="n">
         <v>332357</v>
@@ -44536,7 +44536,7 @@
         <v>166.350006103516</v>
       </c>
       <c r="G1523" t="n">
-        <v>156.302139282227</v>
+        <v>156.302154541016</v>
       </c>
       <c r="H1523" t="n">
         <v>169460</v>
@@ -44565,7 +44565,7 @@
         <v>166</v>
       </c>
       <c r="G1524" t="n">
-        <v>155.973266601562</v>
+        <v>155.973281860352</v>
       </c>
       <c r="H1524" t="n">
         <v>115654</v>
@@ -44623,7 +44623,7 @@
         <v>167.449996948242</v>
       </c>
       <c r="G1526" t="n">
-        <v>157.335678100586</v>
+        <v>157.335693359375</v>
       </c>
       <c r="H1526" t="n">
         <v>110574</v>
@@ -44652,7 +44652,7 @@
         <v>163.199996948242</v>
       </c>
       <c r="G1527" t="n">
-        <v>153.342391967773</v>
+        <v>153.342376708984</v>
       </c>
       <c r="H1527" t="n">
         <v>194658</v>
@@ -44681,7 +44681,7 @@
         <v>158.949996948242</v>
       </c>
       <c r="G1528" t="n">
-        <v>149.349090576172</v>
+        <v>149.349105834961</v>
       </c>
       <c r="H1528" t="n">
         <v>312211</v>
@@ -44710,7 +44710,7 @@
         <v>160.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>150.80549621582</v>
+        <v>150.805480957031</v>
       </c>
       <c r="H1529" t="n">
         <v>187469</v>
@@ -44739,7 +44739,7 @@
         <v>156.100006103516</v>
       </c>
       <c r="G1530" t="n">
-        <v>146.671264648438</v>
+        <v>146.671249389648</v>
       </c>
       <c r="H1530" t="n">
         <v>220701</v>
@@ -44768,7 +44768,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G1531" t="n">
-        <v>145.449783325195</v>
+        <v>145.449798583984</v>
       </c>
       <c r="H1531" t="n">
         <v>146624</v>
@@ -44855,7 +44855,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G1534" t="n">
-        <v>144.886016845703</v>
+        <v>144.886001586914</v>
       </c>
       <c r="H1534" t="n">
         <v>255985</v>
@@ -44884,7 +44884,7 @@
         <v>147.699996948242</v>
       </c>
       <c r="G1535" t="n">
-        <v>138.778625488281</v>
+        <v>138.77864074707</v>
       </c>
       <c r="H1535" t="n">
         <v>278272</v>
@@ -45145,7 +45145,7 @@
         <v>134.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>126.610832214355</v>
+        <v>126.610824584961</v>
       </c>
       <c r="H1544" t="n">
         <v>138490</v>
@@ -45232,7 +45232,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G1547" t="n">
-        <v>128.630950927734</v>
+        <v>128.630935668945</v>
       </c>
       <c r="H1547" t="n">
         <v>116999</v>
@@ -45319,7 +45319,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G1550" t="n">
-        <v>125.34236907959</v>
+        <v>125.342361450195</v>
       </c>
       <c r="H1550" t="n">
         <v>164718</v>
@@ -45348,7 +45348,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G1551" t="n">
-        <v>123.65111541748</v>
+        <v>123.651107788086</v>
       </c>
       <c r="H1551" t="n">
         <v>134476</v>
@@ -45377,7 +45377,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1552" t="n">
-        <v>118.295402526855</v>
+        <v>118.295394897461</v>
       </c>
       <c r="H1552" t="n">
         <v>327942</v>
@@ -45435,7 +45435,7 @@
         <v>127.75</v>
       </c>
       <c r="G1554" t="n">
-        <v>120.033645629883</v>
+        <v>120.033653259277</v>
       </c>
       <c r="H1554" t="n">
         <v>123199</v>
@@ -45493,7 +45493,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G1556" t="n">
-        <v>115.75846862793</v>
+        <v>115.758476257324</v>
       </c>
       <c r="H1556" t="n">
         <v>138833</v>
@@ -45522,7 +45522,7 @@
         <v>119.75</v>
       </c>
       <c r="G1557" t="n">
-        <v>112.516868591309</v>
+        <v>112.51685333252</v>
       </c>
       <c r="H1557" t="n">
         <v>221947</v>
@@ -45580,7 +45580,7 @@
         <v>121.75</v>
       </c>
       <c r="G1559" t="n">
-        <v>114.396057128906</v>
+        <v>114.396064758301</v>
       </c>
       <c r="H1559" t="n">
         <v>108798</v>
@@ -45609,7 +45609,7 @@
         <v>120.75</v>
       </c>
       <c r="G1560" t="n">
-        <v>113.456466674805</v>
+        <v>113.45645904541</v>
       </c>
       <c r="H1560" t="n">
         <v>111428</v>
@@ -45638,7 +45638,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1561" t="n">
-        <v>110.214851379395</v>
+        <v>110.214859008789</v>
       </c>
       <c r="H1561" t="n">
         <v>208572</v>
@@ -45754,7 +45754,7 @@
         <v>128.600006103516</v>
       </c>
       <c r="G1565" t="n">
-        <v>120.832305908203</v>
+        <v>120.832313537598</v>
       </c>
       <c r="H1565" t="n">
         <v>285496</v>
@@ -45812,7 +45812,7 @@
         <v>133.649993896484</v>
       </c>
       <c r="G1567" t="n">
-        <v>125.577270507812</v>
+        <v>125.577262878418</v>
       </c>
       <c r="H1567" t="n">
         <v>224735</v>
@@ -45841,7 +45841,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G1568" t="n">
-        <v>124.778617858887</v>
+        <v>124.778633117676</v>
       </c>
       <c r="H1568" t="n">
         <v>211077</v>
@@ -45899,7 +45899,7 @@
         <v>128.649993896484</v>
       </c>
       <c r="G1570" t="n">
-        <v>120.879280090332</v>
+        <v>120.879272460938</v>
       </c>
       <c r="H1570" t="n">
         <v>92715</v>
@@ -45928,7 +45928,7 @@
         <v>125.449996948242</v>
       </c>
       <c r="G1571" t="n">
-        <v>117.872566223145</v>
+        <v>117.87255859375</v>
       </c>
       <c r="H1571" t="n">
         <v>147318</v>
@@ -45957,7 +45957,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G1572" t="n">
-        <v>119.986663818359</v>
+        <v>119.986656188965</v>
       </c>
       <c r="H1572" t="n">
         <v>252423</v>
@@ -46015,7 +46015,7 @@
         <v>126.199996948242</v>
       </c>
       <c r="G1574" t="n">
-        <v>118.577262878418</v>
+        <v>118.577270507812</v>
       </c>
       <c r="H1574" t="n">
         <v>237226</v>
@@ -46044,7 +46044,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G1575" t="n">
-        <v>113.409469604492</v>
+        <v>113.409484863281</v>
       </c>
       <c r="H1575" t="n">
         <v>141960</v>
@@ -46131,7 +46131,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G1578" t="n">
-        <v>118.295402526855</v>
+        <v>118.295394897461</v>
       </c>
       <c r="H1578" t="n">
         <v>103471</v>
@@ -46160,7 +46160,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G1579" t="n">
-        <v>119.986663818359</v>
+        <v>119.986656188965</v>
       </c>
       <c r="H1579" t="n">
         <v>136323</v>
@@ -46189,7 +46189,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G1580" t="n">
-        <v>129.288696289062</v>
+        <v>129.288681030273</v>
       </c>
       <c r="H1580" t="n">
         <v>351885</v>
@@ -46218,7 +46218,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G1581" t="n">
-        <v>129.852432250977</v>
+        <v>129.852447509766</v>
       </c>
       <c r="H1581" t="n">
         <v>241443</v>
@@ -46276,7 +46276,7 @@
         <v>132.25</v>
       </c>
       <c r="G1583" t="n">
-        <v>124.261833190918</v>
+        <v>124.261840820312</v>
       </c>
       <c r="H1583" t="n">
         <v>127989</v>
@@ -46334,7 +46334,7 @@
         <v>129.75</v>
       </c>
       <c r="G1585" t="n">
-        <v>121.912841796875</v>
+        <v>121.91284942627</v>
       </c>
       <c r="H1585" t="n">
         <v>95622</v>
@@ -46363,7 +46363,7 @@
         <v>128.649993896484</v>
       </c>
       <c r="G1586" t="n">
-        <v>120.879280090332</v>
+        <v>120.879272460938</v>
       </c>
       <c r="H1586" t="n">
         <v>94605</v>
@@ -46508,7 +46508,7 @@
         <v>145.550003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>136.758483886719</v>
+        <v>136.758499145508</v>
       </c>
       <c r="H1591" t="n">
         <v>167885</v>
@@ -46566,7 +46566,7 @@
         <v>148.449996948242</v>
       </c>
       <c r="G1593" t="n">
-        <v>139.483337402344</v>
+        <v>139.483306884766</v>
       </c>
       <c r="H1593" t="n">
         <v>166410</v>
@@ -46653,7 +46653,7 @@
         <v>141.300003051758</v>
       </c>
       <c r="G1596" t="n">
-        <v>132.765213012695</v>
+        <v>132.765197753906</v>
       </c>
       <c r="H1596" t="n">
         <v>104501</v>
@@ -46682,7 +46682,7 @@
         <v>138.550003051758</v>
       </c>
       <c r="G1597" t="n">
-        <v>130.18132019043</v>
+        <v>130.181304931641</v>
       </c>
       <c r="H1597" t="n">
         <v>115375</v>
@@ -46711,7 +46711,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>126.657821655273</v>
+        <v>126.657806396484</v>
       </c>
       <c r="H1598" t="n">
         <v>214371</v>
@@ -46740,7 +46740,7 @@
         <v>134.850006103516</v>
       </c>
       <c r="G1599" t="n">
-        <v>126.704803466797</v>
+        <v>126.704818725586</v>
       </c>
       <c r="H1599" t="n">
         <v>114281</v>
@@ -46769,7 +46769,7 @@
         <v>134.300003051758</v>
       </c>
       <c r="G1600" t="n">
-        <v>126.188011169434</v>
+        <v>126.188026428223</v>
       </c>
       <c r="H1600" t="n">
         <v>82429</v>
@@ -46798,7 +46798,7 @@
         <v>134.149993896484</v>
       </c>
       <c r="G1601" t="n">
-        <v>126.047065734863</v>
+        <v>126.047058105469</v>
       </c>
       <c r="H1601" t="n">
         <v>133305</v>
@@ -46914,7 +46914,7 @@
         <v>124</v>
       </c>
       <c r="G1605" t="n">
-        <v>116.510147094727</v>
+        <v>116.510162353516</v>
       </c>
       <c r="H1605" t="n">
         <v>124325</v>
@@ -46943,7 +46943,7 @@
         <v>120.75</v>
       </c>
       <c r="G1606" t="n">
-        <v>113.456466674805</v>
+        <v>113.45645904541</v>
       </c>
       <c r="H1606" t="n">
         <v>103496</v>
@@ -47001,7 +47001,7 @@
         <v>123.949996948242</v>
       </c>
       <c r="G1608" t="n">
-        <v>116.463172912598</v>
+        <v>116.463165283203</v>
       </c>
       <c r="H1608" t="n">
         <v>144335</v>
@@ -47030,7 +47030,7 @@
         <v>125.050003051758</v>
       </c>
       <c r="G1609" t="n">
-        <v>117.496734619141</v>
+        <v>117.496742248535</v>
       </c>
       <c r="H1609" t="n">
         <v>222303</v>
@@ -47059,7 +47059,7 @@
         <v>123.449996948242</v>
       </c>
       <c r="G1610" t="n">
-        <v>115.993362426758</v>
+        <v>115.993370056152</v>
       </c>
       <c r="H1610" t="n">
         <v>157455</v>
@@ -47088,7 +47088,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G1611" t="n">
-        <v>115.476593017578</v>
+        <v>115.476600646973</v>
       </c>
       <c r="H1611" t="n">
         <v>126786</v>
@@ -47146,7 +47146,7 @@
         <v>119.949996948242</v>
       </c>
       <c r="G1613" t="n">
-        <v>112.704780578613</v>
+        <v>112.704772949219</v>
       </c>
       <c r="H1613" t="n">
         <v>156486</v>
@@ -47204,7 +47204,7 @@
         <v>114.150001525879</v>
       </c>
       <c r="G1615" t="n">
-        <v>107.255111694336</v>
+        <v>107.25511932373</v>
       </c>
       <c r="H1615" t="n">
         <v>216195</v>
@@ -47233,7 +47233,7 @@
         <v>111.349998474121</v>
       </c>
       <c r="G1616" t="n">
-        <v>104.624229431152</v>
+        <v>104.624237060547</v>
       </c>
       <c r="H1616" t="n">
         <v>216406</v>
@@ -47320,7 +47320,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G1619" t="n">
-        <v>111.906120300293</v>
+        <v>111.906127929688</v>
       </c>
       <c r="H1619" t="n">
         <v>174865</v>
@@ -47349,7 +47349,7 @@
         <v>120</v>
       </c>
       <c r="G1620" t="n">
-        <v>112.751770019531</v>
+        <v>112.751762390137</v>
       </c>
       <c r="H1620" t="n">
         <v>140871</v>
@@ -47378,7 +47378,7 @@
         <v>118.5</v>
       </c>
       <c r="G1621" t="n">
-        <v>111.342361450195</v>
+        <v>111.34236907959</v>
       </c>
       <c r="H1621" t="n">
         <v>106069</v>
@@ -47465,7 +47465,7 @@
         <v>119.150001525879</v>
       </c>
       <c r="G1624" t="n">
-        <v>111.953094482422</v>
+        <v>111.953102111816</v>
       </c>
       <c r="H1624" t="n">
         <v>113424</v>
@@ -80154,6 +80154,35 @@
         <v>112380</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>80.4400024414062</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>81.9800033569336</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>81.7600021362305</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>81.7600021362305</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>119964</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
